--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP78"/>
+  <dimension ref="A1:BP94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17126,6 +17126,3154 @@
       <c r="BO78" t="inlineStr"/>
       <c r="BP78" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>zkPwWhT1</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>45522.65625</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="n">
+        <v>3</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M79" t="n">
+        <v>48</v>
+      </c>
+      <c r="N79" t="n">
+        <v>52</v>
+      </c>
+      <c r="O79" t="n">
+        <v>22</v>
+      </c>
+      <c r="P79" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>8</v>
+      </c>
+      <c r="R79" t="n">
+        <v>2</v>
+      </c>
+      <c r="S79" t="n">
+        <v>13</v>
+      </c>
+      <c r="T79" t="n">
+        <v>12</v>
+      </c>
+      <c r="U79" t="n">
+        <v>8</v>
+      </c>
+      <c r="V79" t="n">
+        <v>11</v>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="Y79" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="n">
+        <v>25.875</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>75.625</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>9475000</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>10111111.11111111</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>80</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>24.23076923076923</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>181.9230769230769</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>1.538461538461539</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>73.07692307692308</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>8578846.153846154</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>77.53846153846153</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>23.81818181818182</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>1.681818181818182</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>73.18181818181819</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>5522727.272727272</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>78.81818181818181</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>189</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BI79" t="n">
+        <v>78</v>
+      </c>
+      <c r="BJ79" t="n">
+        <v>31</v>
+      </c>
+      <c r="BK79" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>159</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>2NocJFqd</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F80" t="n">
+        <v>14811</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M80" t="n">
+        <v>44</v>
+      </c>
+      <c r="N80" t="n">
+        <v>56</v>
+      </c>
+      <c r="O80" t="n">
+        <v>4</v>
+      </c>
+      <c r="P80" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>3</v>
+      </c>
+      <c r="R80" t="n">
+        <v>5</v>
+      </c>
+      <c r="S80" t="n">
+        <v>6</v>
+      </c>
+      <c r="T80" t="n">
+        <v>10</v>
+      </c>
+      <c r="U80" t="n">
+        <v>10</v>
+      </c>
+      <c r="V80" t="n">
+        <v>11</v>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="Y80" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="AE80" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>68</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>1587500</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>27.63636363636364</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>179.8181818181818</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>77</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>12381818.18181818</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>78.72727272727273</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>66.45</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>1278750</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>23.90909090909091</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>179.9545454545455</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>72.90909090909091</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>6081818.181818182</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>78.13636363636364</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>266</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>5725000</v>
+      </c>
+      <c r="BI80" t="n">
+        <v>290</v>
+      </c>
+      <c r="BJ80" t="n">
+        <v>25</v>
+      </c>
+      <c r="BK80" t="n">
+        <v>179</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>298</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>28600000</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>M5VGwpVA</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F81" t="n">
+        <v>15706</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L81" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M81" t="n">
+        <v>43</v>
+      </c>
+      <c r="N81" t="n">
+        <v>57</v>
+      </c>
+      <c r="O81" t="n">
+        <v>7</v>
+      </c>
+      <c r="P81" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>5</v>
+      </c>
+      <c r="R81" t="n">
+        <v>4</v>
+      </c>
+      <c r="S81" t="n">
+        <v>20</v>
+      </c>
+      <c r="T81" t="n">
+        <v>18</v>
+      </c>
+      <c r="U81" t="n">
+        <v>3</v>
+      </c>
+      <c r="V81" t="n">
+        <v>9</v>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="Y81" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="AE81" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>6330000</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>21.22222222222222</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>185.4444444444445</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>70.77777777777777</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>4402777.777777778</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>79.88888888888889</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>182</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>3787500</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>76.625</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>21.875</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>67.1875</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>2412500</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>76</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>31</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>186</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>147</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="BI81" t="n">
+        <v>147</v>
+      </c>
+      <c r="BJ81" t="n">
+        <v>19</v>
+      </c>
+      <c r="BK81" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN81" t="n">
+        <v>70</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>6ehlLyFq</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F82" t="n">
+        <v>25491</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M82" t="n">
+        <v>53</v>
+      </c>
+      <c r="N82" t="n">
+        <v>47</v>
+      </c>
+      <c r="O82" t="n">
+        <v>7</v>
+      </c>
+      <c r="P82" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>3</v>
+      </c>
+      <c r="R82" t="n">
+        <v>2</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="n">
+        <v>8</v>
+      </c>
+      <c r="U82" t="n">
+        <v>8</v>
+      </c>
+      <c r="V82" t="n">
+        <v>3</v>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="Y82" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AE82" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>182</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>5310000</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>178.375</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>69.8125</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>2631250</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>75.4375</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>25.76470588235294</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>182.8235294117647</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>1.411764705882353</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>71.76470588235294</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>3450000</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>74.58823529411765</v>
+      </c>
+      <c r="BC82" t="inlineStr"/>
+      <c r="BD82" t="inlineStr"/>
+      <c r="BE82" t="inlineStr"/>
+      <c r="BF82" t="inlineStr"/>
+      <c r="BG82" t="inlineStr"/>
+      <c r="BH82" t="inlineStr"/>
+      <c r="BI82" t="inlineStr"/>
+      <c r="BJ82" t="inlineStr"/>
+      <c r="BK82" t="inlineStr"/>
+      <c r="BL82" t="inlineStr"/>
+      <c r="BM82" t="inlineStr"/>
+      <c r="BN82" t="inlineStr"/>
+      <c r="BO82" t="inlineStr"/>
+      <c r="BP82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>ripawyyS</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>45522.41666666666</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F83" t="n">
+        <v>16354</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M83" t="n">
+        <v>46</v>
+      </c>
+      <c r="N83" t="n">
+        <v>54</v>
+      </c>
+      <c r="O83" t="n">
+        <v>16</v>
+      </c>
+      <c r="P83" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>7</v>
+      </c>
+      <c r="R83" t="n">
+        <v>2</v>
+      </c>
+      <c r="S83" t="n">
+        <v>11</v>
+      </c>
+      <c r="T83" t="n">
+        <v>17</v>
+      </c>
+      <c r="U83" t="n">
+        <v>7</v>
+      </c>
+      <c r="V83" t="n">
+        <v>8</v>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="Y83" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC83" t="inlineStr"/>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="AE83" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>68.22222222222223</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>1708333.333333333</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>184</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>9280000</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>25.08333333333333</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>180.8333333333333</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>65.08333333333333</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>1062500</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>5470000</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>192</v>
+      </c>
+      <c r="BE83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG83" t="n">
+        <v>69</v>
+      </c>
+      <c r="BH83" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="BI83" t="n">
+        <v>74</v>
+      </c>
+      <c r="BJ83" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BK83" t="n">
+        <v>177</v>
+      </c>
+      <c r="BL83" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM83" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN83" t="n">
+        <v>307</v>
+      </c>
+      <c r="BO83" t="n">
+        <v>53500000</v>
+      </c>
+      <c r="BP83" t="n">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>fHYrsJy3</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>45521.66666666666</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F84" t="n">
+        <v>14250</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M84" t="n">
+        <v>61</v>
+      </c>
+      <c r="N84" t="n">
+        <v>39</v>
+      </c>
+      <c r="O84" t="n">
+        <v>13</v>
+      </c>
+      <c r="P84" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>6</v>
+      </c>
+      <c r="R84" t="n">
+        <v>4</v>
+      </c>
+      <c r="S84" t="n">
+        <v>13</v>
+      </c>
+      <c r="T84" t="n">
+        <v>14</v>
+      </c>
+      <c r="U84" t="n">
+        <v>4</v>
+      </c>
+      <c r="V84" t="n">
+        <v>17</v>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="Y84" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr"/>
+      <c r="AE84" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>12650000</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="AK84" t="inlineStr"/>
+      <c r="AL84" t="inlineStr"/>
+      <c r="AM84" t="inlineStr"/>
+      <c r="AN84" t="inlineStr"/>
+      <c r="AO84" t="inlineStr"/>
+      <c r="AP84" t="inlineStr"/>
+      <c r="AQ84" t="n">
+        <v>20.86666666666667</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>72.73333333333333</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>9083333.333333334</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>82</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>182.1818181818182</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>65.81818181818181</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>1463636.363636364</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>74.27272727272727</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>190</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>78</v>
+      </c>
+      <c r="BH84" t="n">
+        <v>20500000</v>
+      </c>
+      <c r="BI84" t="n">
+        <v>84</v>
+      </c>
+      <c r="BJ84" t="n">
+        <v>24</v>
+      </c>
+      <c r="BK84" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN84" t="n">
+        <v>71</v>
+      </c>
+      <c r="BO84" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="BP84" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>jqSiuc6F</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F85" t="n">
+        <v>14755</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M85" t="n">
+        <v>29</v>
+      </c>
+      <c r="N85" t="n">
+        <v>71</v>
+      </c>
+      <c r="O85" t="n">
+        <v>2</v>
+      </c>
+      <c r="P85" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6</v>
+      </c>
+      <c r="S85" t="n">
+        <v>6</v>
+      </c>
+      <c r="T85" t="n">
+        <v>13</v>
+      </c>
+      <c r="U85" t="n">
+        <v>12</v>
+      </c>
+      <c r="V85" t="n">
+        <v>6</v>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="Y85" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC85" t="inlineStr"/>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr"/>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="inlineStr"/>
+      <c r="AH85" t="inlineStr"/>
+      <c r="AI85" t="inlineStr"/>
+      <c r="AJ85" t="inlineStr"/>
+      <c r="AK85" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>75.875</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>10312500</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>68</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>3266666.666666667</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>178.6111111111111</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>72.38888888888889</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>8463888.888888888</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>79.88888888888889</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>221</v>
+      </c>
+      <c r="BH85" t="n">
+        <v>29200000</v>
+      </c>
+      <c r="BI85" t="n">
+        <v>238</v>
+      </c>
+      <c r="BJ85" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="BK85" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="BL85" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM85" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN85" t="n">
+        <v>386</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>55800000</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>0js8u60b</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F86" t="n">
+        <v>14962</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>5</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L86" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M86" t="n">
+        <v>51</v>
+      </c>
+      <c r="N86" t="n">
+        <v>49</v>
+      </c>
+      <c r="O86" t="n">
+        <v>7</v>
+      </c>
+      <c r="P86" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>5</v>
+      </c>
+      <c r="R86" t="n">
+        <v>5</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="n">
+        <v>8</v>
+      </c>
+      <c r="U86" t="n">
+        <v>10</v>
+      </c>
+      <c r="V86" t="n">
+        <v>12</v>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="Y86" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC86" t="inlineStr"/>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="AE86" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>5460000</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK86" t="inlineStr"/>
+      <c r="AL86" t="inlineStr"/>
+      <c r="AM86" t="inlineStr"/>
+      <c r="AN86" t="inlineStr"/>
+      <c r="AO86" t="inlineStr"/>
+      <c r="AP86" t="inlineStr"/>
+      <c r="AQ86" t="n">
+        <v>22.78571428571428</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>178.1428571428571</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>67.71428571428571</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>4185714.285714286</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>74.42857142857143</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>24.36363636363636</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>180.0909090909091</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>75.18181818181819</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>10490909.09090909</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>79.18181818181819</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>172</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>74</v>
+      </c>
+      <c r="BH86" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="BI86" t="n">
+        <v>77</v>
+      </c>
+      <c r="BJ86" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BK86" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="BL86" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BM86" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN86" t="n">
+        <v>296</v>
+      </c>
+      <c r="BO86" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="BP86" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>SOLVXEbk</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>45520.65625</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F87" t="n">
+        <v>23167</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>4</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M87" t="n">
+        <v>26</v>
+      </c>
+      <c r="N87" t="n">
+        <v>74</v>
+      </c>
+      <c r="O87" t="n">
+        <v>5</v>
+      </c>
+      <c r="P87" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>2</v>
+      </c>
+      <c r="R87" t="n">
+        <v>9</v>
+      </c>
+      <c r="S87" t="n">
+        <v>9</v>
+      </c>
+      <c r="T87" t="n">
+        <v>9</v>
+      </c>
+      <c r="U87" t="n">
+        <v>8</v>
+      </c>
+      <c r="V87" t="n">
+        <v>4</v>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="Y87" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC87" t="inlineStr"/>
+      <c r="AD87" t="inlineStr"/>
+      <c r="AE87" t="n">
+        <v>25.18181818181818</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>185.2727272727273</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>2945454.545454545</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK87" t="inlineStr"/>
+      <c r="AL87" t="inlineStr"/>
+      <c r="AM87" t="inlineStr"/>
+      <c r="AN87" t="inlineStr"/>
+      <c r="AO87" t="inlineStr"/>
+      <c r="AP87" t="inlineStr"/>
+      <c r="AQ87" t="n">
+        <v>22.5625</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>180.0625</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>1389062.5</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>23.69230769230769</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>183.5384615384615</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>2.307692307692307</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>80.38461538461539</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>42061538.46153846</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>84.76923076923077</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>188</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG87" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH87" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BI87" t="n">
+        <v>74</v>
+      </c>
+      <c r="BJ87" t="n">
+        <v>27</v>
+      </c>
+      <c r="BK87" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="BL87" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM87" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN87" t="n">
+        <v>165</v>
+      </c>
+      <c r="BO87" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="BP87" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>dvUee9dD</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>45521.39583333334</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gaillouste p 
+  fra </t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade michel d ornano
+  caen </t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>20300</v>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="n">
+        <v>36</v>
+      </c>
+      <c r="N88" t="n">
+        <v>64</v>
+      </c>
+      <c r="O88" t="n">
+        <v>9</v>
+      </c>
+      <c r="P88" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>5</v>
+      </c>
+      <c r="R88" t="n">
+        <v>5</v>
+      </c>
+      <c r="S88" t="n">
+        <v>15</v>
+      </c>
+      <c r="T88" t="n">
+        <v>13</v>
+      </c>
+      <c r="U88" t="n">
+        <v>10</v>
+      </c>
+      <c r="V88" t="n">
+        <v>6</v>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="Y88" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC88" t="inlineStr"/>
+      <c r="AD88" t="inlineStr"/>
+      <c r="AE88" t="n">
+        <v>25.44444444444444</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>181</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>67.55555555555556</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>1638888.888888889</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>74</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>177.8888888888889</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>67.22222222222223</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>1697222.222222222</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>71.55555555555556</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>22.07142857142857</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>179.7857142857143</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>64.21428571428571</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>1037500</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>74.07142857142857</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>1083750</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>69.15000000000001</v>
+      </c>
+      <c r="BC88" t="inlineStr"/>
+      <c r="BD88" t="inlineStr"/>
+      <c r="BE88" t="inlineStr"/>
+      <c r="BF88" t="inlineStr"/>
+      <c r="BG88" t="inlineStr"/>
+      <c r="BH88" t="inlineStr"/>
+      <c r="BI88" t="inlineStr"/>
+      <c r="BJ88" t="inlineStr"/>
+      <c r="BK88" t="inlineStr"/>
+      <c r="BL88" t="inlineStr"/>
+      <c r="BM88" t="inlineStr"/>
+      <c r="BN88" t="inlineStr"/>
+      <c r="BO88" t="inlineStr"/>
+      <c r="BP88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>EeC5phre</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valnet a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michel moretti stadium
+  ajaccio </t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>8470</v>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="n">
+        <v>1</v>
+      </c>
+      <c r="N89" t="n">
+        <v>99</v>
+      </c>
+      <c r="O89" t="n">
+        <v>8</v>
+      </c>
+      <c r="P89" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>4</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>2</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="Y89" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC89" t="inlineStr"/>
+      <c r="AD89" t="inlineStr"/>
+      <c r="AE89" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>872500</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>1090625</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>26.38888888888889</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>180</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>65.05555555555556</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>751388.8888888889</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>69.61111111111111</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>830000</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>71</v>
+      </c>
+      <c r="BC89" t="inlineStr"/>
+      <c r="BD89" t="inlineStr"/>
+      <c r="BE89" t="inlineStr"/>
+      <c r="BF89" t="inlineStr"/>
+      <c r="BG89" t="inlineStr"/>
+      <c r="BH89" t="inlineStr"/>
+      <c r="BI89" t="inlineStr"/>
+      <c r="BJ89" t="inlineStr"/>
+      <c r="BK89" t="inlineStr"/>
+      <c r="BL89" t="inlineStr"/>
+      <c r="BM89" t="inlineStr"/>
+      <c r="BN89" t="inlineStr"/>
+      <c r="BO89" t="inlineStr"/>
+      <c r="BP89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>2Hh06Z4E</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rosier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>12097</v>
+      </c>
+      <c r="F90" t="n">
+        <v>4918</v>
+      </c>
+      <c r="G90" t="n">
+        <v>3</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="n">
+        <v>51</v>
+      </c>
+      <c r="N90" t="n">
+        <v>49</v>
+      </c>
+      <c r="O90" t="n">
+        <v>17</v>
+      </c>
+      <c r="P90" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>6</v>
+      </c>
+      <c r="R90" t="n">
+        <v>3</v>
+      </c>
+      <c r="S90" t="n">
+        <v>11</v>
+      </c>
+      <c r="T90" t="n">
+        <v>13</v>
+      </c>
+      <c r="U90" t="n">
+        <v>11</v>
+      </c>
+      <c r="V90" t="n">
+        <v>13</v>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="Y90" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC90" t="inlineStr"/>
+      <c r="AD90" t="inlineStr"/>
+      <c r="AE90" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AK90" t="inlineStr"/>
+      <c r="AL90" t="inlineStr"/>
+      <c r="AM90" t="inlineStr"/>
+      <c r="AN90" t="inlineStr"/>
+      <c r="AO90" t="inlineStr"/>
+      <c r="AP90" t="inlineStr"/>
+      <c r="AQ90" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AT90" t="n">
+        <v>63.0625</v>
+      </c>
+      <c r="AU90" t="n">
+        <v>751562.5</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>71.4375</v>
+      </c>
+      <c r="AW90" t="inlineStr"/>
+      <c r="AX90" t="inlineStr"/>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr"/>
+      <c r="BA90" t="inlineStr"/>
+      <c r="BB90" t="inlineStr"/>
+      <c r="BC90" t="inlineStr"/>
+      <c r="BD90" t="inlineStr"/>
+      <c r="BE90" t="inlineStr"/>
+      <c r="BF90" t="inlineStr"/>
+      <c r="BG90" t="inlineStr"/>
+      <c r="BH90" t="inlineStr"/>
+      <c r="BI90" t="inlineStr"/>
+      <c r="BJ90" t="inlineStr"/>
+      <c r="BK90" t="inlineStr"/>
+      <c r="BL90" t="inlineStr"/>
+      <c r="BM90" t="inlineStr"/>
+      <c r="BN90" t="inlineStr"/>
+      <c r="BO90" t="inlineStr"/>
+      <c r="BP90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>6V8cnEDr</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landry r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade gabriel montpied
+  clermont ferrand </t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F91" t="n">
+        <v>5582</v>
+      </c>
+      <c r="G91" t="n">
+        <v>2</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="n">
+        <v>56</v>
+      </c>
+      <c r="N91" t="n">
+        <v>44</v>
+      </c>
+      <c r="O91" t="n">
+        <v>13</v>
+      </c>
+      <c r="P91" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>5</v>
+      </c>
+      <c r="R91" t="n">
+        <v>4</v>
+      </c>
+      <c r="S91" t="n">
+        <v>14</v>
+      </c>
+      <c r="T91" t="n">
+        <v>12</v>
+      </c>
+      <c r="U91" t="n">
+        <v>14</v>
+      </c>
+      <c r="V91" t="n">
+        <v>16</v>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="Y91" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC91" t="inlineStr"/>
+      <c r="AD91" t="inlineStr"/>
+      <c r="AE91" t="n">
+        <v>23.88888888888889</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>66.44444444444444</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>1436111.111111111</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>962500</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AQ91" t="n">
+        <v>20.85714285714286</v>
+      </c>
+      <c r="AR91" t="n">
+        <v>176</v>
+      </c>
+      <c r="AS91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT91" t="n">
+        <v>65.28571428571429</v>
+      </c>
+      <c r="AU91" t="n">
+        <v>1614285.714285714</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>75.28571428571429</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>182.7272727272727</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>64.54545454545455</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>709090.9090909091</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>70.27272727272727</v>
+      </c>
+      <c r="BC91" t="inlineStr"/>
+      <c r="BD91" t="inlineStr"/>
+      <c r="BE91" t="inlineStr"/>
+      <c r="BF91" t="inlineStr"/>
+      <c r="BG91" t="inlineStr"/>
+      <c r="BH91" t="inlineStr"/>
+      <c r="BI91" t="inlineStr"/>
+      <c r="BJ91" t="inlineStr"/>
+      <c r="BK91" t="inlineStr"/>
+      <c r="BL91" t="inlineStr"/>
+      <c r="BM91" t="inlineStr"/>
+      <c r="BN91" t="inlineStr"/>
+      <c r="BO91" t="inlineStr"/>
+      <c r="BP91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>zB0ErWC7</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kubler g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade marcel tribut
+  dunkerque </t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>4933</v>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="n">
+        <v>48</v>
+      </c>
+      <c r="N92" t="n">
+        <v>52</v>
+      </c>
+      <c r="O92" t="n">
+        <v>12</v>
+      </c>
+      <c r="P92" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>6</v>
+      </c>
+      <c r="R92" t="n">
+        <v>4</v>
+      </c>
+      <c r="S92" t="n">
+        <v>15</v>
+      </c>
+      <c r="T92" t="n">
+        <v>15</v>
+      </c>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="Y92" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC92" t="inlineStr"/>
+      <c r="AD92" t="inlineStr"/>
+      <c r="AE92" t="inlineStr"/>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="inlineStr"/>
+      <c r="AH92" t="inlineStr"/>
+      <c r="AI92" t="inlineStr"/>
+      <c r="AJ92" t="inlineStr"/>
+      <c r="AK92" t="n">
+        <v>26.44444444444444</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>182.5555555555555</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>64.55555555555556</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>833333.3333333334</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>67.77777777777777</v>
+      </c>
+      <c r="AQ92" t="n">
+        <v>22.83333333333333</v>
+      </c>
+      <c r="AR92" t="n">
+        <v>176.8333333333333</v>
+      </c>
+      <c r="AS92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT92" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="AU92" t="n">
+        <v>804166.6666666666</v>
+      </c>
+      <c r="AV92" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="AX92" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AY92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ92" t="n">
+        <v>61.83333333333334</v>
+      </c>
+      <c r="BA92" t="n">
+        <v>708333.3333333334</v>
+      </c>
+      <c r="BB92" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="BC92" t="inlineStr"/>
+      <c r="BD92" t="inlineStr"/>
+      <c r="BE92" t="inlineStr"/>
+      <c r="BF92" t="inlineStr"/>
+      <c r="BG92" t="inlineStr"/>
+      <c r="BH92" t="inlineStr"/>
+      <c r="BI92" t="inlineStr"/>
+      <c r="BJ92" t="inlineStr"/>
+      <c r="BK92" t="inlineStr"/>
+      <c r="BL92" t="inlineStr"/>
+      <c r="BM92" t="inlineStr"/>
+      <c r="BN92" t="inlineStr"/>
+      <c r="BO92" t="inlineStr"/>
+      <c r="BP92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>dGo94DZQ</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>20068</v>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="n">
+        <v>6</v>
+      </c>
+      <c r="P93" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>4</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1</v>
+      </c>
+      <c r="S93" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="Y93" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC93" t="inlineStr"/>
+      <c r="AD93" t="inlineStr"/>
+      <c r="AE93" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>1495454.545454545</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AK93" t="inlineStr"/>
+      <c r="AL93" t="inlineStr"/>
+      <c r="AM93" t="inlineStr"/>
+      <c r="AN93" t="inlineStr"/>
+      <c r="AO93" t="inlineStr"/>
+      <c r="AP93" t="inlineStr"/>
+      <c r="AQ93" t="n">
+        <v>29.66666666666667</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>185.1666666666667</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT93" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AU93" t="n">
+        <v>1937500</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>24.8125</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>64.3125</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>958750</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>71.3125</v>
+      </c>
+      <c r="BC93" t="inlineStr"/>
+      <c r="BD93" t="inlineStr"/>
+      <c r="BE93" t="inlineStr"/>
+      <c r="BF93" t="inlineStr"/>
+      <c r="BG93" t="inlineStr"/>
+      <c r="BH93" t="inlineStr"/>
+      <c r="BI93" t="inlineStr"/>
+      <c r="BJ93" t="inlineStr"/>
+      <c r="BK93" t="inlineStr"/>
+      <c r="BL93" t="inlineStr"/>
+      <c r="BM93" t="inlineStr"/>
+      <c r="BN93" t="inlineStr"/>
+      <c r="BO93" t="inlineStr"/>
+      <c r="BP93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>b15XX7Nt</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de roudourou
+  guingamp </t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>19060</v>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="n">
+        <v>4</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="n">
+        <v>49</v>
+      </c>
+      <c r="N94" t="n">
+        <v>51</v>
+      </c>
+      <c r="O94" t="n">
+        <v>16</v>
+      </c>
+      <c r="P94" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>5</v>
+      </c>
+      <c r="R94" t="n">
+        <v>3</v>
+      </c>
+      <c r="S94" t="n">
+        <v>9</v>
+      </c>
+      <c r="T94" t="n">
+        <v>12</v>
+      </c>
+      <c r="U94" t="n">
+        <v>9</v>
+      </c>
+      <c r="V94" t="n">
+        <v>14</v>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="Y94" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC94" t="inlineStr"/>
+      <c r="AD94" t="inlineStr"/>
+      <c r="AE94" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>1025000</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>27.625</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>177.625</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>67.375</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>70.375</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>950000</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>20.41666666666667</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>912500</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>70.91666666666667</v>
+      </c>
+      <c r="BC94" t="inlineStr"/>
+      <c r="BD94" t="inlineStr"/>
+      <c r="BE94" t="inlineStr"/>
+      <c r="BF94" t="inlineStr"/>
+      <c r="BG94" t="inlineStr"/>
+      <c r="BH94" t="inlineStr"/>
+      <c r="BI94" t="inlineStr"/>
+      <c r="BJ94" t="inlineStr"/>
+      <c r="BK94" t="inlineStr"/>
+      <c r="BL94" t="inlineStr"/>
+      <c r="BM94" t="inlineStr"/>
+      <c r="BN94" t="inlineStr"/>
+      <c r="BO94" t="inlineStr"/>
+      <c r="BP94" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP78"/>
+  <dimension ref="A1:BP96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17126,6 +17126,3506 @@
       <c r="BO78" t="inlineStr"/>
       <c r="BP78" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>zkPwWhT1</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>45522.65625</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="n">
+        <v>3</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M79" t="n">
+        <v>48</v>
+      </c>
+      <c r="N79" t="n">
+        <v>52</v>
+      </c>
+      <c r="O79" t="n">
+        <v>22</v>
+      </c>
+      <c r="P79" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>8</v>
+      </c>
+      <c r="R79" t="n">
+        <v>2</v>
+      </c>
+      <c r="S79" t="n">
+        <v>13</v>
+      </c>
+      <c r="T79" t="n">
+        <v>12</v>
+      </c>
+      <c r="U79" t="n">
+        <v>8</v>
+      </c>
+      <c r="V79" t="n">
+        <v>11</v>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="Y79" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="n">
+        <v>25.875</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>75.625</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>9475000</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>10111111.11111111</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>80</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>24.23076923076923</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>181.9230769230769</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>1.538461538461539</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>73.07692307692308</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>8578846.153846154</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>77.53846153846153</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>23.81818181818182</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>1.681818181818182</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>73.18181818181819</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>5522727.272727272</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>78.81818181818181</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>189</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BI79" t="n">
+        <v>78</v>
+      </c>
+      <c r="BJ79" t="n">
+        <v>31</v>
+      </c>
+      <c r="BK79" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>159</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>2NocJFqd</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F80" t="n">
+        <v>14811</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M80" t="n">
+        <v>44</v>
+      </c>
+      <c r="N80" t="n">
+        <v>56</v>
+      </c>
+      <c r="O80" t="n">
+        <v>4</v>
+      </c>
+      <c r="P80" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>3</v>
+      </c>
+      <c r="R80" t="n">
+        <v>5</v>
+      </c>
+      <c r="S80" t="n">
+        <v>6</v>
+      </c>
+      <c r="T80" t="n">
+        <v>10</v>
+      </c>
+      <c r="U80" t="n">
+        <v>10</v>
+      </c>
+      <c r="V80" t="n">
+        <v>11</v>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="Y80" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="AE80" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>68</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>1587500</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>27.63636363636364</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>179.8181818181818</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>77</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>12381818.18181818</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>78.72727272727273</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>66.45</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>1278750</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>23.90909090909091</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>179.9545454545455</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>72.90909090909091</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>6081818.181818182</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>78.13636363636364</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>266</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>5725000</v>
+      </c>
+      <c r="BI80" t="n">
+        <v>290</v>
+      </c>
+      <c r="BJ80" t="n">
+        <v>25</v>
+      </c>
+      <c r="BK80" t="n">
+        <v>179</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>298</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>28600000</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>M5VGwpVA</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F81" t="n">
+        <v>15706</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L81" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M81" t="n">
+        <v>43</v>
+      </c>
+      <c r="N81" t="n">
+        <v>57</v>
+      </c>
+      <c r="O81" t="n">
+        <v>7</v>
+      </c>
+      <c r="P81" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>5</v>
+      </c>
+      <c r="R81" t="n">
+        <v>4</v>
+      </c>
+      <c r="S81" t="n">
+        <v>20</v>
+      </c>
+      <c r="T81" t="n">
+        <v>18</v>
+      </c>
+      <c r="U81" t="n">
+        <v>3</v>
+      </c>
+      <c r="V81" t="n">
+        <v>9</v>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="Y81" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="AE81" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>6330000</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>21.22222222222222</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>185.4444444444445</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>70.77777777777777</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>4402777.777777778</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>79.88888888888889</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>182</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>3787500</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>76.625</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>21.875</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>67.1875</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>2412500</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>76</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>31</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>186</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>147</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="BI81" t="n">
+        <v>147</v>
+      </c>
+      <c r="BJ81" t="n">
+        <v>19</v>
+      </c>
+      <c r="BK81" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN81" t="n">
+        <v>70</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>6ehlLyFq</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F82" t="n">
+        <v>25491</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M82" t="n">
+        <v>53</v>
+      </c>
+      <c r="N82" t="n">
+        <v>47</v>
+      </c>
+      <c r="O82" t="n">
+        <v>7</v>
+      </c>
+      <c r="P82" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>3</v>
+      </c>
+      <c r="R82" t="n">
+        <v>2</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="n">
+        <v>8</v>
+      </c>
+      <c r="U82" t="n">
+        <v>8</v>
+      </c>
+      <c r="V82" t="n">
+        <v>3</v>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="Y82" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AE82" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>182</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>5310000</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>178.375</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>69.8125</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>2631250</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>75.4375</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>25.76470588235294</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>182.8235294117647</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>1.411764705882353</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>71.76470588235294</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>3450000</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>74.58823529411765</v>
+      </c>
+      <c r="BC82" t="inlineStr"/>
+      <c r="BD82" t="inlineStr"/>
+      <c r="BE82" t="inlineStr"/>
+      <c r="BF82" t="inlineStr"/>
+      <c r="BG82" t="inlineStr"/>
+      <c r="BH82" t="inlineStr"/>
+      <c r="BI82" t="inlineStr"/>
+      <c r="BJ82" t="inlineStr"/>
+      <c r="BK82" t="inlineStr"/>
+      <c r="BL82" t="inlineStr"/>
+      <c r="BM82" t="inlineStr"/>
+      <c r="BN82" t="inlineStr"/>
+      <c r="BO82" t="inlineStr"/>
+      <c r="BP82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>ripawyyS</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>45522.41666666666</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F83" t="n">
+        <v>16354</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M83" t="n">
+        <v>46</v>
+      </c>
+      <c r="N83" t="n">
+        <v>54</v>
+      </c>
+      <c r="O83" t="n">
+        <v>16</v>
+      </c>
+      <c r="P83" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>7</v>
+      </c>
+      <c r="R83" t="n">
+        <v>2</v>
+      </c>
+      <c r="S83" t="n">
+        <v>11</v>
+      </c>
+      <c r="T83" t="n">
+        <v>17</v>
+      </c>
+      <c r="U83" t="n">
+        <v>7</v>
+      </c>
+      <c r="V83" t="n">
+        <v>8</v>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="Y83" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC83" t="inlineStr"/>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="AE83" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>68.22222222222223</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>1708333.333333333</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>184</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>9280000</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>25.08333333333333</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>180.8333333333333</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>65.08333333333333</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>1062500</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>5470000</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>192</v>
+      </c>
+      <c r="BE83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG83" t="n">
+        <v>69</v>
+      </c>
+      <c r="BH83" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="BI83" t="n">
+        <v>74</v>
+      </c>
+      <c r="BJ83" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BK83" t="n">
+        <v>177</v>
+      </c>
+      <c r="BL83" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM83" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN83" t="n">
+        <v>307</v>
+      </c>
+      <c r="BO83" t="n">
+        <v>53500000</v>
+      </c>
+      <c r="BP83" t="n">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>fHYrsJy3</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>45521.66666666666</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F84" t="n">
+        <v>14250</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M84" t="n">
+        <v>61</v>
+      </c>
+      <c r="N84" t="n">
+        <v>39</v>
+      </c>
+      <c r="O84" t="n">
+        <v>13</v>
+      </c>
+      <c r="P84" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>6</v>
+      </c>
+      <c r="R84" t="n">
+        <v>4</v>
+      </c>
+      <c r="S84" t="n">
+        <v>13</v>
+      </c>
+      <c r="T84" t="n">
+        <v>14</v>
+      </c>
+      <c r="U84" t="n">
+        <v>4</v>
+      </c>
+      <c r="V84" t="n">
+        <v>17</v>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="Y84" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr"/>
+      <c r="AE84" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>12650000</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="AK84" t="inlineStr"/>
+      <c r="AL84" t="inlineStr"/>
+      <c r="AM84" t="inlineStr"/>
+      <c r="AN84" t="inlineStr"/>
+      <c r="AO84" t="inlineStr"/>
+      <c r="AP84" t="inlineStr"/>
+      <c r="AQ84" t="n">
+        <v>20.86666666666667</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>72.73333333333333</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>9083333.333333334</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>82</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>182.1818181818182</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>65.81818181818181</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>1463636.363636364</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>74.27272727272727</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>190</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>78</v>
+      </c>
+      <c r="BH84" t="n">
+        <v>20500000</v>
+      </c>
+      <c r="BI84" t="n">
+        <v>84</v>
+      </c>
+      <c r="BJ84" t="n">
+        <v>24</v>
+      </c>
+      <c r="BK84" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN84" t="n">
+        <v>71</v>
+      </c>
+      <c r="BO84" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="BP84" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>jqSiuc6F</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F85" t="n">
+        <v>14755</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M85" t="n">
+        <v>29</v>
+      </c>
+      <c r="N85" t="n">
+        <v>71</v>
+      </c>
+      <c r="O85" t="n">
+        <v>2</v>
+      </c>
+      <c r="P85" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6</v>
+      </c>
+      <c r="S85" t="n">
+        <v>6</v>
+      </c>
+      <c r="T85" t="n">
+        <v>13</v>
+      </c>
+      <c r="U85" t="n">
+        <v>12</v>
+      </c>
+      <c r="V85" t="n">
+        <v>6</v>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="Y85" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC85" t="inlineStr"/>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr"/>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="inlineStr"/>
+      <c r="AH85" t="inlineStr"/>
+      <c r="AI85" t="inlineStr"/>
+      <c r="AJ85" t="inlineStr"/>
+      <c r="AK85" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>75.875</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>10312500</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>68</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>3266666.666666667</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>178.6111111111111</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>72.38888888888889</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>8463888.888888888</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>79.88888888888889</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>221</v>
+      </c>
+      <c r="BH85" t="n">
+        <v>29200000</v>
+      </c>
+      <c r="BI85" t="n">
+        <v>238</v>
+      </c>
+      <c r="BJ85" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="BK85" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="BL85" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM85" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN85" t="n">
+        <v>386</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>55800000</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>0js8u60b</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F86" t="n">
+        <v>14962</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>5</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L86" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M86" t="n">
+        <v>51</v>
+      </c>
+      <c r="N86" t="n">
+        <v>49</v>
+      </c>
+      <c r="O86" t="n">
+        <v>7</v>
+      </c>
+      <c r="P86" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>5</v>
+      </c>
+      <c r="R86" t="n">
+        <v>5</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="n">
+        <v>8</v>
+      </c>
+      <c r="U86" t="n">
+        <v>10</v>
+      </c>
+      <c r="V86" t="n">
+        <v>12</v>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="Y86" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC86" t="inlineStr"/>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="AE86" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>5460000</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK86" t="inlineStr"/>
+      <c r="AL86" t="inlineStr"/>
+      <c r="AM86" t="inlineStr"/>
+      <c r="AN86" t="inlineStr"/>
+      <c r="AO86" t="inlineStr"/>
+      <c r="AP86" t="inlineStr"/>
+      <c r="AQ86" t="n">
+        <v>22.78571428571428</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>178.1428571428571</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>67.71428571428571</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>4185714.285714286</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>74.42857142857143</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>24.36363636363636</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>180.0909090909091</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>75.18181818181819</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>10490909.09090909</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>79.18181818181819</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>172</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>74</v>
+      </c>
+      <c r="BH86" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="BI86" t="n">
+        <v>77</v>
+      </c>
+      <c r="BJ86" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BK86" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="BL86" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BM86" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN86" t="n">
+        <v>296</v>
+      </c>
+      <c r="BO86" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="BP86" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>SOLVXEbk</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>45520.65625</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F87" t="n">
+        <v>23167</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>4</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M87" t="n">
+        <v>26</v>
+      </c>
+      <c r="N87" t="n">
+        <v>74</v>
+      </c>
+      <c r="O87" t="n">
+        <v>5</v>
+      </c>
+      <c r="P87" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>2</v>
+      </c>
+      <c r="R87" t="n">
+        <v>9</v>
+      </c>
+      <c r="S87" t="n">
+        <v>9</v>
+      </c>
+      <c r="T87" t="n">
+        <v>9</v>
+      </c>
+      <c r="U87" t="n">
+        <v>8</v>
+      </c>
+      <c r="V87" t="n">
+        <v>4</v>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="Y87" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC87" t="inlineStr"/>
+      <c r="AD87" t="inlineStr"/>
+      <c r="AE87" t="n">
+        <v>25.18181818181818</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>185.2727272727273</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>2945454.545454545</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK87" t="inlineStr"/>
+      <c r="AL87" t="inlineStr"/>
+      <c r="AM87" t="inlineStr"/>
+      <c r="AN87" t="inlineStr"/>
+      <c r="AO87" t="inlineStr"/>
+      <c r="AP87" t="inlineStr"/>
+      <c r="AQ87" t="n">
+        <v>22.5625</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>180.0625</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>1389062.5</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>23.69230769230769</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>183.5384615384615</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>2.307692307692307</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>80.38461538461539</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>42061538.46153846</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>84.76923076923077</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>188</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG87" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH87" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BI87" t="n">
+        <v>74</v>
+      </c>
+      <c r="BJ87" t="n">
+        <v>27</v>
+      </c>
+      <c r="BK87" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="BL87" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM87" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN87" t="n">
+        <v>165</v>
+      </c>
+      <c r="BO87" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="BP87" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>dvUee9dD</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>45521.39583333334</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gaillouste p 
+  fra </t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade michel d ornano
+  caen </t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>20300</v>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="n">
+        <v>36</v>
+      </c>
+      <c r="N88" t="n">
+        <v>64</v>
+      </c>
+      <c r="O88" t="n">
+        <v>9</v>
+      </c>
+      <c r="P88" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>5</v>
+      </c>
+      <c r="R88" t="n">
+        <v>5</v>
+      </c>
+      <c r="S88" t="n">
+        <v>15</v>
+      </c>
+      <c r="T88" t="n">
+        <v>13</v>
+      </c>
+      <c r="U88" t="n">
+        <v>10</v>
+      </c>
+      <c r="V88" t="n">
+        <v>6</v>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="Y88" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC88" t="inlineStr"/>
+      <c r="AD88" t="inlineStr"/>
+      <c r="AE88" t="n">
+        <v>25.44444444444444</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>181</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>67.55555555555556</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>1638888.888888889</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>74</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>177.8888888888889</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>67.22222222222223</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>1697222.222222222</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>71.55555555555556</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>22.07142857142857</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>179.7857142857143</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>64.21428571428571</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>1037500</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>74.07142857142857</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>1083750</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>69.15000000000001</v>
+      </c>
+      <c r="BC88" t="inlineStr"/>
+      <c r="BD88" t="inlineStr"/>
+      <c r="BE88" t="inlineStr"/>
+      <c r="BF88" t="inlineStr"/>
+      <c r="BG88" t="inlineStr"/>
+      <c r="BH88" t="inlineStr"/>
+      <c r="BI88" t="inlineStr"/>
+      <c r="BJ88" t="inlineStr"/>
+      <c r="BK88" t="inlineStr"/>
+      <c r="BL88" t="inlineStr"/>
+      <c r="BM88" t="inlineStr"/>
+      <c r="BN88" t="inlineStr"/>
+      <c r="BO88" t="inlineStr"/>
+      <c r="BP88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>EeC5phre</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valnet a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michel moretti stadium
+  ajaccio </t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>8470</v>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="n">
+        <v>1</v>
+      </c>
+      <c r="N89" t="n">
+        <v>99</v>
+      </c>
+      <c r="O89" t="n">
+        <v>8</v>
+      </c>
+      <c r="P89" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>4</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>2</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="Y89" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC89" t="inlineStr"/>
+      <c r="AD89" t="inlineStr"/>
+      <c r="AE89" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>872500</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>1090625</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>26.38888888888889</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>180</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>65.05555555555556</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>751388.8888888889</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>69.61111111111111</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>830000</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>71</v>
+      </c>
+      <c r="BC89" t="inlineStr"/>
+      <c r="BD89" t="inlineStr"/>
+      <c r="BE89" t="inlineStr"/>
+      <c r="BF89" t="inlineStr"/>
+      <c r="BG89" t="inlineStr"/>
+      <c r="BH89" t="inlineStr"/>
+      <c r="BI89" t="inlineStr"/>
+      <c r="BJ89" t="inlineStr"/>
+      <c r="BK89" t="inlineStr"/>
+      <c r="BL89" t="inlineStr"/>
+      <c r="BM89" t="inlineStr"/>
+      <c r="BN89" t="inlineStr"/>
+      <c r="BO89" t="inlineStr"/>
+      <c r="BP89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>2Hh06Z4E</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rosier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>12097</v>
+      </c>
+      <c r="F90" t="n">
+        <v>4918</v>
+      </c>
+      <c r="G90" t="n">
+        <v>3</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="n">
+        <v>51</v>
+      </c>
+      <c r="N90" t="n">
+        <v>49</v>
+      </c>
+      <c r="O90" t="n">
+        <v>17</v>
+      </c>
+      <c r="P90" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>6</v>
+      </c>
+      <c r="R90" t="n">
+        <v>3</v>
+      </c>
+      <c r="S90" t="n">
+        <v>11</v>
+      </c>
+      <c r="T90" t="n">
+        <v>13</v>
+      </c>
+      <c r="U90" t="n">
+        <v>11</v>
+      </c>
+      <c r="V90" t="n">
+        <v>13</v>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="Y90" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC90" t="inlineStr"/>
+      <c r="AD90" t="inlineStr"/>
+      <c r="AE90" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AK90" t="inlineStr"/>
+      <c r="AL90" t="inlineStr"/>
+      <c r="AM90" t="inlineStr"/>
+      <c r="AN90" t="inlineStr"/>
+      <c r="AO90" t="inlineStr"/>
+      <c r="AP90" t="inlineStr"/>
+      <c r="AQ90" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AT90" t="n">
+        <v>63.0625</v>
+      </c>
+      <c r="AU90" t="n">
+        <v>751562.5</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>71.4375</v>
+      </c>
+      <c r="AW90" t="inlineStr"/>
+      <c r="AX90" t="inlineStr"/>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr"/>
+      <c r="BA90" t="inlineStr"/>
+      <c r="BB90" t="inlineStr"/>
+      <c r="BC90" t="inlineStr"/>
+      <c r="BD90" t="inlineStr"/>
+      <c r="BE90" t="inlineStr"/>
+      <c r="BF90" t="inlineStr"/>
+      <c r="BG90" t="inlineStr"/>
+      <c r="BH90" t="inlineStr"/>
+      <c r="BI90" t="inlineStr"/>
+      <c r="BJ90" t="inlineStr"/>
+      <c r="BK90" t="inlineStr"/>
+      <c r="BL90" t="inlineStr"/>
+      <c r="BM90" t="inlineStr"/>
+      <c r="BN90" t="inlineStr"/>
+      <c r="BO90" t="inlineStr"/>
+      <c r="BP90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>6V8cnEDr</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landry r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade gabriel montpied
+  clermont ferrand </t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F91" t="n">
+        <v>5582</v>
+      </c>
+      <c r="G91" t="n">
+        <v>2</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="n">
+        <v>56</v>
+      </c>
+      <c r="N91" t="n">
+        <v>44</v>
+      </c>
+      <c r="O91" t="n">
+        <v>13</v>
+      </c>
+      <c r="P91" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>5</v>
+      </c>
+      <c r="R91" t="n">
+        <v>4</v>
+      </c>
+      <c r="S91" t="n">
+        <v>14</v>
+      </c>
+      <c r="T91" t="n">
+        <v>12</v>
+      </c>
+      <c r="U91" t="n">
+        <v>14</v>
+      </c>
+      <c r="V91" t="n">
+        <v>16</v>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="Y91" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC91" t="inlineStr"/>
+      <c r="AD91" t="inlineStr"/>
+      <c r="AE91" t="n">
+        <v>23.88888888888889</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>66.44444444444444</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>1436111.111111111</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>962500</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AQ91" t="n">
+        <v>20.85714285714286</v>
+      </c>
+      <c r="AR91" t="n">
+        <v>176</v>
+      </c>
+      <c r="AS91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT91" t="n">
+        <v>65.28571428571429</v>
+      </c>
+      <c r="AU91" t="n">
+        <v>1614285.714285714</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>75.28571428571429</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>182.7272727272727</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>64.54545454545455</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>709090.9090909091</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>70.27272727272727</v>
+      </c>
+      <c r="BC91" t="inlineStr"/>
+      <c r="BD91" t="inlineStr"/>
+      <c r="BE91" t="inlineStr"/>
+      <c r="BF91" t="inlineStr"/>
+      <c r="BG91" t="inlineStr"/>
+      <c r="BH91" t="inlineStr"/>
+      <c r="BI91" t="inlineStr"/>
+      <c r="BJ91" t="inlineStr"/>
+      <c r="BK91" t="inlineStr"/>
+      <c r="BL91" t="inlineStr"/>
+      <c r="BM91" t="inlineStr"/>
+      <c r="BN91" t="inlineStr"/>
+      <c r="BO91" t="inlineStr"/>
+      <c r="BP91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>zB0ErWC7</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kubler g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade marcel tribut
+  dunkerque </t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>4933</v>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="n">
+        <v>48</v>
+      </c>
+      <c r="N92" t="n">
+        <v>52</v>
+      </c>
+      <c r="O92" t="n">
+        <v>12</v>
+      </c>
+      <c r="P92" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>6</v>
+      </c>
+      <c r="R92" t="n">
+        <v>4</v>
+      </c>
+      <c r="S92" t="n">
+        <v>15</v>
+      </c>
+      <c r="T92" t="n">
+        <v>15</v>
+      </c>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="Y92" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC92" t="inlineStr"/>
+      <c r="AD92" t="inlineStr"/>
+      <c r="AE92" t="inlineStr"/>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="inlineStr"/>
+      <c r="AH92" t="inlineStr"/>
+      <c r="AI92" t="inlineStr"/>
+      <c r="AJ92" t="inlineStr"/>
+      <c r="AK92" t="n">
+        <v>26.44444444444444</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>182.5555555555555</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>64.55555555555556</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>833333.3333333334</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>67.77777777777777</v>
+      </c>
+      <c r="AQ92" t="n">
+        <v>22.83333333333333</v>
+      </c>
+      <c r="AR92" t="n">
+        <v>176.8333333333333</v>
+      </c>
+      <c r="AS92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT92" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="AU92" t="n">
+        <v>804166.6666666666</v>
+      </c>
+      <c r="AV92" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="AX92" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AY92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ92" t="n">
+        <v>61.83333333333334</v>
+      </c>
+      <c r="BA92" t="n">
+        <v>708333.3333333334</v>
+      </c>
+      <c r="BB92" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="BC92" t="inlineStr"/>
+      <c r="BD92" t="inlineStr"/>
+      <c r="BE92" t="inlineStr"/>
+      <c r="BF92" t="inlineStr"/>
+      <c r="BG92" t="inlineStr"/>
+      <c r="BH92" t="inlineStr"/>
+      <c r="BI92" t="inlineStr"/>
+      <c r="BJ92" t="inlineStr"/>
+      <c r="BK92" t="inlineStr"/>
+      <c r="BL92" t="inlineStr"/>
+      <c r="BM92" t="inlineStr"/>
+      <c r="BN92" t="inlineStr"/>
+      <c r="BO92" t="inlineStr"/>
+      <c r="BP92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>dGo94DZQ</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>20068</v>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="n">
+        <v>6</v>
+      </c>
+      <c r="P93" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>4</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1</v>
+      </c>
+      <c r="S93" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="Y93" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC93" t="inlineStr"/>
+      <c r="AD93" t="inlineStr"/>
+      <c r="AE93" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>1495454.545454545</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AK93" t="inlineStr"/>
+      <c r="AL93" t="inlineStr"/>
+      <c r="AM93" t="inlineStr"/>
+      <c r="AN93" t="inlineStr"/>
+      <c r="AO93" t="inlineStr"/>
+      <c r="AP93" t="inlineStr"/>
+      <c r="AQ93" t="n">
+        <v>29.66666666666667</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>185.1666666666667</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT93" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AU93" t="n">
+        <v>1937500</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>24.8125</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>64.3125</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>958750</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>71.3125</v>
+      </c>
+      <c r="BC93" t="inlineStr"/>
+      <c r="BD93" t="inlineStr"/>
+      <c r="BE93" t="inlineStr"/>
+      <c r="BF93" t="inlineStr"/>
+      <c r="BG93" t="inlineStr"/>
+      <c r="BH93" t="inlineStr"/>
+      <c r="BI93" t="inlineStr"/>
+      <c r="BJ93" t="inlineStr"/>
+      <c r="BK93" t="inlineStr"/>
+      <c r="BL93" t="inlineStr"/>
+      <c r="BM93" t="inlineStr"/>
+      <c r="BN93" t="inlineStr"/>
+      <c r="BO93" t="inlineStr"/>
+      <c r="BP93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>b15XX7Nt</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de roudourou
+  guingamp </t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>19060</v>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="n">
+        <v>4</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="n">
+        <v>49</v>
+      </c>
+      <c r="N94" t="n">
+        <v>51</v>
+      </c>
+      <c r="O94" t="n">
+        <v>16</v>
+      </c>
+      <c r="P94" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>5</v>
+      </c>
+      <c r="R94" t="n">
+        <v>3</v>
+      </c>
+      <c r="S94" t="n">
+        <v>9</v>
+      </c>
+      <c r="T94" t="n">
+        <v>12</v>
+      </c>
+      <c r="U94" t="n">
+        <v>9</v>
+      </c>
+      <c r="V94" t="n">
+        <v>14</v>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="Y94" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC94" t="inlineStr"/>
+      <c r="AD94" t="inlineStr"/>
+      <c r="AE94" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>1025000</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>27.625</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>177.625</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>67.375</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>70.375</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>950000</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>20.41666666666667</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>912500</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>70.91666666666667</v>
+      </c>
+      <c r="BC94" t="inlineStr"/>
+      <c r="BD94" t="inlineStr"/>
+      <c r="BE94" t="inlineStr"/>
+      <c r="BF94" t="inlineStr"/>
+      <c r="BG94" t="inlineStr"/>
+      <c r="BH94" t="inlineStr"/>
+      <c r="BI94" t="inlineStr"/>
+      <c r="BJ94" t="inlineStr"/>
+      <c r="BK94" t="inlineStr"/>
+      <c r="BL94" t="inlineStr"/>
+      <c r="BM94" t="inlineStr"/>
+      <c r="BN94" t="inlineStr"/>
+      <c r="BO94" t="inlineStr"/>
+      <c r="BP94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>OA5YizjL</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>45523.65625</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thual o 
+  fra </t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="n">
+        <v>33</v>
+      </c>
+      <c r="N95" t="n">
+        <v>67</v>
+      </c>
+      <c r="O95" t="n">
+        <v>3</v>
+      </c>
+      <c r="P95" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>1</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7</v>
+      </c>
+      <c r="S95" t="n">
+        <v>8</v>
+      </c>
+      <c r="T95" t="n">
+        <v>13</v>
+      </c>
+      <c r="U95" t="n">
+        <v>16</v>
+      </c>
+      <c r="V95" t="n">
+        <v>6</v>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="Y95" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC95" t="inlineStr"/>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr"/>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="inlineStr"/>
+      <c r="AH95" t="inlineStr"/>
+      <c r="AI95" t="inlineStr"/>
+      <c r="AJ95" t="inlineStr"/>
+      <c r="AK95" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>178.1111111111111</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>71.77777777777777</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>4622222.222222222</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AQ95" t="inlineStr"/>
+      <c r="AR95" t="inlineStr"/>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AU95" t="inlineStr"/>
+      <c r="AV95" t="inlineStr"/>
+      <c r="AW95" t="n">
+        <v>21.73333333333333</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>69.06666666666666</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>2781666.666666667</v>
+      </c>
+      <c r="BB95" t="n">
+        <v>77.53333333333333</v>
+      </c>
+      <c r="BC95" t="inlineStr"/>
+      <c r="BD95" t="inlineStr"/>
+      <c r="BE95" t="inlineStr"/>
+      <c r="BF95" t="inlineStr"/>
+      <c r="BG95" t="inlineStr"/>
+      <c r="BH95" t="inlineStr"/>
+      <c r="BI95" t="inlineStr"/>
+      <c r="BJ95" t="inlineStr"/>
+      <c r="BK95" t="inlineStr"/>
+      <c r="BL95" t="inlineStr"/>
+      <c r="BM95" t="inlineStr"/>
+      <c r="BN95" t="inlineStr"/>
+      <c r="BO95" t="inlineStr"/>
+      <c r="BP95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>lEQmcVR0</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>45523.65625</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petit a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade saint symphorien
+  metz </t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>28786</v>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="n">
+        <v>67</v>
+      </c>
+      <c r="N96" t="n">
+        <v>33</v>
+      </c>
+      <c r="O96" t="n">
+        <v>18</v>
+      </c>
+      <c r="P96" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>5</v>
+      </c>
+      <c r="R96" t="n">
+        <v>3</v>
+      </c>
+      <c r="S96" t="n">
+        <v>13</v>
+      </c>
+      <c r="T96" t="n">
+        <v>15</v>
+      </c>
+      <c r="U96" t="n">
+        <v>12</v>
+      </c>
+      <c r="V96" t="n">
+        <v>6</v>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="Y96" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr"/>
+      <c r="AE96" t="n">
+        <v>24.90909090909091</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>177.8181818181818</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>68.90909090909091</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>1677272.727272727</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>179.625</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>63.625</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>723125</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>68.375</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>181.0909090909091</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT96" t="n">
+        <v>67.81818181818181</v>
+      </c>
+      <c r="AU96" t="n">
+        <v>1718181.818181818</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>75</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>180</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>679166.6666666666</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>68.16666666666667</v>
+      </c>
+      <c r="BC96" t="inlineStr"/>
+      <c r="BD96" t="inlineStr"/>
+      <c r="BE96" t="inlineStr"/>
+      <c r="BF96" t="inlineStr"/>
+      <c r="BG96" t="inlineStr"/>
+      <c r="BH96" t="inlineStr"/>
+      <c r="BI96" t="inlineStr"/>
+      <c r="BJ96" t="inlineStr"/>
+      <c r="BK96" t="inlineStr"/>
+      <c r="BL96" t="inlineStr"/>
+      <c r="BM96" t="inlineStr"/>
+      <c r="BN96" t="inlineStr"/>
+      <c r="BO96" t="inlineStr"/>
+      <c r="BP96" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP96"/>
+  <dimension ref="A1:BP107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20626,6 +20626,2050 @@
       <c r="BO96" t="inlineStr"/>
       <c r="BP96" t="inlineStr"/>
     </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>45528.58333333334</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="n">
+        <v>2</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M97" t="n">
+        <v>67</v>
+      </c>
+      <c r="N97" t="n">
+        <v>33</v>
+      </c>
+      <c r="O97" t="n">
+        <v>11</v>
+      </c>
+      <c r="P97" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>6</v>
+      </c>
+      <c r="R97" t="n">
+        <v>2</v>
+      </c>
+      <c r="S97" t="n">
+        <v>9</v>
+      </c>
+      <c r="T97" t="n">
+        <v>17</v>
+      </c>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="Y97" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr"/>
+      <c r="AE97" t="n">
+        <v>22.625</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>11625000</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AK97" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>1507500</v>
+      </c>
+      <c r="AP97" t="n">
+        <v>73</v>
+      </c>
+      <c r="AQ97" t="n">
+        <v>25.07142857142857</v>
+      </c>
+      <c r="AR97" t="n">
+        <v>179.3571428571429</v>
+      </c>
+      <c r="AS97" t="n">
+        <v>1.357142857142857</v>
+      </c>
+      <c r="AT97" t="n">
+        <v>73</v>
+      </c>
+      <c r="AU97" t="n">
+        <v>6525000</v>
+      </c>
+      <c r="AV97" t="n">
+        <v>78.64285714285714</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX97" t="n">
+        <v>181.1739130434783</v>
+      </c>
+      <c r="AY97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ97" t="n">
+        <v>66.34782608695652</v>
+      </c>
+      <c r="BA97" t="n">
+        <v>1292391.304347826</v>
+      </c>
+      <c r="BB97" t="n">
+        <v>71.95652173913044</v>
+      </c>
+      <c r="BC97" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>178</v>
+      </c>
+      <c r="BE97" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="BF97" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG97" t="n">
+        <v>461</v>
+      </c>
+      <c r="BH97" t="n">
+        <v>66800000</v>
+      </c>
+      <c r="BI97" t="n">
+        <v>471</v>
+      </c>
+      <c r="BJ97" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK97" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN97" t="n">
+        <v>131</v>
+      </c>
+      <c r="BO97" t="n">
+        <v>2325000</v>
+      </c>
+      <c r="BP97" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>45528.5</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F98" t="n">
+        <v>54392</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L98" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="M98" t="n">
+        <v>32</v>
+      </c>
+      <c r="N98" t="n">
+        <v>68</v>
+      </c>
+      <c r="O98" t="n">
+        <v>2</v>
+      </c>
+      <c r="P98" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1</v>
+      </c>
+      <c r="R98" t="n">
+        <v>4</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="n">
+        <v>7</v>
+      </c>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="Y98" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC98" t="inlineStr"/>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="AE98" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>179.7777777777778</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>10300000</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>79.77777777777777</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>11600000</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="AQ98" t="n">
+        <v>24.95652173913043</v>
+      </c>
+      <c r="AR98" t="n">
+        <v>180.7391304347826</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>1.739130434782609</v>
+      </c>
+      <c r="AT98" t="n">
+        <v>74.39130434782609</v>
+      </c>
+      <c r="AU98" t="n">
+        <v>7004347.826086956</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>79.47826086956522</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>21.16666666666667</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>183.1666666666667</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>73.72222222222223</v>
+      </c>
+      <c r="BA98" t="n">
+        <v>11236111.11111111</v>
+      </c>
+      <c r="BB98" t="n">
+        <v>82</v>
+      </c>
+      <c r="BC98" t="inlineStr"/>
+      <c r="BD98" t="inlineStr"/>
+      <c r="BE98" t="inlineStr"/>
+      <c r="BF98" t="inlineStr"/>
+      <c r="BG98" t="inlineStr"/>
+      <c r="BH98" t="inlineStr"/>
+      <c r="BI98" t="inlineStr"/>
+      <c r="BJ98" t="n">
+        <v>18</v>
+      </c>
+      <c r="BK98" t="n">
+        <v>173</v>
+      </c>
+      <c r="BL98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN98" t="n">
+        <v>66</v>
+      </c>
+      <c r="BO98" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="BP98" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>45527.65625</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="n">
+        <v>6</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M99" t="n">
+        <v>71</v>
+      </c>
+      <c r="N99" t="n">
+        <v>29</v>
+      </c>
+      <c r="O99" t="n">
+        <v>21</v>
+      </c>
+      <c r="P99" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>10</v>
+      </c>
+      <c r="R99" t="n">
+        <v>3</v>
+      </c>
+      <c r="S99" t="n">
+        <v>9</v>
+      </c>
+      <c r="T99" t="n">
+        <v>16</v>
+      </c>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="Y99" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC99" t="inlineStr"/>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr"/>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr"/>
+      <c r="AH99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr"/>
+      <c r="AJ99" t="inlineStr"/>
+      <c r="AK99" t="n">
+        <v>26.45454545454545</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>180.2727272727273</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>73.90909090909091</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>5527272.727272728</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>77.27272727272727</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>184</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>1.866666666666667</v>
+      </c>
+      <c r="AT99" t="n">
+        <v>77.93333333333334</v>
+      </c>
+      <c r="AU99" t="n">
+        <v>27520000</v>
+      </c>
+      <c r="AV99" t="n">
+        <v>84.33333333333333</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>25.08333333333333</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AY99" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ99" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="BA99" t="n">
+        <v>5383333.333333333</v>
+      </c>
+      <c r="BB99" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="BC99" t="n">
+        <v>27.71428571428572</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>183.7142857142857</v>
+      </c>
+      <c r="BE99" t="n">
+        <v>2.571428571428572</v>
+      </c>
+      <c r="BF99" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG99" t="n">
+        <v>563</v>
+      </c>
+      <c r="BH99" t="n">
+        <v>162500000</v>
+      </c>
+      <c r="BI99" t="n">
+        <v>568</v>
+      </c>
+      <c r="BJ99" t="n">
+        <v>30</v>
+      </c>
+      <c r="BK99" t="n">
+        <v>196</v>
+      </c>
+      <c r="BL99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN99" t="n">
+        <v>74</v>
+      </c>
+      <c r="BO99" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="BP99" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>2yXIHV57</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>45528.39583333334</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">benchabane f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade du moustoir
+  lorient </t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>16787</v>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="n">
+        <v>2</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="n">
+        <v>52</v>
+      </c>
+      <c r="N100" t="n">
+        <v>48</v>
+      </c>
+      <c r="O100" t="n">
+        <v>12</v>
+      </c>
+      <c r="P100" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>5</v>
+      </c>
+      <c r="R100" t="n">
+        <v>3</v>
+      </c>
+      <c r="S100" t="n">
+        <v>12</v>
+      </c>
+      <c r="T100" t="n">
+        <v>10</v>
+      </c>
+      <c r="U100" t="n">
+        <v>6</v>
+      </c>
+      <c r="V100" t="n">
+        <v>5</v>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="Y100" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr"/>
+      <c r="AE100" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>178.1111111111111</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>71.77777777777777</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>4622222.222222222</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>182.6363636363636</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>1343181.818181818</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>70</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>20.92857142857143</v>
+      </c>
+      <c r="AR100" t="n">
+        <v>178.5714285714286</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT100" t="n">
+        <v>68.28571428571429</v>
+      </c>
+      <c r="AU100" t="n">
+        <v>2466071.428571429</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>78.42857142857143</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>26.38461538461538</v>
+      </c>
+      <c r="AX100" t="n">
+        <v>184.3076923076923</v>
+      </c>
+      <c r="AY100" t="n">
+        <v>1.153846153846154</v>
+      </c>
+      <c r="AZ100" t="n">
+        <v>66.38461538461539</v>
+      </c>
+      <c r="BA100" t="n">
+        <v>1365384.615384615</v>
+      </c>
+      <c r="BB100" t="n">
+        <v>71.69230769230769</v>
+      </c>
+      <c r="BC100" t="inlineStr"/>
+      <c r="BD100" t="inlineStr"/>
+      <c r="BE100" t="inlineStr"/>
+      <c r="BF100" t="inlineStr"/>
+      <c r="BG100" t="inlineStr"/>
+      <c r="BH100" t="inlineStr"/>
+      <c r="BI100" t="inlineStr"/>
+      <c r="BJ100" t="inlineStr"/>
+      <c r="BK100" t="inlineStr"/>
+      <c r="BL100" t="inlineStr"/>
+      <c r="BM100" t="inlineStr"/>
+      <c r="BN100" t="inlineStr"/>
+      <c r="BO100" t="inlineStr"/>
+      <c r="BP100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>GM5aU8kD</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>45527.625</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des sports
+  annecy </t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>15660</v>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="n">
+        <v>2</v>
+      </c>
+      <c r="H101" t="n">
+        <v>4</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="n">
+        <v>59</v>
+      </c>
+      <c r="N101" t="n">
+        <v>41</v>
+      </c>
+      <c r="O101" t="n">
+        <v>25</v>
+      </c>
+      <c r="P101" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>7</v>
+      </c>
+      <c r="R101" t="n">
+        <v>5</v>
+      </c>
+      <c r="S101" t="n">
+        <v>13</v>
+      </c>
+      <c r="T101" t="n">
+        <v>13</v>
+      </c>
+      <c r="U101" t="n">
+        <v>8</v>
+      </c>
+      <c r="V101" t="n">
+        <v>20</v>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="Y101" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC101" t="inlineStr"/>
+      <c r="AD101" t="inlineStr"/>
+      <c r="AE101" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>182</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>64.44444444444444</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>841666.6666666666</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>68.11111111111111</v>
+      </c>
+      <c r="AK101" t="inlineStr"/>
+      <c r="AL101" t="inlineStr"/>
+      <c r="AM101" t="inlineStr"/>
+      <c r="AN101" t="inlineStr"/>
+      <c r="AO101" t="inlineStr"/>
+      <c r="AP101" t="inlineStr"/>
+      <c r="AQ101" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>181.2727272727273</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>64.36363636363636</v>
+      </c>
+      <c r="AU101" t="n">
+        <v>881818.1818181818</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>70.36363636363636</v>
+      </c>
+      <c r="AW101" t="inlineStr"/>
+      <c r="AX101" t="inlineStr"/>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr"/>
+      <c r="BA101" t="inlineStr"/>
+      <c r="BB101" t="inlineStr"/>
+      <c r="BC101" t="inlineStr"/>
+      <c r="BD101" t="inlineStr"/>
+      <c r="BE101" t="inlineStr"/>
+      <c r="BF101" t="inlineStr"/>
+      <c r="BG101" t="inlineStr"/>
+      <c r="BH101" t="inlineStr"/>
+      <c r="BI101" t="inlineStr"/>
+      <c r="BJ101" t="inlineStr"/>
+      <c r="BK101" t="inlineStr"/>
+      <c r="BL101" t="inlineStr"/>
+      <c r="BM101" t="inlineStr"/>
+      <c r="BN101" t="inlineStr"/>
+      <c r="BO101" t="inlineStr"/>
+      <c r="BP101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>r97iWUK0</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>45527.625</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lesage m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade armand cesari
+  bastia </t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>16048</v>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="n">
+        <v>59</v>
+      </c>
+      <c r="N102" t="n">
+        <v>41</v>
+      </c>
+      <c r="O102" t="n">
+        <v>15</v>
+      </c>
+      <c r="P102" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>4</v>
+      </c>
+      <c r="R102" t="n">
+        <v>3</v>
+      </c>
+      <c r="S102" t="n">
+        <v>12</v>
+      </c>
+      <c r="T102" t="n">
+        <v>11</v>
+      </c>
+      <c r="U102" t="n">
+        <v>17</v>
+      </c>
+      <c r="V102" t="n">
+        <v>9</v>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="Y102" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC102" t="inlineStr"/>
+      <c r="AD102" t="inlineStr"/>
+      <c r="AE102" t="inlineStr"/>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="inlineStr"/>
+      <c r="AI102" t="inlineStr"/>
+      <c r="AJ102" t="inlineStr"/>
+      <c r="AK102" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>180.8571428571429</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>63.78571428571428</v>
+      </c>
+      <c r="AU102" t="n">
+        <v>832142.8571428572</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>67.57142857142857</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>181.0666666666667</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>728333.3333333334</v>
+      </c>
+      <c r="BB102" t="n">
+        <v>71.53333333333333</v>
+      </c>
+      <c r="BC102" t="inlineStr"/>
+      <c r="BD102" t="inlineStr"/>
+      <c r="BE102" t="inlineStr"/>
+      <c r="BF102" t="inlineStr"/>
+      <c r="BG102" t="inlineStr"/>
+      <c r="BH102" t="inlineStr"/>
+      <c r="BI102" t="inlineStr"/>
+      <c r="BJ102" t="inlineStr"/>
+      <c r="BK102" t="inlineStr"/>
+      <c r="BL102" t="inlineStr"/>
+      <c r="BM102" t="inlineStr"/>
+      <c r="BN102" t="inlineStr"/>
+      <c r="BO102" t="inlineStr"/>
+      <c r="BP102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>MaSQpUZg</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>45527.625</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thual o 
+  fra </t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le basser
+  laval </t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>11017</v>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="n">
+        <v>47</v>
+      </c>
+      <c r="N103" t="n">
+        <v>53</v>
+      </c>
+      <c r="O103" t="n">
+        <v>16</v>
+      </c>
+      <c r="P103" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>3</v>
+      </c>
+      <c r="R103" t="n">
+        <v>4</v>
+      </c>
+      <c r="S103" t="n">
+        <v>23</v>
+      </c>
+      <c r="T103" t="n">
+        <v>16</v>
+      </c>
+      <c r="U103" t="n">
+        <v>11</v>
+      </c>
+      <c r="V103" t="n">
+        <v>19</v>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="Y103" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC103" t="inlineStr"/>
+      <c r="AD103" t="inlineStr"/>
+      <c r="AE103" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>181.125</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>1281250</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>72.625</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>179.8888888888889</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>65.33333333333333</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>1077777.777777778</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>70.44444444444444</v>
+      </c>
+      <c r="AQ103" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="AR103" t="n">
+        <v>177.75</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT103" t="n">
+        <v>64.58333333333333</v>
+      </c>
+      <c r="AU103" t="n">
+        <v>832500</v>
+      </c>
+      <c r="AV103" t="n">
+        <v>71</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AY103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>60.33333333333334</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>686111.1111111111</v>
+      </c>
+      <c r="BB103" t="n">
+        <v>69.77777777777777</v>
+      </c>
+      <c r="BC103" t="inlineStr"/>
+      <c r="BD103" t="inlineStr"/>
+      <c r="BE103" t="inlineStr"/>
+      <c r="BF103" t="inlineStr"/>
+      <c r="BG103" t="inlineStr"/>
+      <c r="BH103" t="inlineStr"/>
+      <c r="BI103" t="inlineStr"/>
+      <c r="BJ103" t="inlineStr"/>
+      <c r="BK103" t="inlineStr"/>
+      <c r="BL103" t="inlineStr"/>
+      <c r="BM103" t="inlineStr"/>
+      <c r="BN103" t="inlineStr"/>
+      <c r="BO103" t="inlineStr"/>
+      <c r="BP103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>WUmnhCsK</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>45527.625</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taleb a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>12097</v>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="n">
+        <v>3</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="n">
+        <v>66</v>
+      </c>
+      <c r="N104" t="n">
+        <v>34</v>
+      </c>
+      <c r="O104" t="n">
+        <v>9</v>
+      </c>
+      <c r="P104" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>4</v>
+      </c>
+      <c r="R104" t="n">
+        <v>2</v>
+      </c>
+      <c r="S104" t="n">
+        <v>8</v>
+      </c>
+      <c r="T104" t="n">
+        <v>17</v>
+      </c>
+      <c r="U104" t="n">
+        <v>14</v>
+      </c>
+      <c r="V104" t="n">
+        <v>18</v>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="Y104" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC104" t="inlineStr"/>
+      <c r="AD104" t="inlineStr"/>
+      <c r="AE104" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>178.8888888888889</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>67.33333333333333</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>1747222.222222222</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AK104" t="inlineStr"/>
+      <c r="AL104" t="inlineStr"/>
+      <c r="AM104" t="inlineStr"/>
+      <c r="AN104" t="inlineStr"/>
+      <c r="AO104" t="inlineStr"/>
+      <c r="AP104" t="inlineStr"/>
+      <c r="AQ104" t="n">
+        <v>26.17647058823529</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>177.1764705882353</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>66.17647058823529</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>1182352.941176471</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>69.23529411764706</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>179.5833333333333</v>
+      </c>
+      <c r="AY104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>63.83333333333334</v>
+      </c>
+      <c r="BA104" t="n">
+        <v>931250</v>
+      </c>
+      <c r="BB104" t="n">
+        <v>72.91666666666667</v>
+      </c>
+      <c r="BC104" t="inlineStr"/>
+      <c r="BD104" t="inlineStr"/>
+      <c r="BE104" t="inlineStr"/>
+      <c r="BF104" t="inlineStr"/>
+      <c r="BG104" t="inlineStr"/>
+      <c r="BH104" t="inlineStr"/>
+      <c r="BI104" t="inlineStr"/>
+      <c r="BJ104" t="inlineStr"/>
+      <c r="BK104" t="inlineStr"/>
+      <c r="BL104" t="inlineStr"/>
+      <c r="BM104" t="inlineStr"/>
+      <c r="BN104" t="inlineStr"/>
+      <c r="BO104" t="inlineStr"/>
+      <c r="BP104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>nsErYjjl</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>45527.625</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leleu m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nouste camp
+  pau </t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>4031</v>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="n">
+        <v>32</v>
+      </c>
+      <c r="N105" t="n">
+        <v>68</v>
+      </c>
+      <c r="O105" t="n">
+        <v>7</v>
+      </c>
+      <c r="P105" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>2</v>
+      </c>
+      <c r="R105" t="n">
+        <v>4</v>
+      </c>
+      <c r="S105" t="n">
+        <v>12</v>
+      </c>
+      <c r="T105" t="n">
+        <v>20</v>
+      </c>
+      <c r="U105" t="n">
+        <v>9</v>
+      </c>
+      <c r="V105" t="n">
+        <v>8</v>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="Y105" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC105" t="inlineStr"/>
+      <c r="AD105" t="inlineStr"/>
+      <c r="AE105" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>64.88888888888889</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>1066666.666666667</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>73</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>1643750</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="AQ105" t="n">
+        <v>26.84615384615385</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>181.3076923076923</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT105" t="n">
+        <v>65.46153846153847</v>
+      </c>
+      <c r="AU105" t="n">
+        <v>786538.4615384615</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>70.92307692307692</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>20.23076923076923</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>181.4615384615385</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ105" t="n">
+        <v>62.53846153846154</v>
+      </c>
+      <c r="BA105" t="n">
+        <v>875000</v>
+      </c>
+      <c r="BB105" t="n">
+        <v>75.38461538461539</v>
+      </c>
+      <c r="BC105" t="inlineStr"/>
+      <c r="BD105" t="inlineStr"/>
+      <c r="BE105" t="inlineStr"/>
+      <c r="BF105" t="inlineStr"/>
+      <c r="BG105" t="inlineStr"/>
+      <c r="BH105" t="inlineStr"/>
+      <c r="BI105" t="inlineStr"/>
+      <c r="BJ105" t="inlineStr"/>
+      <c r="BK105" t="inlineStr"/>
+      <c r="BL105" t="inlineStr"/>
+      <c r="BM105" t="inlineStr"/>
+      <c r="BN105" t="inlineStr"/>
+      <c r="BO105" t="inlineStr"/>
+      <c r="BP105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>UsP4uZcE</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>45527.625</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landry r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade paul lignon
+  rodez </t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>5955</v>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="n">
+        <v>3</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="n">
+        <v>38</v>
+      </c>
+      <c r="N106" t="n">
+        <v>62</v>
+      </c>
+      <c r="O106" t="n">
+        <v>16</v>
+      </c>
+      <c r="P106" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>4</v>
+      </c>
+      <c r="R106" t="n">
+        <v>4</v>
+      </c>
+      <c r="S106" t="n">
+        <v>14</v>
+      </c>
+      <c r="T106" t="n">
+        <v>13</v>
+      </c>
+      <c r="U106" t="n">
+        <v>9</v>
+      </c>
+      <c r="V106" t="n">
+        <v>11</v>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="Y106" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC106" t="inlineStr"/>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr"/>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="inlineStr"/>
+      <c r="AH106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr"/>
+      <c r="AJ106" t="inlineStr"/>
+      <c r="AK106" t="n">
+        <v>26.81818181818182</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>176.8181818181818</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>1861363.636363636</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>73.90909090909091</v>
+      </c>
+      <c r="AQ106" t="n">
+        <v>20.9375</v>
+      </c>
+      <c r="AR106" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT106" t="n">
+        <v>62.3125</v>
+      </c>
+      <c r="AU106" t="n">
+        <v>829687.5</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>72.4375</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>20.375</v>
+      </c>
+      <c r="AX106" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="AY106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ106" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="BA106" t="n">
+        <v>1696875</v>
+      </c>
+      <c r="BB106" t="n">
+        <v>77</v>
+      </c>
+      <c r="BC106" t="inlineStr"/>
+      <c r="BD106" t="inlineStr"/>
+      <c r="BE106" t="inlineStr"/>
+      <c r="BF106" t="inlineStr"/>
+      <c r="BG106" t="inlineStr"/>
+      <c r="BH106" t="inlineStr"/>
+      <c r="BI106" t="inlineStr"/>
+      <c r="BJ106" t="inlineStr"/>
+      <c r="BK106" t="inlineStr"/>
+      <c r="BL106" t="inlineStr"/>
+      <c r="BM106" t="inlineStr"/>
+      <c r="BN106" t="inlineStr"/>
+      <c r="BO106" t="inlineStr"/>
+      <c r="BP106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>4rrRVcF7</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>45527.625</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapapria r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l aube
+  troyes </t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>20420</v>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="n">
+        <v>48</v>
+      </c>
+      <c r="N107" t="n">
+        <v>52</v>
+      </c>
+      <c r="O107" t="n">
+        <v>16</v>
+      </c>
+      <c r="P107" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>5</v>
+      </c>
+      <c r="R107" t="n">
+        <v>1</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="n">
+        <v>13</v>
+      </c>
+      <c r="U107" t="n">
+        <v>5</v>
+      </c>
+      <c r="V107" t="n">
+        <v>11</v>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="Y107" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC107" t="inlineStr"/>
+      <c r="AD107" t="inlineStr"/>
+      <c r="AE107" t="n">
+        <v>24.22222222222222</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>177.7777777777778</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>64.66666666666667</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>1072222.222222222</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>1553125</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>74</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>27.05882352941176</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>179.3529411764706</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>1.176470588235294</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>67.35294117647059</v>
+      </c>
+      <c r="AU107" t="n">
+        <v>1388235.294117647</v>
+      </c>
+      <c r="AV107" t="n">
+        <v>70.70588235294117</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>178.625</v>
+      </c>
+      <c r="AY107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ107" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="BA107" t="n">
+        <v>1637500</v>
+      </c>
+      <c r="BB107" t="n">
+        <v>72.875</v>
+      </c>
+      <c r="BC107" t="inlineStr"/>
+      <c r="BD107" t="inlineStr"/>
+      <c r="BE107" t="inlineStr"/>
+      <c r="BF107" t="inlineStr"/>
+      <c r="BG107" t="inlineStr"/>
+      <c r="BH107" t="inlineStr"/>
+      <c r="BI107" t="inlineStr"/>
+      <c r="BJ107" t="inlineStr"/>
+      <c r="BK107" t="inlineStr"/>
+      <c r="BL107" t="inlineStr"/>
+      <c r="BM107" t="inlineStr"/>
+      <c r="BN107" t="inlineStr"/>
+      <c r="BO107" t="inlineStr"/>
+      <c r="BP107" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP112"/>
+  <dimension ref="A1:BP114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23741,6 +23741,374 @@
       <c r="BO112" t="inlineStr"/>
       <c r="BP112" t="inlineStr"/>
     </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>45529.65625</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F113" t="n">
+        <v>63841</v>
+      </c>
+      <c r="G113" t="n">
+        <v>2</v>
+      </c>
+      <c r="H113" t="n">
+        <v>2</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M113" t="n">
+        <v>66</v>
+      </c>
+      <c r="N113" t="n">
+        <v>34</v>
+      </c>
+      <c r="O113" t="n">
+        <v>16</v>
+      </c>
+      <c r="P113" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>10</v>
+      </c>
+      <c r="R113" t="n">
+        <v>3</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="n">
+        <v>13</v>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="W113" t="n">
+        <v>55</v>
+      </c>
+      <c r="X113" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA113" t="inlineStr"/>
+      <c r="AB113" t="inlineStr"/>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr"/>
+      <c r="AE113" t="inlineStr"/>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="inlineStr"/>
+      <c r="AH113" t="inlineStr"/>
+      <c r="AI113" t="inlineStr"/>
+      <c r="AJ113" t="inlineStr"/>
+      <c r="AK113" t="inlineStr"/>
+      <c r="AL113" t="inlineStr"/>
+      <c r="AM113" t="inlineStr"/>
+      <c r="AN113" t="inlineStr"/>
+      <c r="AO113" t="inlineStr"/>
+      <c r="AP113" t="inlineStr"/>
+      <c r="AQ113" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>178</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AU113" t="n">
+        <v>11320000</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="AX113" t="n">
+        <v>183.9333333333333</v>
+      </c>
+      <c r="AY113" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="AZ113" t="n">
+        <v>67.86666666666666</v>
+      </c>
+      <c r="BA113" t="n">
+        <v>3386666.666666667</v>
+      </c>
+      <c r="BB113" t="n">
+        <v>77.86666666666666</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD113" t="n">
+        <v>182</v>
+      </c>
+      <c r="BE113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG113" t="n">
+        <v>135</v>
+      </c>
+      <c r="BH113" t="n">
+        <v>5700000</v>
+      </c>
+      <c r="BI113" t="n">
+        <v>153</v>
+      </c>
+      <c r="BJ113" t="n">
+        <v>21</v>
+      </c>
+      <c r="BK113" t="n">
+        <v>180</v>
+      </c>
+      <c r="BL113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN113" t="n">
+        <v>74</v>
+      </c>
+      <c r="BO113" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="BP113" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>0pvInj5s</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>45530.65625</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bouille t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bauer
+  paris   saint ouen </t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F114" t="n">
+        <v>4560</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="n">
+        <v>40</v>
+      </c>
+      <c r="N114" t="n">
+        <v>60</v>
+      </c>
+      <c r="O114" t="n">
+        <v>5</v>
+      </c>
+      <c r="P114" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>2</v>
+      </c>
+      <c r="R114" t="n">
+        <v>2</v>
+      </c>
+      <c r="S114" t="n">
+        <v>15</v>
+      </c>
+      <c r="T114" t="n">
+        <v>15</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="W114" t="n">
+        <v>55</v>
+      </c>
+      <c r="X114" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC114" t="inlineStr"/>
+      <c r="AD114" t="inlineStr"/>
+      <c r="AE114" t="inlineStr"/>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="inlineStr"/>
+      <c r="AH114" t="inlineStr"/>
+      <c r="AI114" t="inlineStr"/>
+      <c r="AJ114" t="inlineStr"/>
+      <c r="AK114" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>176.4444444444445</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>65.11111111111111</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>722222.2222222222</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>68.55555555555556</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>187</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT114" t="n">
+        <v>66</v>
+      </c>
+      <c r="AU114" t="n">
+        <v>1687500</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>77</v>
+      </c>
+      <c r="AW114" t="n">
+        <v>24.52380952380953</v>
+      </c>
+      <c r="AX114" t="n">
+        <v>182.4761904761905</v>
+      </c>
+      <c r="AY114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ114" t="n">
+        <v>65.76190476190476</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>1139285.714285714</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>71.57142857142857</v>
+      </c>
+      <c r="BC114" t="inlineStr"/>
+      <c r="BD114" t="inlineStr"/>
+      <c r="BE114" t="inlineStr"/>
+      <c r="BF114" t="inlineStr"/>
+      <c r="BG114" t="inlineStr"/>
+      <c r="BH114" t="inlineStr"/>
+      <c r="BI114" t="inlineStr"/>
+      <c r="BJ114" t="inlineStr"/>
+      <c r="BK114" t="inlineStr"/>
+      <c r="BL114" t="inlineStr"/>
+      <c r="BM114" t="inlineStr"/>
+      <c r="BN114" t="inlineStr"/>
+      <c r="BO114" t="inlineStr"/>
+      <c r="BP114" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP114"/>
+  <dimension ref="A1:BP122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24109,6 +24109,1400 @@
       <c r="BO114" t="inlineStr"/>
       <c r="BP114" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>45534.65625</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="n">
+        <v>4</v>
+      </c>
+      <c r="H115" t="n">
+        <v>3</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L115" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M115" t="n">
+        <v>47</v>
+      </c>
+      <c r="N115" t="n">
+        <v>53</v>
+      </c>
+      <c r="O115" t="n">
+        <v>22</v>
+      </c>
+      <c r="P115" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>13</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="n">
+        <v>6</v>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="W115" t="n">
+        <v>55</v>
+      </c>
+      <c r="X115" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
+      <c r="AC115" t="inlineStr"/>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="AE115" t="n">
+        <v>27.22222222222222</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>183.2222222222222</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>9666666.666666666</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>78.77777777777777</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>4042500</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>23.15384615384615</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>181.0769230769231</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>1.307692307692308</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>73.30769230769231</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>6023076.923076923</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>80.30769230769231</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>182.1666666666667</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>175</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>152</v>
+      </c>
+      <c r="BH115" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="BI115" t="n">
+        <v>164</v>
+      </c>
+      <c r="BJ115" t="inlineStr"/>
+      <c r="BK115" t="inlineStr"/>
+      <c r="BL115" t="inlineStr"/>
+      <c r="BM115" t="inlineStr"/>
+      <c r="BN115" t="inlineStr"/>
+      <c r="BO115" t="inlineStr"/>
+      <c r="BP115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>WlzDg17E</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>45534.625</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petit a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michel moretti stadium
+  ajaccio </t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>8470</v>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="n">
+        <v>2</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="n">
+        <v>72</v>
+      </c>
+      <c r="N116" t="n">
+        <v>28</v>
+      </c>
+      <c r="O116" t="n">
+        <v>23</v>
+      </c>
+      <c r="P116" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>5</v>
+      </c>
+      <c r="R116" t="n">
+        <v>4</v>
+      </c>
+      <c r="S116" t="n">
+        <v>16</v>
+      </c>
+      <c r="T116" t="n">
+        <v>15</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="W116" t="n">
+        <v>55</v>
+      </c>
+      <c r="X116" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC116" t="inlineStr"/>
+      <c r="AD116" t="inlineStr"/>
+      <c r="AE116" t="n">
+        <v>24.22222222222222</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>182</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>64.66666666666667</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>1016666.666666667</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>70.55555555555556</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>176.375</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>65.125</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>1168750</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>70.875</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>176.1875</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>65.8125</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>715625</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>70.0625</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>27.6875</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>1020312.5</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="BC116" t="inlineStr"/>
+      <c r="BD116" t="inlineStr"/>
+      <c r="BE116" t="inlineStr"/>
+      <c r="BF116" t="inlineStr"/>
+      <c r="BG116" t="inlineStr"/>
+      <c r="BH116" t="inlineStr"/>
+      <c r="BI116" t="inlineStr"/>
+      <c r="BJ116" t="inlineStr"/>
+      <c r="BK116" t="inlineStr"/>
+      <c r="BL116" t="inlineStr"/>
+      <c r="BM116" t="inlineStr"/>
+      <c r="BN116" t="inlineStr"/>
+      <c r="BO116" t="inlineStr"/>
+      <c r="BP116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>IoCT4kRP</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>45534.625</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valnet a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade michel d ornano
+  caen </t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>20300</v>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="n">
+        <v>77</v>
+      </c>
+      <c r="N117" t="n">
+        <v>23</v>
+      </c>
+      <c r="O117" t="n">
+        <v>12</v>
+      </c>
+      <c r="P117" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>1</v>
+      </c>
+      <c r="R117" t="n">
+        <v>4</v>
+      </c>
+      <c r="S117" t="n">
+        <v>6</v>
+      </c>
+      <c r="T117" t="n">
+        <v>20</v>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="W117" t="n">
+        <v>55</v>
+      </c>
+      <c r="X117" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC117" t="inlineStr"/>
+      <c r="AD117" t="inlineStr"/>
+      <c r="AE117" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>1428125</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>74.625</v>
+      </c>
+      <c r="AK117" t="inlineStr"/>
+      <c r="AL117" t="inlineStr"/>
+      <c r="AM117" t="inlineStr"/>
+      <c r="AN117" t="inlineStr"/>
+      <c r="AO117" t="inlineStr"/>
+      <c r="AP117" t="inlineStr"/>
+      <c r="AQ117" t="n">
+        <v>26.72222222222222</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>183.8333333333333</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>67.94444444444444</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1638888.888888889</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>680000</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="BC117" t="inlineStr"/>
+      <c r="BD117" t="inlineStr"/>
+      <c r="BE117" t="inlineStr"/>
+      <c r="BF117" t="inlineStr"/>
+      <c r="BG117" t="inlineStr"/>
+      <c r="BH117" t="inlineStr"/>
+      <c r="BI117" t="inlineStr"/>
+      <c r="BJ117" t="inlineStr"/>
+      <c r="BK117" t="inlineStr"/>
+      <c r="BL117" t="inlineStr"/>
+      <c r="BM117" t="inlineStr"/>
+      <c r="BN117" t="inlineStr"/>
+      <c r="BO117" t="inlineStr"/>
+      <c r="BP117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>zyWS0tQi</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>45534.625</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kubler g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade gabriel montpied
+  clermont ferrand </t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="n">
+        <v>37</v>
+      </c>
+      <c r="N118" t="n">
+        <v>63</v>
+      </c>
+      <c r="O118" t="n">
+        <v>6</v>
+      </c>
+      <c r="P118" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>2</v>
+      </c>
+      <c r="R118" t="n">
+        <v>3</v>
+      </c>
+      <c r="S118" t="n">
+        <v>12</v>
+      </c>
+      <c r="T118" t="n">
+        <v>9</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="W118" t="n">
+        <v>55</v>
+      </c>
+      <c r="X118" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC118" t="inlineStr"/>
+      <c r="AD118" t="inlineStr"/>
+      <c r="AE118" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>68.125</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>1715625</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>177.8888888888889</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>67.22222222222223</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>1697222.222222222</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>71.55555555555556</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>176.125</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>64.375</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1425000</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>72.625</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>26.64285714285714</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>177.7857142857143</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.071428571428571</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>67.21428571428571</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1314285.714285714</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>69.78571428571429</v>
+      </c>
+      <c r="BC118" t="inlineStr"/>
+      <c r="BD118" t="inlineStr"/>
+      <c r="BE118" t="inlineStr"/>
+      <c r="BF118" t="inlineStr"/>
+      <c r="BG118" t="inlineStr"/>
+      <c r="BH118" t="inlineStr"/>
+      <c r="BI118" t="inlineStr"/>
+      <c r="BJ118" t="inlineStr"/>
+      <c r="BK118" t="inlineStr"/>
+      <c r="BL118" t="inlineStr"/>
+      <c r="BM118" t="inlineStr"/>
+      <c r="BN118" t="inlineStr"/>
+      <c r="BO118" t="inlineStr"/>
+      <c r="BP118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>06FhaTlm</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>45534.625</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rosier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade marcel tribut
+  dunkerque </t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>4933</v>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="n">
+        <v>52</v>
+      </c>
+      <c r="N119" t="n">
+        <v>48</v>
+      </c>
+      <c r="O119" t="n">
+        <v>13</v>
+      </c>
+      <c r="P119" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>3</v>
+      </c>
+      <c r="R119" t="n">
+        <v>1</v>
+      </c>
+      <c r="S119" t="n">
+        <v>9</v>
+      </c>
+      <c r="T119" t="n">
+        <v>14</v>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="W119" t="n">
+        <v>55</v>
+      </c>
+      <c r="X119" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC119" t="inlineStr"/>
+      <c r="AD119" t="inlineStr"/>
+      <c r="AE119" t="inlineStr"/>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="inlineStr"/>
+      <c r="AH119" t="inlineStr"/>
+      <c r="AI119" t="inlineStr"/>
+      <c r="AJ119" t="inlineStr"/>
+      <c r="AK119" t="inlineStr"/>
+      <c r="AL119" t="inlineStr"/>
+      <c r="AM119" t="inlineStr"/>
+      <c r="AN119" t="inlineStr"/>
+      <c r="AO119" t="inlineStr"/>
+      <c r="AP119" t="inlineStr"/>
+      <c r="AQ119" t="n">
+        <v>22.92307692307692</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>175.8461538461538</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>64.30769230769231</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>1073076.923076923</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>73.23076923076923</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>21.30769230769231</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>184.0769230769231</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>62</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>726923.0769230769</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>71.30769230769231</v>
+      </c>
+      <c r="BC119" t="inlineStr"/>
+      <c r="BD119" t="inlineStr"/>
+      <c r="BE119" t="inlineStr"/>
+      <c r="BF119" t="inlineStr"/>
+      <c r="BG119" t="inlineStr"/>
+      <c r="BH119" t="inlineStr"/>
+      <c r="BI119" t="inlineStr"/>
+      <c r="BJ119" t="inlineStr"/>
+      <c r="BK119" t="inlineStr"/>
+      <c r="BL119" t="inlineStr"/>
+      <c r="BM119" t="inlineStr"/>
+      <c r="BN119" t="inlineStr"/>
+      <c r="BO119" t="inlineStr"/>
+      <c r="BP119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>UPVYr846</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>45534.625</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lesage m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>20068</v>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="n">
+        <v>49</v>
+      </c>
+      <c r="N120" t="n">
+        <v>51</v>
+      </c>
+      <c r="O120" t="n">
+        <v>7</v>
+      </c>
+      <c r="P120" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>4</v>
+      </c>
+      <c r="R120" t="n">
+        <v>5</v>
+      </c>
+      <c r="S120" t="n">
+        <v>8</v>
+      </c>
+      <c r="T120" t="n">
+        <v>11</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="W120" t="n">
+        <v>55</v>
+      </c>
+      <c r="X120" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC120" t="inlineStr"/>
+      <c r="AD120" t="inlineStr"/>
+      <c r="AE120" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>185.7</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>1597500</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>23.44444444444444</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>182.2222222222222</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>64.11111111111111</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>975000</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>71.88888888888889</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>25.64285714285714</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>181</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>67.71428571428571</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1848214.285714286</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>73.42857142857143</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>27.88888888888889</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>177.6666666666667</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>65.33333333333333</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>736111.1111111111</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>69</v>
+      </c>
+      <c r="BC120" t="inlineStr"/>
+      <c r="BD120" t="inlineStr"/>
+      <c r="BE120" t="inlineStr"/>
+      <c r="BF120" t="inlineStr"/>
+      <c r="BG120" t="inlineStr"/>
+      <c r="BH120" t="inlineStr"/>
+      <c r="BI120" t="inlineStr"/>
+      <c r="BJ120" t="inlineStr"/>
+      <c r="BK120" t="inlineStr"/>
+      <c r="BL120" t="inlineStr"/>
+      <c r="BM120" t="inlineStr"/>
+      <c r="BN120" t="inlineStr"/>
+      <c r="BO120" t="inlineStr"/>
+      <c r="BP120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>8WI0c7Ja</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>45534.625</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapapria r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de roudourou
+  guingamp </t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>19060</v>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="n">
+        <v>3</v>
+      </c>
+      <c r="H121" t="n">
+        <v>4</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="n">
+        <v>62</v>
+      </c>
+      <c r="N121" t="n">
+        <v>38</v>
+      </c>
+      <c r="O121" t="n">
+        <v>21</v>
+      </c>
+      <c r="P121" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>7</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7</v>
+      </c>
+      <c r="S121" t="n">
+        <v>12</v>
+      </c>
+      <c r="T121" t="n">
+        <v>10</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="W121" t="n">
+        <v>55</v>
+      </c>
+      <c r="X121" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC121" t="inlineStr"/>
+      <c r="AD121" t="inlineStr"/>
+      <c r="AE121" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>179.8888888888889</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>65.33333333333333</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>1077777.777777778</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>70.44444444444444</v>
+      </c>
+      <c r="AK121" t="inlineStr"/>
+      <c r="AL121" t="inlineStr"/>
+      <c r="AM121" t="inlineStr"/>
+      <c r="AN121" t="inlineStr"/>
+      <c r="AO121" t="inlineStr"/>
+      <c r="AP121" t="inlineStr"/>
+      <c r="AQ121" t="n">
+        <v>22.92857142857143</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>180.4285714285714</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>61.57142857142857</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>760714.2857142857</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AW121" t="inlineStr"/>
+      <c r="AX121" t="inlineStr"/>
+      <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr"/>
+      <c r="BA121" t="inlineStr"/>
+      <c r="BB121" t="inlineStr"/>
+      <c r="BC121" t="inlineStr"/>
+      <c r="BD121" t="inlineStr"/>
+      <c r="BE121" t="inlineStr"/>
+      <c r="BF121" t="inlineStr"/>
+      <c r="BG121" t="inlineStr"/>
+      <c r="BH121" t="inlineStr"/>
+      <c r="BI121" t="inlineStr"/>
+      <c r="BJ121" t="inlineStr"/>
+      <c r="BK121" t="inlineStr"/>
+      <c r="BL121" t="inlineStr"/>
+      <c r="BM121" t="inlineStr"/>
+      <c r="BN121" t="inlineStr"/>
+      <c r="BO121" t="inlineStr"/>
+      <c r="BP121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>QiPssnZI</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>45534.625</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landry r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="n">
+        <v>48</v>
+      </c>
+      <c r="N122" t="n">
+        <v>52</v>
+      </c>
+      <c r="O122" t="n">
+        <v>13</v>
+      </c>
+      <c r="P122" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>1</v>
+      </c>
+      <c r="R122" t="n">
+        <v>4</v>
+      </c>
+      <c r="S122" t="n">
+        <v>22</v>
+      </c>
+      <c r="T122" t="n">
+        <v>16</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="W122" t="n">
+        <v>55</v>
+      </c>
+      <c r="X122" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC122" t="inlineStr"/>
+      <c r="AD122" t="inlineStr"/>
+      <c r="AE122" t="inlineStr"/>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="inlineStr"/>
+      <c r="AH122" t="inlineStr"/>
+      <c r="AI122" t="inlineStr"/>
+      <c r="AJ122" t="inlineStr"/>
+      <c r="AK122" t="inlineStr"/>
+      <c r="AL122" t="inlineStr"/>
+      <c r="AM122" t="inlineStr"/>
+      <c r="AN122" t="inlineStr"/>
+      <c r="AO122" t="inlineStr"/>
+      <c r="AP122" t="inlineStr"/>
+      <c r="AQ122" t="inlineStr"/>
+      <c r="AR122" t="inlineStr"/>
+      <c r="AS122" t="inlineStr"/>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AU122" t="inlineStr"/>
+      <c r="AV122" t="inlineStr"/>
+      <c r="AW122" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>967500</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>67</v>
+      </c>
+      <c r="BC122" t="inlineStr"/>
+      <c r="BD122" t="inlineStr"/>
+      <c r="BE122" t="inlineStr"/>
+      <c r="BF122" t="inlineStr"/>
+      <c r="BG122" t="inlineStr"/>
+      <c r="BH122" t="inlineStr"/>
+      <c r="BI122" t="inlineStr"/>
+      <c r="BJ122" t="inlineStr"/>
+      <c r="BK122" t="inlineStr"/>
+      <c r="BL122" t="inlineStr"/>
+      <c r="BM122" t="inlineStr"/>
+      <c r="BN122" t="inlineStr"/>
+      <c r="BO122" t="inlineStr"/>
+      <c r="BP122" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP122"/>
+  <dimension ref="A1:BP126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25503,6 +25503,806 @@
       <c r="BO122" t="inlineStr"/>
       <c r="BP122" t="inlineStr"/>
     </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="n">
+        <v>3</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L123" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M123" t="n">
+        <v>68</v>
+      </c>
+      <c r="N123" t="n">
+        <v>32</v>
+      </c>
+      <c r="O123" t="n">
+        <v>11</v>
+      </c>
+      <c r="P123" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>5</v>
+      </c>
+      <c r="R123" t="n">
+        <v>5</v>
+      </c>
+      <c r="S123" t="n">
+        <v>11</v>
+      </c>
+      <c r="T123" t="n">
+        <v>13</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="W123" t="n">
+        <v>55</v>
+      </c>
+      <c r="X123" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA123" t="inlineStr"/>
+      <c r="AB123" t="inlineStr"/>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AE123" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>6170000</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>183</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>4532500</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>23.71428571428572</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>178.2142857142857</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>70</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>2992857.142857143</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>76.78571428571429</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>24.73333333333333</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>180.5333333333333</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>72.13333333333334</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>4318333.333333333</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>356</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>15100000</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>378</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>26</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>179.2</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>355</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>15925000</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angoula g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="n">
+        <v>4</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M124" t="n">
+        <v>53</v>
+      </c>
+      <c r="N124" t="n">
+        <v>47</v>
+      </c>
+      <c r="O124" t="n">
+        <v>17</v>
+      </c>
+      <c r="P124" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>7</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>14</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="W124" t="n">
+        <v>55</v>
+      </c>
+      <c r="X124" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA124" t="inlineStr"/>
+      <c r="AB124" t="inlineStr"/>
+      <c r="AC124" t="inlineStr"/>
+      <c r="AD124" t="inlineStr"/>
+      <c r="AE124" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>74.55555555555556</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>6755555.555555556</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>2278125</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>74.875</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>24.52941176470588</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>178.2352941176471</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.294117647058824</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>68.52941176470588</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>3258823.529411765</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>73.41176470588235</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>68.13636363636364</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>1545454.545454545</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>72.45454545454545</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>180</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>76</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>82</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>183</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>136</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>zoZtwwYp</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>45535.39583333334</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gaillouste p 
+  fra </t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>12097</v>
+      </c>
+      <c r="F125" t="n">
+        <v>5460</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="n">
+        <v>34</v>
+      </c>
+      <c r="N125" t="n">
+        <v>66</v>
+      </c>
+      <c r="O125" t="n">
+        <v>14</v>
+      </c>
+      <c r="P125" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>7</v>
+      </c>
+      <c r="R125" t="n">
+        <v>9</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="n">
+        <v>13</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="W125" t="n">
+        <v>55</v>
+      </c>
+      <c r="X125" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC125" t="inlineStr"/>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AE125" t="n">
+        <v>25.55555555555556</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>178.5555555555555</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>65.88888888888889</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>1094444.444444444</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>71</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>178.2222222222222</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>71.22222222222223</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>4466666.666666667</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>77.44444444444444</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>25.61538461538462</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>185.0769230769231</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>1.230769230769231</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>64.30769230769231</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>828846.1538461539</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>71.07692307692308</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>21.83333333333333</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>177.9166666666667</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>68.41666666666667</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>2485416.666666667</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="BC125" t="inlineStr"/>
+      <c r="BD125" t="inlineStr"/>
+      <c r="BE125" t="inlineStr"/>
+      <c r="BF125" t="inlineStr"/>
+      <c r="BG125" t="inlineStr"/>
+      <c r="BH125" t="inlineStr"/>
+      <c r="BI125" t="inlineStr"/>
+      <c r="BJ125" t="inlineStr"/>
+      <c r="BK125" t="inlineStr"/>
+      <c r="BL125" t="inlineStr"/>
+      <c r="BM125" t="inlineStr"/>
+      <c r="BN125" t="inlineStr"/>
+      <c r="BO125" t="inlineStr"/>
+      <c r="BP125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>8lUzaKf4</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>45535.39583333334</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade saint symphorien
+  metz </t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>28786</v>
+      </c>
+      <c r="F126" t="n">
+        <v>18369</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="n">
+        <v>70</v>
+      </c>
+      <c r="N126" t="n">
+        <v>30</v>
+      </c>
+      <c r="O126" t="n">
+        <v>20</v>
+      </c>
+      <c r="P126" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>3</v>
+      </c>
+      <c r="R126" t="n">
+        <v>4</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="n">
+        <v>19</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="W126" t="n">
+        <v>55</v>
+      </c>
+      <c r="X126" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr"/>
+      <c r="AE126" t="n">
+        <v>26.81818181818182</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>176.8181818181818</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>1861363.636363636</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>73.90909090909091</v>
+      </c>
+      <c r="AK126" t="inlineStr"/>
+      <c r="AL126" t="inlineStr"/>
+      <c r="AM126" t="inlineStr"/>
+      <c r="AN126" t="inlineStr"/>
+      <c r="AO126" t="inlineStr"/>
+      <c r="AP126" t="inlineStr"/>
+      <c r="AQ126" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1797500</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>26.64285714285714</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>180.5714285714286</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>64.57142857142857</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>838571.4285714285</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>70.64285714285714</v>
+      </c>
+      <c r="BC126" t="inlineStr"/>
+      <c r="BD126" t="inlineStr"/>
+      <c r="BE126" t="inlineStr"/>
+      <c r="BF126" t="inlineStr"/>
+      <c r="BG126" t="inlineStr"/>
+      <c r="BH126" t="inlineStr"/>
+      <c r="BI126" t="inlineStr"/>
+      <c r="BJ126" t="inlineStr"/>
+      <c r="BK126" t="inlineStr"/>
+      <c r="BL126" t="inlineStr"/>
+      <c r="BM126" t="inlineStr"/>
+      <c r="BN126" t="inlineStr"/>
+      <c r="BO126" t="inlineStr"/>
+      <c r="BP126" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP126"/>
+  <dimension ref="A1:BP132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26303,6 +26303,1250 @@
       <c r="BO126" t="inlineStr"/>
       <c r="BP126" t="inlineStr"/>
     </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F127" t="n">
+        <v>45434</v>
+      </c>
+      <c r="G127" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" t="n">
+        <v>3</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M127" t="n">
+        <v>42</v>
+      </c>
+      <c r="N127" t="n">
+        <v>58</v>
+      </c>
+      <c r="O127" t="n">
+        <v>8</v>
+      </c>
+      <c r="P127" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>4</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7</v>
+      </c>
+      <c r="S127" t="n">
+        <v>9</v>
+      </c>
+      <c r="T127" t="n">
+        <v>9</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="W127" t="n">
+        <v>55</v>
+      </c>
+      <c r="X127" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA127" t="inlineStr"/>
+      <c r="AB127" t="inlineStr"/>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr"/>
+      <c r="AE127" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>11030000</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>86.75</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>25.81818181818182</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>176.3636363636364</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>1.818181818181818</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>75.45454545454545</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>12288636.36363636</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>79.18181818181819</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>184.4444444444445</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>1.944444444444444</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>76.72222222222223</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>25327777.77777778</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>83.72222222222223</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>307</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>32800000</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>307</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>27</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>165</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>SU02594U</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F128" t="n">
+        <v>9168</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>4</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L128" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M128" t="n">
+        <v>54</v>
+      </c>
+      <c r="N128" t="n">
+        <v>46</v>
+      </c>
+      <c r="O128" t="n">
+        <v>14</v>
+      </c>
+      <c r="P128" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>7</v>
+      </c>
+      <c r="R128" t="n">
+        <v>9</v>
+      </c>
+      <c r="S128" t="n">
+        <v>14</v>
+      </c>
+      <c r="T128" t="n">
+        <v>13</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="W128" t="n">
+        <v>55</v>
+      </c>
+      <c r="X128" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA128" t="inlineStr"/>
+      <c r="AB128" t="inlineStr"/>
+      <c r="AC128" t="inlineStr"/>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="AE128" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>1687500</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>22.77777777777778</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>74.22222222222223</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>10655555.55555556</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>80.22222222222223</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>181.15</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>1565000</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>23.5625</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>182.5625</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>72.6875</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>6451562.5</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>77.8125</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>177.6666666666667</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>200</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>213</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>373</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>50400000</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>ChZKNjKb</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F129" t="n">
+        <v>19715</v>
+      </c>
+      <c r="G129" t="n">
+        <v>3</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M129" t="n">
+        <v>49</v>
+      </c>
+      <c r="N129" t="n">
+        <v>51</v>
+      </c>
+      <c r="O129" t="n">
+        <v>22</v>
+      </c>
+      <c r="P129" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>8</v>
+      </c>
+      <c r="R129" t="n">
+        <v>3</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="n">
+        <v>15</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="W129" t="n">
+        <v>55</v>
+      </c>
+      <c r="X129" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA129" t="inlineStr"/>
+      <c r="AB129" t="inlineStr"/>
+      <c r="AC129" t="inlineStr"/>
+      <c r="AD129" t="inlineStr"/>
+      <c r="AE129" t="n">
+        <v>25.36363636363636</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>185.1818181818182</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>71.18181818181819</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>2790909.090909091</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>74.90909090909091</v>
+      </c>
+      <c r="AK129" t="inlineStr"/>
+      <c r="AL129" t="inlineStr"/>
+      <c r="AM129" t="inlineStr"/>
+      <c r="AN129" t="inlineStr"/>
+      <c r="AO129" t="inlineStr"/>
+      <c r="AP129" t="inlineStr"/>
+      <c r="AQ129" t="n">
+        <v>23.53333333333333</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>182</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>2860000</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>22.80952380952381</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>181.5238095238095</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>64.9047619047619</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1511904.761904762</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>71.9047619047619</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>188</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>74</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>269</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>6350000</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>p6XSLUlB</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="n">
+        <v>2</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L130" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M130" t="n">
+        <v>53</v>
+      </c>
+      <c r="N130" t="n">
+        <v>47</v>
+      </c>
+      <c r="O130" t="n">
+        <v>11</v>
+      </c>
+      <c r="P130" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>7</v>
+      </c>
+      <c r="R130" t="n">
+        <v>5</v>
+      </c>
+      <c r="S130" t="n">
+        <v>9</v>
+      </c>
+      <c r="T130" t="n">
+        <v>13</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="W130" t="n">
+        <v>55</v>
+      </c>
+      <c r="X130" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA130" t="inlineStr"/>
+      <c r="AB130" t="inlineStr"/>
+      <c r="AC130" t="inlineStr"/>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr"/>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="inlineStr"/>
+      <c r="AH130" t="inlineStr"/>
+      <c r="AI130" t="inlineStr"/>
+      <c r="AJ130" t="inlineStr"/>
+      <c r="AK130" t="inlineStr"/>
+      <c r="AL130" t="inlineStr"/>
+      <c r="AM130" t="inlineStr"/>
+      <c r="AN130" t="inlineStr"/>
+      <c r="AO130" t="inlineStr"/>
+      <c r="AP130" t="inlineStr"/>
+      <c r="AQ130" t="n">
+        <v>23.88235294117647</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>183.1176470588235</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>1.058823529411765</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>71.82352941176471</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>6541176.470588235</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>77.70588235294117</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>24.14285714285714</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>179.7142857142857</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>72.92857142857143</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>6760714.285714285</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>78.14285714285714</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>149</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>159</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>189</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>72</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>45536.41666666666</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F131" t="n">
+        <v>9030</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L131" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M131" t="n">
+        <v>61</v>
+      </c>
+      <c r="N131" t="n">
+        <v>39</v>
+      </c>
+      <c r="O131" t="n">
+        <v>14</v>
+      </c>
+      <c r="P131" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>3</v>
+      </c>
+      <c r="R131" t="n">
+        <v>4</v>
+      </c>
+      <c r="S131" t="n">
+        <v>11</v>
+      </c>
+      <c r="T131" t="n">
+        <v>21</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="W131" t="n">
+        <v>55</v>
+      </c>
+      <c r="X131" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA131" t="inlineStr"/>
+      <c r="AB131" t="inlineStr"/>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="AE131" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>183</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>11330000</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>76</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>180.55</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>75.65000000000001</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>13997500</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>177.6111111111111</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>1.277777777777778</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>73</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>6472777.777777778</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>77.16666666666667</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>173</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>66</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>82</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>176.3333333333333</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>222</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>18100000</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>45535.66666666666</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F132" t="n">
+        <v>19178</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="n">
+        <v>3</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L132" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M132" t="n">
+        <v>24</v>
+      </c>
+      <c r="N132" t="n">
+        <v>76</v>
+      </c>
+      <c r="O132" t="n">
+        <v>3</v>
+      </c>
+      <c r="P132" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>1</v>
+      </c>
+      <c r="R132" t="n">
+        <v>4</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="n">
+        <v>15</v>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="W132" t="n">
+        <v>55</v>
+      </c>
+      <c r="X132" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA132" t="inlineStr"/>
+      <c r="AB132" t="inlineStr"/>
+      <c r="AC132" t="inlineStr"/>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="AE132" t="n">
+        <v>23.55555555555556</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>5388888.888888889</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>78.11111111111111</v>
+      </c>
+      <c r="AK132" t="inlineStr"/>
+      <c r="AL132" t="inlineStr"/>
+      <c r="AM132" t="inlineStr"/>
+      <c r="AN132" t="inlineStr"/>
+      <c r="AO132" t="inlineStr"/>
+      <c r="AP132" t="inlineStr"/>
+      <c r="AQ132" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>179.0666666666667</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>70.46666666666667</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>3353333.333333333</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>76.53333333333333</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>178.625</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>15137500</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="BC132" t="inlineStr"/>
+      <c r="BD132" t="inlineStr"/>
+      <c r="BE132" t="inlineStr"/>
+      <c r="BF132" t="inlineStr"/>
+      <c r="BG132" t="inlineStr"/>
+      <c r="BH132" t="inlineStr"/>
+      <c r="BI132" t="inlineStr"/>
+      <c r="BJ132" t="n">
+        <v>21</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>182</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>135</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>5700000</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>153</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP132"/>
+  <dimension ref="A1:BP143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27655,6 +27655,2072 @@
       <c r="BO132" t="inlineStr"/>
       <c r="BP132" t="inlineStr"/>
     </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>CGH7Enso</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>45549.58333333334</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>3</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L133" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M133" t="n">
+        <v>40</v>
+      </c>
+      <c r="N133" t="n">
+        <v>60</v>
+      </c>
+      <c r="O133" t="n">
+        <v>10</v>
+      </c>
+      <c r="P133" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>2</v>
+      </c>
+      <c r="R133" t="n">
+        <v>7</v>
+      </c>
+      <c r="S133" t="n">
+        <v>12</v>
+      </c>
+      <c r="T133" t="n">
+        <v>14</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="W133" t="n">
+        <v>55</v>
+      </c>
+      <c r="X133" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA133" t="inlineStr"/>
+      <c r="AB133" t="inlineStr"/>
+      <c r="AC133" t="inlineStr"/>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="AE133" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>182.4545454545455</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>69.36363636363636</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>2861363.636363636</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>13600000</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>180.55</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1417500</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>71.65000000000001</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>15402500</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>82.05</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>266</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>6650000</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>299</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>183</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>140</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>10200000</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>0dMqm7mA</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>45549.5</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F134" t="n">
+        <v>65803</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L134" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M134" t="n">
+        <v>56</v>
+      </c>
+      <c r="N134" t="n">
+        <v>44</v>
+      </c>
+      <c r="O134" t="n">
+        <v>10</v>
+      </c>
+      <c r="P134" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>5</v>
+      </c>
+      <c r="R134" t="n">
+        <v>4</v>
+      </c>
+      <c r="S134" t="n">
+        <v>18</v>
+      </c>
+      <c r="T134" t="n">
+        <v>4</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="W134" t="n">
+        <v>55</v>
+      </c>
+      <c r="X134" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA134" t="inlineStr"/>
+      <c r="AB134" t="inlineStr"/>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="AE134" t="n">
+        <v>25.44444444444444</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>15400000</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>79.44444444444444</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>11850000</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>23.70588235294118</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>182.3529411764706</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>1.235294117647059</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>73.23529411764706</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>7911764.705882353</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>78.05882352941177</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>22.45454545454545</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>179.6818181818182</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.318181818181818</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>72.18181818181819</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>7704545.454545454</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>78.63636363636364</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>137</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>156</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>369</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>47750000</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>vsYzkTIc</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>45548.65625</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F135" t="n">
+        <v>22144</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M135" t="n">
+        <v>29</v>
+      </c>
+      <c r="N135" t="n">
+        <v>71</v>
+      </c>
+      <c r="O135" t="n">
+        <v>10</v>
+      </c>
+      <c r="P135" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>5</v>
+      </c>
+      <c r="R135" t="n">
+        <v>4</v>
+      </c>
+      <c r="S135" t="n">
+        <v>12</v>
+      </c>
+      <c r="T135" t="n">
+        <v>10</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="W135" t="n">
+        <v>55</v>
+      </c>
+      <c r="X135" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA135" t="inlineStr"/>
+      <c r="AB135" t="inlineStr"/>
+      <c r="AC135" t="inlineStr"/>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="AE135" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>182.125</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>71</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>2475000</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>75.125</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>183</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>10050000</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>25.61538461538462</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>182.3076923076923</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>68.15384615384616</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>1640384.615384615</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>72.76923076923077</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>25.0625</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>178.6875</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>11090625</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>79.375</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>214</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>218</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>379</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>37800000</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>CtRiexfT</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>45549.39583333334</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leleu m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade charlety
+  paris </t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="n">
+        <v>2</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="n">
+        <v>66</v>
+      </c>
+      <c r="N136" t="n">
+        <v>34</v>
+      </c>
+      <c r="O136" t="n">
+        <v>13</v>
+      </c>
+      <c r="P136" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>7</v>
+      </c>
+      <c r="R136" t="n">
+        <v>5</v>
+      </c>
+      <c r="S136" t="n">
+        <v>16</v>
+      </c>
+      <c r="T136" t="n">
+        <v>19</v>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="W136" t="n">
+        <v>55</v>
+      </c>
+      <c r="X136" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC136" t="inlineStr"/>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="AE136" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>1657500</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>177</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>1785000</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>26.77777777777778</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>177.3333333333333</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>69.22222222222223</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>4211111.111111111</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>71.88888888888889</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>25.07692307692308</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>177.4615384615385</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>68.53846153846153</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>1753846.153846154</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>73.15384615384616</v>
+      </c>
+      <c r="BC136" t="inlineStr"/>
+      <c r="BD136" t="inlineStr"/>
+      <c r="BE136" t="inlineStr"/>
+      <c r="BF136" t="inlineStr"/>
+      <c r="BG136" t="inlineStr"/>
+      <c r="BH136" t="inlineStr"/>
+      <c r="BI136" t="inlineStr"/>
+      <c r="BJ136" t="inlineStr"/>
+      <c r="BK136" t="inlineStr"/>
+      <c r="BL136" t="inlineStr"/>
+      <c r="BM136" t="inlineStr"/>
+      <c r="BN136" t="inlineStr"/>
+      <c r="BO136" t="inlineStr"/>
+      <c r="BP136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>WjsR9y9M</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>45548.625</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angoula g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des sports
+  annecy </t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>15660</v>
+      </c>
+      <c r="F137" t="n">
+        <v>5478</v>
+      </c>
+      <c r="G137" t="n">
+        <v>3</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="n">
+        <v>40</v>
+      </c>
+      <c r="N137" t="n">
+        <v>60</v>
+      </c>
+      <c r="O137" t="n">
+        <v>9</v>
+      </c>
+      <c r="P137" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>5</v>
+      </c>
+      <c r="R137" t="n">
+        <v>4</v>
+      </c>
+      <c r="S137" t="n">
+        <v>23</v>
+      </c>
+      <c r="T137" t="n">
+        <v>11</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="W137" t="n">
+        <v>55</v>
+      </c>
+      <c r="X137" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC137" t="inlineStr"/>
+      <c r="AD137" t="inlineStr"/>
+      <c r="AE137" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>681250</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>67</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>1182500</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>22.27272727272727</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>179.3636363636364</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>61.63636363636363</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>677272.7272727273</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>70</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>23.86666666666667</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>178.6666666666667</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>64.66666666666667</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>1143333.333333333</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="BC137" t="inlineStr"/>
+      <c r="BD137" t="inlineStr"/>
+      <c r="BE137" t="inlineStr"/>
+      <c r="BF137" t="inlineStr"/>
+      <c r="BG137" t="inlineStr"/>
+      <c r="BH137" t="inlineStr"/>
+      <c r="BI137" t="inlineStr"/>
+      <c r="BJ137" t="inlineStr"/>
+      <c r="BK137" t="inlineStr"/>
+      <c r="BL137" t="inlineStr"/>
+      <c r="BM137" t="inlineStr"/>
+      <c r="BN137" t="inlineStr"/>
+      <c r="BO137" t="inlineStr"/>
+      <c r="BP137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>SGTLiuxR</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>45548.625</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade armand cesari
+  bastia </t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>16048</v>
+      </c>
+      <c r="F138" t="n">
+        <v>10567</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="n">
+        <v>61</v>
+      </c>
+      <c r="N138" t="n">
+        <v>39</v>
+      </c>
+      <c r="O138" t="n">
+        <v>12</v>
+      </c>
+      <c r="P138" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>3</v>
+      </c>
+      <c r="R138" t="n">
+        <v>2</v>
+      </c>
+      <c r="S138" t="n">
+        <v>9</v>
+      </c>
+      <c r="T138" t="n">
+        <v>18</v>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="W138" t="n">
+        <v>55</v>
+      </c>
+      <c r="X138" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC138" t="inlineStr"/>
+      <c r="AD138" t="inlineStr"/>
+      <c r="AE138" t="inlineStr"/>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="inlineStr"/>
+      <c r="AH138" t="inlineStr"/>
+      <c r="AI138" t="inlineStr"/>
+      <c r="AJ138" t="inlineStr"/>
+      <c r="AK138" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>179.2222222222222</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>66.55555555555556</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1405555.555555556</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>25.35714285714286</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>178.3571428571429</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>64.14285714285714</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>880357.1428571428</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>67.42857142857143</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>178.8888888888889</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>66.44444444444444</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>1345833.333333333</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>72.38888888888889</v>
+      </c>
+      <c r="BC138" t="inlineStr"/>
+      <c r="BD138" t="inlineStr"/>
+      <c r="BE138" t="inlineStr"/>
+      <c r="BF138" t="inlineStr"/>
+      <c r="BG138" t="inlineStr"/>
+      <c r="BH138" t="inlineStr"/>
+      <c r="BI138" t="inlineStr"/>
+      <c r="BJ138" t="inlineStr"/>
+      <c r="BK138" t="inlineStr"/>
+      <c r="BL138" t="inlineStr"/>
+      <c r="BM138" t="inlineStr"/>
+      <c r="BN138" t="inlineStr"/>
+      <c r="BO138" t="inlineStr"/>
+      <c r="BP138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>jyOc4FWq</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>45548.625</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">benchabane f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade gabriel montpied
+  clermont ferrand </t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F139" t="n">
+        <v>4275</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="n">
+        <v>53</v>
+      </c>
+      <c r="N139" t="n">
+        <v>47</v>
+      </c>
+      <c r="O139" t="n">
+        <v>6</v>
+      </c>
+      <c r="P139" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>1</v>
+      </c>
+      <c r="R139" t="n">
+        <v>4</v>
+      </c>
+      <c r="S139" t="n">
+        <v>14</v>
+      </c>
+      <c r="T139" t="n">
+        <v>11</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="W139" t="n">
+        <v>55</v>
+      </c>
+      <c r="X139" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC139" t="inlineStr"/>
+      <c r="AD139" t="inlineStr"/>
+      <c r="AE139" t="n">
+        <v>22.77777777777778</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>181</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>65.11111111111111</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>74.11111111111111</v>
+      </c>
+      <c r="AK139" t="inlineStr"/>
+      <c r="AL139" t="inlineStr"/>
+      <c r="AM139" t="inlineStr"/>
+      <c r="AN139" t="inlineStr"/>
+      <c r="AO139" t="inlineStr"/>
+      <c r="AP139" t="inlineStr"/>
+      <c r="AQ139" t="n">
+        <v>23.76923076923077</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>176.9230769230769</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>66.61538461538461</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>1563461.538461538</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>71.61538461538461</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>179</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>957500</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="BC139" t="inlineStr"/>
+      <c r="BD139" t="inlineStr"/>
+      <c r="BE139" t="inlineStr"/>
+      <c r="BF139" t="inlineStr"/>
+      <c r="BG139" t="inlineStr"/>
+      <c r="BH139" t="inlineStr"/>
+      <c r="BI139" t="inlineStr"/>
+      <c r="BJ139" t="inlineStr"/>
+      <c r="BK139" t="inlineStr"/>
+      <c r="BL139" t="inlineStr"/>
+      <c r="BM139" t="inlineStr"/>
+      <c r="BN139" t="inlineStr"/>
+      <c r="BO139" t="inlineStr"/>
+      <c r="BP139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>xU3hQdg3</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>45548.625</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taleb a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le basser
+  laval </t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>11017</v>
+      </c>
+      <c r="F140" t="n">
+        <v>5748</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="n">
+        <v>47</v>
+      </c>
+      <c r="N140" t="n">
+        <v>53</v>
+      </c>
+      <c r="O140" t="n">
+        <v>1</v>
+      </c>
+      <c r="P140" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>1</v>
+      </c>
+      <c r="R140" t="n">
+        <v>2</v>
+      </c>
+      <c r="S140" t="n">
+        <v>3</v>
+      </c>
+      <c r="T140" t="n">
+        <v>5</v>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="W140" t="n">
+        <v>55</v>
+      </c>
+      <c r="X140" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC140" t="inlineStr"/>
+      <c r="AD140" t="inlineStr"/>
+      <c r="AE140" t="inlineStr"/>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="inlineStr"/>
+      <c r="AH140" t="inlineStr"/>
+      <c r="AI140" t="inlineStr"/>
+      <c r="AJ140" t="inlineStr"/>
+      <c r="AK140" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1002500</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>28.66666666666667</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>182.1333333333333</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>66.53333333333333</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1054333.333333333</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>71</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>23.95454545454545</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>179.5909090909091</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>63.59090909090909</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>809090.9090909091</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>69.77272727272727</v>
+      </c>
+      <c r="BC140" t="inlineStr"/>
+      <c r="BD140" t="inlineStr"/>
+      <c r="BE140" t="inlineStr"/>
+      <c r="BF140" t="inlineStr"/>
+      <c r="BG140" t="inlineStr"/>
+      <c r="BH140" t="inlineStr"/>
+      <c r="BI140" t="inlineStr"/>
+      <c r="BJ140" t="inlineStr"/>
+      <c r="BK140" t="inlineStr"/>
+      <c r="BL140" t="inlineStr"/>
+      <c r="BM140" t="inlineStr"/>
+      <c r="BN140" t="inlineStr"/>
+      <c r="BO140" t="inlineStr"/>
+      <c r="BP140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>dYQ52g1d</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>45548.625</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">legat p 
+  fra </t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade du moustoir
+  lorient </t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>16787</v>
+      </c>
+      <c r="F141" t="n">
+        <v>10017</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2</v>
+      </c>
+      <c r="H141" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="n">
+        <v>53</v>
+      </c>
+      <c r="N141" t="n">
+        <v>47</v>
+      </c>
+      <c r="O141" t="n">
+        <v>14</v>
+      </c>
+      <c r="P141" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>7</v>
+      </c>
+      <c r="R141" t="n">
+        <v>3</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="n">
+        <v>12</v>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="W141" t="n">
+        <v>55</v>
+      </c>
+      <c r="X141" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr"/>
+      <c r="AE141" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>4150000</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AK141" t="inlineStr"/>
+      <c r="AL141" t="inlineStr"/>
+      <c r="AM141" t="inlineStr"/>
+      <c r="AN141" t="inlineStr"/>
+      <c r="AO141" t="inlineStr"/>
+      <c r="AP141" t="inlineStr"/>
+      <c r="AQ141" t="n">
+        <v>22.125</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>176.75</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>68.625</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>2440625</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>77.625</v>
+      </c>
+      <c r="AW141" t="inlineStr"/>
+      <c r="AX141" t="inlineStr"/>
+      <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr"/>
+      <c r="BA141" t="inlineStr"/>
+      <c r="BB141" t="inlineStr"/>
+      <c r="BC141" t="inlineStr"/>
+      <c r="BD141" t="inlineStr"/>
+      <c r="BE141" t="inlineStr"/>
+      <c r="BF141" t="inlineStr"/>
+      <c r="BG141" t="inlineStr"/>
+      <c r="BH141" t="inlineStr"/>
+      <c r="BI141" t="inlineStr"/>
+      <c r="BJ141" t="inlineStr"/>
+      <c r="BK141" t="inlineStr"/>
+      <c r="BL141" t="inlineStr"/>
+      <c r="BM141" t="inlineStr"/>
+      <c r="BN141" t="inlineStr"/>
+      <c r="BO141" t="inlineStr"/>
+      <c r="BP141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>bwqJBcvA</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>45548.625</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bouille t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nouste camp
+  pau </t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>4031</v>
+      </c>
+      <c r="F142" t="n">
+        <v>2741</v>
+      </c>
+      <c r="G142" t="n">
+        <v>3</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="n">
+        <v>54</v>
+      </c>
+      <c r="N142" t="n">
+        <v>46</v>
+      </c>
+      <c r="O142" t="n">
+        <v>19</v>
+      </c>
+      <c r="P142" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>9</v>
+      </c>
+      <c r="R142" t="n">
+        <v>3</v>
+      </c>
+      <c r="S142" t="n">
+        <v>15</v>
+      </c>
+      <c r="T142" t="n">
+        <v>17</v>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="W142" t="n">
+        <v>55</v>
+      </c>
+      <c r="X142" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC142" t="inlineStr"/>
+      <c r="AD142" t="inlineStr"/>
+      <c r="AE142" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>185</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>928125</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>70.875</v>
+      </c>
+      <c r="AK142" t="inlineStr"/>
+      <c r="AL142" t="inlineStr"/>
+      <c r="AM142" t="inlineStr"/>
+      <c r="AN142" t="inlineStr"/>
+      <c r="AO142" t="inlineStr"/>
+      <c r="AP142" t="inlineStr"/>
+      <c r="AQ142" t="n">
+        <v>25.53846153846154</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>180.7692307692308</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>65.07692307692308</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>917307.6923076923</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>71.61538461538461</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>880000</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="BC142" t="inlineStr"/>
+      <c r="BD142" t="inlineStr"/>
+      <c r="BE142" t="inlineStr"/>
+      <c r="BF142" t="inlineStr"/>
+      <c r="BG142" t="inlineStr"/>
+      <c r="BH142" t="inlineStr"/>
+      <c r="BI142" t="inlineStr"/>
+      <c r="BJ142" t="inlineStr"/>
+      <c r="BK142" t="inlineStr"/>
+      <c r="BL142" t="inlineStr"/>
+      <c r="BM142" t="inlineStr"/>
+      <c r="BN142" t="inlineStr"/>
+      <c r="BO142" t="inlineStr"/>
+      <c r="BP142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>2BkADJ9c</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>45548.625</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petit a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade paul lignon
+  rodez </t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>5955</v>
+      </c>
+      <c r="F143" t="n">
+        <v>3991</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" t="n">
+        <v>2</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="n">
+        <v>45</v>
+      </c>
+      <c r="N143" t="n">
+        <v>55</v>
+      </c>
+      <c r="O143" t="n">
+        <v>4</v>
+      </c>
+      <c r="P143" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>2</v>
+      </c>
+      <c r="R143" t="n">
+        <v>3</v>
+      </c>
+      <c r="S143" t="n">
+        <v>4</v>
+      </c>
+      <c r="T143" t="n">
+        <v>4</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="W143" t="n">
+        <v>55</v>
+      </c>
+      <c r="X143" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC143" t="inlineStr"/>
+      <c r="AD143" t="inlineStr"/>
+      <c r="AE143" t="inlineStr"/>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="inlineStr"/>
+      <c r="AH143" t="inlineStr"/>
+      <c r="AI143" t="inlineStr"/>
+      <c r="AJ143" t="inlineStr"/>
+      <c r="AK143" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>25.76923076923077</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>185</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>63.53846153846154</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>626923.0769230769</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>68.92307692307692</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>22.45454545454545</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>179.9090909090909</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>61.90909090909091</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>895454.5454545454</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="BC143" t="inlineStr"/>
+      <c r="BD143" t="inlineStr"/>
+      <c r="BE143" t="inlineStr"/>
+      <c r="BF143" t="inlineStr"/>
+      <c r="BG143" t="inlineStr"/>
+      <c r="BH143" t="inlineStr"/>
+      <c r="BI143" t="inlineStr"/>
+      <c r="BJ143" t="inlineStr"/>
+      <c r="BK143" t="inlineStr"/>
+      <c r="BL143" t="inlineStr"/>
+      <c r="BM143" t="inlineStr"/>
+      <c r="BN143" t="inlineStr"/>
+      <c r="BO143" t="inlineStr"/>
+      <c r="BP143" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP143"/>
+  <dimension ref="A1:BP150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29721,6 +29721,1470 @@
       <c r="BO143" t="inlineStr"/>
       <c r="BP143" t="inlineStr"/>
     </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>Qw81zU34</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>45550.65625</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dechepy b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F144" t="n">
+        <v>38116</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M144" t="n">
+        <v>54</v>
+      </c>
+      <c r="N144" t="n">
+        <v>46</v>
+      </c>
+      <c r="O144" t="n">
+        <v>12</v>
+      </c>
+      <c r="P144" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>5</v>
+      </c>
+      <c r="R144" t="n">
+        <v>3</v>
+      </c>
+      <c r="S144" t="n">
+        <v>12</v>
+      </c>
+      <c r="T144" t="n">
+        <v>11</v>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="W144" t="n">
+        <v>55</v>
+      </c>
+      <c r="X144" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA144" t="inlineStr"/>
+      <c r="AB144" t="inlineStr"/>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr"/>
+      <c r="AE144" t="n">
+        <v>26.36363636363636</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>179.5454545454545</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>76.36363636363636</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>11227272.72727273</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>79</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>184.4444444444445</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>2.111111111111111</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>76.88888888888889</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>9833333.333333334</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>78.33333333333333</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>23.15789473684211</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>181.3157894736842</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>1.105263157894737</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>72.89473684210526</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>79.15789473684211</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>24.26315789473684</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>179.5263157894737</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>1.526315789473684</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>74.68421052631579</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>9057894.736842105</v>
+      </c>
+      <c r="BB144" t="n">
+        <v>80.89473684210526</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>164</v>
+      </c>
+      <c r="BE144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG144" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH144" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="BI144" t="n">
+        <v>72</v>
+      </c>
+      <c r="BJ144" t="inlineStr"/>
+      <c r="BK144" t="inlineStr"/>
+      <c r="BL144" t="inlineStr"/>
+      <c r="BM144" t="inlineStr"/>
+      <c r="BN144" t="inlineStr"/>
+      <c r="BO144" t="inlineStr"/>
+      <c r="BP144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F145" t="n">
+        <v>29811</v>
+      </c>
+      <c r="G145" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" t="n">
+        <v>2</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M145" t="n">
+        <v>45</v>
+      </c>
+      <c r="N145" t="n">
+        <v>55</v>
+      </c>
+      <c r="O145" t="n">
+        <v>18</v>
+      </c>
+      <c r="P145" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>6</v>
+      </c>
+      <c r="R145" t="n">
+        <v>4</v>
+      </c>
+      <c r="S145" t="n">
+        <v>14</v>
+      </c>
+      <c r="T145" t="n">
+        <v>5</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="W145" t="n">
+        <v>55</v>
+      </c>
+      <c r="X145" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA145" t="inlineStr"/>
+      <c r="AB145" t="inlineStr"/>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr"/>
+      <c r="AE145" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>181.3636363636364</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>73.36363636363636</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>5093181.818181818</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>75.54545454545455</v>
+      </c>
+      <c r="AK145" t="inlineStr"/>
+      <c r="AL145" t="inlineStr"/>
+      <c r="AM145" t="inlineStr"/>
+      <c r="AN145" t="inlineStr"/>
+      <c r="AO145" t="inlineStr"/>
+      <c r="AP145" t="inlineStr"/>
+      <c r="AQ145" t="n">
+        <v>24.42105263157895</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>182.6315789473684</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>71.31578947368421</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>3146052.631578947</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>74.36842105263158</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>184.4375</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>71.125</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>5069375</v>
+      </c>
+      <c r="BB145" t="n">
+        <v>77.375</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>180.3333333333333</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>221</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>13200000</v>
+      </c>
+      <c r="BI145" t="n">
+        <v>225</v>
+      </c>
+      <c r="BJ145" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK145" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="BL145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN145" t="n">
+        <v>149</v>
+      </c>
+      <c r="BO145" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="BP145" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>E3tkRPQj</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F146" t="n">
+        <v>19135</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M146" t="n">
+        <v>51</v>
+      </c>
+      <c r="N146" t="n">
+        <v>49</v>
+      </c>
+      <c r="O146" t="n">
+        <v>10</v>
+      </c>
+      <c r="P146" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>5</v>
+      </c>
+      <c r="R146" t="n">
+        <v>2</v>
+      </c>
+      <c r="S146" t="n">
+        <v>11</v>
+      </c>
+      <c r="T146" t="n">
+        <v>14</v>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="W146" t="n">
+        <v>55</v>
+      </c>
+      <c r="X146" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA146" t="inlineStr"/>
+      <c r="AB146" t="inlineStr"/>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr"/>
+      <c r="AE146" t="n">
+        <v>19.44444444444444</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>4566666.666666667</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>81.66666666666667</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>181</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>2033333.333333333</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>73.22222222222223</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>21.0625</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>183.375</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT146" t="n">
+        <v>68.375</v>
+      </c>
+      <c r="AU146" t="n">
+        <v>2995312.5</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>78.125</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>25.05882352941176</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>180.9411764705882</v>
+      </c>
+      <c r="AY146" t="n">
+        <v>1.058823529411765</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>65.64705882352941</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>1167647.058823529</v>
+      </c>
+      <c r="BB146" t="n">
+        <v>71.29411764705883</v>
+      </c>
+      <c r="BC146" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD146" t="n">
+        <v>183</v>
+      </c>
+      <c r="BE146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF146" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG146" t="n">
+        <v>129</v>
+      </c>
+      <c r="BH146" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BI146" t="n">
+        <v>156</v>
+      </c>
+      <c r="BJ146" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BK146" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="BL146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM146" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN146" t="n">
+        <v>130</v>
+      </c>
+      <c r="BO146" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="BP146" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>fJaIWo3T</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F147" t="n">
+        <v>30097</v>
+      </c>
+      <c r="G147" t="n">
+        <v>2</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M147" t="n">
+        <v>54</v>
+      </c>
+      <c r="N147" t="n">
+        <v>46</v>
+      </c>
+      <c r="O147" t="n">
+        <v>15</v>
+      </c>
+      <c r="P147" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>7</v>
+      </c>
+      <c r="R147" t="n">
+        <v>3</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="n">
+        <v>11</v>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="W147" t="n">
+        <v>55</v>
+      </c>
+      <c r="X147" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="inlineStr"/>
+      <c r="AC147" t="inlineStr"/>
+      <c r="AD147" t="inlineStr"/>
+      <c r="AE147" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>182.125</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>5525000</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>77.875</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>183.8181818181818</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>3081818.181818182</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>75</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>23.17647058823529</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>180.6470588235294</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>71</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>3405882.352941176</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>77.41176470588235</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>182</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>2060000</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>72.95</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>178</v>
+      </c>
+      <c r="BE147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG147" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH147" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="BI147" t="n">
+        <v>78</v>
+      </c>
+      <c r="BJ147" t="n">
+        <v>19</v>
+      </c>
+      <c r="BK147" t="n">
+        <v>188</v>
+      </c>
+      <c r="BL147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN147" t="n">
+        <v>64</v>
+      </c>
+      <c r="BO147" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BP147" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>hCffxjZi</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F148" t="n">
+        <v>27451</v>
+      </c>
+      <c r="G148" t="n">
+        <v>3</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M148" t="n">
+        <v>51</v>
+      </c>
+      <c r="N148" t="n">
+        <v>49</v>
+      </c>
+      <c r="O148" t="n">
+        <v>11</v>
+      </c>
+      <c r="P148" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>6</v>
+      </c>
+      <c r="R148" t="n">
+        <v>4</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="n">
+        <v>7</v>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="W148" t="n">
+        <v>55</v>
+      </c>
+      <c r="X148" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA148" t="inlineStr"/>
+      <c r="AB148" t="inlineStr"/>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="AE148" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>8330000</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>24.88888888888889</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>5433333.333333333</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>77.66666666666667</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>22.05263157894737</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>178.8421052631579</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>1.368421052631579</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>71.15789473684211</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>6905263.157894737</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>78.10526315789474</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>71.83333333333333</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>3516666.666666667</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>187</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>145</v>
+      </c>
+      <c r="BH148" t="n">
+        <v>8400000</v>
+      </c>
+      <c r="BI148" t="n">
+        <v>158</v>
+      </c>
+      <c r="BJ148" t="n">
+        <v>24</v>
+      </c>
+      <c r="BK148" t="n">
+        <v>185.6</v>
+      </c>
+      <c r="BL148" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BM148" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN148" t="n">
+        <v>358</v>
+      </c>
+      <c r="BO148" t="n">
+        <v>19600000</v>
+      </c>
+      <c r="BP148" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>8MPiooIM</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F149" t="n">
+        <v>47628</v>
+      </c>
+      <c r="G149" t="n">
+        <v>3</v>
+      </c>
+      <c r="H149" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="K149" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M149" t="n">
+        <v>67</v>
+      </c>
+      <c r="N149" t="n">
+        <v>33</v>
+      </c>
+      <c r="O149" t="n">
+        <v>22</v>
+      </c>
+      <c r="P149" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>9</v>
+      </c>
+      <c r="R149" t="n">
+        <v>3</v>
+      </c>
+      <c r="S149" t="n">
+        <v>7</v>
+      </c>
+      <c r="T149" t="n">
+        <v>13</v>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="W149" t="n">
+        <v>55</v>
+      </c>
+      <c r="X149" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA149" t="inlineStr"/>
+      <c r="AB149" t="inlineStr"/>
+      <c r="AC149" t="inlineStr"/>
+      <c r="AD149" t="inlineStr"/>
+      <c r="AE149" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>82</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>43812500</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>85.125</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>6170000</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>76</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>21.375</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>76.375</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>28337500</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>84.875</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>180.8636363636364</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>1.227272727272727</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>72</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>4059090.909090909</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>75.09090909090909</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>326</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>147500000</v>
+      </c>
+      <c r="BI149" t="n">
+        <v>343</v>
+      </c>
+      <c r="BJ149" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BK149" t="n">
+        <v>183</v>
+      </c>
+      <c r="BL149" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN149" t="n">
+        <v>154</v>
+      </c>
+      <c r="BO149" t="n">
+        <v>23500000</v>
+      </c>
+      <c r="BP149" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>4GNqcbPG</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>45551.65625</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thual o 
+  fra </t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>20068</v>
+      </c>
+      <c r="F150" t="n">
+        <v>4079</v>
+      </c>
+      <c r="G150" t="n">
+        <v>3</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="n">
+        <v>51</v>
+      </c>
+      <c r="N150" t="n">
+        <v>49</v>
+      </c>
+      <c r="O150" t="n">
+        <v>12</v>
+      </c>
+      <c r="P150" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>5</v>
+      </c>
+      <c r="R150" t="n">
+        <v>4</v>
+      </c>
+      <c r="S150" t="n">
+        <v>15</v>
+      </c>
+      <c r="T150" t="n">
+        <v>12</v>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="W150" t="n">
+        <v>55</v>
+      </c>
+      <c r="X150" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC150" t="inlineStr"/>
+      <c r="AD150" t="inlineStr"/>
+      <c r="AE150" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>185.6</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>1527500</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>71</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>180.1111111111111</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>67.88888888888889</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>1877777.777777778</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>73.88888888888889</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>24.64705882352941</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>186.1176470588235</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>65.47058823529412</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>1447058.823529412</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>71.29411764705883</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>24.8125</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>185.125</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>65.5625</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>1184375</v>
+      </c>
+      <c r="BB150" t="n">
+        <v>73</v>
+      </c>
+      <c r="BC150" t="inlineStr"/>
+      <c r="BD150" t="inlineStr"/>
+      <c r="BE150" t="inlineStr"/>
+      <c r="BF150" t="inlineStr"/>
+      <c r="BG150" t="inlineStr"/>
+      <c r="BH150" t="inlineStr"/>
+      <c r="BI150" t="inlineStr"/>
+      <c r="BJ150" t="inlineStr"/>
+      <c r="BK150" t="inlineStr"/>
+      <c r="BL150" t="inlineStr"/>
+      <c r="BM150" t="inlineStr"/>
+      <c r="BN150" t="inlineStr"/>
+      <c r="BO150" t="inlineStr"/>
+      <c r="BP150" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN168"/>
+  <dimension ref="A1:CN177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44215,6 +44215,2140 @@
       <c r="CM168" t="inlineStr"/>
       <c r="CN168" t="inlineStr"/>
     </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>Aw6Go4Lt</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="n">
+        <v>45559.64583333334</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angoula g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michel moretti stadium
+  ajaccio </t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>8470</v>
+      </c>
+      <c r="F169" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G169" t="n">
+        <v>2</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="n">
+        <v>44</v>
+      </c>
+      <c r="N169" t="n">
+        <v>56</v>
+      </c>
+      <c r="O169" t="n">
+        <v>12</v>
+      </c>
+      <c r="P169" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>3</v>
+      </c>
+      <c r="R169" t="n">
+        <v>1</v>
+      </c>
+      <c r="S169" t="n">
+        <v>3</v>
+      </c>
+      <c r="T169" t="n">
+        <v>5</v>
+      </c>
+      <c r="U169" t="n">
+        <v>6</v>
+      </c>
+      <c r="V169" t="n">
+        <v>1</v>
+      </c>
+      <c r="W169" t="inlineStr"/>
+      <c r="X169" t="inlineStr"/>
+      <c r="Y169" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC169" t="inlineStr"/>
+      <c r="AD169" t="inlineStr"/>
+      <c r="AE169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>73</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>52</v>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AQ169" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU169" t="inlineStr"/>
+      <c r="AV169" t="inlineStr"/>
+      <c r="AW169" t="n">
+        <v>392</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>485</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>267</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>354</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG169" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH169" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI169" t="inlineStr"/>
+      <c r="BJ169" t="inlineStr"/>
+      <c r="BK169" t="inlineStr"/>
+      <c r="BL169" t="inlineStr"/>
+      <c r="BM169" t="n">
+        <v>24</v>
+      </c>
+      <c r="BN169" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="BO169" t="n">
+        <v>64.55555555555556</v>
+      </c>
+      <c r="BP169" t="inlineStr"/>
+      <c r="BQ169" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="BR169" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="BS169" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="BT169" t="inlineStr"/>
+      <c r="BU169" t="n">
+        <v>26</v>
+      </c>
+      <c r="BV169" t="n">
+        <v>179.8636363636364</v>
+      </c>
+      <c r="BW169" t="n">
+        <v>65.45454545454545</v>
+      </c>
+      <c r="BX169" t="inlineStr"/>
+      <c r="BY169" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="BZ169" t="n">
+        <v>182.8888888888889</v>
+      </c>
+      <c r="CA169" t="n">
+        <v>68.44444444444444</v>
+      </c>
+      <c r="CB169" t="n">
+        <v>7555.555555555556</v>
+      </c>
+      <c r="CC169" t="inlineStr"/>
+      <c r="CD169" t="inlineStr"/>
+      <c r="CE169" t="inlineStr"/>
+      <c r="CF169" t="inlineStr"/>
+      <c r="CG169" t="inlineStr"/>
+      <c r="CH169" t="inlineStr"/>
+      <c r="CI169" t="inlineStr"/>
+      <c r="CJ169" t="inlineStr"/>
+      <c r="CK169" t="inlineStr"/>
+      <c r="CL169" t="inlineStr"/>
+      <c r="CM169" t="inlineStr"/>
+      <c r="CN169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>rkVhpcU0</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="n">
+        <v>45559.64583333334</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">benchabane f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des sports
+  annecy </t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>15660</v>
+      </c>
+      <c r="F170" t="n">
+        <v>4005</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="n">
+        <v>33</v>
+      </c>
+      <c r="N170" t="n">
+        <v>67</v>
+      </c>
+      <c r="O170" t="n">
+        <v>9</v>
+      </c>
+      <c r="P170" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>2</v>
+      </c>
+      <c r="R170" t="n">
+        <v>3</v>
+      </c>
+      <c r="S170" t="n">
+        <v>6</v>
+      </c>
+      <c r="T170" t="n">
+        <v>8</v>
+      </c>
+      <c r="U170" t="n">
+        <v>1</v>
+      </c>
+      <c r="V170" t="n">
+        <v>7</v>
+      </c>
+      <c r="W170" t="inlineStr"/>
+      <c r="X170" t="inlineStr"/>
+      <c r="Y170" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC170" t="inlineStr"/>
+      <c r="AD170" t="inlineStr"/>
+      <c r="AE170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>92</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>149</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>51</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>109</v>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="AQ170" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU170" t="inlineStr"/>
+      <c r="AV170" t="inlineStr"/>
+      <c r="AW170" t="n">
+        <v>240</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>443</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>134</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>311</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG170" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH170" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI170" t="inlineStr"/>
+      <c r="BJ170" t="inlineStr"/>
+      <c r="BK170" t="inlineStr"/>
+      <c r="BL170" t="inlineStr"/>
+      <c r="BM170" t="n">
+        <v>28.125</v>
+      </c>
+      <c r="BN170" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="BO170" t="n">
+        <v>65</v>
+      </c>
+      <c r="BP170" t="inlineStr"/>
+      <c r="BQ170" t="n">
+        <v>25.55555555555556</v>
+      </c>
+      <c r="BR170" t="n">
+        <v>179.8888888888889</v>
+      </c>
+      <c r="BS170" t="n">
+        <v>65.66666666666667</v>
+      </c>
+      <c r="BT170" t="inlineStr"/>
+      <c r="BU170" t="n">
+        <v>22.875</v>
+      </c>
+      <c r="BV170" t="n">
+        <v>181.375</v>
+      </c>
+      <c r="BW170" t="n">
+        <v>62.125</v>
+      </c>
+      <c r="BX170" t="inlineStr"/>
+      <c r="BY170" t="n">
+        <v>24</v>
+      </c>
+      <c r="BZ170" t="n">
+        <v>178.1111111111111</v>
+      </c>
+      <c r="CA170" t="n">
+        <v>66.22222222222223</v>
+      </c>
+      <c r="CB170" t="inlineStr"/>
+      <c r="CC170" t="inlineStr"/>
+      <c r="CD170" t="inlineStr"/>
+      <c r="CE170" t="inlineStr"/>
+      <c r="CF170" t="inlineStr"/>
+      <c r="CG170" t="inlineStr"/>
+      <c r="CH170" t="inlineStr"/>
+      <c r="CI170" t="inlineStr"/>
+      <c r="CJ170" t="inlineStr"/>
+      <c r="CK170" t="inlineStr"/>
+      <c r="CL170" t="inlineStr"/>
+      <c r="CM170" t="inlineStr"/>
+      <c r="CN170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>pUN9kDME</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="n">
+        <v>45559.64583333334</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bouille t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade michel d ornano
+  caen </t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>20300</v>
+      </c>
+      <c r="F171" t="n">
+        <v>14204</v>
+      </c>
+      <c r="G171" t="n">
+        <v>2</v>
+      </c>
+      <c r="H171" t="n">
+        <v>1</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="n">
+        <v>62</v>
+      </c>
+      <c r="N171" t="n">
+        <v>38</v>
+      </c>
+      <c r="O171" t="n">
+        <v>15</v>
+      </c>
+      <c r="P171" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>3</v>
+      </c>
+      <c r="R171" t="n">
+        <v>4</v>
+      </c>
+      <c r="S171" t="n">
+        <v>8</v>
+      </c>
+      <c r="T171" t="n">
+        <v>3</v>
+      </c>
+      <c r="U171" t="n">
+        <v>4</v>
+      </c>
+      <c r="V171" t="n">
+        <v>0</v>
+      </c>
+      <c r="W171" t="inlineStr"/>
+      <c r="X171" t="inlineStr"/>
+      <c r="Y171" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC171" t="inlineStr"/>
+      <c r="AD171" t="inlineStr"/>
+      <c r="AE171" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>102</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>108</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AQ171" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU171" t="inlineStr"/>
+      <c r="AV171" t="inlineStr"/>
+      <c r="AW171" t="n">
+        <v>564</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>407</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>506</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>335</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>37</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG171" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH171" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI171" t="inlineStr"/>
+      <c r="BJ171" t="inlineStr"/>
+      <c r="BK171" t="inlineStr"/>
+      <c r="BL171" t="inlineStr"/>
+      <c r="BM171" t="n">
+        <v>24.625</v>
+      </c>
+      <c r="BN171" t="n">
+        <v>180</v>
+      </c>
+      <c r="BO171" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="BP171" t="inlineStr"/>
+      <c r="BQ171" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="BR171" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="BS171" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="BT171" t="inlineStr"/>
+      <c r="BU171" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="BV171" t="n">
+        <v>182.95</v>
+      </c>
+      <c r="BW171" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="BX171" t="inlineStr"/>
+      <c r="BY171" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="BZ171" t="n">
+        <v>178.125</v>
+      </c>
+      <c r="CA171" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="CB171" t="inlineStr"/>
+      <c r="CC171" t="inlineStr"/>
+      <c r="CD171" t="inlineStr"/>
+      <c r="CE171" t="inlineStr"/>
+      <c r="CF171" t="inlineStr"/>
+      <c r="CG171" t="inlineStr"/>
+      <c r="CH171" t="inlineStr"/>
+      <c r="CI171" t="inlineStr"/>
+      <c r="CJ171" t="inlineStr"/>
+      <c r="CK171" t="inlineStr"/>
+      <c r="CL171" t="inlineStr"/>
+      <c r="CM171" t="inlineStr"/>
+      <c r="CN171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>bDHWsMK5</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="n">
+        <v>45559.64583333334</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taleb a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade gabriel montpied
+  clermont ferrand </t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F172" t="n">
+        <v>4556</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="n">
+        <v>1</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="n">
+        <v>52</v>
+      </c>
+      <c r="N172" t="n">
+        <v>48</v>
+      </c>
+      <c r="O172" t="n">
+        <v>11</v>
+      </c>
+      <c r="P172" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>4</v>
+      </c>
+      <c r="R172" t="n">
+        <v>3</v>
+      </c>
+      <c r="S172" t="n">
+        <v>3</v>
+      </c>
+      <c r="T172" t="n">
+        <v>3</v>
+      </c>
+      <c r="U172" t="n">
+        <v>4</v>
+      </c>
+      <c r="V172" t="n">
+        <v>0</v>
+      </c>
+      <c r="W172" t="inlineStr"/>
+      <c r="X172" t="inlineStr"/>
+      <c r="Y172" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC172" t="inlineStr"/>
+      <c r="AD172" t="inlineStr"/>
+      <c r="AE172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>99</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>84</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AQ172" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU172" t="inlineStr"/>
+      <c r="AV172" t="inlineStr"/>
+      <c r="AW172" t="n">
+        <v>456</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>439</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>358</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>357</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF172" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG172" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH172" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI172" t="inlineStr"/>
+      <c r="BJ172" t="inlineStr"/>
+      <c r="BK172" t="inlineStr"/>
+      <c r="BL172" t="inlineStr"/>
+      <c r="BM172" t="n">
+        <v>22.875</v>
+      </c>
+      <c r="BN172" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="BO172" t="n">
+        <v>66</v>
+      </c>
+      <c r="BP172" t="inlineStr"/>
+      <c r="BQ172" t="inlineStr"/>
+      <c r="BR172" t="inlineStr"/>
+      <c r="BS172" t="inlineStr"/>
+      <c r="BT172" t="inlineStr"/>
+      <c r="BU172" t="n">
+        <v>24.16666666666667</v>
+      </c>
+      <c r="BV172" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="BW172" t="n">
+        <v>64.41666666666667</v>
+      </c>
+      <c r="BX172" t="inlineStr"/>
+      <c r="BY172" t="inlineStr"/>
+      <c r="BZ172" t="inlineStr"/>
+      <c r="CA172" t="inlineStr"/>
+      <c r="CB172" t="inlineStr"/>
+      <c r="CC172" t="inlineStr"/>
+      <c r="CD172" t="inlineStr"/>
+      <c r="CE172" t="inlineStr"/>
+      <c r="CF172" t="inlineStr"/>
+      <c r="CG172" t="inlineStr"/>
+      <c r="CH172" t="inlineStr"/>
+      <c r="CI172" t="inlineStr"/>
+      <c r="CJ172" t="inlineStr"/>
+      <c r="CK172" t="inlineStr"/>
+      <c r="CL172" t="inlineStr"/>
+      <c r="CM172" t="inlineStr"/>
+      <c r="CN172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>65aPqrjg</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="n">
+        <v>45559.64583333334</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">legat p 
+  fra </t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade marcel tribut
+  dunkerque </t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>4933</v>
+      </c>
+      <c r="F173" t="n">
+        <v>3636</v>
+      </c>
+      <c r="G173" t="n">
+        <v>2</v>
+      </c>
+      <c r="H173" t="n">
+        <v>1</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="n">
+        <v>51</v>
+      </c>
+      <c r="N173" t="n">
+        <v>49</v>
+      </c>
+      <c r="O173" t="n">
+        <v>12</v>
+      </c>
+      <c r="P173" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>3</v>
+      </c>
+      <c r="R173" t="n">
+        <v>4</v>
+      </c>
+      <c r="S173" t="n">
+        <v>4</v>
+      </c>
+      <c r="T173" t="n">
+        <v>6</v>
+      </c>
+      <c r="U173" t="n">
+        <v>5</v>
+      </c>
+      <c r="V173" t="n">
+        <v>1</v>
+      </c>
+      <c r="W173" t="inlineStr"/>
+      <c r="X173" t="inlineStr"/>
+      <c r="Y173" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC173" t="inlineStr"/>
+      <c r="AD173" t="inlineStr"/>
+      <c r="AE173" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>98</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>56</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>45</v>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AQ173" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU173" t="inlineStr"/>
+      <c r="AV173" t="inlineStr"/>
+      <c r="AW173" t="n">
+        <v>446</v>
+      </c>
+      <c r="AX173" t="n">
+        <v>377</v>
+      </c>
+      <c r="AY173" t="n">
+        <v>343</v>
+      </c>
+      <c r="AZ173" t="n">
+        <v>278</v>
+      </c>
+      <c r="BA173" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB173" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC173" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE173" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF173" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG173" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH173" t="n">
+        <v>13</v>
+      </c>
+      <c r="BI173" t="inlineStr"/>
+      <c r="BJ173" t="inlineStr"/>
+      <c r="BK173" t="inlineStr"/>
+      <c r="BL173" t="inlineStr"/>
+      <c r="BM173" t="inlineStr"/>
+      <c r="BN173" t="inlineStr"/>
+      <c r="BO173" t="inlineStr"/>
+      <c r="BP173" t="inlineStr"/>
+      <c r="BQ173" t="inlineStr"/>
+      <c r="BR173" t="inlineStr"/>
+      <c r="BS173" t="inlineStr"/>
+      <c r="BT173" t="inlineStr"/>
+      <c r="BU173" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="BV173" t="n">
+        <v>178.1</v>
+      </c>
+      <c r="BW173" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="BX173" t="inlineStr"/>
+      <c r="BY173" t="n">
+        <v>23.72222222222222</v>
+      </c>
+      <c r="BZ173" t="n">
+        <v>178.5555555555555</v>
+      </c>
+      <c r="CA173" t="n">
+        <v>63.44444444444444</v>
+      </c>
+      <c r="CB173" t="inlineStr"/>
+      <c r="CC173" t="inlineStr"/>
+      <c r="CD173" t="inlineStr"/>
+      <c r="CE173" t="inlineStr"/>
+      <c r="CF173" t="inlineStr"/>
+      <c r="CG173" t="inlineStr"/>
+      <c r="CH173" t="inlineStr"/>
+      <c r="CI173" t="inlineStr"/>
+      <c r="CJ173" t="inlineStr"/>
+      <c r="CK173" t="inlineStr"/>
+      <c r="CL173" t="inlineStr"/>
+      <c r="CM173" t="inlineStr"/>
+      <c r="CN173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>CrvjVry0</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="n">
+        <v>45559.64583333334</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thual o 
+  fra </t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade saint symphorien
+  metz </t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>28786</v>
+      </c>
+      <c r="F174" t="n">
+        <v>16675</v>
+      </c>
+      <c r="G174" t="n">
+        <v>6</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="n">
+        <v>68</v>
+      </c>
+      <c r="N174" t="n">
+        <v>32</v>
+      </c>
+      <c r="O174" t="n">
+        <v>18</v>
+      </c>
+      <c r="P174" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>9</v>
+      </c>
+      <c r="R174" t="n">
+        <v>5</v>
+      </c>
+      <c r="S174" t="n">
+        <v>8</v>
+      </c>
+      <c r="T174" t="n">
+        <v>4</v>
+      </c>
+      <c r="U174" t="n">
+        <v>1</v>
+      </c>
+      <c r="V174" t="n">
+        <v>3</v>
+      </c>
+      <c r="W174" t="inlineStr"/>
+      <c r="X174" t="inlineStr"/>
+      <c r="Y174" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC174" t="inlineStr"/>
+      <c r="AD174" t="inlineStr"/>
+      <c r="AE174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>111</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>106</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>76</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AQ174" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU174" t="inlineStr"/>
+      <c r="AV174" t="inlineStr"/>
+      <c r="AW174" t="n">
+        <v>707</v>
+      </c>
+      <c r="AX174" t="n">
+        <v>334</v>
+      </c>
+      <c r="AY174" t="n">
+        <v>651</v>
+      </c>
+      <c r="AZ174" t="n">
+        <v>254</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB174" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE174" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF174" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG174" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH174" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI174" t="inlineStr"/>
+      <c r="BJ174" t="inlineStr"/>
+      <c r="BK174" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="BL174" t="inlineStr"/>
+      <c r="BM174" t="n">
+        <v>25.88888888888889</v>
+      </c>
+      <c r="BN174" t="n">
+        <v>176.8888888888889</v>
+      </c>
+      <c r="BO174" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="BP174" t="n">
+        <v>9444.444444444445</v>
+      </c>
+      <c r="BQ174" t="inlineStr"/>
+      <c r="BR174" t="inlineStr"/>
+      <c r="BS174" t="inlineStr"/>
+      <c r="BT174" t="inlineStr"/>
+      <c r="BU174" t="n">
+        <v>24.70588235294118</v>
+      </c>
+      <c r="BV174" t="n">
+        <v>178.3529411764706</v>
+      </c>
+      <c r="BW174" t="n">
+        <v>69</v>
+      </c>
+      <c r="BX174" t="n">
+        <v>9176.470588235294</v>
+      </c>
+      <c r="BY174" t="n">
+        <v>25</v>
+      </c>
+      <c r="BZ174" t="n">
+        <v>182.1666666666667</v>
+      </c>
+      <c r="CA174" t="n">
+        <v>64.83333333333333</v>
+      </c>
+      <c r="CB174" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CC174" t="inlineStr"/>
+      <c r="CD174" t="inlineStr"/>
+      <c r="CE174" t="inlineStr"/>
+      <c r="CF174" t="inlineStr"/>
+      <c r="CG174" t="inlineStr"/>
+      <c r="CH174" t="inlineStr"/>
+      <c r="CI174" t="inlineStr"/>
+      <c r="CJ174" t="inlineStr"/>
+      <c r="CK174" t="inlineStr"/>
+      <c r="CL174" t="inlineStr"/>
+      <c r="CM174" t="inlineStr"/>
+      <c r="CN174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>baxbTM5C</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="n">
+        <v>45559.64583333334</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paradis g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade charlety
+  paris </t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F175" t="n">
+        <v>6448</v>
+      </c>
+      <c r="G175" t="n">
+        <v>2</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="n">
+        <v>54</v>
+      </c>
+      <c r="N175" t="n">
+        <v>46</v>
+      </c>
+      <c r="O175" t="n">
+        <v>10</v>
+      </c>
+      <c r="P175" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>8</v>
+      </c>
+      <c r="R175" t="n">
+        <v>5</v>
+      </c>
+      <c r="S175" t="n">
+        <v>0</v>
+      </c>
+      <c r="T175" t="n">
+        <v>3</v>
+      </c>
+      <c r="U175" t="n">
+        <v>2</v>
+      </c>
+      <c r="V175" t="n">
+        <v>1</v>
+      </c>
+      <c r="W175" t="inlineStr"/>
+      <c r="X175" t="inlineStr"/>
+      <c r="Y175" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC175" t="inlineStr"/>
+      <c r="AD175" t="inlineStr"/>
+      <c r="AE175" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>119</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>114</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="AQ175" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU175" t="inlineStr"/>
+      <c r="AV175" t="inlineStr"/>
+      <c r="AW175" t="n">
+        <v>550</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>473</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>475</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>407</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE175" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF175" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG175" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH175" t="n">
+        <v>17</v>
+      </c>
+      <c r="BI175" t="inlineStr"/>
+      <c r="BJ175" t="inlineStr"/>
+      <c r="BK175" t="inlineStr"/>
+      <c r="BL175" t="inlineStr"/>
+      <c r="BM175" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="BN175" t="n">
+        <v>176.7</v>
+      </c>
+      <c r="BO175" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="BP175" t="n">
+        <v>4700</v>
+      </c>
+      <c r="BQ175" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="BR175" t="n">
+        <v>180.375</v>
+      </c>
+      <c r="BS175" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="BT175" t="n">
+        <v>2375</v>
+      </c>
+      <c r="BU175" t="n">
+        <v>27.07142857142857</v>
+      </c>
+      <c r="BV175" t="n">
+        <v>179.5714285714286</v>
+      </c>
+      <c r="BW175" t="n">
+        <v>67.21428571428571</v>
+      </c>
+      <c r="BX175" t="n">
+        <v>4357.142857142857</v>
+      </c>
+      <c r="BY175" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="BZ175" t="n">
+        <v>179.4285714285714</v>
+      </c>
+      <c r="CA175" t="n">
+        <v>63.57142857142857</v>
+      </c>
+      <c r="CB175" t="n">
+        <v>1523.809523809524</v>
+      </c>
+      <c r="CC175" t="inlineStr"/>
+      <c r="CD175" t="inlineStr"/>
+      <c r="CE175" t="inlineStr"/>
+      <c r="CF175" t="inlineStr"/>
+      <c r="CG175" t="inlineStr"/>
+      <c r="CH175" t="inlineStr"/>
+      <c r="CI175" t="inlineStr"/>
+      <c r="CJ175" t="inlineStr"/>
+      <c r="CK175" t="inlineStr"/>
+      <c r="CL175" t="inlineStr"/>
+      <c r="CM175" t="inlineStr"/>
+      <c r="CN175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>fRV6R0zP</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="n">
+        <v>45559.64583333334</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petit a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nouste camp
+  pau </t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>4031</v>
+      </c>
+      <c r="F176" t="n">
+        <v>3054</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="n">
+        <v>55</v>
+      </c>
+      <c r="N176" t="n">
+        <v>45</v>
+      </c>
+      <c r="O176" t="n">
+        <v>19</v>
+      </c>
+      <c r="P176" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>7</v>
+      </c>
+      <c r="R176" t="n">
+        <v>2</v>
+      </c>
+      <c r="S176" t="n">
+        <v>5</v>
+      </c>
+      <c r="T176" t="n">
+        <v>2</v>
+      </c>
+      <c r="U176" t="n">
+        <v>7</v>
+      </c>
+      <c r="V176" t="n">
+        <v>2</v>
+      </c>
+      <c r="W176" t="inlineStr"/>
+      <c r="X176" t="inlineStr"/>
+      <c r="Y176" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC176" t="inlineStr"/>
+      <c r="AD176" t="inlineStr"/>
+      <c r="AE176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>105</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>57</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="AQ176" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR176" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT176" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>470</v>
+      </c>
+      <c r="AX176" t="n">
+        <v>425</v>
+      </c>
+      <c r="AY176" t="n">
+        <v>413</v>
+      </c>
+      <c r="AZ176" t="n">
+        <v>350</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB176" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>31</v>
+      </c>
+      <c r="BE176" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG176" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH176" t="n">
+        <v>13</v>
+      </c>
+      <c r="BI176" t="inlineStr"/>
+      <c r="BJ176" t="inlineStr"/>
+      <c r="BK176" t="inlineStr"/>
+      <c r="BL176" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="BM176" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="BN176" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="BO176" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="BP176" t="inlineStr"/>
+      <c r="BQ176" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BR176" t="n">
+        <v>179.125</v>
+      </c>
+      <c r="BS176" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="BT176" t="n">
+        <v>15250</v>
+      </c>
+      <c r="BU176" t="n">
+        <v>27.93333333333333</v>
+      </c>
+      <c r="BV176" t="n">
+        <v>182.1333333333333</v>
+      </c>
+      <c r="BW176" t="n">
+        <v>65.26666666666667</v>
+      </c>
+      <c r="BX176" t="inlineStr"/>
+      <c r="BY176" t="n">
+        <v>22.23076923076923</v>
+      </c>
+      <c r="BZ176" t="n">
+        <v>178</v>
+      </c>
+      <c r="CA176" t="n">
+        <v>69</v>
+      </c>
+      <c r="CB176" t="n">
+        <v>7769.23076923077</v>
+      </c>
+      <c r="CC176" t="inlineStr"/>
+      <c r="CD176" t="inlineStr"/>
+      <c r="CE176" t="inlineStr"/>
+      <c r="CF176" t="inlineStr"/>
+      <c r="CG176" t="inlineStr"/>
+      <c r="CH176" t="inlineStr"/>
+      <c r="CI176" t="inlineStr"/>
+      <c r="CJ176" t="inlineStr"/>
+      <c r="CK176" t="inlineStr"/>
+      <c r="CL176" t="inlineStr"/>
+      <c r="CM176" t="inlineStr"/>
+      <c r="CN176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>KS5ut0kI</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="n">
+        <v>45559.64583333334</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leleu m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade paul lignon
+  rodez </t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>5955</v>
+      </c>
+      <c r="F177" t="n">
+        <v>4017</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" t="n">
+        <v>3</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="n">
+        <v>46</v>
+      </c>
+      <c r="N177" t="n">
+        <v>54</v>
+      </c>
+      <c r="O177" t="n">
+        <v>14</v>
+      </c>
+      <c r="P177" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>2</v>
+      </c>
+      <c r="R177" t="n">
+        <v>6</v>
+      </c>
+      <c r="S177" t="n">
+        <v>8</v>
+      </c>
+      <c r="T177" t="n">
+        <v>0</v>
+      </c>
+      <c r="U177" t="n">
+        <v>4</v>
+      </c>
+      <c r="V177" t="n">
+        <v>4</v>
+      </c>
+      <c r="W177" t="inlineStr"/>
+      <c r="X177" t="inlineStr"/>
+      <c r="Y177" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC177" t="inlineStr"/>
+      <c r="AD177" t="inlineStr"/>
+      <c r="AE177" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>135</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>112</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>77</v>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AQ177" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR177" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU177" t="inlineStr"/>
+      <c r="AV177" t="inlineStr"/>
+      <c r="AW177" t="n">
+        <v>361</v>
+      </c>
+      <c r="AX177" t="n">
+        <v>409</v>
+      </c>
+      <c r="AY177" t="n">
+        <v>264</v>
+      </c>
+      <c r="AZ177" t="n">
+        <v>298</v>
+      </c>
+      <c r="BA177" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB177" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC177" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>31</v>
+      </c>
+      <c r="BE177" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF177" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG177" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH177" t="n">
+        <v>17</v>
+      </c>
+      <c r="BI177" t="inlineStr"/>
+      <c r="BJ177" t="inlineStr"/>
+      <c r="BK177" t="inlineStr"/>
+      <c r="BL177" t="inlineStr"/>
+      <c r="BM177" t="inlineStr"/>
+      <c r="BN177" t="inlineStr"/>
+      <c r="BO177" t="inlineStr"/>
+      <c r="BP177" t="inlineStr"/>
+      <c r="BQ177" t="inlineStr"/>
+      <c r="BR177" t="inlineStr"/>
+      <c r="BS177" t="inlineStr"/>
+      <c r="BT177" t="inlineStr"/>
+      <c r="BU177" t="n">
+        <v>21.46153846153846</v>
+      </c>
+      <c r="BV177" t="n">
+        <v>180.7692307692308</v>
+      </c>
+      <c r="BW177" t="n">
+        <v>62.23076923076923</v>
+      </c>
+      <c r="BX177" t="inlineStr"/>
+      <c r="BY177" t="n">
+        <v>30.84615384615385</v>
+      </c>
+      <c r="BZ177" t="n">
+        <v>182</v>
+      </c>
+      <c r="CA177" t="n">
+        <v>67.30769230769231</v>
+      </c>
+      <c r="CB177" t="n">
+        <v>2538.461538461539</v>
+      </c>
+      <c r="CC177" t="inlineStr"/>
+      <c r="CD177" t="inlineStr"/>
+      <c r="CE177" t="inlineStr"/>
+      <c r="CF177" t="inlineStr"/>
+      <c r="CG177" t="inlineStr"/>
+      <c r="CH177" t="inlineStr"/>
+      <c r="CI177" t="inlineStr"/>
+      <c r="CJ177" t="inlineStr"/>
+      <c r="CK177" t="inlineStr"/>
+      <c r="CL177" t="inlineStr"/>
+      <c r="CM177" t="inlineStr"/>
+      <c r="CN177" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN177"/>
+  <dimension ref="A1:CN190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46349,6 +46349,2944 @@
       <c r="CM177" t="inlineStr"/>
       <c r="CN177" t="inlineStr"/>
     </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>lxyu7Met</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="n">
+        <v>45563.66666666666</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="n">
+        <v>2</v>
+      </c>
+      <c r="H178" t="n">
+        <v>1</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="K178" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M178" t="n">
+        <v>65</v>
+      </c>
+      <c r="N178" t="n">
+        <v>35</v>
+      </c>
+      <c r="O178" t="n">
+        <v>21</v>
+      </c>
+      <c r="P178" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>7</v>
+      </c>
+      <c r="R178" t="n">
+        <v>4</v>
+      </c>
+      <c r="S178" t="n">
+        <v>10</v>
+      </c>
+      <c r="T178" t="n">
+        <v>3</v>
+      </c>
+      <c r="U178" t="n">
+        <v>4</v>
+      </c>
+      <c r="V178" t="n">
+        <v>2</v>
+      </c>
+      <c r="W178" t="n">
+        <v>20</v>
+      </c>
+      <c r="X178" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK178" t="inlineStr"/>
+      <c r="AL178" t="inlineStr"/>
+      <c r="AM178" t="inlineStr"/>
+      <c r="AN178" t="inlineStr"/>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="AQ178" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW178" t="inlineStr"/>
+      <c r="AX178" t="inlineStr"/>
+      <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr"/>
+      <c r="BA178" t="inlineStr"/>
+      <c r="BB178" t="inlineStr"/>
+      <c r="BC178" t="inlineStr"/>
+      <c r="BD178" t="inlineStr"/>
+      <c r="BE178" t="inlineStr"/>
+      <c r="BF178" t="inlineStr"/>
+      <c r="BG178" t="inlineStr"/>
+      <c r="BH178" t="inlineStr"/>
+      <c r="BI178" t="inlineStr"/>
+      <c r="BJ178" t="inlineStr"/>
+      <c r="BK178" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="BL178" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="BM178" t="n">
+        <v>23.36363636363636</v>
+      </c>
+      <c r="BN178" t="n">
+        <v>183.3636363636364</v>
+      </c>
+      <c r="BO178" t="n">
+        <v>76.90909090909091</v>
+      </c>
+      <c r="BP178" t="n">
+        <v>43272.72727272727</v>
+      </c>
+      <c r="BQ178" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="BR178" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="BS178" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="BT178" t="n">
+        <v>14400</v>
+      </c>
+      <c r="BU178" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="BV178" t="n">
+        <v>179.1666666666667</v>
+      </c>
+      <c r="BW178" t="n">
+        <v>72</v>
+      </c>
+      <c r="BX178" t="n">
+        <v>21750</v>
+      </c>
+      <c r="BY178" t="n">
+        <v>26.64285714285714</v>
+      </c>
+      <c r="BZ178" t="n">
+        <v>181.7142857142857</v>
+      </c>
+      <c r="CA178" t="n">
+        <v>71.57142857142857</v>
+      </c>
+      <c r="CB178" t="n">
+        <v>15071.42857142857</v>
+      </c>
+      <c r="CC178" t="inlineStr"/>
+      <c r="CD178" t="inlineStr"/>
+      <c r="CE178" t="inlineStr"/>
+      <c r="CF178" t="inlineStr"/>
+      <c r="CG178" t="inlineStr"/>
+      <c r="CH178" t="inlineStr"/>
+      <c r="CI178" t="inlineStr"/>
+      <c r="CJ178" t="inlineStr"/>
+      <c r="CK178" t="inlineStr"/>
+      <c r="CL178" t="inlineStr"/>
+      <c r="CM178" t="inlineStr"/>
+      <c r="CN178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="n">
+        <v>45563.58333333334</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dechepy b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>3</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="K179" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L179" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="M179" t="n">
+        <v>38</v>
+      </c>
+      <c r="N179" t="n">
+        <v>62</v>
+      </c>
+      <c r="O179" t="n">
+        <v>7</v>
+      </c>
+      <c r="P179" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>4</v>
+      </c>
+      <c r="R179" t="n">
+        <v>10</v>
+      </c>
+      <c r="S179" t="n">
+        <v>2</v>
+      </c>
+      <c r="T179" t="n">
+        <v>5</v>
+      </c>
+      <c r="U179" t="n">
+        <v>1</v>
+      </c>
+      <c r="V179" t="n">
+        <v>3</v>
+      </c>
+      <c r="W179" t="n">
+        <v>10</v>
+      </c>
+      <c r="X179" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK179" t="inlineStr"/>
+      <c r="AL179" t="inlineStr"/>
+      <c r="AM179" t="inlineStr"/>
+      <c r="AN179" t="inlineStr"/>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="AP179" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AQ179" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR179" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU179" t="inlineStr"/>
+      <c r="AV179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr"/>
+      <c r="AX179" t="inlineStr"/>
+      <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr"/>
+      <c r="BA179" t="inlineStr"/>
+      <c r="BB179" t="inlineStr"/>
+      <c r="BC179" t="inlineStr"/>
+      <c r="BD179" t="inlineStr"/>
+      <c r="BE179" t="inlineStr"/>
+      <c r="BF179" t="inlineStr"/>
+      <c r="BG179" t="inlineStr"/>
+      <c r="BH179" t="inlineStr"/>
+      <c r="BI179" t="inlineStr"/>
+      <c r="BJ179" t="inlineStr"/>
+      <c r="BK179" t="inlineStr"/>
+      <c r="BL179" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="BM179" t="n">
+        <v>24.45454545454545</v>
+      </c>
+      <c r="BN179" t="n">
+        <v>186.1818181818182</v>
+      </c>
+      <c r="BO179" t="n">
+        <v>71</v>
+      </c>
+      <c r="BP179" t="n">
+        <v>10454.54545454545</v>
+      </c>
+      <c r="BQ179" t="n">
+        <v>24</v>
+      </c>
+      <c r="BR179" t="n">
+        <v>181</v>
+      </c>
+      <c r="BS179" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="BT179" t="n">
+        <v>26600</v>
+      </c>
+      <c r="BU179" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="BV179" t="n">
+        <v>182.05</v>
+      </c>
+      <c r="BW179" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="BX179" t="n">
+        <v>9350</v>
+      </c>
+      <c r="BY179" t="n">
+        <v>26.31578947368421</v>
+      </c>
+      <c r="BZ179" t="n">
+        <v>181.4736842105263</v>
+      </c>
+      <c r="CA179" t="n">
+        <v>72.94736842105263</v>
+      </c>
+      <c r="CB179" t="n">
+        <v>23578.94736842105</v>
+      </c>
+      <c r="CC179" t="inlineStr"/>
+      <c r="CD179" t="inlineStr"/>
+      <c r="CE179" t="inlineStr"/>
+      <c r="CF179" t="inlineStr"/>
+      <c r="CG179" t="inlineStr"/>
+      <c r="CH179" t="inlineStr"/>
+      <c r="CI179" t="inlineStr"/>
+      <c r="CJ179" t="inlineStr"/>
+      <c r="CK179" t="inlineStr"/>
+      <c r="CL179" t="inlineStr"/>
+      <c r="CM179" t="inlineStr"/>
+      <c r="CN179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="n">
+        <v>45563.5</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F180" t="n">
+        <v>37301</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="K180" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M180" t="n">
+        <v>55</v>
+      </c>
+      <c r="N180" t="n">
+        <v>45</v>
+      </c>
+      <c r="O180" t="n">
+        <v>22</v>
+      </c>
+      <c r="P180" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>7</v>
+      </c>
+      <c r="R180" t="n">
+        <v>4</v>
+      </c>
+      <c r="S180" t="n">
+        <v>10</v>
+      </c>
+      <c r="T180" t="n">
+        <v>6</v>
+      </c>
+      <c r="U180" t="n">
+        <v>5</v>
+      </c>
+      <c r="V180" t="n">
+        <v>5</v>
+      </c>
+      <c r="W180" t="n">
+        <v>9</v>
+      </c>
+      <c r="X180" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK180" t="inlineStr"/>
+      <c r="AL180" t="inlineStr"/>
+      <c r="AM180" t="inlineStr"/>
+      <c r="AN180" t="inlineStr"/>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AP180" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AQ180" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW180" t="inlineStr"/>
+      <c r="AX180" t="inlineStr"/>
+      <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr"/>
+      <c r="BA180" t="inlineStr"/>
+      <c r="BB180" t="inlineStr"/>
+      <c r="BC180" t="inlineStr"/>
+      <c r="BD180" t="inlineStr"/>
+      <c r="BE180" t="inlineStr"/>
+      <c r="BF180" t="inlineStr"/>
+      <c r="BG180" t="inlineStr"/>
+      <c r="BH180" t="inlineStr"/>
+      <c r="BI180" t="inlineStr"/>
+      <c r="BJ180" t="inlineStr"/>
+      <c r="BK180" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="BL180" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="BM180" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="BN180" t="n">
+        <v>180.6363636363636</v>
+      </c>
+      <c r="BO180" t="n">
+        <v>76.54545454545455</v>
+      </c>
+      <c r="BP180" t="n">
+        <v>33454.54545454546</v>
+      </c>
+      <c r="BQ180" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="BR180" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="BS180" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="BT180" t="n">
+        <v>21700</v>
+      </c>
+      <c r="BU180" t="n">
+        <v>25.20833333333333</v>
+      </c>
+      <c r="BV180" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="BW180" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BX180" t="n">
+        <v>31000</v>
+      </c>
+      <c r="BY180" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="BZ180" t="n">
+        <v>178.45</v>
+      </c>
+      <c r="CA180" t="n">
+        <v>73.15000000000001</v>
+      </c>
+      <c r="CB180" t="n">
+        <v>22600</v>
+      </c>
+      <c r="CC180" t="inlineStr"/>
+      <c r="CD180" t="inlineStr"/>
+      <c r="CE180" t="inlineStr"/>
+      <c r="CF180" t="inlineStr"/>
+      <c r="CG180" t="inlineStr"/>
+      <c r="CH180" t="inlineStr"/>
+      <c r="CI180" t="inlineStr"/>
+      <c r="CJ180" t="inlineStr"/>
+      <c r="CK180" t="inlineStr"/>
+      <c r="CL180" t="inlineStr"/>
+      <c r="CM180" t="inlineStr"/>
+      <c r="CN180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="n">
+        <v>45562.66666666666</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F181" t="n">
+        <v>47000</v>
+      </c>
+      <c r="G181" t="n">
+        <v>3</v>
+      </c>
+      <c r="H181" t="n">
+        <v>1</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="K181" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="L181" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M181" t="n">
+        <v>62</v>
+      </c>
+      <c r="N181" t="n">
+        <v>38</v>
+      </c>
+      <c r="O181" t="n">
+        <v>24</v>
+      </c>
+      <c r="P181" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>8</v>
+      </c>
+      <c r="R181" t="n">
+        <v>5</v>
+      </c>
+      <c r="S181" t="n">
+        <v>10</v>
+      </c>
+      <c r="T181" t="n">
+        <v>3</v>
+      </c>
+      <c r="U181" t="n">
+        <v>6</v>
+      </c>
+      <c r="V181" t="n">
+        <v>4</v>
+      </c>
+      <c r="W181" t="n">
+        <v>15</v>
+      </c>
+      <c r="X181" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK181" t="inlineStr"/>
+      <c r="AL181" t="inlineStr"/>
+      <c r="AM181" t="inlineStr"/>
+      <c r="AN181" t="inlineStr"/>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AP181" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AQ181" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU181" t="inlineStr"/>
+      <c r="AV181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr"/>
+      <c r="AX181" t="inlineStr"/>
+      <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr"/>
+      <c r="BA181" t="inlineStr"/>
+      <c r="BB181" t="inlineStr"/>
+      <c r="BC181" t="inlineStr"/>
+      <c r="BD181" t="inlineStr"/>
+      <c r="BE181" t="inlineStr"/>
+      <c r="BF181" t="inlineStr"/>
+      <c r="BG181" t="inlineStr"/>
+      <c r="BH181" t="inlineStr"/>
+      <c r="BI181" t="inlineStr"/>
+      <c r="BJ181" t="inlineStr"/>
+      <c r="BK181" t="inlineStr"/>
+      <c r="BL181" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="BM181" t="n">
+        <v>22.875</v>
+      </c>
+      <c r="BN181" t="n">
+        <v>182.875</v>
+      </c>
+      <c r="BO181" t="n">
+        <v>80.875</v>
+      </c>
+      <c r="BP181" t="n">
+        <v>73125</v>
+      </c>
+      <c r="BQ181" t="n">
+        <v>24.63636363636364</v>
+      </c>
+      <c r="BR181" t="n">
+        <v>180.2727272727273</v>
+      </c>
+      <c r="BS181" t="n">
+        <v>75.72727272727273</v>
+      </c>
+      <c r="BT181" t="n">
+        <v>32818.18181818182</v>
+      </c>
+      <c r="BU181" t="n">
+        <v>23.64285714285714</v>
+      </c>
+      <c r="BV181" t="n">
+        <v>185.3571428571429</v>
+      </c>
+      <c r="BW181" t="n">
+        <v>77.71428571428571</v>
+      </c>
+      <c r="BX181" t="n">
+        <v>74214.28571428571</v>
+      </c>
+      <c r="BY181" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="BZ181" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="CA181" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="CB181" t="n">
+        <v>23100</v>
+      </c>
+      <c r="CC181" t="inlineStr"/>
+      <c r="CD181" t="inlineStr"/>
+      <c r="CE181" t="inlineStr"/>
+      <c r="CF181" t="inlineStr"/>
+      <c r="CG181" t="inlineStr"/>
+      <c r="CH181" t="inlineStr"/>
+      <c r="CI181" t="inlineStr"/>
+      <c r="CJ181" t="inlineStr"/>
+      <c r="CK181" t="inlineStr"/>
+      <c r="CL181" t="inlineStr"/>
+      <c r="CM181" t="inlineStr"/>
+      <c r="CN181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>MRfkjXaJ</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="n">
+        <v>45562.58333333334</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F182" t="n">
+        <v>15381</v>
+      </c>
+      <c r="G182" t="n">
+        <v>3</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="K182" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M182" t="n">
+        <v>38</v>
+      </c>
+      <c r="N182" t="n">
+        <v>62</v>
+      </c>
+      <c r="O182" t="n">
+        <v>15</v>
+      </c>
+      <c r="P182" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>4</v>
+      </c>
+      <c r="R182" t="n">
+        <v>4</v>
+      </c>
+      <c r="S182" t="n">
+        <v>6</v>
+      </c>
+      <c r="T182" t="n">
+        <v>4</v>
+      </c>
+      <c r="U182" t="n">
+        <v>5</v>
+      </c>
+      <c r="V182" t="n">
+        <v>0</v>
+      </c>
+      <c r="W182" t="n">
+        <v>18</v>
+      </c>
+      <c r="X182" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG182" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH182" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK182" t="inlineStr"/>
+      <c r="AL182" t="inlineStr"/>
+      <c r="AM182" t="inlineStr"/>
+      <c r="AN182" t="inlineStr"/>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AQ182" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR182" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU182" t="inlineStr"/>
+      <c r="AV182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr"/>
+      <c r="AX182" t="inlineStr"/>
+      <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr"/>
+      <c r="BA182" t="inlineStr"/>
+      <c r="BB182" t="inlineStr"/>
+      <c r="BC182" t="inlineStr"/>
+      <c r="BD182" t="inlineStr"/>
+      <c r="BE182" t="inlineStr"/>
+      <c r="BF182" t="inlineStr"/>
+      <c r="BG182" t="inlineStr"/>
+      <c r="BH182" t="inlineStr"/>
+      <c r="BI182" t="inlineStr"/>
+      <c r="BJ182" t="inlineStr"/>
+      <c r="BK182" t="inlineStr"/>
+      <c r="BL182" t="inlineStr"/>
+      <c r="BM182" t="n">
+        <v>24</v>
+      </c>
+      <c r="BN182" t="n">
+        <v>183.5454545454545</v>
+      </c>
+      <c r="BO182" t="n">
+        <v>67.81818181818181</v>
+      </c>
+      <c r="BP182" t="inlineStr"/>
+      <c r="BQ182" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="BR182" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="BS182" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="BT182" t="n">
+        <v>20900</v>
+      </c>
+      <c r="BU182" t="n">
+        <v>25.19047619047619</v>
+      </c>
+      <c r="BV182" t="n">
+        <v>179.5714285714286</v>
+      </c>
+      <c r="BW182" t="n">
+        <v>68.76190476190476</v>
+      </c>
+      <c r="BX182" t="inlineStr"/>
+      <c r="BY182" t="n">
+        <v>25.68181818181818</v>
+      </c>
+      <c r="BZ182" t="n">
+        <v>179.6363636363636</v>
+      </c>
+      <c r="CA182" t="n">
+        <v>72.72727272727273</v>
+      </c>
+      <c r="CB182" t="n">
+        <v>16318.18181818182</v>
+      </c>
+      <c r="CC182" t="inlineStr"/>
+      <c r="CD182" t="inlineStr"/>
+      <c r="CE182" t="inlineStr"/>
+      <c r="CF182" t="inlineStr"/>
+      <c r="CG182" t="inlineStr"/>
+      <c r="CH182" t="inlineStr"/>
+      <c r="CI182" t="inlineStr"/>
+      <c r="CJ182" t="inlineStr"/>
+      <c r="CK182" t="inlineStr"/>
+      <c r="CL182" t="inlineStr"/>
+      <c r="CM182" t="inlineStr"/>
+      <c r="CN182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>jFY0ryaD</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="n">
+        <v>45563.625</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valnet a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l aube
+  troyes </t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>20420</v>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="n">
+        <v>2</v>
+      </c>
+      <c r="H183" t="n">
+        <v>1</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="n">
+        <v>21</v>
+      </c>
+      <c r="N183" t="n">
+        <v>79</v>
+      </c>
+      <c r="O183" t="n">
+        <v>6</v>
+      </c>
+      <c r="P183" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>5</v>
+      </c>
+      <c r="R183" t="n">
+        <v>2</v>
+      </c>
+      <c r="S183" t="n">
+        <v>1</v>
+      </c>
+      <c r="T183" t="n">
+        <v>7</v>
+      </c>
+      <c r="U183" t="n">
+        <v>0</v>
+      </c>
+      <c r="V183" t="n">
+        <v>3</v>
+      </c>
+      <c r="W183" t="inlineStr"/>
+      <c r="X183" t="inlineStr"/>
+      <c r="Y183" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC183" t="inlineStr"/>
+      <c r="AD183" t="inlineStr"/>
+      <c r="AE183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH183" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI183" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK183" t="inlineStr"/>
+      <c r="AL183" t="inlineStr"/>
+      <c r="AM183" t="inlineStr"/>
+      <c r="AN183" t="inlineStr"/>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="AP183" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AQ183" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR183" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU183" t="inlineStr"/>
+      <c r="AV183" t="inlineStr"/>
+      <c r="AW183" t="n">
+        <v>224</v>
+      </c>
+      <c r="AX183" t="n">
+        <v>807</v>
+      </c>
+      <c r="AY183" t="n">
+        <v>138</v>
+      </c>
+      <c r="AZ183" t="n">
+        <v>734</v>
+      </c>
+      <c r="BA183" t="inlineStr"/>
+      <c r="BB183" t="inlineStr"/>
+      <c r="BC183" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD183" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF183" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG183" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH183" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI183" t="inlineStr"/>
+      <c r="BJ183" t="inlineStr"/>
+      <c r="BK183" t="inlineStr"/>
+      <c r="BL183" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="BM183" t="n">
+        <v>26.125</v>
+      </c>
+      <c r="BN183" t="n">
+        <v>178.375</v>
+      </c>
+      <c r="BO183" t="n">
+        <v>66.125</v>
+      </c>
+      <c r="BP183" t="inlineStr"/>
+      <c r="BQ183" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="BR183" t="n">
+        <v>176.9</v>
+      </c>
+      <c r="BS183" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="BT183" t="n">
+        <v>9600</v>
+      </c>
+      <c r="BU183" t="n">
+        <v>24.94444444444444</v>
+      </c>
+      <c r="BV183" t="n">
+        <v>178.4444444444445</v>
+      </c>
+      <c r="BW183" t="n">
+        <v>67.44444444444444</v>
+      </c>
+      <c r="BX183" t="inlineStr"/>
+      <c r="BY183" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="BZ183" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="CA183" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="CB183" t="n">
+        <v>7900</v>
+      </c>
+      <c r="CC183" t="inlineStr"/>
+      <c r="CD183" t="inlineStr"/>
+      <c r="CE183" t="inlineStr"/>
+      <c r="CF183" t="inlineStr"/>
+      <c r="CG183" t="inlineStr"/>
+      <c r="CH183" t="inlineStr"/>
+      <c r="CI183" t="inlineStr"/>
+      <c r="CJ183" t="inlineStr"/>
+      <c r="CK183" t="inlineStr"/>
+      <c r="CL183" t="inlineStr"/>
+      <c r="CM183" t="inlineStr"/>
+      <c r="CN183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>8SrDxn0N</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="n">
+        <v>45563.375</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lesage m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bauer
+  paris   saint ouen </t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" t="n">
+        <v>3</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="n">
+        <v>51</v>
+      </c>
+      <c r="N184" t="n">
+        <v>49</v>
+      </c>
+      <c r="O184" t="n">
+        <v>12</v>
+      </c>
+      <c r="P184" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>4</v>
+      </c>
+      <c r="R184" t="n">
+        <v>6</v>
+      </c>
+      <c r="S184" t="n">
+        <v>7</v>
+      </c>
+      <c r="T184" t="n">
+        <v>3</v>
+      </c>
+      <c r="U184" t="n">
+        <v>1</v>
+      </c>
+      <c r="V184" t="n">
+        <v>2</v>
+      </c>
+      <c r="W184" t="inlineStr"/>
+      <c r="X184" t="inlineStr"/>
+      <c r="Y184" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z184" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC184" t="inlineStr"/>
+      <c r="AD184" t="inlineStr"/>
+      <c r="AE184" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF184" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG184" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH184" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI184" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK184" t="inlineStr"/>
+      <c r="AL184" t="inlineStr"/>
+      <c r="AM184" t="inlineStr"/>
+      <c r="AN184" t="inlineStr"/>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AP184" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="AQ184" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR184" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU184" t="inlineStr"/>
+      <c r="AV184" t="inlineStr"/>
+      <c r="AW184" t="n">
+        <v>461</v>
+      </c>
+      <c r="AX184" t="n">
+        <v>503</v>
+      </c>
+      <c r="AY184" t="n">
+        <v>402</v>
+      </c>
+      <c r="AZ184" t="n">
+        <v>432</v>
+      </c>
+      <c r="BA184" t="inlineStr"/>
+      <c r="BB184" t="inlineStr"/>
+      <c r="BC184" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE184" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF184" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG184" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH184" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI184" t="inlineStr"/>
+      <c r="BJ184" t="inlineStr"/>
+      <c r="BK184" t="inlineStr"/>
+      <c r="BL184" t="inlineStr"/>
+      <c r="BM184" t="inlineStr"/>
+      <c r="BN184" t="inlineStr"/>
+      <c r="BO184" t="inlineStr"/>
+      <c r="BP184" t="inlineStr"/>
+      <c r="BQ184" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="BR184" t="n">
+        <v>178.1111111111111</v>
+      </c>
+      <c r="BS184" t="n">
+        <v>68.55555555555556</v>
+      </c>
+      <c r="BT184" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BU184" t="inlineStr"/>
+      <c r="BV184" t="inlineStr"/>
+      <c r="BW184" t="inlineStr"/>
+      <c r="BX184" t="inlineStr"/>
+      <c r="BY184" t="n">
+        <v>29.07142857142857</v>
+      </c>
+      <c r="BZ184" t="n">
+        <v>178.9285714285714</v>
+      </c>
+      <c r="CA184" t="n">
+        <v>67.57142857142857</v>
+      </c>
+      <c r="CB184" t="n">
+        <v>3642.857142857143</v>
+      </c>
+      <c r="CC184" t="inlineStr"/>
+      <c r="CD184" t="inlineStr"/>
+      <c r="CE184" t="inlineStr"/>
+      <c r="CF184" t="inlineStr"/>
+      <c r="CG184" t="inlineStr"/>
+      <c r="CH184" t="inlineStr"/>
+      <c r="CI184" t="inlineStr"/>
+      <c r="CJ184" t="inlineStr"/>
+      <c r="CK184" t="inlineStr"/>
+      <c r="CL184" t="inlineStr"/>
+      <c r="CM184" t="inlineStr"/>
+      <c r="CN184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>8nRerjWo</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="n">
+        <v>45562.625</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapapria r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>12097</v>
+      </c>
+      <c r="F185" t="n">
+        <v>4931</v>
+      </c>
+      <c r="G185" t="n">
+        <v>2</v>
+      </c>
+      <c r="H185" t="n">
+        <v>1</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="n">
+        <v>62</v>
+      </c>
+      <c r="N185" t="n">
+        <v>38</v>
+      </c>
+      <c r="O185" t="n">
+        <v>20</v>
+      </c>
+      <c r="P185" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>11</v>
+      </c>
+      <c r="R185" t="n">
+        <v>3</v>
+      </c>
+      <c r="S185" t="n">
+        <v>3</v>
+      </c>
+      <c r="T185" t="n">
+        <v>6</v>
+      </c>
+      <c r="U185" t="n">
+        <v>6</v>
+      </c>
+      <c r="V185" t="n">
+        <v>3</v>
+      </c>
+      <c r="W185" t="inlineStr"/>
+      <c r="X185" t="inlineStr"/>
+      <c r="Y185" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z185" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC185" t="inlineStr"/>
+      <c r="AD185" t="inlineStr"/>
+      <c r="AE185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF185" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG185" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH185" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ185" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK185" t="inlineStr"/>
+      <c r="AL185" t="inlineStr"/>
+      <c r="AM185" t="inlineStr"/>
+      <c r="AN185" t="inlineStr"/>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AP185" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AQ185" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR185" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT185" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW185" t="n">
+        <v>503</v>
+      </c>
+      <c r="AX185" t="n">
+        <v>307</v>
+      </c>
+      <c r="AY185" t="n">
+        <v>407</v>
+      </c>
+      <c r="AZ185" t="n">
+        <v>224</v>
+      </c>
+      <c r="BA185" t="inlineStr"/>
+      <c r="BB185" t="inlineStr"/>
+      <c r="BC185" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD185" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF185" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG185" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH185" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI185" t="inlineStr"/>
+      <c r="BJ185" t="inlineStr"/>
+      <c r="BK185" t="inlineStr"/>
+      <c r="BL185" t="inlineStr"/>
+      <c r="BM185" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="BN185" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="BO185" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="BP185" t="inlineStr"/>
+      <c r="BQ185" t="inlineStr"/>
+      <c r="BR185" t="inlineStr"/>
+      <c r="BS185" t="inlineStr"/>
+      <c r="BT185" t="inlineStr"/>
+      <c r="BU185" t="n">
+        <v>24.16666666666667</v>
+      </c>
+      <c r="BV185" t="n">
+        <v>181.2222222222222</v>
+      </c>
+      <c r="BW185" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="BX185" t="inlineStr"/>
+      <c r="BY185" t="n">
+        <v>21.76923076923077</v>
+      </c>
+      <c r="BZ185" t="n">
+        <v>178.9230769230769</v>
+      </c>
+      <c r="CA185" t="n">
+        <v>62.76923076923077</v>
+      </c>
+      <c r="CB185" t="inlineStr"/>
+      <c r="CC185" t="inlineStr"/>
+      <c r="CD185" t="inlineStr"/>
+      <c r="CE185" t="inlineStr"/>
+      <c r="CF185" t="inlineStr"/>
+      <c r="CG185" t="inlineStr"/>
+      <c r="CH185" t="inlineStr"/>
+      <c r="CI185" t="inlineStr"/>
+      <c r="CJ185" t="inlineStr"/>
+      <c r="CK185" t="inlineStr"/>
+      <c r="CL185" t="inlineStr"/>
+      <c r="CM185" t="inlineStr"/>
+      <c r="CN185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>t0P3tU0b</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="n">
+        <v>45562.625</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bouille t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade armand cesari
+  bastia </t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>16048</v>
+      </c>
+      <c r="F186" t="n">
+        <v>10578</v>
+      </c>
+      <c r="G186" t="n">
+        <v>2</v>
+      </c>
+      <c r="H186" t="n">
+        <v>2</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="n">
+        <v>53</v>
+      </c>
+      <c r="N186" t="n">
+        <v>47</v>
+      </c>
+      <c r="O186" t="n">
+        <v>20</v>
+      </c>
+      <c r="P186" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>10</v>
+      </c>
+      <c r="R186" t="n">
+        <v>2</v>
+      </c>
+      <c r="S186" t="n">
+        <v>8</v>
+      </c>
+      <c r="T186" t="n">
+        <v>4</v>
+      </c>
+      <c r="U186" t="n">
+        <v>2</v>
+      </c>
+      <c r="V186" t="n">
+        <v>3</v>
+      </c>
+      <c r="W186" t="inlineStr"/>
+      <c r="X186" t="inlineStr"/>
+      <c r="Y186" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z186" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA186" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB186" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC186" t="inlineStr"/>
+      <c r="AD186" t="inlineStr"/>
+      <c r="AE186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF186" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG186" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH186" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ186" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK186" t="inlineStr"/>
+      <c r="AL186" t="inlineStr"/>
+      <c r="AM186" t="inlineStr"/>
+      <c r="AN186" t="inlineStr"/>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AP186" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="AQ186" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR186" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU186" t="inlineStr"/>
+      <c r="AV186" t="inlineStr"/>
+      <c r="AW186" t="n">
+        <v>418</v>
+      </c>
+      <c r="AX186" t="n">
+        <v>332</v>
+      </c>
+      <c r="AY186" t="n">
+        <v>277</v>
+      </c>
+      <c r="AZ186" t="n">
+        <v>192</v>
+      </c>
+      <c r="BA186" t="inlineStr"/>
+      <c r="BB186" t="inlineStr"/>
+      <c r="BC186" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD186" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE186" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF186" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG186" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH186" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI186" t="inlineStr"/>
+      <c r="BJ186" t="inlineStr"/>
+      <c r="BK186" t="inlineStr"/>
+      <c r="BL186" t="inlineStr"/>
+      <c r="BM186" t="inlineStr"/>
+      <c r="BN186" t="inlineStr"/>
+      <c r="BO186" t="inlineStr"/>
+      <c r="BP186" t="inlineStr"/>
+      <c r="BQ186" t="inlineStr"/>
+      <c r="BR186" t="inlineStr"/>
+      <c r="BS186" t="inlineStr"/>
+      <c r="BT186" t="inlineStr"/>
+      <c r="BU186" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="BV186" t="n">
+        <v>180.2777777777778</v>
+      </c>
+      <c r="BW186" t="n">
+        <v>62.38888888888889</v>
+      </c>
+      <c r="BX186" t="inlineStr"/>
+      <c r="BY186" t="n">
+        <v>23.78571428571428</v>
+      </c>
+      <c r="BZ186" t="n">
+        <v>183.6428571428571</v>
+      </c>
+      <c r="CA186" t="n">
+        <v>63.07142857142857</v>
+      </c>
+      <c r="CB186" t="inlineStr"/>
+      <c r="CC186" t="inlineStr"/>
+      <c r="CD186" t="inlineStr"/>
+      <c r="CE186" t="inlineStr"/>
+      <c r="CF186" t="inlineStr"/>
+      <c r="CG186" t="inlineStr"/>
+      <c r="CH186" t="inlineStr"/>
+      <c r="CI186" t="inlineStr"/>
+      <c r="CJ186" t="inlineStr"/>
+      <c r="CK186" t="inlineStr"/>
+      <c r="CL186" t="inlineStr"/>
+      <c r="CM186" t="inlineStr"/>
+      <c r="CN186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>Sh9mvvKU</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="n">
+        <v>45562.625</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gaillouste p 
+  fra </t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>20068</v>
+      </c>
+      <c r="F187" t="n">
+        <v>4176</v>
+      </c>
+      <c r="G187" t="n">
+        <v>3</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="n">
+        <v>42</v>
+      </c>
+      <c r="N187" t="n">
+        <v>58</v>
+      </c>
+      <c r="O187" t="n">
+        <v>10</v>
+      </c>
+      <c r="P187" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>5</v>
+      </c>
+      <c r="R187" t="n">
+        <v>3</v>
+      </c>
+      <c r="S187" t="n">
+        <v>3</v>
+      </c>
+      <c r="T187" t="n">
+        <v>4</v>
+      </c>
+      <c r="U187" t="n">
+        <v>2</v>
+      </c>
+      <c r="V187" t="n">
+        <v>0</v>
+      </c>
+      <c r="W187" t="inlineStr"/>
+      <c r="X187" t="inlineStr"/>
+      <c r="Y187" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z187" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA187" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC187" t="inlineStr"/>
+      <c r="AD187" t="inlineStr"/>
+      <c r="AE187" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF187" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG187" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH187" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK187" t="inlineStr"/>
+      <c r="AL187" t="inlineStr"/>
+      <c r="AM187" t="inlineStr"/>
+      <c r="AN187" t="inlineStr"/>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AP187" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="AQ187" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR187" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW187" t="n">
+        <v>402</v>
+      </c>
+      <c r="AX187" t="n">
+        <v>533</v>
+      </c>
+      <c r="AY187" t="n">
+        <v>310</v>
+      </c>
+      <c r="AZ187" t="n">
+        <v>431</v>
+      </c>
+      <c r="BA187" t="inlineStr"/>
+      <c r="BB187" t="inlineStr"/>
+      <c r="BC187" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD187" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE187" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF187" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG187" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH187" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI187" t="inlineStr"/>
+      <c r="BJ187" t="inlineStr"/>
+      <c r="BK187" t="inlineStr"/>
+      <c r="BL187" t="inlineStr"/>
+      <c r="BM187" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="BN187" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="BO187" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="BP187" t="inlineStr"/>
+      <c r="BQ187" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="BR187" t="n">
+        <v>181.375</v>
+      </c>
+      <c r="BS187" t="n">
+        <v>66.875</v>
+      </c>
+      <c r="BT187" t="n">
+        <v>5375</v>
+      </c>
+      <c r="BU187" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="BV187" t="n">
+        <v>179.1333333333333</v>
+      </c>
+      <c r="BW187" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="BX187" t="inlineStr"/>
+      <c r="BY187" t="n">
+        <v>22</v>
+      </c>
+      <c r="BZ187" t="n">
+        <v>179.0909090909091</v>
+      </c>
+      <c r="CA187" t="n">
+        <v>63.63636363636363</v>
+      </c>
+      <c r="CB187" t="n">
+        <v>3909.090909090909</v>
+      </c>
+      <c r="CC187" t="inlineStr"/>
+      <c r="CD187" t="inlineStr"/>
+      <c r="CE187" t="inlineStr"/>
+      <c r="CF187" t="inlineStr"/>
+      <c r="CG187" t="inlineStr"/>
+      <c r="CH187" t="inlineStr"/>
+      <c r="CI187" t="inlineStr"/>
+      <c r="CJ187" t="inlineStr"/>
+      <c r="CK187" t="inlineStr"/>
+      <c r="CL187" t="inlineStr"/>
+      <c r="CM187" t="inlineStr"/>
+      <c r="CN187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>h0KqXPNp</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="n">
+        <v>45562.625</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landry r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le basser
+  laval </t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>11017</v>
+      </c>
+      <c r="F188" t="n">
+        <v>5994</v>
+      </c>
+      <c r="G188" t="n">
+        <v>3</v>
+      </c>
+      <c r="H188" t="n">
+        <v>1</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="n">
+        <v>35</v>
+      </c>
+      <c r="N188" t="n">
+        <v>65</v>
+      </c>
+      <c r="O188" t="n">
+        <v>7</v>
+      </c>
+      <c r="P188" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>5</v>
+      </c>
+      <c r="R188" t="n">
+        <v>2</v>
+      </c>
+      <c r="S188" t="n">
+        <v>1</v>
+      </c>
+      <c r="T188" t="n">
+        <v>3</v>
+      </c>
+      <c r="U188" t="n">
+        <v>1</v>
+      </c>
+      <c r="V188" t="n">
+        <v>2</v>
+      </c>
+      <c r="W188" t="inlineStr"/>
+      <c r="X188" t="inlineStr"/>
+      <c r="Y188" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC188" t="inlineStr"/>
+      <c r="AD188" t="inlineStr"/>
+      <c r="AE188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ188" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK188" t="inlineStr"/>
+      <c r="AL188" t="inlineStr"/>
+      <c r="AM188" t="inlineStr"/>
+      <c r="AN188" t="inlineStr"/>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AP188" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AQ188" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR188" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT188" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU188" t="inlineStr"/>
+      <c r="AV188" t="inlineStr"/>
+      <c r="AW188" t="n">
+        <v>292</v>
+      </c>
+      <c r="AX188" t="n">
+        <v>574</v>
+      </c>
+      <c r="AY188" t="n">
+        <v>190</v>
+      </c>
+      <c r="AZ188" t="n">
+        <v>470</v>
+      </c>
+      <c r="BA188" t="inlineStr"/>
+      <c r="BB188" t="inlineStr"/>
+      <c r="BC188" t="n">
+        <v>33</v>
+      </c>
+      <c r="BD188" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF188" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG188" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH188" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI188" t="inlineStr"/>
+      <c r="BJ188" t="inlineStr"/>
+      <c r="BK188" t="inlineStr"/>
+      <c r="BL188" t="inlineStr"/>
+      <c r="BM188" t="inlineStr"/>
+      <c r="BN188" t="inlineStr"/>
+      <c r="BO188" t="inlineStr"/>
+      <c r="BP188" t="inlineStr"/>
+      <c r="BQ188" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="BR188" t="n">
+        <v>183</v>
+      </c>
+      <c r="BS188" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="BT188" t="inlineStr"/>
+      <c r="BU188" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="BV188" t="n">
+        <v>181.2666666666667</v>
+      </c>
+      <c r="BW188" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="BX188" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BY188" t="n">
+        <v>23.13333333333333</v>
+      </c>
+      <c r="BZ188" t="n">
+        <v>183.5333333333333</v>
+      </c>
+      <c r="CA188" t="n">
+        <v>63.13333333333333</v>
+      </c>
+      <c r="CB188" t="inlineStr"/>
+      <c r="CC188" t="inlineStr"/>
+      <c r="CD188" t="inlineStr"/>
+      <c r="CE188" t="inlineStr"/>
+      <c r="CF188" t="inlineStr"/>
+      <c r="CG188" t="inlineStr"/>
+      <c r="CH188" t="inlineStr"/>
+      <c r="CI188" t="inlineStr"/>
+      <c r="CJ188" t="inlineStr"/>
+      <c r="CK188" t="inlineStr"/>
+      <c r="CL188" t="inlineStr"/>
+      <c r="CM188" t="inlineStr"/>
+      <c r="CN188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>K6CVfTFi</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="n">
+        <v>45562.625</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rosier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade du moustoir
+  lorient </t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>16787</v>
+      </c>
+      <c r="F189" t="n">
+        <v>10042</v>
+      </c>
+      <c r="G189" t="n">
+        <v>3</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="n">
+        <v>70</v>
+      </c>
+      <c r="N189" t="n">
+        <v>30</v>
+      </c>
+      <c r="O189" t="n">
+        <v>27</v>
+      </c>
+      <c r="P189" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>10</v>
+      </c>
+      <c r="R189" t="n">
+        <v>3</v>
+      </c>
+      <c r="S189" t="n">
+        <v>13</v>
+      </c>
+      <c r="T189" t="n">
+        <v>2</v>
+      </c>
+      <c r="U189" t="n">
+        <v>4</v>
+      </c>
+      <c r="V189" t="n">
+        <v>2</v>
+      </c>
+      <c r="W189" t="inlineStr"/>
+      <c r="X189" t="inlineStr"/>
+      <c r="Y189" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z189" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA189" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC189" t="inlineStr"/>
+      <c r="AD189" t="inlineStr"/>
+      <c r="AE189" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF189" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG189" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH189" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK189" t="inlineStr"/>
+      <c r="AL189" t="inlineStr"/>
+      <c r="AM189" t="inlineStr"/>
+      <c r="AN189" t="inlineStr"/>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="AP189" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AQ189" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR189" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT189" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW189" t="n">
+        <v>510</v>
+      </c>
+      <c r="AX189" t="n">
+        <v>275</v>
+      </c>
+      <c r="AY189" t="n">
+        <v>449</v>
+      </c>
+      <c r="AZ189" t="n">
+        <v>189</v>
+      </c>
+      <c r="BA189" t="inlineStr"/>
+      <c r="BB189" t="inlineStr"/>
+      <c r="BC189" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD189" t="n">
+        <v>35</v>
+      </c>
+      <c r="BE189" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF189" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG189" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH189" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI189" t="inlineStr"/>
+      <c r="BJ189" t="inlineStr"/>
+      <c r="BK189" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="BL189" t="inlineStr"/>
+      <c r="BM189" t="inlineStr"/>
+      <c r="BN189" t="inlineStr"/>
+      <c r="BO189" t="inlineStr"/>
+      <c r="BP189" t="inlineStr"/>
+      <c r="BQ189" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="BR189" t="n">
+        <v>180.2222222222222</v>
+      </c>
+      <c r="BS189" t="n">
+        <v>65.66666666666667</v>
+      </c>
+      <c r="BT189" t="inlineStr"/>
+      <c r="BU189" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="BV189" t="n">
+        <v>176.0833333333333</v>
+      </c>
+      <c r="BW189" t="n">
+        <v>70.08333333333333</v>
+      </c>
+      <c r="BX189" t="n">
+        <v>10750</v>
+      </c>
+      <c r="BY189" t="n">
+        <v>25.52631578947368</v>
+      </c>
+      <c r="BZ189" t="n">
+        <v>181.7894736842105</v>
+      </c>
+      <c r="CA189" t="n">
+        <v>65.36842105263158</v>
+      </c>
+      <c r="CB189" t="inlineStr"/>
+      <c r="CC189" t="inlineStr"/>
+      <c r="CD189" t="inlineStr"/>
+      <c r="CE189" t="inlineStr"/>
+      <c r="CF189" t="inlineStr"/>
+      <c r="CG189" t="inlineStr"/>
+      <c r="CH189" t="inlineStr"/>
+      <c r="CI189" t="inlineStr"/>
+      <c r="CJ189" t="inlineStr"/>
+      <c r="CK189" t="inlineStr"/>
+      <c r="CL189" t="inlineStr"/>
+      <c r="CM189" t="inlineStr"/>
+      <c r="CN189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>02u5v8VA</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="n">
+        <v>45562.625</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kubler g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F190" t="n">
+        <v>500</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" t="n">
+        <v>1</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="n">
+        <v>30</v>
+      </c>
+      <c r="N190" t="n">
+        <v>70</v>
+      </c>
+      <c r="O190" t="n">
+        <v>5</v>
+      </c>
+      <c r="P190" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>1</v>
+      </c>
+      <c r="R190" t="n">
+        <v>7</v>
+      </c>
+      <c r="S190" t="n">
+        <v>3</v>
+      </c>
+      <c r="T190" t="n">
+        <v>6</v>
+      </c>
+      <c r="U190" t="n">
+        <v>1</v>
+      </c>
+      <c r="V190" t="n">
+        <v>5</v>
+      </c>
+      <c r="W190" t="inlineStr"/>
+      <c r="X190" t="inlineStr"/>
+      <c r="Y190" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z190" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA190" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC190" t="inlineStr"/>
+      <c r="AD190" t="inlineStr"/>
+      <c r="AE190" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG190" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH190" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ190" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK190" t="inlineStr"/>
+      <c r="AL190" t="inlineStr"/>
+      <c r="AM190" t="inlineStr"/>
+      <c r="AN190" t="inlineStr"/>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AP190" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AQ190" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR190" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW190" t="n">
+        <v>265</v>
+      </c>
+      <c r="AX190" t="n">
+        <v>612</v>
+      </c>
+      <c r="AY190" t="n">
+        <v>173</v>
+      </c>
+      <c r="AZ190" t="n">
+        <v>515</v>
+      </c>
+      <c r="BA190" t="inlineStr"/>
+      <c r="BB190" t="inlineStr"/>
+      <c r="BC190" t="n">
+        <v>45</v>
+      </c>
+      <c r="BD190" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE190" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF190" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG190" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH190" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI190" t="inlineStr"/>
+      <c r="BJ190" t="inlineStr"/>
+      <c r="BK190" t="inlineStr"/>
+      <c r="BL190" t="inlineStr"/>
+      <c r="BM190" t="inlineStr"/>
+      <c r="BN190" t="inlineStr"/>
+      <c r="BO190" t="inlineStr"/>
+      <c r="BP190" t="inlineStr"/>
+      <c r="BQ190" t="inlineStr"/>
+      <c r="BR190" t="inlineStr"/>
+      <c r="BS190" t="inlineStr"/>
+      <c r="BT190" t="inlineStr"/>
+      <c r="BU190" t="inlineStr"/>
+      <c r="BV190" t="inlineStr"/>
+      <c r="BW190" t="inlineStr"/>
+      <c r="BX190" t="inlineStr"/>
+      <c r="BY190" t="n">
+        <v>24</v>
+      </c>
+      <c r="BZ190" t="n">
+        <v>173.6</v>
+      </c>
+      <c r="CA190" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="CB190" t="inlineStr"/>
+      <c r="CC190" t="inlineStr"/>
+      <c r="CD190" t="inlineStr"/>
+      <c r="CE190" t="inlineStr"/>
+      <c r="CF190" t="inlineStr"/>
+      <c r="CG190" t="inlineStr"/>
+      <c r="CH190" t="inlineStr"/>
+      <c r="CI190" t="inlineStr"/>
+      <c r="CJ190" t="inlineStr"/>
+      <c r="CK190" t="inlineStr"/>
+      <c r="CL190" t="inlineStr"/>
+      <c r="CM190" t="inlineStr"/>
+      <c r="CN190" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN190"/>
+  <dimension ref="A1:CN194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49287,6 +49287,998 @@
       <c r="CM190" t="inlineStr"/>
       <c r="CN190" t="inlineStr"/>
     </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="n">
+        <v>45564.65625</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F191" t="n">
+        <v>19790</v>
+      </c>
+      <c r="G191" t="n">
+        <v>1</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="K191" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M191" t="n">
+        <v>41</v>
+      </c>
+      <c r="N191" t="n">
+        <v>59</v>
+      </c>
+      <c r="O191" t="n">
+        <v>14</v>
+      </c>
+      <c r="P191" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>6</v>
+      </c>
+      <c r="R191" t="n">
+        <v>3</v>
+      </c>
+      <c r="S191" t="n">
+        <v>6</v>
+      </c>
+      <c r="T191" t="n">
+        <v>6</v>
+      </c>
+      <c r="U191" t="n">
+        <v>2</v>
+      </c>
+      <c r="V191" t="n">
+        <v>1</v>
+      </c>
+      <c r="W191" t="n">
+        <v>11</v>
+      </c>
+      <c r="X191" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH191" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK191" t="inlineStr"/>
+      <c r="AL191" t="inlineStr"/>
+      <c r="AM191" t="inlineStr"/>
+      <c r="AN191" t="inlineStr"/>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AP191" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="AQ191" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR191" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT191" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU191" t="inlineStr"/>
+      <c r="AV191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr"/>
+      <c r="AX191" t="inlineStr"/>
+      <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr"/>
+      <c r="BA191" t="inlineStr"/>
+      <c r="BB191" t="inlineStr"/>
+      <c r="BC191" t="inlineStr"/>
+      <c r="BD191" t="inlineStr"/>
+      <c r="BE191" t="inlineStr"/>
+      <c r="BF191" t="inlineStr"/>
+      <c r="BG191" t="inlineStr"/>
+      <c r="BH191" t="inlineStr"/>
+      <c r="BI191" t="inlineStr"/>
+      <c r="BJ191" t="inlineStr"/>
+      <c r="BK191" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="BL191" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="BM191" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="BN191" t="n">
+        <v>184.75</v>
+      </c>
+      <c r="BO191" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="BP191" t="inlineStr"/>
+      <c r="BQ191" t="n">
+        <v>24</v>
+      </c>
+      <c r="BR191" t="n">
+        <v>184</v>
+      </c>
+      <c r="BS191" t="n">
+        <v>76.44444444444444</v>
+      </c>
+      <c r="BT191" t="n">
+        <v>40666.66666666666</v>
+      </c>
+      <c r="BU191" t="n">
+        <v>21.44444444444444</v>
+      </c>
+      <c r="BV191" t="n">
+        <v>184</v>
+      </c>
+      <c r="BW191" t="n">
+        <v>70.22222222222223</v>
+      </c>
+      <c r="BX191" t="n">
+        <v>11722.22222222222</v>
+      </c>
+      <c r="BY191" t="n">
+        <v>24.05555555555556</v>
+      </c>
+      <c r="BZ191" t="n">
+        <v>183.0555555555555</v>
+      </c>
+      <c r="CA191" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="CB191" t="n">
+        <v>43666.66666666666</v>
+      </c>
+      <c r="CC191" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="CD191" t="n">
+        <v>183</v>
+      </c>
+      <c r="CE191" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="CF191" t="inlineStr"/>
+      <c r="CG191" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH191" t="n">
+        <v>129</v>
+      </c>
+      <c r="CI191" t="n">
+        <v>23</v>
+      </c>
+      <c r="CJ191" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="CK191" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="CL191" t="n">
+        <v>24400</v>
+      </c>
+      <c r="CM191" t="n">
+        <v>5</v>
+      </c>
+      <c r="CN191" t="n">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F192" t="n">
+        <v>8526</v>
+      </c>
+      <c r="G192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H192" t="n">
+        <v>3</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="K192" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L192" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="M192" t="n">
+        <v>53</v>
+      </c>
+      <c r="N192" t="n">
+        <v>47</v>
+      </c>
+      <c r="O192" t="n">
+        <v>14</v>
+      </c>
+      <c r="P192" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>3</v>
+      </c>
+      <c r="R192" t="n">
+        <v>10</v>
+      </c>
+      <c r="S192" t="n">
+        <v>8</v>
+      </c>
+      <c r="T192" t="n">
+        <v>10</v>
+      </c>
+      <c r="U192" t="n">
+        <v>3</v>
+      </c>
+      <c r="V192" t="n">
+        <v>1</v>
+      </c>
+      <c r="W192" t="n">
+        <v>13</v>
+      </c>
+      <c r="X192" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG192" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH192" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ192" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK192" t="inlineStr"/>
+      <c r="AL192" t="inlineStr"/>
+      <c r="AM192" t="inlineStr"/>
+      <c r="AN192" t="inlineStr"/>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AQ192" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR192" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT192" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU192" t="inlineStr"/>
+      <c r="AV192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr"/>
+      <c r="AX192" t="inlineStr"/>
+      <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr"/>
+      <c r="BA192" t="inlineStr"/>
+      <c r="BB192" t="inlineStr"/>
+      <c r="BC192" t="inlineStr"/>
+      <c r="BD192" t="inlineStr"/>
+      <c r="BE192" t="inlineStr"/>
+      <c r="BF192" t="inlineStr"/>
+      <c r="BG192" t="inlineStr"/>
+      <c r="BH192" t="inlineStr"/>
+      <c r="BI192" t="inlineStr"/>
+      <c r="BJ192" t="inlineStr"/>
+      <c r="BK192" t="inlineStr"/>
+      <c r="BL192" t="inlineStr"/>
+      <c r="BM192" t="n">
+        <v>26.11111111111111</v>
+      </c>
+      <c r="BN192" t="n">
+        <v>182.5555555555555</v>
+      </c>
+      <c r="BO192" t="n">
+        <v>68.55555555555556</v>
+      </c>
+      <c r="BP192" t="inlineStr"/>
+      <c r="BQ192" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="BR192" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="BS192" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="BT192" t="inlineStr"/>
+      <c r="BU192" t="n">
+        <v>26.68421052631579</v>
+      </c>
+      <c r="BV192" t="n">
+        <v>180.7368421052632</v>
+      </c>
+      <c r="BW192" t="n">
+        <v>67.57894736842105</v>
+      </c>
+      <c r="BX192" t="inlineStr"/>
+      <c r="BY192" t="n">
+        <v>23.35294117647059</v>
+      </c>
+      <c r="BZ192" t="n">
+        <v>181.6470588235294</v>
+      </c>
+      <c r="CA192" t="n">
+        <v>71.70588235294117</v>
+      </c>
+      <c r="CB192" t="n">
+        <v>16294.11764705882</v>
+      </c>
+      <c r="CC192" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="CD192" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="CE192" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="CF192" t="inlineStr"/>
+      <c r="CG192" t="n">
+        <v>5</v>
+      </c>
+      <c r="CH192" t="n">
+        <v>327</v>
+      </c>
+      <c r="CI192" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="CJ192" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="CK192" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="CL192" t="n">
+        <v>17500</v>
+      </c>
+      <c r="CM192" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN192" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F193" t="n">
+        <v>34005</v>
+      </c>
+      <c r="G193" t="n">
+        <v>2</v>
+      </c>
+      <c r="H193" t="n">
+        <v>2</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="K193" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M193" t="n">
+        <v>61</v>
+      </c>
+      <c r="N193" t="n">
+        <v>39</v>
+      </c>
+      <c r="O193" t="n">
+        <v>16</v>
+      </c>
+      <c r="P193" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>3</v>
+      </c>
+      <c r="R193" t="n">
+        <v>3</v>
+      </c>
+      <c r="S193" t="n">
+        <v>9</v>
+      </c>
+      <c r="T193" t="n">
+        <v>2</v>
+      </c>
+      <c r="U193" t="n">
+        <v>4</v>
+      </c>
+      <c r="V193" t="n">
+        <v>0</v>
+      </c>
+      <c r="W193" t="n">
+        <v>12</v>
+      </c>
+      <c r="X193" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG193" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH193" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK193" t="inlineStr"/>
+      <c r="AL193" t="inlineStr"/>
+      <c r="AM193" t="inlineStr"/>
+      <c r="AN193" t="inlineStr"/>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AP193" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AQ193" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR193" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT193" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW193" t="inlineStr"/>
+      <c r="AX193" t="inlineStr"/>
+      <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr"/>
+      <c r="BA193" t="inlineStr"/>
+      <c r="BB193" t="inlineStr"/>
+      <c r="BC193" t="inlineStr"/>
+      <c r="BD193" t="inlineStr"/>
+      <c r="BE193" t="inlineStr"/>
+      <c r="BF193" t="inlineStr"/>
+      <c r="BG193" t="inlineStr"/>
+      <c r="BH193" t="inlineStr"/>
+      <c r="BI193" t="inlineStr"/>
+      <c r="BJ193" t="inlineStr"/>
+      <c r="BK193" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="BL193" t="inlineStr"/>
+      <c r="BM193" t="n">
+        <v>24</v>
+      </c>
+      <c r="BN193" t="n">
+        <v>181.4545454545455</v>
+      </c>
+      <c r="BO193" t="n">
+        <v>72.90909090909091</v>
+      </c>
+      <c r="BP193" t="n">
+        <v>16454.54545454546</v>
+      </c>
+      <c r="BQ193" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="BR193" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="BS193" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="BT193" t="n">
+        <v>5625</v>
+      </c>
+      <c r="BU193" t="n">
+        <v>26.0625</v>
+      </c>
+      <c r="BV193" t="n">
+        <v>180.0625</v>
+      </c>
+      <c r="BW193" t="n">
+        <v>73.0625</v>
+      </c>
+      <c r="BX193" t="n">
+        <v>18312.5</v>
+      </c>
+      <c r="BY193" t="n">
+        <v>26.09090909090909</v>
+      </c>
+      <c r="BZ193" t="n">
+        <v>178</v>
+      </c>
+      <c r="CA193" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="CB193" t="n">
+        <v>5818.181818181818</v>
+      </c>
+      <c r="CC193" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="CD193" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="CE193" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="CF193" t="n">
+        <v>14500</v>
+      </c>
+      <c r="CG193" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH193" t="n">
+        <v>277</v>
+      </c>
+      <c r="CI193" t="n">
+        <v>28</v>
+      </c>
+      <c r="CJ193" t="n">
+        <v>180</v>
+      </c>
+      <c r="CK193" t="n">
+        <v>70</v>
+      </c>
+      <c r="CL193" t="n">
+        <v>5250</v>
+      </c>
+      <c r="CM193" t="n">
+        <v>4</v>
+      </c>
+      <c r="CN193" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angoula g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F194" t="n">
+        <v>30026</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" t="n">
+        <v>2</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="K194" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M194" t="n">
+        <v>45</v>
+      </c>
+      <c r="N194" t="n">
+        <v>55</v>
+      </c>
+      <c r="O194" t="n">
+        <v>10</v>
+      </c>
+      <c r="P194" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>4</v>
+      </c>
+      <c r="R194" t="n">
+        <v>1</v>
+      </c>
+      <c r="S194" t="n">
+        <v>4</v>
+      </c>
+      <c r="T194" t="n">
+        <v>1</v>
+      </c>
+      <c r="U194" t="n">
+        <v>2</v>
+      </c>
+      <c r="V194" t="n">
+        <v>2</v>
+      </c>
+      <c r="W194" t="n">
+        <v>16</v>
+      </c>
+      <c r="X194" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK194" t="inlineStr"/>
+      <c r="AL194" t="inlineStr"/>
+      <c r="AM194" t="inlineStr"/>
+      <c r="AN194" t="inlineStr"/>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AP194" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AQ194" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR194" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT194" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU194" t="inlineStr"/>
+      <c r="AV194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr"/>
+      <c r="AX194" t="inlineStr"/>
+      <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr"/>
+      <c r="BA194" t="inlineStr"/>
+      <c r="BB194" t="inlineStr"/>
+      <c r="BC194" t="inlineStr"/>
+      <c r="BD194" t="inlineStr"/>
+      <c r="BE194" t="inlineStr"/>
+      <c r="BF194" t="inlineStr"/>
+      <c r="BG194" t="inlineStr"/>
+      <c r="BH194" t="inlineStr"/>
+      <c r="BI194" t="inlineStr"/>
+      <c r="BJ194" t="inlineStr"/>
+      <c r="BK194" t="inlineStr"/>
+      <c r="BL194" t="inlineStr"/>
+      <c r="BM194" t="n">
+        <v>23.22222222222222</v>
+      </c>
+      <c r="BN194" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="BO194" t="n">
+        <v>72</v>
+      </c>
+      <c r="BP194" t="n">
+        <v>13000</v>
+      </c>
+      <c r="BQ194" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="BR194" t="n">
+        <v>181.1111111111111</v>
+      </c>
+      <c r="BS194" t="n">
+        <v>75.44444444444444</v>
+      </c>
+      <c r="BT194" t="n">
+        <v>28333.33333333333</v>
+      </c>
+      <c r="BU194" t="n">
+        <v>23.82352941176471</v>
+      </c>
+      <c r="BV194" t="n">
+        <v>179.5294117647059</v>
+      </c>
+      <c r="BW194" t="n">
+        <v>71.76470588235294</v>
+      </c>
+      <c r="BX194" t="n">
+        <v>14588.23529411765</v>
+      </c>
+      <c r="BY194" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="BZ194" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="CA194" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="CB194" t="n">
+        <v>27550</v>
+      </c>
+      <c r="CC194" t="n">
+        <v>18</v>
+      </c>
+      <c r="CD194" t="n">
+        <v>177</v>
+      </c>
+      <c r="CE194" t="n">
+        <v>62</v>
+      </c>
+      <c r="CF194" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CG194" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH194" t="n">
+        <v>62</v>
+      </c>
+      <c r="CI194" t="inlineStr"/>
+      <c r="CJ194" t="inlineStr"/>
+      <c r="CK194" t="inlineStr"/>
+      <c r="CL194" t="inlineStr"/>
+      <c r="CM194" t="inlineStr"/>
+      <c r="CN194" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB195"/>
+  <dimension ref="A1:DB205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53145,6 +53145,2588 @@
       <c r="DA195" t="inlineStr"/>
       <c r="DB195" t="inlineStr"/>
     </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>Wf14adfU</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="n">
+        <v>45570.58333333334</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="n">
+        <v>2</v>
+      </c>
+      <c r="H196" t="n">
+        <v>1</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="K196" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L196" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M196" t="n">
+        <v>57</v>
+      </c>
+      <c r="N196" t="n">
+        <v>43</v>
+      </c>
+      <c r="O196" t="n">
+        <v>11</v>
+      </c>
+      <c r="P196" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>4</v>
+      </c>
+      <c r="R196" t="n">
+        <v>2</v>
+      </c>
+      <c r="S196" t="n">
+        <v>4</v>
+      </c>
+      <c r="T196" t="n">
+        <v>5</v>
+      </c>
+      <c r="U196" t="n">
+        <v>3</v>
+      </c>
+      <c r="V196" t="n">
+        <v>1</v>
+      </c>
+      <c r="W196" t="n">
+        <v>8</v>
+      </c>
+      <c r="X196" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AL196" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AM196" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN196" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ196" t="inlineStr"/>
+      <c r="AR196" t="inlineStr"/>
+      <c r="AS196" t="inlineStr"/>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AU196" t="inlineStr"/>
+      <c r="AV196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr"/>
+      <c r="AX196" t="inlineStr"/>
+      <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr"/>
+      <c r="BA196" t="inlineStr"/>
+      <c r="BB196" t="inlineStr"/>
+      <c r="BC196" t="inlineStr"/>
+      <c r="BD196" t="inlineStr"/>
+      <c r="BE196" t="inlineStr"/>
+      <c r="BF196" t="inlineStr"/>
+      <c r="BG196" t="inlineStr"/>
+      <c r="BH196" t="inlineStr"/>
+      <c r="BI196" t="inlineStr"/>
+      <c r="BJ196" t="inlineStr"/>
+      <c r="BK196" t="inlineStr"/>
+      <c r="BL196" t="inlineStr"/>
+      <c r="BM196" t="inlineStr"/>
+      <c r="BN196" t="inlineStr"/>
+      <c r="BO196" t="inlineStr"/>
+      <c r="BP196" t="inlineStr"/>
+      <c r="BQ196" t="inlineStr"/>
+      <c r="BR196" t="inlineStr"/>
+      <c r="BS196" t="inlineStr"/>
+      <c r="BT196" t="inlineStr"/>
+      <c r="BU196" t="inlineStr"/>
+      <c r="BV196" t="inlineStr"/>
+      <c r="BW196" t="inlineStr"/>
+      <c r="BX196" t="inlineStr"/>
+      <c r="BY196" t="inlineStr"/>
+      <c r="BZ196" t="inlineStr"/>
+      <c r="CA196" t="inlineStr"/>
+      <c r="CB196" t="inlineStr"/>
+      <c r="CC196" t="inlineStr"/>
+      <c r="CD196" t="inlineStr"/>
+      <c r="CE196" t="inlineStr"/>
+      <c r="CF196" t="inlineStr"/>
+      <c r="CG196" t="inlineStr"/>
+      <c r="CH196" t="inlineStr"/>
+      <c r="CI196" t="inlineStr"/>
+      <c r="CJ196" t="inlineStr"/>
+      <c r="CK196" t="inlineStr"/>
+      <c r="CL196" t="inlineStr"/>
+      <c r="CM196" t="n">
+        <v>28</v>
+      </c>
+      <c r="CN196" t="n">
+        <v>187</v>
+      </c>
+      <c r="CO196" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP196" t="n">
+        <v>75</v>
+      </c>
+      <c r="CQ196" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CR196" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="CS196" t="n">
+        <v>76</v>
+      </c>
+      <c r="CT196" t="n">
+        <v>2</v>
+      </c>
+      <c r="CU196" t="inlineStr"/>
+      <c r="CV196" t="inlineStr"/>
+      <c r="CW196" t="inlineStr"/>
+      <c r="CX196" t="inlineStr"/>
+      <c r="CY196" t="inlineStr"/>
+      <c r="CZ196" t="inlineStr"/>
+      <c r="DA196" t="inlineStr"/>
+      <c r="DB196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>z9REJaun</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="n">
+        <v>45570.5</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="n">
+        <v>3</v>
+      </c>
+      <c r="H197" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="K197" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M197" t="n">
+        <v>41</v>
+      </c>
+      <c r="N197" t="n">
+        <v>59</v>
+      </c>
+      <c r="O197" t="n">
+        <v>13</v>
+      </c>
+      <c r="P197" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>5</v>
+      </c>
+      <c r="R197" t="n">
+        <v>3</v>
+      </c>
+      <c r="S197" t="n">
+        <v>5</v>
+      </c>
+      <c r="T197" t="n">
+        <v>5</v>
+      </c>
+      <c r="U197" t="n">
+        <v>3</v>
+      </c>
+      <c r="V197" t="n">
+        <v>3</v>
+      </c>
+      <c r="W197" t="n">
+        <v>11</v>
+      </c>
+      <c r="X197" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AL197" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="AM197" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ197" t="inlineStr"/>
+      <c r="AR197" t="inlineStr"/>
+      <c r="AS197" t="inlineStr"/>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AU197" t="inlineStr"/>
+      <c r="AV197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr"/>
+      <c r="AX197" t="inlineStr"/>
+      <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr"/>
+      <c r="BA197" t="inlineStr"/>
+      <c r="BB197" t="inlineStr"/>
+      <c r="BC197" t="inlineStr"/>
+      <c r="BD197" t="inlineStr"/>
+      <c r="BE197" t="inlineStr"/>
+      <c r="BF197" t="inlineStr"/>
+      <c r="BG197" t="inlineStr"/>
+      <c r="BH197" t="inlineStr"/>
+      <c r="BI197" t="inlineStr"/>
+      <c r="BJ197" t="inlineStr"/>
+      <c r="BK197" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="BL197" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="BM197" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="BN197" t="n">
+        <v>5500</v>
+      </c>
+      <c r="BO197" t="n">
+        <v>2275000</v>
+      </c>
+      <c r="BP197" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="BQ197" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR197" t="inlineStr"/>
+      <c r="BS197" t="inlineStr"/>
+      <c r="BT197" t="inlineStr"/>
+      <c r="BU197" t="inlineStr"/>
+      <c r="BV197" t="inlineStr"/>
+      <c r="BW197" t="inlineStr"/>
+      <c r="BX197" t="inlineStr"/>
+      <c r="BY197" t="n">
+        <v>25.29411764705882</v>
+      </c>
+      <c r="BZ197" t="n">
+        <v>179.4705882352941</v>
+      </c>
+      <c r="CA197" t="n">
+        <v>68.64705882352941</v>
+      </c>
+      <c r="CB197" t="n">
+        <v>4411.764705882353</v>
+      </c>
+      <c r="CC197" t="n">
+        <v>1901470.588235294</v>
+      </c>
+      <c r="CD197" t="n">
+        <v>73.17647058823529</v>
+      </c>
+      <c r="CE197" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF197" t="n">
+        <v>25.15789473684211</v>
+      </c>
+      <c r="CG197" t="n">
+        <v>180.2105263157895</v>
+      </c>
+      <c r="CH197" t="n">
+        <v>68.10526315789474</v>
+      </c>
+      <c r="CI197" t="inlineStr"/>
+      <c r="CJ197" t="n">
+        <v>1793421.052631579</v>
+      </c>
+      <c r="CK197" t="n">
+        <v>71.73684210526316</v>
+      </c>
+      <c r="CL197" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM197" t="n">
+        <v>28</v>
+      </c>
+      <c r="CN197" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="CO197" t="n">
+        <v>4</v>
+      </c>
+      <c r="CP197" t="n">
+        <v>280</v>
+      </c>
+      <c r="CQ197" t="n">
+        <v>21000</v>
+      </c>
+      <c r="CR197" t="n">
+        <v>6675000</v>
+      </c>
+      <c r="CS197" t="n">
+        <v>284</v>
+      </c>
+      <c r="CT197" t="n">
+        <v>4</v>
+      </c>
+      <c r="CU197" t="n">
+        <v>22</v>
+      </c>
+      <c r="CV197" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="CW197" t="n">
+        <v>2</v>
+      </c>
+      <c r="CX197" t="n">
+        <v>129</v>
+      </c>
+      <c r="CY197" t="inlineStr"/>
+      <c r="CZ197" t="n">
+        <v>2350000</v>
+      </c>
+      <c r="DA197" t="n">
+        <v>149</v>
+      </c>
+      <c r="DB197" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>xYNVFHvB</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="n">
+        <v>45569.65625</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F198" t="n">
+        <v>54568</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="n">
+        <v>1</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="K198" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M198" t="n">
+        <v>76</v>
+      </c>
+      <c r="N198" t="n">
+        <v>24</v>
+      </c>
+      <c r="O198" t="n">
+        <v>16</v>
+      </c>
+      <c r="P198" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>4</v>
+      </c>
+      <c r="R198" t="n">
+        <v>3</v>
+      </c>
+      <c r="S198" t="n">
+        <v>8</v>
+      </c>
+      <c r="T198" t="n">
+        <v>5</v>
+      </c>
+      <c r="U198" t="n">
+        <v>4</v>
+      </c>
+      <c r="V198" t="n">
+        <v>2</v>
+      </c>
+      <c r="W198" t="n">
+        <v>10</v>
+      </c>
+      <c r="X198" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="AL198" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AM198" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS198" t="inlineStr"/>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AU198" t="inlineStr"/>
+      <c r="AV198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr"/>
+      <c r="AX198" t="inlineStr"/>
+      <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr"/>
+      <c r="BA198" t="inlineStr"/>
+      <c r="BB198" t="inlineStr"/>
+      <c r="BC198" t="inlineStr"/>
+      <c r="BD198" t="inlineStr"/>
+      <c r="BE198" t="inlineStr"/>
+      <c r="BF198" t="inlineStr"/>
+      <c r="BG198" t="inlineStr"/>
+      <c r="BH198" t="inlineStr"/>
+      <c r="BI198" t="inlineStr"/>
+      <c r="BJ198" t="inlineStr"/>
+      <c r="BK198" t="inlineStr"/>
+      <c r="BL198" t="inlineStr"/>
+      <c r="BM198" t="inlineStr"/>
+      <c r="BN198" t="inlineStr"/>
+      <c r="BO198" t="inlineStr"/>
+      <c r="BP198" t="inlineStr"/>
+      <c r="BQ198" t="inlineStr"/>
+      <c r="BR198" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="BS198" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BT198" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="BU198" t="inlineStr"/>
+      <c r="BV198" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="BW198" t="n">
+        <v>72.875</v>
+      </c>
+      <c r="BX198" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY198" t="inlineStr"/>
+      <c r="BZ198" t="inlineStr"/>
+      <c r="CA198" t="inlineStr"/>
+      <c r="CB198" t="inlineStr"/>
+      <c r="CC198" t="inlineStr"/>
+      <c r="CD198" t="inlineStr"/>
+      <c r="CE198" t="inlineStr"/>
+      <c r="CF198" t="n">
+        <v>25</v>
+      </c>
+      <c r="CG198" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="CH198" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="CI198" t="inlineStr"/>
+      <c r="CJ198" t="n">
+        <v>1238333.333333333</v>
+      </c>
+      <c r="CK198" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="CL198" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM198" t="inlineStr"/>
+      <c r="CN198" t="inlineStr"/>
+      <c r="CO198" t="inlineStr"/>
+      <c r="CP198" t="inlineStr"/>
+      <c r="CQ198" t="inlineStr"/>
+      <c r="CR198" t="inlineStr"/>
+      <c r="CS198" t="inlineStr"/>
+      <c r="CT198" t="inlineStr"/>
+      <c r="CU198" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="CV198" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="CW198" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX198" t="n">
+        <v>188</v>
+      </c>
+      <c r="CY198" t="inlineStr"/>
+      <c r="CZ198" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="DA198" t="n">
+        <v>217</v>
+      </c>
+      <c r="DB198" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>jXmAqfD7</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="n">
+        <v>45570.375</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leleu m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michel moretti stadium
+  ajaccio </t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>8470</v>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" t="n">
+        <v>1</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="n">
+        <v>46</v>
+      </c>
+      <c r="N199" t="n">
+        <v>54</v>
+      </c>
+      <c r="O199" t="n">
+        <v>3</v>
+      </c>
+      <c r="P199" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>1</v>
+      </c>
+      <c r="R199" t="n">
+        <v>1</v>
+      </c>
+      <c r="S199" t="n">
+        <v>2</v>
+      </c>
+      <c r="T199" t="n">
+        <v>2</v>
+      </c>
+      <c r="U199" t="inlineStr"/>
+      <c r="V199" t="inlineStr"/>
+      <c r="W199" t="inlineStr"/>
+      <c r="X199" t="inlineStr"/>
+      <c r="Y199" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="inlineStr"/>
+      <c r="AH199" t="inlineStr"/>
+      <c r="AI199" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AL199" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AM199" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS199" t="inlineStr"/>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AU199" t="inlineStr"/>
+      <c r="AV199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr"/>
+      <c r="AX199" t="inlineStr"/>
+      <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr"/>
+      <c r="BA199" t="inlineStr"/>
+      <c r="BB199" t="inlineStr"/>
+      <c r="BC199" t="inlineStr"/>
+      <c r="BD199" t="inlineStr"/>
+      <c r="BE199" t="inlineStr"/>
+      <c r="BF199" t="inlineStr"/>
+      <c r="BG199" t="inlineStr"/>
+      <c r="BH199" t="inlineStr"/>
+      <c r="BI199" t="inlineStr"/>
+      <c r="BJ199" t="inlineStr"/>
+      <c r="BK199" t="n">
+        <v>26.77777777777778</v>
+      </c>
+      <c r="BL199" t="n">
+        <v>180.2222222222222</v>
+      </c>
+      <c r="BM199" t="n">
+        <v>66.44444444444444</v>
+      </c>
+      <c r="BN199" t="inlineStr"/>
+      <c r="BO199" t="n">
+        <v>963888.8888888889</v>
+      </c>
+      <c r="BP199" t="n">
+        <v>70.22222222222223</v>
+      </c>
+      <c r="BQ199" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR199" t="inlineStr"/>
+      <c r="BS199" t="inlineStr"/>
+      <c r="BT199" t="inlineStr"/>
+      <c r="BU199" t="inlineStr"/>
+      <c r="BV199" t="inlineStr"/>
+      <c r="BW199" t="inlineStr"/>
+      <c r="BX199" t="inlineStr"/>
+      <c r="BY199" t="n">
+        <v>24.92857142857143</v>
+      </c>
+      <c r="BZ199" t="n">
+        <v>179.7142857142857</v>
+      </c>
+      <c r="CA199" t="n">
+        <v>63.28571428571428</v>
+      </c>
+      <c r="CB199" t="inlineStr"/>
+      <c r="CC199" t="n">
+        <v>607142.8571428572</v>
+      </c>
+      <c r="CD199" t="n">
+        <v>70.21428571428571</v>
+      </c>
+      <c r="CE199" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF199" t="inlineStr"/>
+      <c r="CG199" t="inlineStr"/>
+      <c r="CH199" t="inlineStr"/>
+      <c r="CI199" t="inlineStr"/>
+      <c r="CJ199" t="inlineStr"/>
+      <c r="CK199" t="inlineStr"/>
+      <c r="CL199" t="inlineStr"/>
+      <c r="CM199" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="CN199" t="n">
+        <v>180</v>
+      </c>
+      <c r="CO199" t="n">
+        <v>2</v>
+      </c>
+      <c r="CP199" t="n">
+        <v>131</v>
+      </c>
+      <c r="CQ199" t="n">
+        <v>6000</v>
+      </c>
+      <c r="CR199" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="CS199" t="n">
+        <v>137</v>
+      </c>
+      <c r="CT199" t="n">
+        <v>2</v>
+      </c>
+      <c r="CU199" t="inlineStr"/>
+      <c r="CV199" t="inlineStr"/>
+      <c r="CW199" t="inlineStr"/>
+      <c r="CX199" t="inlineStr"/>
+      <c r="CY199" t="inlineStr"/>
+      <c r="CZ199" t="inlineStr"/>
+      <c r="DA199" t="inlineStr"/>
+      <c r="DB199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>ETmRq37j</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="n">
+        <v>45570.375</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade michel d ornano
+  caen </t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>20300</v>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" t="n">
+        <v>2</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="n">
+        <v>43</v>
+      </c>
+      <c r="N200" t="n">
+        <v>57</v>
+      </c>
+      <c r="O200" t="n">
+        <v>4</v>
+      </c>
+      <c r="P200" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>1</v>
+      </c>
+      <c r="R200" t="n">
+        <v>5</v>
+      </c>
+      <c r="S200" t="n">
+        <v>3</v>
+      </c>
+      <c r="T200" t="n">
+        <v>3</v>
+      </c>
+      <c r="U200" t="n">
+        <v>0</v>
+      </c>
+      <c r="V200" t="n">
+        <v>6</v>
+      </c>
+      <c r="W200" t="inlineStr"/>
+      <c r="X200" t="inlineStr"/>
+      <c r="Y200" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC200" t="inlineStr"/>
+      <c r="AD200" t="inlineStr"/>
+      <c r="AE200" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG200" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH200" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI200" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AL200" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="AM200" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN200" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP200" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ200" t="inlineStr"/>
+      <c r="AR200" t="inlineStr"/>
+      <c r="AS200" t="n">
+        <v>414</v>
+      </c>
+      <c r="AT200" t="n">
+        <v>528</v>
+      </c>
+      <c r="AU200" t="inlineStr"/>
+      <c r="AV200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr"/>
+      <c r="AX200" t="inlineStr"/>
+      <c r="AY200" t="n">
+        <v>346</v>
+      </c>
+      <c r="AZ200" t="n">
+        <v>459</v>
+      </c>
+      <c r="BA200" t="inlineStr"/>
+      <c r="BB200" t="inlineStr"/>
+      <c r="BC200" t="n">
+        <v>35</v>
+      </c>
+      <c r="BD200" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE200" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF200" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG200" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH200" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI200" t="inlineStr"/>
+      <c r="BJ200" t="inlineStr"/>
+      <c r="BK200" t="inlineStr"/>
+      <c r="BL200" t="inlineStr"/>
+      <c r="BM200" t="inlineStr"/>
+      <c r="BN200" t="inlineStr"/>
+      <c r="BO200" t="inlineStr"/>
+      <c r="BP200" t="inlineStr"/>
+      <c r="BQ200" t="inlineStr"/>
+      <c r="BR200" t="inlineStr"/>
+      <c r="BS200" t="inlineStr"/>
+      <c r="BT200" t="inlineStr"/>
+      <c r="BU200" t="inlineStr"/>
+      <c r="BV200" t="inlineStr"/>
+      <c r="BW200" t="inlineStr"/>
+      <c r="BX200" t="inlineStr"/>
+      <c r="BY200" t="n">
+        <v>22.42857142857143</v>
+      </c>
+      <c r="BZ200" t="n">
+        <v>181.2857142857143</v>
+      </c>
+      <c r="CA200" t="n">
+        <v>63.71428571428572</v>
+      </c>
+      <c r="CB200" t="inlineStr"/>
+      <c r="CC200" t="n">
+        <v>1014285.714285714</v>
+      </c>
+      <c r="CD200" t="n">
+        <v>73.07142857142857</v>
+      </c>
+      <c r="CE200" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF200" t="inlineStr"/>
+      <c r="CG200" t="inlineStr"/>
+      <c r="CH200" t="inlineStr"/>
+      <c r="CI200" t="inlineStr"/>
+      <c r="CJ200" t="inlineStr"/>
+      <c r="CK200" t="inlineStr"/>
+      <c r="CL200" t="inlineStr"/>
+      <c r="CM200" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="CN200" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="CO200" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP200" t="n">
+        <v>198</v>
+      </c>
+      <c r="CQ200" t="inlineStr"/>
+      <c r="CR200" t="n">
+        <v>3150000</v>
+      </c>
+      <c r="CS200" t="n">
+        <v>214</v>
+      </c>
+      <c r="CT200" t="n">
+        <v>3</v>
+      </c>
+      <c r="CU200" t="n">
+        <v>22</v>
+      </c>
+      <c r="CV200" t="n">
+        <v>177</v>
+      </c>
+      <c r="CW200" t="n">
+        <v>2</v>
+      </c>
+      <c r="CX200" t="n">
+        <v>136</v>
+      </c>
+      <c r="CY200" t="n">
+        <v>18000</v>
+      </c>
+      <c r="CZ200" t="n">
+        <v>4300000</v>
+      </c>
+      <c r="DA200" t="n">
+        <v>152</v>
+      </c>
+      <c r="DB200" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>rocekPqT</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="n">
+        <v>45570.375</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">legat p 
+  fra </t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade gabriel montpied
+  clermont ferrand </t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="n">
+        <v>4</v>
+      </c>
+      <c r="H201" t="n">
+        <v>1</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="n">
+        <v>36</v>
+      </c>
+      <c r="N201" t="n">
+        <v>64</v>
+      </c>
+      <c r="O201" t="n">
+        <v>9</v>
+      </c>
+      <c r="P201" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>6</v>
+      </c>
+      <c r="R201" t="n">
+        <v>7</v>
+      </c>
+      <c r="S201" t="n">
+        <v>3</v>
+      </c>
+      <c r="T201" t="n">
+        <v>12</v>
+      </c>
+      <c r="U201" t="n">
+        <v>0</v>
+      </c>
+      <c r="V201" t="n">
+        <v>4</v>
+      </c>
+      <c r="W201" t="inlineStr"/>
+      <c r="X201" t="inlineStr"/>
+      <c r="Y201" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC201" t="inlineStr"/>
+      <c r="AD201" t="inlineStr"/>
+      <c r="AE201" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="AL201" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="AM201" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP201" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ201" t="inlineStr"/>
+      <c r="AR201" t="inlineStr"/>
+      <c r="AS201" t="n">
+        <v>344</v>
+      </c>
+      <c r="AT201" t="n">
+        <v>647</v>
+      </c>
+      <c r="AU201" t="inlineStr"/>
+      <c r="AV201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr"/>
+      <c r="AX201" t="inlineStr"/>
+      <c r="AY201" t="n">
+        <v>276</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>555</v>
+      </c>
+      <c r="BA201" t="inlineStr"/>
+      <c r="BB201" t="inlineStr"/>
+      <c r="BC201" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD201" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE201" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF201" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG201" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH201" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI201" t="inlineStr"/>
+      <c r="BJ201" t="inlineStr"/>
+      <c r="BK201" t="inlineStr"/>
+      <c r="BL201" t="inlineStr"/>
+      <c r="BM201" t="inlineStr"/>
+      <c r="BN201" t="inlineStr"/>
+      <c r="BO201" t="inlineStr"/>
+      <c r="BP201" t="inlineStr"/>
+      <c r="BQ201" t="inlineStr"/>
+      <c r="BR201" t="n">
+        <v>24.77777777777778</v>
+      </c>
+      <c r="BS201" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="BT201" t="n">
+        <v>65.22222222222223</v>
+      </c>
+      <c r="BU201" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BV201" t="n">
+        <v>1005555.555555556</v>
+      </c>
+      <c r="BW201" t="n">
+        <v>69.77777777777777</v>
+      </c>
+      <c r="BX201" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY201" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="BZ201" t="n">
+        <v>175.4</v>
+      </c>
+      <c r="CA201" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="CB201" t="n">
+        <v>2800</v>
+      </c>
+      <c r="CC201" t="n">
+        <v>1145000</v>
+      </c>
+      <c r="CD201" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="CE201" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF201" t="n">
+        <v>23.06666666666667</v>
+      </c>
+      <c r="CG201" t="n">
+        <v>177</v>
+      </c>
+      <c r="CH201" t="n">
+        <v>63.46666666666667</v>
+      </c>
+      <c r="CI201" t="n">
+        <v>1533.333333333333</v>
+      </c>
+      <c r="CJ201" t="n">
+        <v>931666.6666666666</v>
+      </c>
+      <c r="CK201" t="n">
+        <v>69.93333333333334</v>
+      </c>
+      <c r="CL201" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM201" t="inlineStr"/>
+      <c r="CN201" t="inlineStr"/>
+      <c r="CO201" t="inlineStr"/>
+      <c r="CP201" t="inlineStr"/>
+      <c r="CQ201" t="inlineStr"/>
+      <c r="CR201" t="inlineStr"/>
+      <c r="CS201" t="inlineStr"/>
+      <c r="CT201" t="inlineStr"/>
+      <c r="CU201" t="inlineStr"/>
+      <c r="CV201" t="inlineStr"/>
+      <c r="CW201" t="inlineStr"/>
+      <c r="CX201" t="inlineStr"/>
+      <c r="CY201" t="inlineStr"/>
+      <c r="CZ201" t="inlineStr"/>
+      <c r="DA201" t="inlineStr"/>
+      <c r="DB201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>GAud7c5E</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="n">
+        <v>45569.625</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thual o 
+  fra </t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des sports
+  annecy </t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>15660</v>
+      </c>
+      <c r="F202" t="n">
+        <v>5181</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="n">
+        <v>43</v>
+      </c>
+      <c r="N202" t="n">
+        <v>57</v>
+      </c>
+      <c r="O202" t="n">
+        <v>13</v>
+      </c>
+      <c r="P202" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>4</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="n">
+        <v>6</v>
+      </c>
+      <c r="T202" t="n">
+        <v>3</v>
+      </c>
+      <c r="U202" t="n">
+        <v>3</v>
+      </c>
+      <c r="V202" t="n">
+        <v>6</v>
+      </c>
+      <c r="W202" t="inlineStr"/>
+      <c r="X202" t="inlineStr"/>
+      <c r="Y202" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC202" t="inlineStr"/>
+      <c r="AD202" t="inlineStr"/>
+      <c r="AE202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="AL202" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AM202" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ202" t="inlineStr"/>
+      <c r="AR202" t="inlineStr"/>
+      <c r="AS202" t="n">
+        <v>320</v>
+      </c>
+      <c r="AT202" t="n">
+        <v>453</v>
+      </c>
+      <c r="AU202" t="inlineStr"/>
+      <c r="AV202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr"/>
+      <c r="AX202" t="inlineStr"/>
+      <c r="AY202" t="n">
+        <v>194</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>296</v>
+      </c>
+      <c r="BA202" t="inlineStr"/>
+      <c r="BB202" t="inlineStr"/>
+      <c r="BC202" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE202" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF202" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG202" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH202" t="n">
+        <v>11</v>
+      </c>
+      <c r="BI202" t="inlineStr"/>
+      <c r="BJ202" t="inlineStr"/>
+      <c r="BK202" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="BL202" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="BM202" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="BN202" t="inlineStr"/>
+      <c r="BO202" t="n">
+        <v>681250</v>
+      </c>
+      <c r="BP202" t="n">
+        <v>67</v>
+      </c>
+      <c r="BQ202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR202" t="inlineStr"/>
+      <c r="BS202" t="inlineStr"/>
+      <c r="BT202" t="inlineStr"/>
+      <c r="BU202" t="inlineStr"/>
+      <c r="BV202" t="inlineStr"/>
+      <c r="BW202" t="inlineStr"/>
+      <c r="BX202" t="inlineStr"/>
+      <c r="BY202" t="inlineStr"/>
+      <c r="BZ202" t="inlineStr"/>
+      <c r="CA202" t="inlineStr"/>
+      <c r="CB202" t="inlineStr"/>
+      <c r="CC202" t="inlineStr"/>
+      <c r="CD202" t="inlineStr"/>
+      <c r="CE202" t="inlineStr"/>
+      <c r="CF202" t="inlineStr"/>
+      <c r="CG202" t="inlineStr"/>
+      <c r="CH202" t="inlineStr"/>
+      <c r="CI202" t="inlineStr"/>
+      <c r="CJ202" t="inlineStr"/>
+      <c r="CK202" t="inlineStr"/>
+      <c r="CL202" t="inlineStr"/>
+      <c r="CM202" t="n">
+        <v>27</v>
+      </c>
+      <c r="CN202" t="n">
+        <v>187</v>
+      </c>
+      <c r="CO202" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP202" t="n">
+        <v>64</v>
+      </c>
+      <c r="CQ202" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CR202" t="n">
+        <v>575000</v>
+      </c>
+      <c r="CS202" t="n">
+        <v>64</v>
+      </c>
+      <c r="CT202" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU202" t="n">
+        <v>25</v>
+      </c>
+      <c r="CV202" t="n">
+        <v>182</v>
+      </c>
+      <c r="CW202" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX202" t="n">
+        <v>68</v>
+      </c>
+      <c r="CY202" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CZ202" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="DA202" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB202" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>WABm6viK</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="n">
+        <v>45569.625</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taleb a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade marcel tribut
+  dunkerque </t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>4933</v>
+      </c>
+      <c r="F203" t="n">
+        <v>3817</v>
+      </c>
+      <c r="G203" t="n">
+        <v>2</v>
+      </c>
+      <c r="H203" t="n">
+        <v>1</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="n">
+        <v>63</v>
+      </c>
+      <c r="N203" t="n">
+        <v>37</v>
+      </c>
+      <c r="O203" t="n">
+        <v>12</v>
+      </c>
+      <c r="P203" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>7</v>
+      </c>
+      <c r="R203" t="n">
+        <v>11</v>
+      </c>
+      <c r="S203" t="n">
+        <v>2</v>
+      </c>
+      <c r="T203" t="n">
+        <v>4</v>
+      </c>
+      <c r="U203" t="n">
+        <v>3</v>
+      </c>
+      <c r="V203" t="n">
+        <v>7</v>
+      </c>
+      <c r="W203" t="inlineStr"/>
+      <c r="X203" t="inlineStr"/>
+      <c r="Y203" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC203" t="inlineStr"/>
+      <c r="AD203" t="inlineStr"/>
+      <c r="AE203" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AL203" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="AM203" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN203" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP203" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS203" t="n">
+        <v>612</v>
+      </c>
+      <c r="AT203" t="n">
+        <v>361</v>
+      </c>
+      <c r="AU203" t="inlineStr"/>
+      <c r="AV203" t="inlineStr"/>
+      <c r="AW203" t="inlineStr"/>
+      <c r="AX203" t="inlineStr"/>
+      <c r="AY203" t="n">
+        <v>512</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>281</v>
+      </c>
+      <c r="BA203" t="inlineStr"/>
+      <c r="BB203" t="inlineStr"/>
+      <c r="BC203" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD203" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE203" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF203" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG203" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH203" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI203" t="inlineStr"/>
+      <c r="BJ203" t="inlineStr"/>
+      <c r="BK203" t="inlineStr"/>
+      <c r="BL203" t="inlineStr"/>
+      <c r="BM203" t="inlineStr"/>
+      <c r="BN203" t="inlineStr"/>
+      <c r="BO203" t="inlineStr"/>
+      <c r="BP203" t="inlineStr"/>
+      <c r="BQ203" t="inlineStr"/>
+      <c r="BR203" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BS203" t="n">
+        <v>179</v>
+      </c>
+      <c r="BT203" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="BU203" t="inlineStr"/>
+      <c r="BV203" t="n">
+        <v>1240625</v>
+      </c>
+      <c r="BW203" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BX203" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY203" t="n">
+        <v>26.125</v>
+      </c>
+      <c r="BZ203" t="n">
+        <v>176.625</v>
+      </c>
+      <c r="CA203" t="n">
+        <v>65.125</v>
+      </c>
+      <c r="CB203" t="inlineStr"/>
+      <c r="CC203" t="n">
+        <v>825000</v>
+      </c>
+      <c r="CD203" t="n">
+        <v>71</v>
+      </c>
+      <c r="CE203" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF203" t="n">
+        <v>23.35294117647059</v>
+      </c>
+      <c r="CG203" t="n">
+        <v>177.5882352941177</v>
+      </c>
+      <c r="CH203" t="n">
+        <v>66.41176470588235</v>
+      </c>
+      <c r="CI203" t="inlineStr"/>
+      <c r="CJ203" t="n">
+        <v>1586764.705882353</v>
+      </c>
+      <c r="CK203" t="n">
+        <v>72.76470588235294</v>
+      </c>
+      <c r="CL203" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM203" t="inlineStr"/>
+      <c r="CN203" t="inlineStr"/>
+      <c r="CO203" t="inlineStr"/>
+      <c r="CP203" t="inlineStr"/>
+      <c r="CQ203" t="inlineStr"/>
+      <c r="CR203" t="inlineStr"/>
+      <c r="CS203" t="inlineStr"/>
+      <c r="CT203" t="inlineStr"/>
+      <c r="CU203" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="CV203" t="n">
+        <v>184</v>
+      </c>
+      <c r="CW203" t="n">
+        <v>2</v>
+      </c>
+      <c r="CX203" t="n">
+        <v>135</v>
+      </c>
+      <c r="CY203" t="n">
+        <v>6000</v>
+      </c>
+      <c r="CZ203" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="DA203" t="n">
+        <v>135</v>
+      </c>
+      <c r="DB203" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>xQT45yzR</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="n">
+        <v>45569.625</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petit a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade charlety
+  paris </t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F204" t="n">
+        <v>5062</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="n">
+        <v>69</v>
+      </c>
+      <c r="N204" t="n">
+        <v>31</v>
+      </c>
+      <c r="O204" t="n">
+        <v>21</v>
+      </c>
+      <c r="P204" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>8</v>
+      </c>
+      <c r="R204" t="n">
+        <v>1</v>
+      </c>
+      <c r="S204" t="n">
+        <v>7</v>
+      </c>
+      <c r="T204" t="n">
+        <v>2</v>
+      </c>
+      <c r="U204" t="n">
+        <v>6</v>
+      </c>
+      <c r="V204" t="n">
+        <v>3</v>
+      </c>
+      <c r="W204" t="inlineStr"/>
+      <c r="X204" t="inlineStr"/>
+      <c r="Y204" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC204" t="inlineStr"/>
+      <c r="AD204" t="inlineStr"/>
+      <c r="AE204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="AL204" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AM204" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN204" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP204" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ204" t="inlineStr"/>
+      <c r="AR204" t="inlineStr"/>
+      <c r="AS204" t="n">
+        <v>729</v>
+      </c>
+      <c r="AT204" t="n">
+        <v>288</v>
+      </c>
+      <c r="AU204" t="inlineStr"/>
+      <c r="AV204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr"/>
+      <c r="AX204" t="inlineStr"/>
+      <c r="AY204" t="n">
+        <v>647</v>
+      </c>
+      <c r="AZ204" t="n">
+        <v>212</v>
+      </c>
+      <c r="BA204" t="inlineStr"/>
+      <c r="BB204" t="inlineStr"/>
+      <c r="BC204" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>35</v>
+      </c>
+      <c r="BE204" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF204" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG204" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH204" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI204" t="inlineStr"/>
+      <c r="BJ204" t="inlineStr"/>
+      <c r="BK204" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="BL204" t="n">
+        <v>178.625</v>
+      </c>
+      <c r="BM204" t="n">
+        <v>67.375</v>
+      </c>
+      <c r="BN204" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BO204" t="n">
+        <v>1603125</v>
+      </c>
+      <c r="BP204" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="BQ204" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="BR204" t="inlineStr"/>
+      <c r="BS204" t="inlineStr"/>
+      <c r="BT204" t="inlineStr"/>
+      <c r="BU204" t="inlineStr"/>
+      <c r="BV204" t="inlineStr"/>
+      <c r="BW204" t="inlineStr"/>
+      <c r="BX204" t="inlineStr"/>
+      <c r="BY204" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="BZ204" t="n">
+        <v>179.4666666666667</v>
+      </c>
+      <c r="CA204" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="CB204" t="n">
+        <v>3600</v>
+      </c>
+      <c r="CC204" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="CD204" t="n">
+        <v>70.06666666666666</v>
+      </c>
+      <c r="CE204" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="CF204" t="n">
+        <v>27.70588235294118</v>
+      </c>
+      <c r="CG204" t="n">
+        <v>182.5294117647059</v>
+      </c>
+      <c r="CH204" t="n">
+        <v>66.29411764705883</v>
+      </c>
+      <c r="CI204" t="n">
+        <v>2470.588235294118</v>
+      </c>
+      <c r="CJ204" t="n">
+        <v>1099411.764705882</v>
+      </c>
+      <c r="CK204" t="n">
+        <v>71.47058823529412</v>
+      </c>
+      <c r="CL204" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM204" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="CN204" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="CO204" t="n">
+        <v>4</v>
+      </c>
+      <c r="CP204" t="n">
+        <v>268</v>
+      </c>
+      <c r="CQ204" t="inlineStr"/>
+      <c r="CR204" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="CS204" t="n">
+        <v>287</v>
+      </c>
+      <c r="CT204" t="n">
+        <v>4</v>
+      </c>
+      <c r="CU204" t="inlineStr"/>
+      <c r="CV204" t="inlineStr"/>
+      <c r="CW204" t="inlineStr"/>
+      <c r="CX204" t="inlineStr"/>
+      <c r="CY204" t="inlineStr"/>
+      <c r="CZ204" t="inlineStr"/>
+      <c r="DA204" t="inlineStr"/>
+      <c r="DB204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>MidgmxEr</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="n">
+        <v>45569.625</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valnet a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade paul lignon
+  rodez </t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>5955</v>
+      </c>
+      <c r="F205" t="n">
+        <v>4049</v>
+      </c>
+      <c r="G205" t="n">
+        <v>2</v>
+      </c>
+      <c r="H205" t="n">
+        <v>1</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="n">
+        <v>38</v>
+      </c>
+      <c r="N205" t="n">
+        <v>62</v>
+      </c>
+      <c r="O205" t="n">
+        <v>12</v>
+      </c>
+      <c r="P205" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>6</v>
+      </c>
+      <c r="R205" t="n">
+        <v>2</v>
+      </c>
+      <c r="S205" t="n">
+        <v>4</v>
+      </c>
+      <c r="T205" t="n">
+        <v>2</v>
+      </c>
+      <c r="U205" t="n">
+        <v>2</v>
+      </c>
+      <c r="V205" t="n">
+        <v>0</v>
+      </c>
+      <c r="W205" t="inlineStr"/>
+      <c r="X205" t="inlineStr"/>
+      <c r="Y205" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC205" t="inlineStr"/>
+      <c r="AD205" t="inlineStr"/>
+      <c r="AE205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AL205" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AM205" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN205" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP205" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ205" t="inlineStr"/>
+      <c r="AR205" t="inlineStr"/>
+      <c r="AS205" t="n">
+        <v>388</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>685</v>
+      </c>
+      <c r="AU205" t="inlineStr"/>
+      <c r="AV205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr"/>
+      <c r="AX205" t="inlineStr"/>
+      <c r="AY205" t="n">
+        <v>304</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>587</v>
+      </c>
+      <c r="BA205" t="inlineStr"/>
+      <c r="BB205" t="inlineStr"/>
+      <c r="BC205" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF205" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG205" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH205" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI205" t="inlineStr"/>
+      <c r="BJ205" t="inlineStr"/>
+      <c r="BK205" t="inlineStr"/>
+      <c r="BL205" t="inlineStr"/>
+      <c r="BM205" t="inlineStr"/>
+      <c r="BN205" t="inlineStr"/>
+      <c r="BO205" t="inlineStr"/>
+      <c r="BP205" t="inlineStr"/>
+      <c r="BQ205" t="inlineStr"/>
+      <c r="BR205" t="n">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="BS205" t="n">
+        <v>186.1111111111111</v>
+      </c>
+      <c r="BT205" t="n">
+        <v>66.77777777777777</v>
+      </c>
+      <c r="BU205" t="inlineStr"/>
+      <c r="BV205" t="n">
+        <v>1497222.222222222</v>
+      </c>
+      <c r="BW205" t="n">
+        <v>70.77777777777777</v>
+      </c>
+      <c r="BX205" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY205" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="BZ205" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="CA205" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="CB205" t="inlineStr"/>
+      <c r="CC205" t="n">
+        <v>1280000</v>
+      </c>
+      <c r="CD205" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="CE205" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF205" t="n">
+        <v>25</v>
+      </c>
+      <c r="CG205" t="n">
+        <v>178.6428571428571</v>
+      </c>
+      <c r="CH205" t="n">
+        <v>66.71428571428571</v>
+      </c>
+      <c r="CI205" t="n">
+        <v>3642.857142857143</v>
+      </c>
+      <c r="CJ205" t="n">
+        <v>1541071.428571429</v>
+      </c>
+      <c r="CK205" t="n">
+        <v>71.28571428571429</v>
+      </c>
+      <c r="CL205" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM205" t="n">
+        <v>20</v>
+      </c>
+      <c r="CN205" t="n">
+        <v>181</v>
+      </c>
+      <c r="CO205" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP205" t="n">
+        <v>61</v>
+      </c>
+      <c r="CQ205" t="inlineStr"/>
+      <c r="CR205" t="n">
+        <v>675000</v>
+      </c>
+      <c r="CS205" t="n">
+        <v>69</v>
+      </c>
+      <c r="CT205" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU205" t="n">
+        <v>34</v>
+      </c>
+      <c r="CV205" t="n">
+        <v>179</v>
+      </c>
+      <c r="CW205" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX205" t="n">
+        <v>68</v>
+      </c>
+      <c r="CY205" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CZ205" t="n">
+        <v>400000</v>
+      </c>
+      <c r="DA205" t="n">
+        <v>68</v>
+      </c>
+      <c r="DB205" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB205"/>
+  <dimension ref="A1:DB212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55727,6 +55727,1540 @@
         <v>1</v>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F206" t="n">
+        <v>30247</v>
+      </c>
+      <c r="G206" t="n">
+        <v>1</v>
+      </c>
+      <c r="H206" t="n">
+        <v>1</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="K206" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L206" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M206" t="n">
+        <v>29</v>
+      </c>
+      <c r="N206" t="n">
+        <v>71</v>
+      </c>
+      <c r="O206" t="n">
+        <v>8</v>
+      </c>
+      <c r="P206" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>3</v>
+      </c>
+      <c r="R206" t="n">
+        <v>9</v>
+      </c>
+      <c r="S206" t="n">
+        <v>3</v>
+      </c>
+      <c r="T206" t="n">
+        <v>5</v>
+      </c>
+      <c r="U206" t="n">
+        <v>2</v>
+      </c>
+      <c r="V206" t="n">
+        <v>5</v>
+      </c>
+      <c r="W206" t="n">
+        <v>9</v>
+      </c>
+      <c r="X206" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AL206" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AM206" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ206" t="inlineStr"/>
+      <c r="AR206" t="inlineStr"/>
+      <c r="AS206" t="inlineStr"/>
+      <c r="AT206" t="inlineStr"/>
+      <c r="AU206" t="inlineStr"/>
+      <c r="AV206" t="inlineStr"/>
+      <c r="AW206" t="inlineStr"/>
+      <c r="AX206" t="inlineStr"/>
+      <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr"/>
+      <c r="BA206" t="inlineStr"/>
+      <c r="BB206" t="inlineStr"/>
+      <c r="BC206" t="inlineStr"/>
+      <c r="BD206" t="inlineStr"/>
+      <c r="BE206" t="inlineStr"/>
+      <c r="BF206" t="inlineStr"/>
+      <c r="BG206" t="inlineStr"/>
+      <c r="BH206" t="inlineStr"/>
+      <c r="BI206" t="inlineStr"/>
+      <c r="BJ206" t="inlineStr"/>
+      <c r="BK206" t="inlineStr"/>
+      <c r="BL206" t="inlineStr"/>
+      <c r="BM206" t="inlineStr"/>
+      <c r="BN206" t="inlineStr"/>
+      <c r="BO206" t="inlineStr"/>
+      <c r="BP206" t="inlineStr"/>
+      <c r="BQ206" t="inlineStr"/>
+      <c r="BR206" t="inlineStr"/>
+      <c r="BS206" t="inlineStr"/>
+      <c r="BT206" t="inlineStr"/>
+      <c r="BU206" t="inlineStr"/>
+      <c r="BV206" t="inlineStr"/>
+      <c r="BW206" t="inlineStr"/>
+      <c r="BX206" t="inlineStr"/>
+      <c r="BY206" t="inlineStr"/>
+      <c r="BZ206" t="inlineStr"/>
+      <c r="CA206" t="inlineStr"/>
+      <c r="CB206" t="inlineStr"/>
+      <c r="CC206" t="inlineStr"/>
+      <c r="CD206" t="inlineStr"/>
+      <c r="CE206" t="inlineStr"/>
+      <c r="CF206" t="inlineStr"/>
+      <c r="CG206" t="inlineStr"/>
+      <c r="CH206" t="inlineStr"/>
+      <c r="CI206" t="inlineStr"/>
+      <c r="CJ206" t="inlineStr"/>
+      <c r="CK206" t="inlineStr"/>
+      <c r="CL206" t="inlineStr"/>
+      <c r="CM206" t="inlineStr"/>
+      <c r="CN206" t="inlineStr"/>
+      <c r="CO206" t="inlineStr"/>
+      <c r="CP206" t="inlineStr"/>
+      <c r="CQ206" t="inlineStr"/>
+      <c r="CR206" t="inlineStr"/>
+      <c r="CS206" t="inlineStr"/>
+      <c r="CT206" t="inlineStr"/>
+      <c r="CU206" t="inlineStr"/>
+      <c r="CV206" t="inlineStr"/>
+      <c r="CW206" t="inlineStr"/>
+      <c r="CX206" t="inlineStr"/>
+      <c r="CY206" t="inlineStr"/>
+      <c r="CZ206" t="inlineStr"/>
+      <c r="DA206" t="inlineStr"/>
+      <c r="DB206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F207" t="n">
+        <v>14572</v>
+      </c>
+      <c r="G207" t="n">
+        <v>2</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="K207" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L207" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M207" t="n">
+        <v>53</v>
+      </c>
+      <c r="N207" t="n">
+        <v>47</v>
+      </c>
+      <c r="O207" t="n">
+        <v>8</v>
+      </c>
+      <c r="P207" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>3</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" t="n">
+        <v>2</v>
+      </c>
+      <c r="T207" t="n">
+        <v>9</v>
+      </c>
+      <c r="U207" t="n">
+        <v>3</v>
+      </c>
+      <c r="V207" t="n">
+        <v>5</v>
+      </c>
+      <c r="W207" t="n">
+        <v>13</v>
+      </c>
+      <c r="X207" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH207" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI207" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AL207" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="AM207" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN207" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS207" t="inlineStr"/>
+      <c r="AT207" t="inlineStr"/>
+      <c r="AU207" t="inlineStr"/>
+      <c r="AV207" t="inlineStr"/>
+      <c r="AW207" t="inlineStr"/>
+      <c r="AX207" t="inlineStr"/>
+      <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr"/>
+      <c r="BA207" t="inlineStr"/>
+      <c r="BB207" t="inlineStr"/>
+      <c r="BC207" t="inlineStr"/>
+      <c r="BD207" t="inlineStr"/>
+      <c r="BE207" t="inlineStr"/>
+      <c r="BF207" t="inlineStr"/>
+      <c r="BG207" t="inlineStr"/>
+      <c r="BH207" t="inlineStr"/>
+      <c r="BI207" t="inlineStr"/>
+      <c r="BJ207" t="inlineStr"/>
+      <c r="BK207" t="inlineStr"/>
+      <c r="BL207" t="inlineStr"/>
+      <c r="BM207" t="inlineStr"/>
+      <c r="BN207" t="inlineStr"/>
+      <c r="BO207" t="inlineStr"/>
+      <c r="BP207" t="inlineStr"/>
+      <c r="BQ207" t="inlineStr"/>
+      <c r="BR207" t="inlineStr"/>
+      <c r="BS207" t="inlineStr"/>
+      <c r="BT207" t="inlineStr"/>
+      <c r="BU207" t="inlineStr"/>
+      <c r="BV207" t="inlineStr"/>
+      <c r="BW207" t="inlineStr"/>
+      <c r="BX207" t="inlineStr"/>
+      <c r="BY207" t="inlineStr"/>
+      <c r="BZ207" t="inlineStr"/>
+      <c r="CA207" t="inlineStr"/>
+      <c r="CB207" t="inlineStr"/>
+      <c r="CC207" t="inlineStr"/>
+      <c r="CD207" t="inlineStr"/>
+      <c r="CE207" t="inlineStr"/>
+      <c r="CF207" t="inlineStr"/>
+      <c r="CG207" t="inlineStr"/>
+      <c r="CH207" t="inlineStr"/>
+      <c r="CI207" t="inlineStr"/>
+      <c r="CJ207" t="inlineStr"/>
+      <c r="CK207" t="inlineStr"/>
+      <c r="CL207" t="inlineStr"/>
+      <c r="CM207" t="inlineStr"/>
+      <c r="CN207" t="inlineStr"/>
+      <c r="CO207" t="inlineStr"/>
+      <c r="CP207" t="inlineStr"/>
+      <c r="CQ207" t="inlineStr"/>
+      <c r="CR207" t="inlineStr"/>
+      <c r="CS207" t="inlineStr"/>
+      <c r="CT207" t="inlineStr"/>
+      <c r="CU207" t="inlineStr"/>
+      <c r="CV207" t="inlineStr"/>
+      <c r="CW207" t="inlineStr"/>
+      <c r="CX207" t="inlineStr"/>
+      <c r="CY207" t="inlineStr"/>
+      <c r="CZ207" t="inlineStr"/>
+      <c r="DA207" t="inlineStr"/>
+      <c r="DB207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F208" t="n">
+        <v>14903</v>
+      </c>
+      <c r="G208" t="n">
+        <v>4</v>
+      </c>
+      <c r="H208" t="n">
+        <v>2</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="K208" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M208" t="n">
+        <v>48</v>
+      </c>
+      <c r="N208" t="n">
+        <v>52</v>
+      </c>
+      <c r="O208" t="n">
+        <v>18</v>
+      </c>
+      <c r="P208" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>5</v>
+      </c>
+      <c r="R208" t="n">
+        <v>3</v>
+      </c>
+      <c r="S208" t="n">
+        <v>8</v>
+      </c>
+      <c r="T208" t="n">
+        <v>5</v>
+      </c>
+      <c r="U208" t="n">
+        <v>5</v>
+      </c>
+      <c r="V208" t="n">
+        <v>2</v>
+      </c>
+      <c r="W208" t="n">
+        <v>17</v>
+      </c>
+      <c r="X208" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD208" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG208" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH208" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI208" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ208" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AL208" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="AM208" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN208" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP208" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ208" t="inlineStr"/>
+      <c r="AR208" t="inlineStr"/>
+      <c r="AS208" t="inlineStr"/>
+      <c r="AT208" t="inlineStr"/>
+      <c r="AU208" t="inlineStr"/>
+      <c r="AV208" t="inlineStr"/>
+      <c r="AW208" t="inlineStr"/>
+      <c r="AX208" t="inlineStr"/>
+      <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr"/>
+      <c r="BA208" t="inlineStr"/>
+      <c r="BB208" t="inlineStr"/>
+      <c r="BC208" t="inlineStr"/>
+      <c r="BD208" t="inlineStr"/>
+      <c r="BE208" t="inlineStr"/>
+      <c r="BF208" t="inlineStr"/>
+      <c r="BG208" t="inlineStr"/>
+      <c r="BH208" t="inlineStr"/>
+      <c r="BI208" t="inlineStr"/>
+      <c r="BJ208" t="inlineStr"/>
+      <c r="BK208" t="inlineStr"/>
+      <c r="BL208" t="inlineStr"/>
+      <c r="BM208" t="inlineStr"/>
+      <c r="BN208" t="inlineStr"/>
+      <c r="BO208" t="inlineStr"/>
+      <c r="BP208" t="inlineStr"/>
+      <c r="BQ208" t="inlineStr"/>
+      <c r="BR208" t="inlineStr"/>
+      <c r="BS208" t="inlineStr"/>
+      <c r="BT208" t="inlineStr"/>
+      <c r="BU208" t="inlineStr"/>
+      <c r="BV208" t="inlineStr"/>
+      <c r="BW208" t="inlineStr"/>
+      <c r="BX208" t="inlineStr"/>
+      <c r="BY208" t="inlineStr"/>
+      <c r="BZ208" t="inlineStr"/>
+      <c r="CA208" t="inlineStr"/>
+      <c r="CB208" t="inlineStr"/>
+      <c r="CC208" t="inlineStr"/>
+      <c r="CD208" t="inlineStr"/>
+      <c r="CE208" t="inlineStr"/>
+      <c r="CF208" t="inlineStr"/>
+      <c r="CG208" t="inlineStr"/>
+      <c r="CH208" t="inlineStr"/>
+      <c r="CI208" t="inlineStr"/>
+      <c r="CJ208" t="inlineStr"/>
+      <c r="CK208" t="inlineStr"/>
+      <c r="CL208" t="inlineStr"/>
+      <c r="CM208" t="inlineStr"/>
+      <c r="CN208" t="inlineStr"/>
+      <c r="CO208" t="inlineStr"/>
+      <c r="CP208" t="inlineStr"/>
+      <c r="CQ208" t="inlineStr"/>
+      <c r="CR208" t="inlineStr"/>
+      <c r="CS208" t="inlineStr"/>
+      <c r="CT208" t="inlineStr"/>
+      <c r="CU208" t="inlineStr"/>
+      <c r="CV208" t="inlineStr"/>
+      <c r="CW208" t="inlineStr"/>
+      <c r="CX208" t="inlineStr"/>
+      <c r="CY208" t="inlineStr"/>
+      <c r="CZ208" t="inlineStr"/>
+      <c r="DA208" t="inlineStr"/>
+      <c r="DB208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F209" t="n">
+        <v>19968</v>
+      </c>
+      <c r="G209" t="n">
+        <v>2</v>
+      </c>
+      <c r="H209" t="n">
+        <v>2</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="K209" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M209" t="n">
+        <v>37</v>
+      </c>
+      <c r="N209" t="n">
+        <v>63</v>
+      </c>
+      <c r="O209" t="n">
+        <v>8</v>
+      </c>
+      <c r="P209" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>5</v>
+      </c>
+      <c r="R209" t="n">
+        <v>5</v>
+      </c>
+      <c r="S209" t="n">
+        <v>3</v>
+      </c>
+      <c r="T209" t="n">
+        <v>3</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0</v>
+      </c>
+      <c r="V209" t="n">
+        <v>4</v>
+      </c>
+      <c r="W209" t="n">
+        <v>22</v>
+      </c>
+      <c r="X209" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD209" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF209" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG209" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH209" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI209" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ209" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AL209" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AM209" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN209" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP209" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ209" t="inlineStr"/>
+      <c r="AR209" t="inlineStr"/>
+      <c r="AS209" t="inlineStr"/>
+      <c r="AT209" t="inlineStr"/>
+      <c r="AU209" t="inlineStr"/>
+      <c r="AV209" t="inlineStr"/>
+      <c r="AW209" t="inlineStr"/>
+      <c r="AX209" t="inlineStr"/>
+      <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr"/>
+      <c r="BA209" t="inlineStr"/>
+      <c r="BB209" t="inlineStr"/>
+      <c r="BC209" t="inlineStr"/>
+      <c r="BD209" t="inlineStr"/>
+      <c r="BE209" t="inlineStr"/>
+      <c r="BF209" t="inlineStr"/>
+      <c r="BG209" t="inlineStr"/>
+      <c r="BH209" t="inlineStr"/>
+      <c r="BI209" t="inlineStr"/>
+      <c r="BJ209" t="inlineStr"/>
+      <c r="BK209" t="inlineStr"/>
+      <c r="BL209" t="inlineStr"/>
+      <c r="BM209" t="inlineStr"/>
+      <c r="BN209" t="inlineStr"/>
+      <c r="BO209" t="inlineStr"/>
+      <c r="BP209" t="inlineStr"/>
+      <c r="BQ209" t="inlineStr"/>
+      <c r="BR209" t="inlineStr"/>
+      <c r="BS209" t="inlineStr"/>
+      <c r="BT209" t="inlineStr"/>
+      <c r="BU209" t="inlineStr"/>
+      <c r="BV209" t="inlineStr"/>
+      <c r="BW209" t="inlineStr"/>
+      <c r="BX209" t="inlineStr"/>
+      <c r="BY209" t="inlineStr"/>
+      <c r="BZ209" t="inlineStr"/>
+      <c r="CA209" t="inlineStr"/>
+      <c r="CB209" t="inlineStr"/>
+      <c r="CC209" t="inlineStr"/>
+      <c r="CD209" t="inlineStr"/>
+      <c r="CE209" t="inlineStr"/>
+      <c r="CF209" t="inlineStr"/>
+      <c r="CG209" t="inlineStr"/>
+      <c r="CH209" t="inlineStr"/>
+      <c r="CI209" t="inlineStr"/>
+      <c r="CJ209" t="inlineStr"/>
+      <c r="CK209" t="inlineStr"/>
+      <c r="CL209" t="inlineStr"/>
+      <c r="CM209" t="inlineStr"/>
+      <c r="CN209" t="inlineStr"/>
+      <c r="CO209" t="inlineStr"/>
+      <c r="CP209" t="inlineStr"/>
+      <c r="CQ209" t="inlineStr"/>
+      <c r="CR209" t="inlineStr"/>
+      <c r="CS209" t="inlineStr"/>
+      <c r="CT209" t="inlineStr"/>
+      <c r="CU209" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV209" t="n">
+        <v>184</v>
+      </c>
+      <c r="CW209" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX209" t="n">
+        <v>64</v>
+      </c>
+      <c r="CY209" t="n">
+        <v>6000</v>
+      </c>
+      <c r="CZ209" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="DA209" t="n">
+        <v>76</v>
+      </c>
+      <c r="DB209" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F210" t="n">
+        <v>51888</v>
+      </c>
+      <c r="G210" t="n">
+        <v>2</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="K210" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M210" t="n">
+        <v>62</v>
+      </c>
+      <c r="N210" t="n">
+        <v>38</v>
+      </c>
+      <c r="O210" t="n">
+        <v>17</v>
+      </c>
+      <c r="P210" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>6</v>
+      </c>
+      <c r="R210" t="n">
+        <v>6</v>
+      </c>
+      <c r="S210" t="n">
+        <v>8</v>
+      </c>
+      <c r="T210" t="n">
+        <v>4</v>
+      </c>
+      <c r="U210" t="n">
+        <v>3</v>
+      </c>
+      <c r="V210" t="n">
+        <v>1</v>
+      </c>
+      <c r="W210" t="n">
+        <v>5</v>
+      </c>
+      <c r="X210" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AL210" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AM210" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN210" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP210" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ210" t="inlineStr"/>
+      <c r="AR210" t="inlineStr"/>
+      <c r="AS210" t="inlineStr"/>
+      <c r="AT210" t="inlineStr"/>
+      <c r="AU210" t="inlineStr"/>
+      <c r="AV210" t="inlineStr"/>
+      <c r="AW210" t="inlineStr"/>
+      <c r="AX210" t="inlineStr"/>
+      <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr"/>
+      <c r="BA210" t="inlineStr"/>
+      <c r="BB210" t="inlineStr"/>
+      <c r="BC210" t="inlineStr"/>
+      <c r="BD210" t="inlineStr"/>
+      <c r="BE210" t="inlineStr"/>
+      <c r="BF210" t="inlineStr"/>
+      <c r="BG210" t="inlineStr"/>
+      <c r="BH210" t="inlineStr"/>
+      <c r="BI210" t="inlineStr"/>
+      <c r="BJ210" t="inlineStr"/>
+      <c r="BK210" t="inlineStr"/>
+      <c r="BL210" t="inlineStr"/>
+      <c r="BM210" t="inlineStr"/>
+      <c r="BN210" t="inlineStr"/>
+      <c r="BO210" t="inlineStr"/>
+      <c r="BP210" t="inlineStr"/>
+      <c r="BQ210" t="inlineStr"/>
+      <c r="BR210" t="inlineStr"/>
+      <c r="BS210" t="inlineStr"/>
+      <c r="BT210" t="inlineStr"/>
+      <c r="BU210" t="inlineStr"/>
+      <c r="BV210" t="inlineStr"/>
+      <c r="BW210" t="inlineStr"/>
+      <c r="BX210" t="inlineStr"/>
+      <c r="BY210" t="inlineStr"/>
+      <c r="BZ210" t="inlineStr"/>
+      <c r="CA210" t="inlineStr"/>
+      <c r="CB210" t="inlineStr"/>
+      <c r="CC210" t="inlineStr"/>
+      <c r="CD210" t="inlineStr"/>
+      <c r="CE210" t="inlineStr"/>
+      <c r="CF210" t="inlineStr"/>
+      <c r="CG210" t="inlineStr"/>
+      <c r="CH210" t="inlineStr"/>
+      <c r="CI210" t="inlineStr"/>
+      <c r="CJ210" t="inlineStr"/>
+      <c r="CK210" t="inlineStr"/>
+      <c r="CL210" t="inlineStr"/>
+      <c r="CM210" t="inlineStr"/>
+      <c r="CN210" t="inlineStr"/>
+      <c r="CO210" t="inlineStr"/>
+      <c r="CP210" t="inlineStr"/>
+      <c r="CQ210" t="inlineStr"/>
+      <c r="CR210" t="inlineStr"/>
+      <c r="CS210" t="inlineStr"/>
+      <c r="CT210" t="inlineStr"/>
+      <c r="CU210" t="inlineStr"/>
+      <c r="CV210" t="inlineStr"/>
+      <c r="CW210" t="inlineStr"/>
+      <c r="CX210" t="inlineStr"/>
+      <c r="CY210" t="inlineStr"/>
+      <c r="CZ210" t="inlineStr"/>
+      <c r="DA210" t="inlineStr"/>
+      <c r="DB210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>8Kp3c9Oq</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="n">
+        <v>45570.66666666666</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F211" t="n">
+        <v>26533</v>
+      </c>
+      <c r="G211" t="n">
+        <v>1</v>
+      </c>
+      <c r="H211" t="n">
+        <v>2</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="K211" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M211" t="n">
+        <v>58</v>
+      </c>
+      <c r="N211" t="n">
+        <v>42</v>
+      </c>
+      <c r="O211" t="n">
+        <v>14</v>
+      </c>
+      <c r="P211" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>3</v>
+      </c>
+      <c r="R211" t="n">
+        <v>2</v>
+      </c>
+      <c r="S211" t="n">
+        <v>5</v>
+      </c>
+      <c r="T211" t="n">
+        <v>2</v>
+      </c>
+      <c r="U211" t="n">
+        <v>6</v>
+      </c>
+      <c r="V211" t="n">
+        <v>1</v>
+      </c>
+      <c r="W211" t="n">
+        <v>19</v>
+      </c>
+      <c r="X211" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AL211" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AM211" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN211" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP211" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ211" t="inlineStr"/>
+      <c r="AR211" t="inlineStr"/>
+      <c r="AS211" t="inlineStr"/>
+      <c r="AT211" t="inlineStr"/>
+      <c r="AU211" t="inlineStr"/>
+      <c r="AV211" t="inlineStr"/>
+      <c r="AW211" t="inlineStr"/>
+      <c r="AX211" t="inlineStr"/>
+      <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr"/>
+      <c r="BA211" t="inlineStr"/>
+      <c r="BB211" t="inlineStr"/>
+      <c r="BC211" t="inlineStr"/>
+      <c r="BD211" t="inlineStr"/>
+      <c r="BE211" t="inlineStr"/>
+      <c r="BF211" t="inlineStr"/>
+      <c r="BG211" t="inlineStr"/>
+      <c r="BH211" t="inlineStr"/>
+      <c r="BI211" t="inlineStr"/>
+      <c r="BJ211" t="inlineStr"/>
+      <c r="BK211" t="inlineStr"/>
+      <c r="BL211" t="inlineStr"/>
+      <c r="BM211" t="inlineStr"/>
+      <c r="BN211" t="inlineStr"/>
+      <c r="BO211" t="inlineStr"/>
+      <c r="BP211" t="inlineStr"/>
+      <c r="BQ211" t="inlineStr"/>
+      <c r="BR211" t="inlineStr"/>
+      <c r="BS211" t="inlineStr"/>
+      <c r="BT211" t="inlineStr"/>
+      <c r="BU211" t="inlineStr"/>
+      <c r="BV211" t="inlineStr"/>
+      <c r="BW211" t="inlineStr"/>
+      <c r="BX211" t="inlineStr"/>
+      <c r="BY211" t="inlineStr"/>
+      <c r="BZ211" t="inlineStr"/>
+      <c r="CA211" t="inlineStr"/>
+      <c r="CB211" t="inlineStr"/>
+      <c r="CC211" t="inlineStr"/>
+      <c r="CD211" t="inlineStr"/>
+      <c r="CE211" t="inlineStr"/>
+      <c r="CF211" t="inlineStr"/>
+      <c r="CG211" t="inlineStr"/>
+      <c r="CH211" t="inlineStr"/>
+      <c r="CI211" t="inlineStr"/>
+      <c r="CJ211" t="inlineStr"/>
+      <c r="CK211" t="inlineStr"/>
+      <c r="CL211" t="inlineStr"/>
+      <c r="CM211" t="n">
+        <v>20</v>
+      </c>
+      <c r="CN211" t="n">
+        <v>189</v>
+      </c>
+      <c r="CO211" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP211" t="n">
+        <v>72</v>
+      </c>
+      <c r="CQ211" t="n">
+        <v>14000</v>
+      </c>
+      <c r="CR211" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="CS211" t="n">
+        <v>78</v>
+      </c>
+      <c r="CT211" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU211" t="inlineStr"/>
+      <c r="CV211" t="inlineStr"/>
+      <c r="CW211" t="inlineStr"/>
+      <c r="CX211" t="inlineStr"/>
+      <c r="CY211" t="inlineStr"/>
+      <c r="CZ211" t="inlineStr"/>
+      <c r="DA211" t="inlineStr"/>
+      <c r="DB211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>fPQD76ac</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="n">
+        <v>45570.625</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paradis g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade saint symphorien
+  metz </t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>28786</v>
+      </c>
+      <c r="F212" t="n">
+        <v>18279</v>
+      </c>
+      <c r="G212" t="n">
+        <v>3</v>
+      </c>
+      <c r="H212" t="n">
+        <v>2</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="n">
+        <v>59</v>
+      </c>
+      <c r="N212" t="n">
+        <v>41</v>
+      </c>
+      <c r="O212" t="n">
+        <v>15</v>
+      </c>
+      <c r="P212" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>7</v>
+      </c>
+      <c r="R212" t="n">
+        <v>4</v>
+      </c>
+      <c r="S212" t="n">
+        <v>6</v>
+      </c>
+      <c r="T212" t="n">
+        <v>1</v>
+      </c>
+      <c r="U212" t="n">
+        <v>2</v>
+      </c>
+      <c r="V212" t="n">
+        <v>1</v>
+      </c>
+      <c r="W212" t="inlineStr"/>
+      <c r="X212" t="inlineStr"/>
+      <c r="Y212" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC212" t="inlineStr"/>
+      <c r="AD212" t="inlineStr"/>
+      <c r="AE212" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI212" t="inlineStr"/>
+      <c r="AJ212" t="inlineStr"/>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AL212" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AM212" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN212" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP212" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ212" t="inlineStr"/>
+      <c r="AR212" t="inlineStr"/>
+      <c r="AS212" t="n">
+        <v>631</v>
+      </c>
+      <c r="AT212" t="n">
+        <v>466</v>
+      </c>
+      <c r="AU212" t="inlineStr"/>
+      <c r="AV212" t="inlineStr"/>
+      <c r="AW212" t="inlineStr"/>
+      <c r="AX212" t="inlineStr"/>
+      <c r="AY212" t="n">
+        <v>562</v>
+      </c>
+      <c r="AZ212" t="n">
+        <v>379</v>
+      </c>
+      <c r="BA212" t="inlineStr"/>
+      <c r="BB212" t="inlineStr"/>
+      <c r="BC212" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD212" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE212" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF212" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG212" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH212" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI212" t="inlineStr"/>
+      <c r="BJ212" t="inlineStr"/>
+      <c r="BK212" t="inlineStr"/>
+      <c r="BL212" t="inlineStr"/>
+      <c r="BM212" t="inlineStr"/>
+      <c r="BN212" t="inlineStr"/>
+      <c r="BO212" t="inlineStr"/>
+      <c r="BP212" t="inlineStr"/>
+      <c r="BQ212" t="inlineStr"/>
+      <c r="BR212" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BS212" t="n">
+        <v>181</v>
+      </c>
+      <c r="BT212" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="BU212" t="inlineStr"/>
+      <c r="BV212" t="n">
+        <v>1235000</v>
+      </c>
+      <c r="BW212" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="BX212" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY212" t="inlineStr"/>
+      <c r="BZ212" t="inlineStr"/>
+      <c r="CA212" t="inlineStr"/>
+      <c r="CB212" t="inlineStr"/>
+      <c r="CC212" t="inlineStr"/>
+      <c r="CD212" t="inlineStr"/>
+      <c r="CE212" t="inlineStr"/>
+      <c r="CF212" t="n">
+        <v>22.53846153846154</v>
+      </c>
+      <c r="CG212" t="n">
+        <v>179.0769230769231</v>
+      </c>
+      <c r="CH212" t="n">
+        <v>63.46153846153846</v>
+      </c>
+      <c r="CI212" t="inlineStr"/>
+      <c r="CJ212" t="n">
+        <v>998076.9230769231</v>
+      </c>
+      <c r="CK212" t="n">
+        <v>71.84615384615384</v>
+      </c>
+      <c r="CL212" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM212" t="inlineStr"/>
+      <c r="CN212" t="inlineStr"/>
+      <c r="CO212" t="inlineStr"/>
+      <c r="CP212" t="inlineStr"/>
+      <c r="CQ212" t="inlineStr"/>
+      <c r="CR212" t="inlineStr"/>
+      <c r="CS212" t="inlineStr"/>
+      <c r="CT212" t="inlineStr"/>
+      <c r="CU212" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV212" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="CW212" t="n">
+        <v>2</v>
+      </c>
+      <c r="CX212" t="n">
+        <v>117</v>
+      </c>
+      <c r="CY212" t="inlineStr"/>
+      <c r="CZ212" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="DA212" t="n">
+        <v>150</v>
+      </c>
+      <c r="DB212" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB212"/>
+  <dimension ref="A1:DB222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57261,6 +57261,2620 @@
         <v>2</v>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>OAZJOoNr</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="n">
+        <v>45584.58333333334</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>2</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="K213" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L213" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M213" t="n">
+        <v>36</v>
+      </c>
+      <c r="N213" t="n">
+        <v>64</v>
+      </c>
+      <c r="O213" t="n">
+        <v>15</v>
+      </c>
+      <c r="P213" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>1</v>
+      </c>
+      <c r="R213" t="n">
+        <v>5</v>
+      </c>
+      <c r="S213" t="n">
+        <v>7</v>
+      </c>
+      <c r="T213" t="n">
+        <v>7</v>
+      </c>
+      <c r="U213" t="n">
+        <v>7</v>
+      </c>
+      <c r="V213" t="n">
+        <v>1</v>
+      </c>
+      <c r="W213" t="n">
+        <v>16</v>
+      </c>
+      <c r="X213" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AL213" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AM213" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN213" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP213" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ213" t="inlineStr"/>
+      <c r="AR213" t="inlineStr"/>
+      <c r="AS213" t="n">
+        <v>331</v>
+      </c>
+      <c r="AT213" t="n">
+        <v>568</v>
+      </c>
+      <c r="AU213" t="inlineStr"/>
+      <c r="AV213" t="inlineStr"/>
+      <c r="AW213" t="inlineStr"/>
+      <c r="AX213" t="inlineStr"/>
+      <c r="AY213" t="n">
+        <v>248</v>
+      </c>
+      <c r="AZ213" t="n">
+        <v>500</v>
+      </c>
+      <c r="BA213" t="inlineStr"/>
+      <c r="BB213" t="inlineStr"/>
+      <c r="BC213" t="inlineStr"/>
+      <c r="BD213" t="inlineStr"/>
+      <c r="BE213" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF213" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG213" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH213" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI213" t="inlineStr"/>
+      <c r="BJ213" t="inlineStr"/>
+      <c r="BK213" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BL213" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BM213" t="n">
+        <v>70.625</v>
+      </c>
+      <c r="BN213" t="n">
+        <v>5875</v>
+      </c>
+      <c r="BO213" t="n">
+        <v>2475000</v>
+      </c>
+      <c r="BP213" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="BQ213" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR213" t="inlineStr"/>
+      <c r="BS213" t="inlineStr"/>
+      <c r="BT213" t="inlineStr"/>
+      <c r="BU213" t="inlineStr"/>
+      <c r="BV213" t="inlineStr"/>
+      <c r="BW213" t="inlineStr"/>
+      <c r="BX213" t="inlineStr"/>
+      <c r="BY213" t="n">
+        <v>24.73333333333333</v>
+      </c>
+      <c r="BZ213" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="CA213" t="n">
+        <v>68</v>
+      </c>
+      <c r="CB213" t="n">
+        <v>3800</v>
+      </c>
+      <c r="CC213" t="n">
+        <v>1768333.333333333</v>
+      </c>
+      <c r="CD213" t="n">
+        <v>73.26666666666667</v>
+      </c>
+      <c r="CE213" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF213" t="inlineStr"/>
+      <c r="CG213" t="inlineStr"/>
+      <c r="CH213" t="inlineStr"/>
+      <c r="CI213" t="inlineStr"/>
+      <c r="CJ213" t="inlineStr"/>
+      <c r="CK213" t="inlineStr"/>
+      <c r="CL213" t="inlineStr"/>
+      <c r="CM213" t="n">
+        <v>28</v>
+      </c>
+      <c r="CN213" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="CO213" t="n">
+        <v>4</v>
+      </c>
+      <c r="CP213" t="n">
+        <v>280</v>
+      </c>
+      <c r="CQ213" t="n">
+        <v>21000</v>
+      </c>
+      <c r="CR213" t="n">
+        <v>6675000</v>
+      </c>
+      <c r="CS213" t="n">
+        <v>284</v>
+      </c>
+      <c r="CT213" t="n">
+        <v>4</v>
+      </c>
+      <c r="CU213" t="inlineStr"/>
+      <c r="CV213" t="inlineStr"/>
+      <c r="CW213" t="inlineStr"/>
+      <c r="CX213" t="inlineStr"/>
+      <c r="CY213" t="inlineStr"/>
+      <c r="CZ213" t="inlineStr"/>
+      <c r="DA213" t="inlineStr"/>
+      <c r="DB213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>WzwSMPie</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="n">
+        <v>45584.5</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dechepy b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="n">
+        <v>1</v>
+      </c>
+      <c r="H214" t="n">
+        <v>1</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="K214" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L214" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="M214" t="n">
+        <v>56</v>
+      </c>
+      <c r="N214" t="n">
+        <v>44</v>
+      </c>
+      <c r="O214" t="n">
+        <v>12</v>
+      </c>
+      <c r="P214" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>2</v>
+      </c>
+      <c r="R214" t="n">
+        <v>4</v>
+      </c>
+      <c r="S214" t="n">
+        <v>7</v>
+      </c>
+      <c r="T214" t="n">
+        <v>2</v>
+      </c>
+      <c r="U214" t="n">
+        <v>3</v>
+      </c>
+      <c r="V214" t="n">
+        <v>0</v>
+      </c>
+      <c r="W214" t="n">
+        <v>15</v>
+      </c>
+      <c r="X214" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AL214" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AM214" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ214" t="inlineStr"/>
+      <c r="AR214" t="inlineStr"/>
+      <c r="AS214" t="n">
+        <v>459</v>
+      </c>
+      <c r="AT214" t="n">
+        <v>365</v>
+      </c>
+      <c r="AU214" t="inlineStr"/>
+      <c r="AV214" t="inlineStr"/>
+      <c r="AW214" t="inlineStr"/>
+      <c r="AX214" t="inlineStr"/>
+      <c r="AY214" t="n">
+        <v>353</v>
+      </c>
+      <c r="AZ214" t="n">
+        <v>292</v>
+      </c>
+      <c r="BA214" t="inlineStr"/>
+      <c r="BB214" t="inlineStr"/>
+      <c r="BC214" t="inlineStr"/>
+      <c r="BD214" t="inlineStr"/>
+      <c r="BE214" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG214" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH214" t="n">
+        <v>11</v>
+      </c>
+      <c r="BI214" t="inlineStr"/>
+      <c r="BJ214" t="inlineStr"/>
+      <c r="BK214" t="inlineStr"/>
+      <c r="BL214" t="inlineStr"/>
+      <c r="BM214" t="inlineStr"/>
+      <c r="BN214" t="inlineStr"/>
+      <c r="BO214" t="inlineStr"/>
+      <c r="BP214" t="inlineStr"/>
+      <c r="BQ214" t="inlineStr"/>
+      <c r="BR214" t="inlineStr"/>
+      <c r="BS214" t="inlineStr"/>
+      <c r="BT214" t="inlineStr"/>
+      <c r="BU214" t="inlineStr"/>
+      <c r="BV214" t="inlineStr"/>
+      <c r="BW214" t="inlineStr"/>
+      <c r="BX214" t="inlineStr"/>
+      <c r="BY214" t="inlineStr"/>
+      <c r="BZ214" t="inlineStr"/>
+      <c r="CA214" t="inlineStr"/>
+      <c r="CB214" t="inlineStr"/>
+      <c r="CC214" t="inlineStr"/>
+      <c r="CD214" t="inlineStr"/>
+      <c r="CE214" t="inlineStr"/>
+      <c r="CF214" t="inlineStr"/>
+      <c r="CG214" t="inlineStr"/>
+      <c r="CH214" t="inlineStr"/>
+      <c r="CI214" t="inlineStr"/>
+      <c r="CJ214" t="inlineStr"/>
+      <c r="CK214" t="inlineStr"/>
+      <c r="CL214" t="inlineStr"/>
+      <c r="CM214" t="inlineStr"/>
+      <c r="CN214" t="inlineStr"/>
+      <c r="CO214" t="inlineStr"/>
+      <c r="CP214" t="inlineStr"/>
+      <c r="CQ214" t="inlineStr"/>
+      <c r="CR214" t="inlineStr"/>
+      <c r="CS214" t="inlineStr"/>
+      <c r="CT214" t="inlineStr"/>
+      <c r="CU214" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV214" t="n">
+        <v>189</v>
+      </c>
+      <c r="CW214" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX214" t="n">
+        <v>72</v>
+      </c>
+      <c r="CY214" t="n">
+        <v>14000</v>
+      </c>
+      <c r="CZ214" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="DA214" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB214" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="n">
+        <v>45583.65625</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F215" t="n">
+        <v>7246</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="K215" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M215" t="n">
+        <v>51</v>
+      </c>
+      <c r="N215" t="n">
+        <v>49</v>
+      </c>
+      <c r="O215" t="n">
+        <v>14</v>
+      </c>
+      <c r="P215" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>4</v>
+      </c>
+      <c r="R215" t="n">
+        <v>1</v>
+      </c>
+      <c r="S215" t="n">
+        <v>7</v>
+      </c>
+      <c r="T215" t="n">
+        <v>2</v>
+      </c>
+      <c r="U215" t="n">
+        <v>3</v>
+      </c>
+      <c r="V215" t="n">
+        <v>0</v>
+      </c>
+      <c r="W215" t="n">
+        <v>14</v>
+      </c>
+      <c r="X215" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AL215" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AM215" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS215" t="n">
+        <v>458</v>
+      </c>
+      <c r="AT215" t="n">
+        <v>444</v>
+      </c>
+      <c r="AU215" t="inlineStr"/>
+      <c r="AV215" t="inlineStr"/>
+      <c r="AW215" t="inlineStr"/>
+      <c r="AX215" t="inlineStr"/>
+      <c r="AY215" t="n">
+        <v>385</v>
+      </c>
+      <c r="AZ215" t="n">
+        <v>358</v>
+      </c>
+      <c r="BA215" t="inlineStr"/>
+      <c r="BB215" t="inlineStr"/>
+      <c r="BC215" t="inlineStr"/>
+      <c r="BD215" t="inlineStr"/>
+      <c r="BE215" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF215" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG215" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH215" t="n">
+        <v>18</v>
+      </c>
+      <c r="BI215" t="inlineStr"/>
+      <c r="BJ215" t="inlineStr"/>
+      <c r="BK215" t="inlineStr"/>
+      <c r="BL215" t="inlineStr"/>
+      <c r="BM215" t="inlineStr"/>
+      <c r="BN215" t="inlineStr"/>
+      <c r="BO215" t="inlineStr"/>
+      <c r="BP215" t="inlineStr"/>
+      <c r="BQ215" t="inlineStr"/>
+      <c r="BR215" t="inlineStr"/>
+      <c r="BS215" t="inlineStr"/>
+      <c r="BT215" t="inlineStr"/>
+      <c r="BU215" t="inlineStr"/>
+      <c r="BV215" t="inlineStr"/>
+      <c r="BW215" t="inlineStr"/>
+      <c r="BX215" t="inlineStr"/>
+      <c r="BY215" t="inlineStr"/>
+      <c r="BZ215" t="inlineStr"/>
+      <c r="CA215" t="inlineStr"/>
+      <c r="CB215" t="inlineStr"/>
+      <c r="CC215" t="inlineStr"/>
+      <c r="CD215" t="inlineStr"/>
+      <c r="CE215" t="inlineStr"/>
+      <c r="CF215" t="inlineStr"/>
+      <c r="CG215" t="inlineStr"/>
+      <c r="CH215" t="inlineStr"/>
+      <c r="CI215" t="inlineStr"/>
+      <c r="CJ215" t="inlineStr"/>
+      <c r="CK215" t="inlineStr"/>
+      <c r="CL215" t="inlineStr"/>
+      <c r="CM215" t="inlineStr"/>
+      <c r="CN215" t="inlineStr"/>
+      <c r="CO215" t="inlineStr"/>
+      <c r="CP215" t="inlineStr"/>
+      <c r="CQ215" t="inlineStr"/>
+      <c r="CR215" t="inlineStr"/>
+      <c r="CS215" t="inlineStr"/>
+      <c r="CT215" t="inlineStr"/>
+      <c r="CU215" t="n">
+        <v>28</v>
+      </c>
+      <c r="CV215" t="n">
+        <v>187</v>
+      </c>
+      <c r="CW215" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX215" t="n">
+        <v>75</v>
+      </c>
+      <c r="CY215" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CZ215" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="DA215" t="n">
+        <v>76</v>
+      </c>
+      <c r="DB215" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>xlCidXdD</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="n">
+        <v>45584.375</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taleb a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>12097</v>
+      </c>
+      <c r="F216" t="n">
+        <v>5956</v>
+      </c>
+      <c r="G216" t="n">
+        <v>3</v>
+      </c>
+      <c r="H216" t="n">
+        <v>1</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="n">
+        <v>42</v>
+      </c>
+      <c r="N216" t="n">
+        <v>58</v>
+      </c>
+      <c r="O216" t="n">
+        <v>15</v>
+      </c>
+      <c r="P216" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>9</v>
+      </c>
+      <c r="R216" t="n">
+        <v>4</v>
+      </c>
+      <c r="S216" t="n">
+        <v>3</v>
+      </c>
+      <c r="T216" t="n">
+        <v>8</v>
+      </c>
+      <c r="U216" t="n">
+        <v>3</v>
+      </c>
+      <c r="V216" t="n">
+        <v>2</v>
+      </c>
+      <c r="W216" t="inlineStr"/>
+      <c r="X216" t="inlineStr"/>
+      <c r="Y216" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC216" t="inlineStr"/>
+      <c r="AD216" t="inlineStr"/>
+      <c r="AE216" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AL216" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AM216" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ216" t="inlineStr"/>
+      <c r="AR216" t="inlineStr"/>
+      <c r="AS216" t="n">
+        <v>363</v>
+      </c>
+      <c r="AT216" t="n">
+        <v>506</v>
+      </c>
+      <c r="AU216" t="inlineStr"/>
+      <c r="AV216" t="inlineStr"/>
+      <c r="AW216" t="inlineStr"/>
+      <c r="AX216" t="inlineStr"/>
+      <c r="AY216" t="n">
+        <v>274</v>
+      </c>
+      <c r="AZ216" t="n">
+        <v>409</v>
+      </c>
+      <c r="BA216" t="inlineStr"/>
+      <c r="BB216" t="inlineStr"/>
+      <c r="BC216" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD216" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE216" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF216" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG216" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH216" t="n">
+        <v>16</v>
+      </c>
+      <c r="BI216" t="inlineStr"/>
+      <c r="BJ216" t="inlineStr"/>
+      <c r="BK216" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="BL216" t="n">
+        <v>177.2</v>
+      </c>
+      <c r="BM216" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="BN216" t="inlineStr"/>
+      <c r="BO216" t="n">
+        <v>1125000</v>
+      </c>
+      <c r="BP216" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BQ216" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR216" t="inlineStr"/>
+      <c r="BS216" t="inlineStr"/>
+      <c r="BT216" t="inlineStr"/>
+      <c r="BU216" t="inlineStr"/>
+      <c r="BV216" t="inlineStr"/>
+      <c r="BW216" t="inlineStr"/>
+      <c r="BX216" t="inlineStr"/>
+      <c r="BY216" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="BZ216" t="n">
+        <v>184.4166666666667</v>
+      </c>
+      <c r="CA216" t="n">
+        <v>65.91666666666667</v>
+      </c>
+      <c r="CB216" t="inlineStr"/>
+      <c r="CC216" t="n">
+        <v>1137500</v>
+      </c>
+      <c r="CD216" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="CE216" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF216" t="n">
+        <v>24.92307692307692</v>
+      </c>
+      <c r="CG216" t="n">
+        <v>179.1538461538462</v>
+      </c>
+      <c r="CH216" t="n">
+        <v>63.46153846153846</v>
+      </c>
+      <c r="CI216" t="inlineStr"/>
+      <c r="CJ216" t="n">
+        <v>646153.8461538461</v>
+      </c>
+      <c r="CK216" t="n">
+        <v>69.30769230769231</v>
+      </c>
+      <c r="CL216" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM216" t="n">
+        <v>18</v>
+      </c>
+      <c r="CN216" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="CO216" t="n">
+        <v>2</v>
+      </c>
+      <c r="CP216" t="n">
+        <v>117</v>
+      </c>
+      <c r="CQ216" t="inlineStr"/>
+      <c r="CR216" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="CS216" t="n">
+        <v>150</v>
+      </c>
+      <c r="CT216" t="n">
+        <v>2</v>
+      </c>
+      <c r="CU216" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="CV216" t="n">
+        <v>180.8</v>
+      </c>
+      <c r="CW216" t="n">
+        <v>5</v>
+      </c>
+      <c r="CX216" t="n">
+        <v>339</v>
+      </c>
+      <c r="CY216" t="n">
+        <v>14000</v>
+      </c>
+      <c r="CZ216" t="n">
+        <v>4325000</v>
+      </c>
+      <c r="DA216" t="n">
+        <v>346</v>
+      </c>
+      <c r="DB216" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>lbfDWDYP</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="n">
+        <v>45583.625</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade armand cesari
+  bastia </t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>16048</v>
+      </c>
+      <c r="F217" t="n">
+        <v>9967</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="n">
+        <v>58</v>
+      </c>
+      <c r="N217" t="n">
+        <v>42</v>
+      </c>
+      <c r="O217" t="n">
+        <v>20</v>
+      </c>
+      <c r="P217" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>4</v>
+      </c>
+      <c r="R217" t="n">
+        <v>2</v>
+      </c>
+      <c r="S217" t="n">
+        <v>10</v>
+      </c>
+      <c r="T217" t="n">
+        <v>1</v>
+      </c>
+      <c r="U217" t="n">
+        <v>6</v>
+      </c>
+      <c r="V217" t="n">
+        <v>3</v>
+      </c>
+      <c r="W217" t="inlineStr"/>
+      <c r="X217" t="inlineStr"/>
+      <c r="Y217" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA217" t="inlineStr"/>
+      <c r="AB217" t="inlineStr"/>
+      <c r="AC217" t="inlineStr"/>
+      <c r="AD217" t="inlineStr"/>
+      <c r="AE217" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AL217" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="AM217" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS217" t="n">
+        <v>525</v>
+      </c>
+      <c r="AT217" t="n">
+        <v>363</v>
+      </c>
+      <c r="AU217" t="inlineStr"/>
+      <c r="AV217" t="inlineStr"/>
+      <c r="AW217" t="inlineStr"/>
+      <c r="AX217" t="inlineStr"/>
+      <c r="AY217" t="n">
+        <v>444</v>
+      </c>
+      <c r="AZ217" t="n">
+        <v>262</v>
+      </c>
+      <c r="BA217" t="inlineStr"/>
+      <c r="BB217" t="inlineStr"/>
+      <c r="BC217" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD217" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE217" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF217" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG217" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH217" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI217" t="inlineStr"/>
+      <c r="BJ217" t="inlineStr"/>
+      <c r="BK217" t="inlineStr"/>
+      <c r="BL217" t="inlineStr"/>
+      <c r="BM217" t="inlineStr"/>
+      <c r="BN217" t="inlineStr"/>
+      <c r="BO217" t="inlineStr"/>
+      <c r="BP217" t="inlineStr"/>
+      <c r="BQ217" t="inlineStr"/>
+      <c r="BR217" t="inlineStr"/>
+      <c r="BS217" t="inlineStr"/>
+      <c r="BT217" t="inlineStr"/>
+      <c r="BU217" t="inlineStr"/>
+      <c r="BV217" t="inlineStr"/>
+      <c r="BW217" t="inlineStr"/>
+      <c r="BX217" t="inlineStr"/>
+      <c r="BY217" t="n">
+        <v>24.21428571428572</v>
+      </c>
+      <c r="BZ217" t="n">
+        <v>180.4285714285714</v>
+      </c>
+      <c r="CA217" t="n">
+        <v>61.71428571428572</v>
+      </c>
+      <c r="CB217" t="inlineStr"/>
+      <c r="CC217" t="n">
+        <v>610714.2857142857</v>
+      </c>
+      <c r="CD217" t="n">
+        <v>66.07142857142857</v>
+      </c>
+      <c r="CE217" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF217" t="inlineStr"/>
+      <c r="CG217" t="inlineStr"/>
+      <c r="CH217" t="inlineStr"/>
+      <c r="CI217" t="inlineStr"/>
+      <c r="CJ217" t="inlineStr"/>
+      <c r="CK217" t="inlineStr"/>
+      <c r="CL217" t="inlineStr"/>
+      <c r="CM217" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="CN217" t="n">
+        <v>179</v>
+      </c>
+      <c r="CO217" t="n">
+        <v>2</v>
+      </c>
+      <c r="CP217" t="n">
+        <v>131</v>
+      </c>
+      <c r="CQ217" t="inlineStr"/>
+      <c r="CR217" t="n">
+        <v>1825000</v>
+      </c>
+      <c r="CS217" t="n">
+        <v>142</v>
+      </c>
+      <c r="CT217" t="n">
+        <v>2</v>
+      </c>
+      <c r="CU217" t="inlineStr"/>
+      <c r="CV217" t="inlineStr"/>
+      <c r="CW217" t="inlineStr"/>
+      <c r="CX217" t="inlineStr"/>
+      <c r="CY217" t="inlineStr"/>
+      <c r="CZ217" t="inlineStr"/>
+      <c r="DA217" t="inlineStr"/>
+      <c r="DB217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>d47R8AtJ</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="n">
+        <v>45583.625</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">benchabane f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>20068</v>
+      </c>
+      <c r="F218" t="n">
+        <v>5916</v>
+      </c>
+      <c r="G218" t="n">
+        <v>2</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="n">
+        <v>35</v>
+      </c>
+      <c r="N218" t="n">
+        <v>65</v>
+      </c>
+      <c r="O218" t="n">
+        <v>13</v>
+      </c>
+      <c r="P218" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>5</v>
+      </c>
+      <c r="R218" t="n">
+        <v>7</v>
+      </c>
+      <c r="S218" t="n">
+        <v>6</v>
+      </c>
+      <c r="T218" t="n">
+        <v>5</v>
+      </c>
+      <c r="U218" t="n">
+        <v>2</v>
+      </c>
+      <c r="V218" t="n">
+        <v>1</v>
+      </c>
+      <c r="W218" t="inlineStr"/>
+      <c r="X218" t="inlineStr"/>
+      <c r="Y218" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC218" t="inlineStr"/>
+      <c r="AD218" t="inlineStr"/>
+      <c r="AE218" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AL218" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AM218" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ218" t="inlineStr"/>
+      <c r="AR218" t="inlineStr"/>
+      <c r="AS218" t="n">
+        <v>338</v>
+      </c>
+      <c r="AT218" t="n">
+        <v>632</v>
+      </c>
+      <c r="AU218" t="inlineStr"/>
+      <c r="AV218" t="inlineStr"/>
+      <c r="AW218" t="inlineStr"/>
+      <c r="AX218" t="inlineStr"/>
+      <c r="AY218" t="n">
+        <v>250</v>
+      </c>
+      <c r="AZ218" t="n">
+        <v>548</v>
+      </c>
+      <c r="BA218" t="inlineStr"/>
+      <c r="BB218" t="inlineStr"/>
+      <c r="BC218" t="n">
+        <v>46</v>
+      </c>
+      <c r="BD218" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE218" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF218" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG218" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH218" t="n">
+        <v>18</v>
+      </c>
+      <c r="BI218" t="inlineStr"/>
+      <c r="BJ218" t="inlineStr"/>
+      <c r="BK218" t="n">
+        <v>26.22222222222222</v>
+      </c>
+      <c r="BL218" t="n">
+        <v>184.2222222222222</v>
+      </c>
+      <c r="BM218" t="n">
+        <v>67.11111111111111</v>
+      </c>
+      <c r="BN218" t="n">
+        <v>2888.888888888889</v>
+      </c>
+      <c r="BO218" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BP218" t="n">
+        <v>70.44444444444444</v>
+      </c>
+      <c r="BQ218" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR218" t="inlineStr"/>
+      <c r="BS218" t="inlineStr"/>
+      <c r="BT218" t="inlineStr"/>
+      <c r="BU218" t="inlineStr"/>
+      <c r="BV218" t="inlineStr"/>
+      <c r="BW218" t="inlineStr"/>
+      <c r="BX218" t="inlineStr"/>
+      <c r="BY218" t="n">
+        <v>23.22222222222222</v>
+      </c>
+      <c r="BZ218" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="CA218" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="CB218" t="inlineStr"/>
+      <c r="CC218" t="n">
+        <v>1454166.666666667</v>
+      </c>
+      <c r="CD218" t="n">
+        <v>71.44444444444444</v>
+      </c>
+      <c r="CE218" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF218" t="inlineStr"/>
+      <c r="CG218" t="inlineStr"/>
+      <c r="CH218" t="inlineStr"/>
+      <c r="CI218" t="inlineStr"/>
+      <c r="CJ218" t="inlineStr"/>
+      <c r="CK218" t="inlineStr"/>
+      <c r="CL218" t="inlineStr"/>
+      <c r="CM218" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="CN218" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="CO218" t="n">
+        <v>2</v>
+      </c>
+      <c r="CP218" t="n">
+        <v>139</v>
+      </c>
+      <c r="CQ218" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CR218" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="CS218" t="n">
+        <v>139</v>
+      </c>
+      <c r="CT218" t="n">
+        <v>2</v>
+      </c>
+      <c r="CU218" t="n">
+        <v>23</v>
+      </c>
+      <c r="CV218" t="n">
+        <v>186</v>
+      </c>
+      <c r="CW218" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX218" t="n">
+        <v>69</v>
+      </c>
+      <c r="CY218" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CZ218" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="DA218" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB218" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>4zEqbgS0</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="n">
+        <v>45583.625</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rosier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de roudourou
+  guingamp </t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>19060</v>
+      </c>
+      <c r="F219" t="n">
+        <v>8112</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>1</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="n">
+        <v>61</v>
+      </c>
+      <c r="N219" t="n">
+        <v>39</v>
+      </c>
+      <c r="O219" t="n">
+        <v>15</v>
+      </c>
+      <c r="P219" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>6</v>
+      </c>
+      <c r="R219" t="n">
+        <v>7</v>
+      </c>
+      <c r="S219" t="n">
+        <v>7</v>
+      </c>
+      <c r="T219" t="n">
+        <v>4</v>
+      </c>
+      <c r="U219" t="n">
+        <v>2</v>
+      </c>
+      <c r="V219" t="n">
+        <v>2</v>
+      </c>
+      <c r="W219" t="inlineStr"/>
+      <c r="X219" t="inlineStr"/>
+      <c r="Y219" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC219" t="inlineStr"/>
+      <c r="AD219" t="inlineStr"/>
+      <c r="AE219" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="AL219" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AM219" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN219" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP219" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ219" t="inlineStr"/>
+      <c r="AR219" t="inlineStr"/>
+      <c r="AS219" t="n">
+        <v>638</v>
+      </c>
+      <c r="AT219" t="n">
+        <v>361</v>
+      </c>
+      <c r="AU219" t="inlineStr"/>
+      <c r="AV219" t="inlineStr"/>
+      <c r="AW219" t="inlineStr"/>
+      <c r="AX219" t="inlineStr"/>
+      <c r="AY219" t="n">
+        <v>546</v>
+      </c>
+      <c r="AZ219" t="n">
+        <v>256</v>
+      </c>
+      <c r="BA219" t="inlineStr"/>
+      <c r="BB219" t="inlineStr"/>
+      <c r="BC219" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD219" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE219" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF219" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG219" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH219" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI219" t="inlineStr"/>
+      <c r="BJ219" t="inlineStr"/>
+      <c r="BK219" t="n">
+        <v>24.36363636363636</v>
+      </c>
+      <c r="BL219" t="n">
+        <v>180.6363636363636</v>
+      </c>
+      <c r="BM219" t="n">
+        <v>64.72727272727273</v>
+      </c>
+      <c r="BN219" t="n">
+        <v>1818.181818181818</v>
+      </c>
+      <c r="BO219" t="n">
+        <v>954545.4545454546</v>
+      </c>
+      <c r="BP219" t="n">
+        <v>69.63636363636364</v>
+      </c>
+      <c r="BQ219" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR219" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="BS219" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="BT219" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="BU219" t="inlineStr"/>
+      <c r="BV219" t="n">
+        <v>1118750</v>
+      </c>
+      <c r="BW219" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="BX219" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY219" t="n">
+        <v>23.14285714285714</v>
+      </c>
+      <c r="BZ219" t="n">
+        <v>174</v>
+      </c>
+      <c r="CA219" t="n">
+        <v>64.71428571428571</v>
+      </c>
+      <c r="CB219" t="n">
+        <v>2142.857142857143</v>
+      </c>
+      <c r="CC219" t="n">
+        <v>1246428.571428571</v>
+      </c>
+      <c r="CD219" t="n">
+        <v>71.85714285714286</v>
+      </c>
+      <c r="CE219" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF219" t="n">
+        <v>26.72222222222222</v>
+      </c>
+      <c r="CG219" t="n">
+        <v>180.5555555555555</v>
+      </c>
+      <c r="CH219" t="n">
+        <v>65.22222222222223</v>
+      </c>
+      <c r="CI219" t="inlineStr"/>
+      <c r="CJ219" t="n">
+        <v>784722.2222222222</v>
+      </c>
+      <c r="CK219" t="n">
+        <v>68.83333333333333</v>
+      </c>
+      <c r="CL219" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM219" t="inlineStr"/>
+      <c r="CN219" t="inlineStr"/>
+      <c r="CO219" t="inlineStr"/>
+      <c r="CP219" t="inlineStr"/>
+      <c r="CQ219" t="inlineStr"/>
+      <c r="CR219" t="inlineStr"/>
+      <c r="CS219" t="inlineStr"/>
+      <c r="CT219" t="inlineStr"/>
+      <c r="CU219" t="n">
+        <v>29</v>
+      </c>
+      <c r="CV219" t="n">
+        <v>170</v>
+      </c>
+      <c r="CW219" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX219" t="n">
+        <v>66</v>
+      </c>
+      <c r="CY219" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CZ219" t="n">
+        <v>750000</v>
+      </c>
+      <c r="DA219" t="n">
+        <v>66</v>
+      </c>
+      <c r="DB219" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>8UeBChsf</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="n">
+        <v>45583.625</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bouille t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le basser
+  laval </t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>11017</v>
+      </c>
+      <c r="F220" t="n">
+        <v>5948</v>
+      </c>
+      <c r="G220" t="n">
+        <v>3</v>
+      </c>
+      <c r="H220" t="n">
+        <v>2</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="n">
+        <v>31</v>
+      </c>
+      <c r="N220" t="n">
+        <v>69</v>
+      </c>
+      <c r="O220" t="n">
+        <v>3</v>
+      </c>
+      <c r="P220" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>3</v>
+      </c>
+      <c r="R220" t="n">
+        <v>7</v>
+      </c>
+      <c r="S220" t="n">
+        <v>0</v>
+      </c>
+      <c r="T220" t="n">
+        <v>6</v>
+      </c>
+      <c r="U220" t="n">
+        <v>0</v>
+      </c>
+      <c r="V220" t="n">
+        <v>1</v>
+      </c>
+      <c r="W220" t="inlineStr"/>
+      <c r="X220" t="inlineStr"/>
+      <c r="Y220" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC220" t="inlineStr"/>
+      <c r="AD220" t="inlineStr"/>
+      <c r="AE220" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AL220" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AM220" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ220" t="inlineStr"/>
+      <c r="AR220" t="inlineStr"/>
+      <c r="AS220" t="n">
+        <v>287</v>
+      </c>
+      <c r="AT220" t="n">
+        <v>663</v>
+      </c>
+      <c r="AU220" t="inlineStr"/>
+      <c r="AV220" t="inlineStr"/>
+      <c r="AW220" t="inlineStr"/>
+      <c r="AX220" t="inlineStr"/>
+      <c r="AY220" t="n">
+        <v>191</v>
+      </c>
+      <c r="AZ220" t="n">
+        <v>550</v>
+      </c>
+      <c r="BA220" t="inlineStr"/>
+      <c r="BB220" t="inlineStr"/>
+      <c r="BC220" t="n">
+        <v>33</v>
+      </c>
+      <c r="BD220" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE220" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF220" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG220" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH220" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI220" t="inlineStr"/>
+      <c r="BJ220" t="inlineStr"/>
+      <c r="BK220" t="inlineStr"/>
+      <c r="BL220" t="inlineStr"/>
+      <c r="BM220" t="inlineStr"/>
+      <c r="BN220" t="inlineStr"/>
+      <c r="BO220" t="inlineStr"/>
+      <c r="BP220" t="inlineStr"/>
+      <c r="BQ220" t="inlineStr"/>
+      <c r="BR220" t="inlineStr"/>
+      <c r="BS220" t="inlineStr"/>
+      <c r="BT220" t="inlineStr"/>
+      <c r="BU220" t="inlineStr"/>
+      <c r="BV220" t="inlineStr"/>
+      <c r="BW220" t="inlineStr"/>
+      <c r="BX220" t="inlineStr"/>
+      <c r="BY220" t="n">
+        <v>26.94736842105263</v>
+      </c>
+      <c r="BZ220" t="n">
+        <v>184.4736842105263</v>
+      </c>
+      <c r="CA220" t="n">
+        <v>66</v>
+      </c>
+      <c r="CB220" t="n">
+        <v>2631.578947368421</v>
+      </c>
+      <c r="CC220" t="n">
+        <v>1041578.947368421</v>
+      </c>
+      <c r="CD220" t="n">
+        <v>70.89473684210526</v>
+      </c>
+      <c r="CE220" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF220" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="CG220" t="n">
+        <v>178</v>
+      </c>
+      <c r="CH220" t="n">
+        <v>61.875</v>
+      </c>
+      <c r="CI220" t="inlineStr"/>
+      <c r="CJ220" t="n">
+        <v>784375</v>
+      </c>
+      <c r="CK220" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="CL220" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM220" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="CN220" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="CO220" t="n">
+        <v>2</v>
+      </c>
+      <c r="CP220" t="n">
+        <v>131</v>
+      </c>
+      <c r="CQ220" t="n">
+        <v>4000</v>
+      </c>
+      <c r="CR220" t="n">
+        <v>925000</v>
+      </c>
+      <c r="CS220" t="n">
+        <v>131</v>
+      </c>
+      <c r="CT220" t="n">
+        <v>2</v>
+      </c>
+      <c r="CU220" t="inlineStr"/>
+      <c r="CV220" t="inlineStr"/>
+      <c r="CW220" t="inlineStr"/>
+      <c r="CX220" t="inlineStr"/>
+      <c r="CY220" t="inlineStr"/>
+      <c r="CZ220" t="inlineStr"/>
+      <c r="DA220" t="inlineStr"/>
+      <c r="DB220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>88Kz0Fcl</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="n">
+        <v>45583.625</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landry r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis turcan
+  martigues </t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>11500</v>
+      </c>
+      <c r="F221" t="n">
+        <v>409</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>2</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="n">
+        <v>59</v>
+      </c>
+      <c r="N221" t="n">
+        <v>41</v>
+      </c>
+      <c r="O221" t="n">
+        <v>12</v>
+      </c>
+      <c r="P221" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>6</v>
+      </c>
+      <c r="R221" t="n">
+        <v>6</v>
+      </c>
+      <c r="S221" t="n">
+        <v>4</v>
+      </c>
+      <c r="T221" t="n">
+        <v>6</v>
+      </c>
+      <c r="U221" t="n">
+        <v>2</v>
+      </c>
+      <c r="V221" t="n">
+        <v>0</v>
+      </c>
+      <c r="W221" t="inlineStr"/>
+      <c r="X221" t="inlineStr"/>
+      <c r="Y221" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC221" t="inlineStr"/>
+      <c r="AD221" t="inlineStr"/>
+      <c r="AE221" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AL221" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AM221" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ221" t="inlineStr"/>
+      <c r="AR221" t="inlineStr"/>
+      <c r="AS221" t="n">
+        <v>549</v>
+      </c>
+      <c r="AT221" t="n">
+        <v>414</v>
+      </c>
+      <c r="AU221" t="inlineStr"/>
+      <c r="AV221" t="inlineStr"/>
+      <c r="AW221" t="inlineStr"/>
+      <c r="AX221" t="inlineStr"/>
+      <c r="AY221" t="n">
+        <v>452</v>
+      </c>
+      <c r="AZ221" t="n">
+        <v>334</v>
+      </c>
+      <c r="BA221" t="inlineStr"/>
+      <c r="BB221" t="inlineStr"/>
+      <c r="BC221" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>33</v>
+      </c>
+      <c r="BE221" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF221" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG221" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH221" t="n">
+        <v>17</v>
+      </c>
+      <c r="BI221" t="inlineStr"/>
+      <c r="BJ221" t="inlineStr"/>
+      <c r="BK221" t="inlineStr"/>
+      <c r="BL221" t="inlineStr"/>
+      <c r="BM221" t="inlineStr"/>
+      <c r="BN221" t="inlineStr"/>
+      <c r="BO221" t="inlineStr"/>
+      <c r="BP221" t="inlineStr"/>
+      <c r="BQ221" t="inlineStr"/>
+      <c r="BR221" t="inlineStr"/>
+      <c r="BS221" t="inlineStr"/>
+      <c r="BT221" t="inlineStr"/>
+      <c r="BU221" t="inlineStr"/>
+      <c r="BV221" t="inlineStr"/>
+      <c r="BW221" t="inlineStr"/>
+      <c r="BX221" t="inlineStr"/>
+      <c r="BY221" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="BZ221" t="n">
+        <v>183</v>
+      </c>
+      <c r="CA221" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="CB221" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CC221" t="n">
+        <v>840000</v>
+      </c>
+      <c r="CD221" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="CE221" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF221" t="n">
+        <v>20.88888888888889</v>
+      </c>
+      <c r="CG221" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="CH221" t="n">
+        <v>62</v>
+      </c>
+      <c r="CI221" t="inlineStr"/>
+      <c r="CJ221" t="n">
+        <v>761111.1111111111</v>
+      </c>
+      <c r="CK221" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="CL221" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM221" t="inlineStr"/>
+      <c r="CN221" t="inlineStr"/>
+      <c r="CO221" t="inlineStr"/>
+      <c r="CP221" t="inlineStr"/>
+      <c r="CQ221" t="inlineStr"/>
+      <c r="CR221" t="inlineStr"/>
+      <c r="CS221" t="inlineStr"/>
+      <c r="CT221" t="inlineStr"/>
+      <c r="CU221" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="CV221" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="CW221" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX221" t="n">
+        <v>191</v>
+      </c>
+      <c r="CY221" t="inlineStr"/>
+      <c r="CZ221" t="n">
+        <v>2075000</v>
+      </c>
+      <c r="DA221" t="n">
+        <v>204</v>
+      </c>
+      <c r="DB221" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>nF72EECs</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="n">
+        <v>45583.625</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gaillouste p 
+  fra </t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bauer
+  paris   saint ouen </t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F222" t="n">
+        <v>4643</v>
+      </c>
+      <c r="G222" t="n">
+        <v>2</v>
+      </c>
+      <c r="H222" t="n">
+        <v>2</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="n">
+        <v>52</v>
+      </c>
+      <c r="N222" t="n">
+        <v>48</v>
+      </c>
+      <c r="O222" t="n">
+        <v>17</v>
+      </c>
+      <c r="P222" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>10</v>
+      </c>
+      <c r="R222" t="n">
+        <v>2</v>
+      </c>
+      <c r="S222" t="n">
+        <v>5</v>
+      </c>
+      <c r="T222" t="n">
+        <v>3</v>
+      </c>
+      <c r="U222" t="n">
+        <v>2</v>
+      </c>
+      <c r="V222" t="n">
+        <v>5</v>
+      </c>
+      <c r="W222" t="inlineStr"/>
+      <c r="X222" t="inlineStr"/>
+      <c r="Y222" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC222" t="inlineStr"/>
+      <c r="AD222" t="inlineStr"/>
+      <c r="AE222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AL222" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AM222" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN222" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP222" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ222" t="inlineStr"/>
+      <c r="AR222" t="inlineStr"/>
+      <c r="AS222" t="n">
+        <v>504</v>
+      </c>
+      <c r="AT222" t="n">
+        <v>410</v>
+      </c>
+      <c r="AU222" t="inlineStr"/>
+      <c r="AV222" t="inlineStr"/>
+      <c r="AW222" t="inlineStr"/>
+      <c r="AX222" t="inlineStr"/>
+      <c r="AY222" t="n">
+        <v>430</v>
+      </c>
+      <c r="AZ222" t="n">
+        <v>336</v>
+      </c>
+      <c r="BA222" t="inlineStr"/>
+      <c r="BB222" t="inlineStr"/>
+      <c r="BC222" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD222" t="n">
+        <v>35</v>
+      </c>
+      <c r="BE222" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF222" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG222" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH222" t="n">
+        <v>19</v>
+      </c>
+      <c r="BI222" t="inlineStr"/>
+      <c r="BJ222" t="inlineStr"/>
+      <c r="BK222" t="inlineStr"/>
+      <c r="BL222" t="inlineStr"/>
+      <c r="BM222" t="inlineStr"/>
+      <c r="BN222" t="inlineStr"/>
+      <c r="BO222" t="inlineStr"/>
+      <c r="BP222" t="inlineStr"/>
+      <c r="BQ222" t="inlineStr"/>
+      <c r="BR222" t="n">
+        <v>24.77777777777778</v>
+      </c>
+      <c r="BS222" t="n">
+        <v>182.5555555555555</v>
+      </c>
+      <c r="BT222" t="n">
+        <v>67.11111111111111</v>
+      </c>
+      <c r="BU222" t="inlineStr"/>
+      <c r="BV222" t="n">
+        <v>1430555.555555556</v>
+      </c>
+      <c r="BW222" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="BX222" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY222" t="inlineStr"/>
+      <c r="BZ222" t="inlineStr"/>
+      <c r="CA222" t="inlineStr"/>
+      <c r="CB222" t="inlineStr"/>
+      <c r="CC222" t="inlineStr"/>
+      <c r="CD222" t="inlineStr"/>
+      <c r="CE222" t="inlineStr"/>
+      <c r="CF222" t="n">
+        <v>22.08333333333333</v>
+      </c>
+      <c r="CG222" t="n">
+        <v>180</v>
+      </c>
+      <c r="CH222" t="n">
+        <v>64.58333333333333</v>
+      </c>
+      <c r="CI222" t="inlineStr"/>
+      <c r="CJ222" t="n">
+        <v>1343750</v>
+      </c>
+      <c r="CK222" t="n">
+        <v>75</v>
+      </c>
+      <c r="CL222" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM222" t="n">
+        <v>25</v>
+      </c>
+      <c r="CN222" t="n">
+        <v>182</v>
+      </c>
+      <c r="CO222" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP222" t="n">
+        <v>68</v>
+      </c>
+      <c r="CQ222" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CR222" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="CS222" t="n">
+        <v>70</v>
+      </c>
+      <c r="CT222" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU222" t="n">
+        <v>26</v>
+      </c>
+      <c r="CV222" t="n">
+        <v>183</v>
+      </c>
+      <c r="CW222" t="n">
+        <v>2</v>
+      </c>
+      <c r="CX222" t="n">
+        <v>131</v>
+      </c>
+      <c r="CY222" t="inlineStr"/>
+      <c r="CZ222" t="n">
+        <v>2050000</v>
+      </c>
+      <c r="DA222" t="n">
+        <v>145</v>
+      </c>
+      <c r="DB222" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB222"/>
+  <dimension ref="A1:DB230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59875,6 +59875,1974 @@
         <v>2</v>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>nVutWTU8</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="n">
+        <v>45585.65625</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F223" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>5</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="K223" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L223" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="M223" t="n">
+        <v>35</v>
+      </c>
+      <c r="N223" t="n">
+        <v>65</v>
+      </c>
+      <c r="O223" t="n">
+        <v>13</v>
+      </c>
+      <c r="P223" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>5</v>
+      </c>
+      <c r="R223" t="n">
+        <v>10</v>
+      </c>
+      <c r="S223" t="n">
+        <v>3</v>
+      </c>
+      <c r="T223" t="n">
+        <v>9</v>
+      </c>
+      <c r="U223" t="n">
+        <v>5</v>
+      </c>
+      <c r="V223" t="n">
+        <v>2</v>
+      </c>
+      <c r="W223" t="n">
+        <v>17</v>
+      </c>
+      <c r="X223" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ223" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="AL223" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="AM223" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN223" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP223" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS223" t="n">
+        <v>293</v>
+      </c>
+      <c r="AT223" t="n">
+        <v>562</v>
+      </c>
+      <c r="AU223" t="inlineStr"/>
+      <c r="AV223" t="inlineStr"/>
+      <c r="AW223" t="inlineStr"/>
+      <c r="AX223" t="inlineStr"/>
+      <c r="AY223" t="n">
+        <v>238</v>
+      </c>
+      <c r="AZ223" t="n">
+        <v>513</v>
+      </c>
+      <c r="BA223" t="inlineStr"/>
+      <c r="BB223" t="inlineStr"/>
+      <c r="BC223" t="inlineStr"/>
+      <c r="BD223" t="inlineStr"/>
+      <c r="BE223" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF223" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG223" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH223" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI223" t="inlineStr"/>
+      <c r="BJ223" t="inlineStr"/>
+      <c r="BK223" t="inlineStr"/>
+      <c r="BL223" t="inlineStr"/>
+      <c r="BM223" t="inlineStr"/>
+      <c r="BN223" t="inlineStr"/>
+      <c r="BO223" t="inlineStr"/>
+      <c r="BP223" t="inlineStr"/>
+      <c r="BQ223" t="inlineStr"/>
+      <c r="BR223" t="inlineStr"/>
+      <c r="BS223" t="inlineStr"/>
+      <c r="BT223" t="inlineStr"/>
+      <c r="BU223" t="inlineStr"/>
+      <c r="BV223" t="inlineStr"/>
+      <c r="BW223" t="inlineStr"/>
+      <c r="BX223" t="inlineStr"/>
+      <c r="BY223" t="inlineStr"/>
+      <c r="BZ223" t="inlineStr"/>
+      <c r="CA223" t="inlineStr"/>
+      <c r="CB223" t="inlineStr"/>
+      <c r="CC223" t="inlineStr"/>
+      <c r="CD223" t="inlineStr"/>
+      <c r="CE223" t="inlineStr"/>
+      <c r="CF223" t="inlineStr"/>
+      <c r="CG223" t="inlineStr"/>
+      <c r="CH223" t="inlineStr"/>
+      <c r="CI223" t="inlineStr"/>
+      <c r="CJ223" t="inlineStr"/>
+      <c r="CK223" t="inlineStr"/>
+      <c r="CL223" t="inlineStr"/>
+      <c r="CM223" t="inlineStr"/>
+      <c r="CN223" t="inlineStr"/>
+      <c r="CO223" t="inlineStr"/>
+      <c r="CP223" t="inlineStr"/>
+      <c r="CQ223" t="inlineStr"/>
+      <c r="CR223" t="inlineStr"/>
+      <c r="CS223" t="inlineStr"/>
+      <c r="CT223" t="inlineStr"/>
+      <c r="CU223" t="inlineStr"/>
+      <c r="CV223" t="inlineStr"/>
+      <c r="CW223" t="inlineStr"/>
+      <c r="CX223" t="inlineStr"/>
+      <c r="CY223" t="inlineStr"/>
+      <c r="CZ223" t="inlineStr"/>
+      <c r="DA223" t="inlineStr"/>
+      <c r="DB223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>h8K6HUFF</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F224" t="n">
+        <v>17016</v>
+      </c>
+      <c r="G224" t="n">
+        <v>2</v>
+      </c>
+      <c r="H224" t="n">
+        <v>1</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="K224" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L224" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="M224" t="n">
+        <v>36</v>
+      </c>
+      <c r="N224" t="n">
+        <v>64</v>
+      </c>
+      <c r="O224" t="n">
+        <v>10</v>
+      </c>
+      <c r="P224" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>8</v>
+      </c>
+      <c r="R224" t="n">
+        <v>3</v>
+      </c>
+      <c r="S224" t="n">
+        <v>2</v>
+      </c>
+      <c r="T224" t="n">
+        <v>4</v>
+      </c>
+      <c r="U224" t="n">
+        <v>0</v>
+      </c>
+      <c r="V224" t="n">
+        <v>8</v>
+      </c>
+      <c r="W224" t="n">
+        <v>10</v>
+      </c>
+      <c r="X224" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>33</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF224" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG224" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH224" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ224" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="AL224" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AM224" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN224" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP224" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ224" t="inlineStr"/>
+      <c r="AR224" t="inlineStr"/>
+      <c r="AS224" t="n">
+        <v>264</v>
+      </c>
+      <c r="AT224" t="n">
+        <v>477</v>
+      </c>
+      <c r="AU224" t="inlineStr"/>
+      <c r="AV224" t="inlineStr"/>
+      <c r="AW224" t="inlineStr"/>
+      <c r="AX224" t="inlineStr"/>
+      <c r="AY224" t="n">
+        <v>197</v>
+      </c>
+      <c r="AZ224" t="n">
+        <v>409</v>
+      </c>
+      <c r="BA224" t="inlineStr"/>
+      <c r="BB224" t="inlineStr"/>
+      <c r="BC224" t="inlineStr"/>
+      <c r="BD224" t="inlineStr"/>
+      <c r="BE224" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF224" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG224" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH224" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI224" t="inlineStr"/>
+      <c r="BJ224" t="inlineStr"/>
+      <c r="BK224" t="inlineStr"/>
+      <c r="BL224" t="inlineStr"/>
+      <c r="BM224" t="inlineStr"/>
+      <c r="BN224" t="inlineStr"/>
+      <c r="BO224" t="inlineStr"/>
+      <c r="BP224" t="inlineStr"/>
+      <c r="BQ224" t="inlineStr"/>
+      <c r="BR224" t="inlineStr"/>
+      <c r="BS224" t="inlineStr"/>
+      <c r="BT224" t="inlineStr"/>
+      <c r="BU224" t="inlineStr"/>
+      <c r="BV224" t="inlineStr"/>
+      <c r="BW224" t="inlineStr"/>
+      <c r="BX224" t="inlineStr"/>
+      <c r="BY224" t="n">
+        <v>24.06666666666667</v>
+      </c>
+      <c r="BZ224" t="n">
+        <v>181.5333333333333</v>
+      </c>
+      <c r="CA224" t="n">
+        <v>65.73333333333333</v>
+      </c>
+      <c r="CB224" t="inlineStr"/>
+      <c r="CC224" t="n">
+        <v>1255000</v>
+      </c>
+      <c r="CD224" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="CE224" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF224" t="inlineStr"/>
+      <c r="CG224" t="inlineStr"/>
+      <c r="CH224" t="inlineStr"/>
+      <c r="CI224" t="inlineStr"/>
+      <c r="CJ224" t="inlineStr"/>
+      <c r="CK224" t="inlineStr"/>
+      <c r="CL224" t="inlineStr"/>
+      <c r="CM224" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="CN224" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="CO224" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP224" t="n">
+        <v>205</v>
+      </c>
+      <c r="CQ224" t="n">
+        <v>11000</v>
+      </c>
+      <c r="CR224" t="n">
+        <v>6100000</v>
+      </c>
+      <c r="CS224" t="n">
+        <v>223</v>
+      </c>
+      <c r="CT224" t="n">
+        <v>3</v>
+      </c>
+      <c r="CU224" t="inlineStr"/>
+      <c r="CV224" t="inlineStr"/>
+      <c r="CW224" t="inlineStr"/>
+      <c r="CX224" t="inlineStr"/>
+      <c r="CY224" t="inlineStr"/>
+      <c r="CZ224" t="inlineStr"/>
+      <c r="DA224" t="inlineStr"/>
+      <c r="DB224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>WMcg8Qx2</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angoula g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F225" t="n">
+        <v>28141</v>
+      </c>
+      <c r="G225" t="n">
+        <v>1</v>
+      </c>
+      <c r="H225" t="n">
+        <v>1</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="K225" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M225" t="n">
+        <v>42</v>
+      </c>
+      <c r="N225" t="n">
+        <v>58</v>
+      </c>
+      <c r="O225" t="n">
+        <v>11</v>
+      </c>
+      <c r="P225" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>7</v>
+      </c>
+      <c r="R225" t="n">
+        <v>7</v>
+      </c>
+      <c r="S225" t="n">
+        <v>3</v>
+      </c>
+      <c r="T225" t="n">
+        <v>5</v>
+      </c>
+      <c r="U225" t="n">
+        <v>1</v>
+      </c>
+      <c r="V225" t="n">
+        <v>1</v>
+      </c>
+      <c r="W225" t="n">
+        <v>10</v>
+      </c>
+      <c r="X225" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z225" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC225" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD225" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF225" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG225" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH225" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AL225" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AM225" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN225" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP225" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ225" t="inlineStr"/>
+      <c r="AR225" t="inlineStr"/>
+      <c r="AS225" t="n">
+        <v>390</v>
+      </c>
+      <c r="AT225" t="n">
+        <v>535</v>
+      </c>
+      <c r="AU225" t="inlineStr"/>
+      <c r="AV225" t="inlineStr"/>
+      <c r="AW225" t="inlineStr"/>
+      <c r="AX225" t="inlineStr"/>
+      <c r="AY225" t="n">
+        <v>320</v>
+      </c>
+      <c r="AZ225" t="n">
+        <v>466</v>
+      </c>
+      <c r="BA225" t="inlineStr"/>
+      <c r="BB225" t="inlineStr"/>
+      <c r="BC225" t="inlineStr"/>
+      <c r="BD225" t="inlineStr"/>
+      <c r="BE225" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF225" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG225" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH225" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI225" t="inlineStr"/>
+      <c r="BJ225" t="inlineStr"/>
+      <c r="BK225" t="inlineStr"/>
+      <c r="BL225" t="inlineStr"/>
+      <c r="BM225" t="inlineStr"/>
+      <c r="BN225" t="inlineStr"/>
+      <c r="BO225" t="inlineStr"/>
+      <c r="BP225" t="inlineStr"/>
+      <c r="BQ225" t="inlineStr"/>
+      <c r="BR225" t="inlineStr"/>
+      <c r="BS225" t="inlineStr"/>
+      <c r="BT225" t="inlineStr"/>
+      <c r="BU225" t="inlineStr"/>
+      <c r="BV225" t="inlineStr"/>
+      <c r="BW225" t="inlineStr"/>
+      <c r="BX225" t="inlineStr"/>
+      <c r="BY225" t="inlineStr"/>
+      <c r="BZ225" t="inlineStr"/>
+      <c r="CA225" t="inlineStr"/>
+      <c r="CB225" t="inlineStr"/>
+      <c r="CC225" t="inlineStr"/>
+      <c r="CD225" t="inlineStr"/>
+      <c r="CE225" t="inlineStr"/>
+      <c r="CF225" t="inlineStr"/>
+      <c r="CG225" t="inlineStr"/>
+      <c r="CH225" t="inlineStr"/>
+      <c r="CI225" t="inlineStr"/>
+      <c r="CJ225" t="inlineStr"/>
+      <c r="CK225" t="inlineStr"/>
+      <c r="CL225" t="inlineStr"/>
+      <c r="CM225" t="inlineStr"/>
+      <c r="CN225" t="inlineStr"/>
+      <c r="CO225" t="inlineStr"/>
+      <c r="CP225" t="inlineStr"/>
+      <c r="CQ225" t="inlineStr"/>
+      <c r="CR225" t="inlineStr"/>
+      <c r="CS225" t="inlineStr"/>
+      <c r="CT225" t="inlineStr"/>
+      <c r="CU225" t="inlineStr"/>
+      <c r="CV225" t="inlineStr"/>
+      <c r="CW225" t="inlineStr"/>
+      <c r="CX225" t="inlineStr"/>
+      <c r="CY225" t="inlineStr"/>
+      <c r="CZ225" t="inlineStr"/>
+      <c r="DA225" t="inlineStr"/>
+      <c r="DB225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>vPIEF8pS</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F226" t="n">
+        <v>24107</v>
+      </c>
+      <c r="G226" t="n">
+        <v>1</v>
+      </c>
+      <c r="H226" t="n">
+        <v>1</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="K226" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="L226" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M226" t="n">
+        <v>66</v>
+      </c>
+      <c r="N226" t="n">
+        <v>34</v>
+      </c>
+      <c r="O226" t="n">
+        <v>18</v>
+      </c>
+      <c r="P226" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>6</v>
+      </c>
+      <c r="R226" t="n">
+        <v>4</v>
+      </c>
+      <c r="S226" t="n">
+        <v>7</v>
+      </c>
+      <c r="T226" t="n">
+        <v>2</v>
+      </c>
+      <c r="U226" t="n">
+        <v>5</v>
+      </c>
+      <c r="V226" t="n">
+        <v>2</v>
+      </c>
+      <c r="W226" t="n">
+        <v>9</v>
+      </c>
+      <c r="X226" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH226" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ226" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AL226" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AM226" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN226" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP226" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ226" t="inlineStr"/>
+      <c r="AR226" t="inlineStr"/>
+      <c r="AS226" t="n">
+        <v>535</v>
+      </c>
+      <c r="AT226" t="n">
+        <v>278</v>
+      </c>
+      <c r="AU226" t="inlineStr"/>
+      <c r="AV226" t="inlineStr"/>
+      <c r="AW226" t="inlineStr"/>
+      <c r="AX226" t="inlineStr"/>
+      <c r="AY226" t="n">
+        <v>451</v>
+      </c>
+      <c r="AZ226" t="n">
+        <v>197</v>
+      </c>
+      <c r="BA226" t="inlineStr"/>
+      <c r="BB226" t="inlineStr"/>
+      <c r="BC226" t="inlineStr"/>
+      <c r="BD226" t="inlineStr"/>
+      <c r="BE226" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF226" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG226" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH226" t="n">
+        <v>11</v>
+      </c>
+      <c r="BI226" t="inlineStr"/>
+      <c r="BJ226" t="inlineStr"/>
+      <c r="BK226" t="inlineStr"/>
+      <c r="BL226" t="inlineStr"/>
+      <c r="BM226" t="inlineStr"/>
+      <c r="BN226" t="inlineStr"/>
+      <c r="BO226" t="inlineStr"/>
+      <c r="BP226" t="inlineStr"/>
+      <c r="BQ226" t="inlineStr"/>
+      <c r="BR226" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BS226" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="BT226" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="BU226" t="inlineStr"/>
+      <c r="BV226" t="n">
+        <v>1631250</v>
+      </c>
+      <c r="BW226" t="n">
+        <v>72.625</v>
+      </c>
+      <c r="BX226" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY226" t="inlineStr"/>
+      <c r="BZ226" t="inlineStr"/>
+      <c r="CA226" t="inlineStr"/>
+      <c r="CB226" t="inlineStr"/>
+      <c r="CC226" t="inlineStr"/>
+      <c r="CD226" t="inlineStr"/>
+      <c r="CE226" t="inlineStr"/>
+      <c r="CF226" t="n">
+        <v>27.84615384615385</v>
+      </c>
+      <c r="CG226" t="n">
+        <v>180.9230769230769</v>
+      </c>
+      <c r="CH226" t="n">
+        <v>66.38461538461539</v>
+      </c>
+      <c r="CI226" t="inlineStr"/>
+      <c r="CJ226" t="n">
+        <v>848076.9230769231</v>
+      </c>
+      <c r="CK226" t="n">
+        <v>70.92307692307692</v>
+      </c>
+      <c r="CL226" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM226" t="inlineStr"/>
+      <c r="CN226" t="inlineStr"/>
+      <c r="CO226" t="inlineStr"/>
+      <c r="CP226" t="inlineStr"/>
+      <c r="CQ226" t="inlineStr"/>
+      <c r="CR226" t="inlineStr"/>
+      <c r="CS226" t="inlineStr"/>
+      <c r="CT226" t="inlineStr"/>
+      <c r="CU226" t="n">
+        <v>23.83333333333333</v>
+      </c>
+      <c r="CV226" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="CW226" t="n">
+        <v>6</v>
+      </c>
+      <c r="CX226" t="n">
+        <v>397</v>
+      </c>
+      <c r="CY226" t="inlineStr"/>
+      <c r="CZ226" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="DA226" t="n">
+        <v>436</v>
+      </c>
+      <c r="DB226" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>b9aoAn8k</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="n">
+        <v>45585.41666666666</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F227" t="n">
+        <v>22490</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>4</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="K227" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L227" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M227" t="n">
+        <v>38</v>
+      </c>
+      <c r="N227" t="n">
+        <v>62</v>
+      </c>
+      <c r="O227" t="n">
+        <v>7</v>
+      </c>
+      <c r="P227" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>1</v>
+      </c>
+      <c r="R227" t="n">
+        <v>8</v>
+      </c>
+      <c r="S227" t="n">
+        <v>3</v>
+      </c>
+      <c r="T227" t="n">
+        <v>4</v>
+      </c>
+      <c r="U227" t="n">
+        <v>3</v>
+      </c>
+      <c r="V227" t="n">
+        <v>4</v>
+      </c>
+      <c r="W227" t="n">
+        <v>11</v>
+      </c>
+      <c r="X227" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD227" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG227" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH227" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI227" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ227" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="AL227" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AM227" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN227" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP227" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ227" t="inlineStr"/>
+      <c r="AR227" t="inlineStr"/>
+      <c r="AS227" t="n">
+        <v>303</v>
+      </c>
+      <c r="AT227" t="n">
+        <v>508</v>
+      </c>
+      <c r="AU227" t="inlineStr"/>
+      <c r="AV227" t="inlineStr"/>
+      <c r="AW227" t="inlineStr"/>
+      <c r="AX227" t="inlineStr"/>
+      <c r="AY227" t="n">
+        <v>241</v>
+      </c>
+      <c r="AZ227" t="n">
+        <v>437</v>
+      </c>
+      <c r="BA227" t="inlineStr"/>
+      <c r="BB227" t="inlineStr"/>
+      <c r="BC227" t="inlineStr"/>
+      <c r="BD227" t="inlineStr"/>
+      <c r="BE227" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF227" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG227" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH227" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI227" t="inlineStr"/>
+      <c r="BJ227" t="inlineStr"/>
+      <c r="BK227" t="inlineStr"/>
+      <c r="BL227" t="inlineStr"/>
+      <c r="BM227" t="inlineStr"/>
+      <c r="BN227" t="inlineStr"/>
+      <c r="BO227" t="inlineStr"/>
+      <c r="BP227" t="inlineStr"/>
+      <c r="BQ227" t="inlineStr"/>
+      <c r="BR227" t="inlineStr"/>
+      <c r="BS227" t="inlineStr"/>
+      <c r="BT227" t="inlineStr"/>
+      <c r="BU227" t="inlineStr"/>
+      <c r="BV227" t="inlineStr"/>
+      <c r="BW227" t="inlineStr"/>
+      <c r="BX227" t="inlineStr"/>
+      <c r="BY227" t="inlineStr"/>
+      <c r="BZ227" t="inlineStr"/>
+      <c r="CA227" t="inlineStr"/>
+      <c r="CB227" t="inlineStr"/>
+      <c r="CC227" t="inlineStr"/>
+      <c r="CD227" t="inlineStr"/>
+      <c r="CE227" t="inlineStr"/>
+      <c r="CF227" t="inlineStr"/>
+      <c r="CG227" t="inlineStr"/>
+      <c r="CH227" t="inlineStr"/>
+      <c r="CI227" t="inlineStr"/>
+      <c r="CJ227" t="inlineStr"/>
+      <c r="CK227" t="inlineStr"/>
+      <c r="CL227" t="inlineStr"/>
+      <c r="CM227" t="inlineStr"/>
+      <c r="CN227" t="inlineStr"/>
+      <c r="CO227" t="inlineStr"/>
+      <c r="CP227" t="inlineStr"/>
+      <c r="CQ227" t="inlineStr"/>
+      <c r="CR227" t="inlineStr"/>
+      <c r="CS227" t="inlineStr"/>
+      <c r="CT227" t="inlineStr"/>
+      <c r="CU227" t="inlineStr"/>
+      <c r="CV227" t="inlineStr"/>
+      <c r="CW227" t="inlineStr"/>
+      <c r="CX227" t="inlineStr"/>
+      <c r="CY227" t="inlineStr"/>
+      <c r="CZ227" t="inlineStr"/>
+      <c r="DA227" t="inlineStr"/>
+      <c r="DB227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>S2WzL3M7</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="n">
+        <v>45584.66666666666</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F228" t="n">
+        <v>47590</v>
+      </c>
+      <c r="G228" t="n">
+        <v>4</v>
+      </c>
+      <c r="H228" t="n">
+        <v>2</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="K228" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="L228" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M228" t="n">
+        <v>56</v>
+      </c>
+      <c r="N228" t="n">
+        <v>44</v>
+      </c>
+      <c r="O228" t="n">
+        <v>18</v>
+      </c>
+      <c r="P228" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>10</v>
+      </c>
+      <c r="R228" t="n">
+        <v>8</v>
+      </c>
+      <c r="S228" t="n">
+        <v>5</v>
+      </c>
+      <c r="T228" t="n">
+        <v>1</v>
+      </c>
+      <c r="U228" t="n">
+        <v>3</v>
+      </c>
+      <c r="V228" t="n">
+        <v>7</v>
+      </c>
+      <c r="W228" t="n">
+        <v>12</v>
+      </c>
+      <c r="X228" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AL228" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AM228" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN228" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP228" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ228" t="inlineStr"/>
+      <c r="AR228" t="inlineStr"/>
+      <c r="AS228" t="n">
+        <v>560</v>
+      </c>
+      <c r="AT228" t="n">
+        <v>445</v>
+      </c>
+      <c r="AU228" t="inlineStr"/>
+      <c r="AV228" t="inlineStr"/>
+      <c r="AW228" t="inlineStr"/>
+      <c r="AX228" t="inlineStr"/>
+      <c r="AY228" t="n">
+        <v>492</v>
+      </c>
+      <c r="AZ228" t="n">
+        <v>378</v>
+      </c>
+      <c r="BA228" t="inlineStr"/>
+      <c r="BB228" t="inlineStr"/>
+      <c r="BC228" t="inlineStr"/>
+      <c r="BD228" t="inlineStr"/>
+      <c r="BE228" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF228" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG228" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH228" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI228" t="inlineStr"/>
+      <c r="BJ228" t="inlineStr"/>
+      <c r="BK228" t="inlineStr"/>
+      <c r="BL228" t="inlineStr"/>
+      <c r="BM228" t="inlineStr"/>
+      <c r="BN228" t="inlineStr"/>
+      <c r="BO228" t="inlineStr"/>
+      <c r="BP228" t="inlineStr"/>
+      <c r="BQ228" t="inlineStr"/>
+      <c r="BR228" t="inlineStr"/>
+      <c r="BS228" t="inlineStr"/>
+      <c r="BT228" t="inlineStr"/>
+      <c r="BU228" t="inlineStr"/>
+      <c r="BV228" t="inlineStr"/>
+      <c r="BW228" t="inlineStr"/>
+      <c r="BX228" t="inlineStr"/>
+      <c r="BY228" t="inlineStr"/>
+      <c r="BZ228" t="inlineStr"/>
+      <c r="CA228" t="inlineStr"/>
+      <c r="CB228" t="inlineStr"/>
+      <c r="CC228" t="inlineStr"/>
+      <c r="CD228" t="inlineStr"/>
+      <c r="CE228" t="inlineStr"/>
+      <c r="CF228" t="n">
+        <v>22.16666666666667</v>
+      </c>
+      <c r="CG228" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="CH228" t="n">
+        <v>68.83333333333333</v>
+      </c>
+      <c r="CI228" t="n">
+        <v>3166.666666666667</v>
+      </c>
+      <c r="CJ228" t="n">
+        <v>2620833.333333333</v>
+      </c>
+      <c r="CK228" t="n">
+        <v>77</v>
+      </c>
+      <c r="CL228" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM228" t="inlineStr"/>
+      <c r="CN228" t="inlineStr"/>
+      <c r="CO228" t="inlineStr"/>
+      <c r="CP228" t="inlineStr"/>
+      <c r="CQ228" t="inlineStr"/>
+      <c r="CR228" t="inlineStr"/>
+      <c r="CS228" t="inlineStr"/>
+      <c r="CT228" t="inlineStr"/>
+      <c r="CU228" t="inlineStr"/>
+      <c r="CV228" t="inlineStr"/>
+      <c r="CW228" t="inlineStr"/>
+      <c r="CX228" t="inlineStr"/>
+      <c r="CY228" t="inlineStr"/>
+      <c r="CZ228" t="inlineStr"/>
+      <c r="DA228" t="inlineStr"/>
+      <c r="DB228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>GWGWJzkK</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="n">
+        <v>45584.625</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapapria r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade du moustoir
+  lorient </t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>16787</v>
+      </c>
+      <c r="F229" t="n">
+        <v>11512</v>
+      </c>
+      <c r="G229" t="n">
+        <v>4</v>
+      </c>
+      <c r="H229" t="n">
+        <v>2</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="n">
+        <v>65</v>
+      </c>
+      <c r="N229" t="n">
+        <v>35</v>
+      </c>
+      <c r="O229" t="n">
+        <v>19</v>
+      </c>
+      <c r="P229" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>9</v>
+      </c>
+      <c r="R229" t="n">
+        <v>4</v>
+      </c>
+      <c r="S229" t="n">
+        <v>7</v>
+      </c>
+      <c r="T229" t="n">
+        <v>5</v>
+      </c>
+      <c r="U229" t="n">
+        <v>3</v>
+      </c>
+      <c r="V229" t="n">
+        <v>0</v>
+      </c>
+      <c r="W229" t="inlineStr"/>
+      <c r="X229" t="inlineStr"/>
+      <c r="Y229" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC229" t="inlineStr"/>
+      <c r="AD229" t="inlineStr"/>
+      <c r="AE229" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF229" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH229" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ229" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="AL229" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="AM229" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN229" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP229" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ229" t="inlineStr"/>
+      <c r="AR229" t="inlineStr"/>
+      <c r="AS229" t="n">
+        <v>629</v>
+      </c>
+      <c r="AT229" t="n">
+        <v>361</v>
+      </c>
+      <c r="AU229" t="inlineStr"/>
+      <c r="AV229" t="inlineStr"/>
+      <c r="AW229" t="inlineStr"/>
+      <c r="AX229" t="inlineStr"/>
+      <c r="AY229" t="n">
+        <v>499</v>
+      </c>
+      <c r="AZ229" t="n">
+        <v>249</v>
+      </c>
+      <c r="BA229" t="inlineStr"/>
+      <c r="BB229" t="inlineStr"/>
+      <c r="BC229" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD229" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE229" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF229" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG229" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH229" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI229" t="inlineStr"/>
+      <c r="BJ229" t="inlineStr"/>
+      <c r="BK229" t="inlineStr"/>
+      <c r="BL229" t="inlineStr"/>
+      <c r="BM229" t="inlineStr"/>
+      <c r="BN229" t="inlineStr"/>
+      <c r="BO229" t="inlineStr"/>
+      <c r="BP229" t="inlineStr"/>
+      <c r="BQ229" t="inlineStr"/>
+      <c r="BR229" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="BS229" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="BT229" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="BU229" t="inlineStr"/>
+      <c r="BV229" t="n">
+        <v>681250</v>
+      </c>
+      <c r="BW229" t="n">
+        <v>67</v>
+      </c>
+      <c r="BX229" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY229" t="inlineStr"/>
+      <c r="BZ229" t="inlineStr"/>
+      <c r="CA229" t="inlineStr"/>
+      <c r="CB229" t="inlineStr"/>
+      <c r="CC229" t="inlineStr"/>
+      <c r="CD229" t="inlineStr"/>
+      <c r="CE229" t="inlineStr"/>
+      <c r="CF229" t="n">
+        <v>24</v>
+      </c>
+      <c r="CG229" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="CH229" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="CI229" t="inlineStr"/>
+      <c r="CJ229" t="n">
+        <v>530000</v>
+      </c>
+      <c r="CK229" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="CL229" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM229" t="n">
+        <v>22</v>
+      </c>
+      <c r="CN229" t="n">
+        <v>177</v>
+      </c>
+      <c r="CO229" t="n">
+        <v>2</v>
+      </c>
+      <c r="CP229" t="n">
+        <v>136</v>
+      </c>
+      <c r="CQ229" t="n">
+        <v>18000</v>
+      </c>
+      <c r="CR229" t="n">
+        <v>4300000</v>
+      </c>
+      <c r="CS229" t="n">
+        <v>152</v>
+      </c>
+      <c r="CT229" t="n">
+        <v>2</v>
+      </c>
+      <c r="CU229" t="inlineStr"/>
+      <c r="CV229" t="inlineStr"/>
+      <c r="CW229" t="inlineStr"/>
+      <c r="CX229" t="inlineStr"/>
+      <c r="CY229" t="inlineStr"/>
+      <c r="CZ229" t="inlineStr"/>
+      <c r="DA229" t="inlineStr"/>
+      <c r="DB229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>2g2J0IEs</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="n">
+        <v>45586.65625</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kubler g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l aube
+  troyes </t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>20420</v>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>3</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="n">
+        <v>40</v>
+      </c>
+      <c r="N230" t="n">
+        <v>60</v>
+      </c>
+      <c r="O230" t="n">
+        <v>11</v>
+      </c>
+      <c r="P230" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>3</v>
+      </c>
+      <c r="R230" t="n">
+        <v>6</v>
+      </c>
+      <c r="S230" t="n">
+        <v>7</v>
+      </c>
+      <c r="T230" t="n">
+        <v>3</v>
+      </c>
+      <c r="U230" t="n">
+        <v>1</v>
+      </c>
+      <c r="V230" t="n">
+        <v>2</v>
+      </c>
+      <c r="W230" t="inlineStr"/>
+      <c r="X230" t="inlineStr"/>
+      <c r="Y230" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC230" t="inlineStr"/>
+      <c r="AD230" t="inlineStr"/>
+      <c r="AE230" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF230" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH230" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="AL230" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="AM230" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN230" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP230" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ230" t="inlineStr"/>
+      <c r="AR230" t="inlineStr"/>
+      <c r="AS230" t="n">
+        <v>411</v>
+      </c>
+      <c r="AT230" t="n">
+        <v>697</v>
+      </c>
+      <c r="AU230" t="inlineStr"/>
+      <c r="AV230" t="inlineStr"/>
+      <c r="AW230" t="inlineStr"/>
+      <c r="AX230" t="inlineStr"/>
+      <c r="AY230" t="n">
+        <v>347</v>
+      </c>
+      <c r="AZ230" t="n">
+        <v>604</v>
+      </c>
+      <c r="BA230" t="inlineStr"/>
+      <c r="BB230" t="inlineStr"/>
+      <c r="BC230" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD230" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE230" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF230" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG230" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH230" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI230" t="inlineStr"/>
+      <c r="BJ230" t="inlineStr"/>
+      <c r="BK230" t="inlineStr"/>
+      <c r="BL230" t="inlineStr"/>
+      <c r="BM230" t="inlineStr"/>
+      <c r="BN230" t="inlineStr"/>
+      <c r="BO230" t="inlineStr"/>
+      <c r="BP230" t="inlineStr"/>
+      <c r="BQ230" t="inlineStr"/>
+      <c r="BR230" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS230" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BT230" t="n">
+        <v>67.375</v>
+      </c>
+      <c r="BU230" t="n">
+        <v>3250</v>
+      </c>
+      <c r="BV230" t="n">
+        <v>1759375</v>
+      </c>
+      <c r="BW230" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="BX230" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="BY230" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="BZ230" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="CA230" t="n">
+        <v>66.125</v>
+      </c>
+      <c r="CB230" t="inlineStr"/>
+      <c r="CC230" t="n">
+        <v>1285937.5</v>
+      </c>
+      <c r="CD230" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="CE230" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF230" t="n">
+        <v>28.4375</v>
+      </c>
+      <c r="CG230" t="n">
+        <v>179.9375</v>
+      </c>
+      <c r="CH230" t="n">
+        <v>67.9375</v>
+      </c>
+      <c r="CI230" t="n">
+        <v>3625</v>
+      </c>
+      <c r="CJ230" t="n">
+        <v>1217187.5</v>
+      </c>
+      <c r="CK230" t="n">
+        <v>69</v>
+      </c>
+      <c r="CL230" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="CM230" t="n">
+        <v>33</v>
+      </c>
+      <c r="CN230" t="n">
+        <v>193</v>
+      </c>
+      <c r="CO230" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP230" t="n">
+        <v>66</v>
+      </c>
+      <c r="CQ230" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CR230" t="n">
+        <v>400000</v>
+      </c>
+      <c r="CS230" t="n">
+        <v>66</v>
+      </c>
+      <c r="CT230" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU230" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="CV230" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="CW230" t="n">
+        <v>4</v>
+      </c>
+      <c r="CX230" t="n">
+        <v>268</v>
+      </c>
+      <c r="CY230" t="inlineStr"/>
+      <c r="CZ230" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="DA230" t="n">
+        <v>287</v>
+      </c>
+      <c r="DB230" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB230"/>
+  <dimension ref="A1:DB231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61843,6 +61843,302 @@
         <v>4</v>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>f5f1oGre</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="n">
+        <v>45587.60416666666</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gaillouste p 
+  fra </t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nouste camp
+  pau </t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>4031</v>
+      </c>
+      <c r="F231" t="n">
+        <v>3431</v>
+      </c>
+      <c r="G231" t="n">
+        <v>1</v>
+      </c>
+      <c r="H231" t="n">
+        <v>1</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="n">
+        <v>39</v>
+      </c>
+      <c r="N231" t="n">
+        <v>61</v>
+      </c>
+      <c r="O231" t="n">
+        <v>8</v>
+      </c>
+      <c r="P231" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>4</v>
+      </c>
+      <c r="R231" t="n">
+        <v>4</v>
+      </c>
+      <c r="S231" t="n">
+        <v>0</v>
+      </c>
+      <c r="T231" t="n">
+        <v>4</v>
+      </c>
+      <c r="U231" t="n">
+        <v>4</v>
+      </c>
+      <c r="V231" t="n">
+        <v>2</v>
+      </c>
+      <c r="W231" t="inlineStr"/>
+      <c r="X231" t="inlineStr"/>
+      <c r="Y231" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC231" t="inlineStr"/>
+      <c r="AD231" t="inlineStr"/>
+      <c r="AE231" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AL231" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AM231" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN231" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP231" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ231" t="inlineStr"/>
+      <c r="AR231" t="inlineStr"/>
+      <c r="AS231" t="n">
+        <v>361</v>
+      </c>
+      <c r="AT231" t="n">
+        <v>591</v>
+      </c>
+      <c r="AU231" t="inlineStr"/>
+      <c r="AV231" t="inlineStr"/>
+      <c r="AW231" t="inlineStr"/>
+      <c r="AX231" t="inlineStr"/>
+      <c r="AY231" t="n">
+        <v>273</v>
+      </c>
+      <c r="AZ231" t="n">
+        <v>489</v>
+      </c>
+      <c r="BA231" t="inlineStr"/>
+      <c r="BB231" t="inlineStr"/>
+      <c r="BC231" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD231" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE231" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF231" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG231" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH231" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI231" t="inlineStr"/>
+      <c r="BJ231" t="inlineStr"/>
+      <c r="BK231" t="n">
+        <v>24</v>
+      </c>
+      <c r="BL231" t="n">
+        <v>186.25</v>
+      </c>
+      <c r="BM231" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="BN231" t="inlineStr"/>
+      <c r="BO231" t="n">
+        <v>1065625</v>
+      </c>
+      <c r="BP231" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="BQ231" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR231" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="BS231" t="n">
+        <v>178.375</v>
+      </c>
+      <c r="BT231" t="n">
+        <v>65</v>
+      </c>
+      <c r="BU231" t="inlineStr"/>
+      <c r="BV231" t="n">
+        <v>845000</v>
+      </c>
+      <c r="BW231" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="BX231" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY231" t="n">
+        <v>27.0625</v>
+      </c>
+      <c r="BZ231" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="CA231" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="CB231" t="inlineStr"/>
+      <c r="CC231" t="n">
+        <v>778125</v>
+      </c>
+      <c r="CD231" t="n">
+        <v>68.3125</v>
+      </c>
+      <c r="CE231" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF231" t="n">
+        <v>23.8125</v>
+      </c>
+      <c r="CG231" t="n">
+        <v>179.375</v>
+      </c>
+      <c r="CH231" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="CI231" t="inlineStr"/>
+      <c r="CJ231" t="n">
+        <v>826562.5</v>
+      </c>
+      <c r="CK231" t="n">
+        <v>68.375</v>
+      </c>
+      <c r="CL231" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM231" t="n">
+        <v>29</v>
+      </c>
+      <c r="CN231" t="n">
+        <v>170</v>
+      </c>
+      <c r="CO231" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP231" t="n">
+        <v>66</v>
+      </c>
+      <c r="CQ231" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CR231" t="n">
+        <v>750000</v>
+      </c>
+      <c r="CS231" t="n">
+        <v>66</v>
+      </c>
+      <c r="CT231" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU231" t="n">
+        <v>31</v>
+      </c>
+      <c r="CV231" t="n">
+        <v>180</v>
+      </c>
+      <c r="CW231" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX231" t="n">
+        <v>69</v>
+      </c>
+      <c r="CY231" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CZ231" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="DA231" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB231" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB231"/>
+  <dimension ref="A1:DB249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62139,6 +62139,4574 @@
         <v>1</v>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>vaZNtoqR</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="n">
+        <v>45591.66666666666</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>2</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="K232" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L232" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M232" t="n">
+        <v>58</v>
+      </c>
+      <c r="N232" t="n">
+        <v>42</v>
+      </c>
+      <c r="O232" t="n">
+        <v>11</v>
+      </c>
+      <c r="P232" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>4</v>
+      </c>
+      <c r="R232" t="n">
+        <v>3</v>
+      </c>
+      <c r="S232" t="n">
+        <v>2</v>
+      </c>
+      <c r="T232" t="n">
+        <v>1</v>
+      </c>
+      <c r="U232" t="n">
+        <v>5</v>
+      </c>
+      <c r="V232" t="n">
+        <v>7</v>
+      </c>
+      <c r="W232" t="n">
+        <v>14</v>
+      </c>
+      <c r="X232" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA232" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD232" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF232" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG232" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH232" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI232" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ232" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK232" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AL232" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AM232" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN232" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP232" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ232" t="inlineStr"/>
+      <c r="AR232" t="inlineStr"/>
+      <c r="AS232" t="n">
+        <v>429</v>
+      </c>
+      <c r="AT232" t="n">
+        <v>316</v>
+      </c>
+      <c r="AU232" t="inlineStr"/>
+      <c r="AV232" t="inlineStr"/>
+      <c r="AW232" t="inlineStr"/>
+      <c r="AX232" t="inlineStr"/>
+      <c r="AY232" t="n">
+        <v>326</v>
+      </c>
+      <c r="AZ232" t="n">
+        <v>233</v>
+      </c>
+      <c r="BA232" t="inlineStr"/>
+      <c r="BB232" t="inlineStr"/>
+      <c r="BC232" t="inlineStr"/>
+      <c r="BD232" t="inlineStr"/>
+      <c r="BE232" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF232" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG232" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH232" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI232" t="inlineStr"/>
+      <c r="BJ232" t="inlineStr"/>
+      <c r="BK232" t="inlineStr"/>
+      <c r="BL232" t="inlineStr"/>
+      <c r="BM232" t="inlineStr"/>
+      <c r="BN232" t="inlineStr"/>
+      <c r="BO232" t="inlineStr"/>
+      <c r="BP232" t="inlineStr"/>
+      <c r="BQ232" t="inlineStr"/>
+      <c r="BR232" t="inlineStr"/>
+      <c r="BS232" t="inlineStr"/>
+      <c r="BT232" t="inlineStr"/>
+      <c r="BU232" t="inlineStr"/>
+      <c r="BV232" t="inlineStr"/>
+      <c r="BW232" t="inlineStr"/>
+      <c r="BX232" t="inlineStr"/>
+      <c r="BY232" t="inlineStr"/>
+      <c r="BZ232" t="inlineStr"/>
+      <c r="CA232" t="inlineStr"/>
+      <c r="CB232" t="inlineStr"/>
+      <c r="CC232" t="inlineStr"/>
+      <c r="CD232" t="inlineStr"/>
+      <c r="CE232" t="inlineStr"/>
+      <c r="CF232" t="inlineStr"/>
+      <c r="CG232" t="inlineStr"/>
+      <c r="CH232" t="inlineStr"/>
+      <c r="CI232" t="inlineStr"/>
+      <c r="CJ232" t="inlineStr"/>
+      <c r="CK232" t="inlineStr"/>
+      <c r="CL232" t="inlineStr"/>
+      <c r="CM232" t="inlineStr"/>
+      <c r="CN232" t="inlineStr"/>
+      <c r="CO232" t="inlineStr"/>
+      <c r="CP232" t="inlineStr"/>
+      <c r="CQ232" t="inlineStr"/>
+      <c r="CR232" t="inlineStr"/>
+      <c r="CS232" t="inlineStr"/>
+      <c r="CT232" t="inlineStr"/>
+      <c r="CU232" t="n">
+        <v>28</v>
+      </c>
+      <c r="CV232" t="n">
+        <v>187</v>
+      </c>
+      <c r="CW232" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX232" t="n">
+        <v>75</v>
+      </c>
+      <c r="CY232" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CZ232" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="DA232" t="n">
+        <v>76</v>
+      </c>
+      <c r="DB232" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>hQspntL6</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="n">
+        <v>45591.58333333334</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="n">
+        <v>1</v>
+      </c>
+      <c r="H233" t="n">
+        <v>2</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="K233" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L233" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M233" t="n">
+        <v>53</v>
+      </c>
+      <c r="N233" t="n">
+        <v>47</v>
+      </c>
+      <c r="O233" t="n">
+        <v>11</v>
+      </c>
+      <c r="P233" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>3</v>
+      </c>
+      <c r="R233" t="n">
+        <v>4</v>
+      </c>
+      <c r="S233" t="n">
+        <v>6</v>
+      </c>
+      <c r="T233" t="n">
+        <v>4</v>
+      </c>
+      <c r="U233" t="n">
+        <v>2</v>
+      </c>
+      <c r="V233" t="n">
+        <v>5</v>
+      </c>
+      <c r="W233" t="n">
+        <v>11</v>
+      </c>
+      <c r="X233" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG233" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH233" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI233" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AL233" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AM233" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN233" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP233" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ233" t="inlineStr"/>
+      <c r="AR233" t="inlineStr"/>
+      <c r="AS233" t="n">
+        <v>412</v>
+      </c>
+      <c r="AT233" t="n">
+        <v>377</v>
+      </c>
+      <c r="AU233" t="inlineStr"/>
+      <c r="AV233" t="inlineStr"/>
+      <c r="AW233" t="inlineStr"/>
+      <c r="AX233" t="inlineStr"/>
+      <c r="AY233" t="n">
+        <v>348</v>
+      </c>
+      <c r="AZ233" t="n">
+        <v>297</v>
+      </c>
+      <c r="BA233" t="inlineStr"/>
+      <c r="BB233" t="inlineStr"/>
+      <c r="BC233" t="inlineStr"/>
+      <c r="BD233" t="inlineStr"/>
+      <c r="BE233" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF233" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG233" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH233" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI233" t="inlineStr"/>
+      <c r="BJ233" t="inlineStr"/>
+      <c r="BK233" t="inlineStr"/>
+      <c r="BL233" t="inlineStr"/>
+      <c r="BM233" t="inlineStr"/>
+      <c r="BN233" t="inlineStr"/>
+      <c r="BO233" t="inlineStr"/>
+      <c r="BP233" t="inlineStr"/>
+      <c r="BQ233" t="inlineStr"/>
+      <c r="BR233" t="inlineStr"/>
+      <c r="BS233" t="inlineStr"/>
+      <c r="BT233" t="inlineStr"/>
+      <c r="BU233" t="inlineStr"/>
+      <c r="BV233" t="inlineStr"/>
+      <c r="BW233" t="inlineStr"/>
+      <c r="BX233" t="inlineStr"/>
+      <c r="BY233" t="inlineStr"/>
+      <c r="BZ233" t="inlineStr"/>
+      <c r="CA233" t="inlineStr"/>
+      <c r="CB233" t="inlineStr"/>
+      <c r="CC233" t="inlineStr"/>
+      <c r="CD233" t="inlineStr"/>
+      <c r="CE233" t="inlineStr"/>
+      <c r="CF233" t="inlineStr"/>
+      <c r="CG233" t="inlineStr"/>
+      <c r="CH233" t="inlineStr"/>
+      <c r="CI233" t="inlineStr"/>
+      <c r="CJ233" t="inlineStr"/>
+      <c r="CK233" t="inlineStr"/>
+      <c r="CL233" t="inlineStr"/>
+      <c r="CM233" t="inlineStr"/>
+      <c r="CN233" t="inlineStr"/>
+      <c r="CO233" t="inlineStr"/>
+      <c r="CP233" t="inlineStr"/>
+      <c r="CQ233" t="inlineStr"/>
+      <c r="CR233" t="inlineStr"/>
+      <c r="CS233" t="inlineStr"/>
+      <c r="CT233" t="inlineStr"/>
+      <c r="CU233" t="inlineStr"/>
+      <c r="CV233" t="inlineStr"/>
+      <c r="CW233" t="inlineStr"/>
+      <c r="CX233" t="inlineStr"/>
+      <c r="CY233" t="inlineStr"/>
+      <c r="CZ233" t="inlineStr"/>
+      <c r="DA233" t="inlineStr"/>
+      <c r="DB233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>p0vxl2jf</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="n">
+        <v>45591.5</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F234" t="n">
+        <v>13796</v>
+      </c>
+      <c r="G234" t="n">
+        <v>4</v>
+      </c>
+      <c r="H234" t="n">
+        <v>2</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="K234" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L234" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M234" t="n">
+        <v>42</v>
+      </c>
+      <c r="N234" t="n">
+        <v>58</v>
+      </c>
+      <c r="O234" t="n">
+        <v>13</v>
+      </c>
+      <c r="P234" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>8</v>
+      </c>
+      <c r="R234" t="n">
+        <v>7</v>
+      </c>
+      <c r="S234" t="n">
+        <v>4</v>
+      </c>
+      <c r="T234" t="n">
+        <v>5</v>
+      </c>
+      <c r="U234" t="n">
+        <v>1</v>
+      </c>
+      <c r="V234" t="n">
+        <v>7</v>
+      </c>
+      <c r="W234" t="n">
+        <v>13</v>
+      </c>
+      <c r="X234" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH234" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ234" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AL234" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AM234" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN234" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP234" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ234" t="inlineStr"/>
+      <c r="AR234" t="inlineStr"/>
+      <c r="AS234" t="n">
+        <v>397</v>
+      </c>
+      <c r="AT234" t="n">
+        <v>564</v>
+      </c>
+      <c r="AU234" t="inlineStr"/>
+      <c r="AV234" t="inlineStr"/>
+      <c r="AW234" t="inlineStr"/>
+      <c r="AX234" t="inlineStr"/>
+      <c r="AY234" t="n">
+        <v>318</v>
+      </c>
+      <c r="AZ234" t="n">
+        <v>483</v>
+      </c>
+      <c r="BA234" t="inlineStr"/>
+      <c r="BB234" t="inlineStr"/>
+      <c r="BC234" t="inlineStr"/>
+      <c r="BD234" t="inlineStr"/>
+      <c r="BE234" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF234" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG234" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH234" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI234" t="inlineStr"/>
+      <c r="BJ234" t="inlineStr"/>
+      <c r="BK234" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BL234" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="BM234" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="BN234" t="inlineStr"/>
+      <c r="BO234" t="n">
+        <v>1631250</v>
+      </c>
+      <c r="BP234" t="n">
+        <v>72.625</v>
+      </c>
+      <c r="BQ234" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR234" t="inlineStr"/>
+      <c r="BS234" t="inlineStr"/>
+      <c r="BT234" t="inlineStr"/>
+      <c r="BU234" t="inlineStr"/>
+      <c r="BV234" t="inlineStr"/>
+      <c r="BW234" t="inlineStr"/>
+      <c r="BX234" t="inlineStr"/>
+      <c r="BY234" t="n">
+        <v>26.15384615384615</v>
+      </c>
+      <c r="BZ234" t="n">
+        <v>180.6153846153846</v>
+      </c>
+      <c r="CA234" t="n">
+        <v>65.69230769230769</v>
+      </c>
+      <c r="CB234" t="inlineStr"/>
+      <c r="CC234" t="n">
+        <v>971153.8461538461</v>
+      </c>
+      <c r="CD234" t="n">
+        <v>71.30769230769231</v>
+      </c>
+      <c r="CE234" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF234" t="n">
+        <v>25.27777777777778</v>
+      </c>
+      <c r="CG234" t="n">
+        <v>183.0555555555555</v>
+      </c>
+      <c r="CH234" t="n">
+        <v>69.22222222222223</v>
+      </c>
+      <c r="CI234" t="inlineStr"/>
+      <c r="CJ234" t="n">
+        <v>2041666.666666667</v>
+      </c>
+      <c r="CK234" t="n">
+        <v>73.27777777777777</v>
+      </c>
+      <c r="CL234" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM234" t="n">
+        <v>23.83333333333333</v>
+      </c>
+      <c r="CN234" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="CO234" t="n">
+        <v>6</v>
+      </c>
+      <c r="CP234" t="n">
+        <v>397</v>
+      </c>
+      <c r="CQ234" t="inlineStr"/>
+      <c r="CR234" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="CS234" t="n">
+        <v>436</v>
+      </c>
+      <c r="CT234" t="n">
+        <v>6</v>
+      </c>
+      <c r="CU234" t="n">
+        <v>28</v>
+      </c>
+      <c r="CV234" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="CW234" t="n">
+        <v>4</v>
+      </c>
+      <c r="CX234" t="n">
+        <v>280</v>
+      </c>
+      <c r="CY234" t="n">
+        <v>21000</v>
+      </c>
+      <c r="CZ234" t="n">
+        <v>6675000</v>
+      </c>
+      <c r="DA234" t="n">
+        <v>284</v>
+      </c>
+      <c r="DB234" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>lYpTkOLs</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="n">
+        <v>45590.65625</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F235" t="n">
+        <v>27130</v>
+      </c>
+      <c r="G235" t="n">
+        <v>1</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="K235" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L235" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M235" t="n">
+        <v>61</v>
+      </c>
+      <c r="N235" t="n">
+        <v>39</v>
+      </c>
+      <c r="O235" t="n">
+        <v>20</v>
+      </c>
+      <c r="P235" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>4</v>
+      </c>
+      <c r="R235" t="n">
+        <v>1</v>
+      </c>
+      <c r="S235" t="n">
+        <v>8</v>
+      </c>
+      <c r="T235" t="n">
+        <v>2</v>
+      </c>
+      <c r="U235" t="n">
+        <v>8</v>
+      </c>
+      <c r="V235" t="n">
+        <v>2</v>
+      </c>
+      <c r="W235" t="n">
+        <v>7</v>
+      </c>
+      <c r="X235" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH235" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ235" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AL235" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="AM235" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN235" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP235" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS235" t="n">
+        <v>538</v>
+      </c>
+      <c r="AT235" t="n">
+        <v>361</v>
+      </c>
+      <c r="AU235" t="inlineStr"/>
+      <c r="AV235" t="inlineStr"/>
+      <c r="AW235" t="inlineStr"/>
+      <c r="AX235" t="inlineStr"/>
+      <c r="AY235" t="n">
+        <v>465</v>
+      </c>
+      <c r="AZ235" t="n">
+        <v>287</v>
+      </c>
+      <c r="BA235" t="inlineStr"/>
+      <c r="BB235" t="inlineStr"/>
+      <c r="BC235" t="inlineStr"/>
+      <c r="BD235" t="inlineStr"/>
+      <c r="BE235" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF235" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG235" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH235" t="n">
+        <v>13</v>
+      </c>
+      <c r="BI235" t="inlineStr"/>
+      <c r="BJ235" t="inlineStr"/>
+      <c r="BK235" t="inlineStr"/>
+      <c r="BL235" t="inlineStr"/>
+      <c r="BM235" t="inlineStr"/>
+      <c r="BN235" t="inlineStr"/>
+      <c r="BO235" t="inlineStr"/>
+      <c r="BP235" t="inlineStr"/>
+      <c r="BQ235" t="inlineStr"/>
+      <c r="BR235" t="inlineStr"/>
+      <c r="BS235" t="inlineStr"/>
+      <c r="BT235" t="inlineStr"/>
+      <c r="BU235" t="inlineStr"/>
+      <c r="BV235" t="inlineStr"/>
+      <c r="BW235" t="inlineStr"/>
+      <c r="BX235" t="inlineStr"/>
+      <c r="BY235" t="inlineStr"/>
+      <c r="BZ235" t="inlineStr"/>
+      <c r="CA235" t="inlineStr"/>
+      <c r="CB235" t="inlineStr"/>
+      <c r="CC235" t="inlineStr"/>
+      <c r="CD235" t="inlineStr"/>
+      <c r="CE235" t="inlineStr"/>
+      <c r="CF235" t="inlineStr"/>
+      <c r="CG235" t="inlineStr"/>
+      <c r="CH235" t="inlineStr"/>
+      <c r="CI235" t="inlineStr"/>
+      <c r="CJ235" t="inlineStr"/>
+      <c r="CK235" t="inlineStr"/>
+      <c r="CL235" t="inlineStr"/>
+      <c r="CM235" t="n">
+        <v>20</v>
+      </c>
+      <c r="CN235" t="n">
+        <v>189</v>
+      </c>
+      <c r="CO235" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP235" t="n">
+        <v>72</v>
+      </c>
+      <c r="CQ235" t="n">
+        <v>14000</v>
+      </c>
+      <c r="CR235" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="CS235" t="n">
+        <v>78</v>
+      </c>
+      <c r="CT235" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU235" t="inlineStr"/>
+      <c r="CV235" t="inlineStr"/>
+      <c r="CW235" t="inlineStr"/>
+      <c r="CX235" t="inlineStr"/>
+      <c r="CY235" t="inlineStr"/>
+      <c r="CZ235" t="inlineStr"/>
+      <c r="DA235" t="inlineStr"/>
+      <c r="DB235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>Wplzx9A5</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="n">
+        <v>45591.625</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thual o 
+  fra </t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michel moretti stadium
+  ajaccio </t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>8470</v>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="n">
+        <v>49</v>
+      </c>
+      <c r="N236" t="n">
+        <v>51</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>0</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0</v>
+      </c>
+      <c r="S236" t="n">
+        <v>0</v>
+      </c>
+      <c r="T236" t="n">
+        <v>2</v>
+      </c>
+      <c r="U236" t="n">
+        <v>0</v>
+      </c>
+      <c r="V236" t="n">
+        <v>2</v>
+      </c>
+      <c r="W236" t="inlineStr"/>
+      <c r="X236" t="inlineStr"/>
+      <c r="Y236" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC236" t="inlineStr"/>
+      <c r="AD236" t="inlineStr"/>
+      <c r="AE236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG236" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH236" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI236" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AL236" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AM236" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN236" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP236" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ236" t="inlineStr"/>
+      <c r="AR236" t="inlineStr"/>
+      <c r="AS236" t="n">
+        <v>153</v>
+      </c>
+      <c r="AT236" t="n">
+        <v>146</v>
+      </c>
+      <c r="AU236" t="inlineStr"/>
+      <c r="AV236" t="inlineStr"/>
+      <c r="AW236" t="inlineStr"/>
+      <c r="AX236" t="inlineStr"/>
+      <c r="AY236" t="n">
+        <v>111</v>
+      </c>
+      <c r="AZ236" t="n">
+        <v>99</v>
+      </c>
+      <c r="BA236" t="inlineStr"/>
+      <c r="BB236" t="inlineStr"/>
+      <c r="BC236" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD236" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE236" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF236" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG236" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH236" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI236" t="inlineStr"/>
+      <c r="BJ236" t="inlineStr"/>
+      <c r="BK236" t="inlineStr"/>
+      <c r="BL236" t="inlineStr"/>
+      <c r="BM236" t="inlineStr"/>
+      <c r="BN236" t="inlineStr"/>
+      <c r="BO236" t="inlineStr"/>
+      <c r="BP236" t="inlineStr"/>
+      <c r="BQ236" t="inlineStr"/>
+      <c r="BR236" t="inlineStr"/>
+      <c r="BS236" t="inlineStr"/>
+      <c r="BT236" t="inlineStr"/>
+      <c r="BU236" t="inlineStr"/>
+      <c r="BV236" t="inlineStr"/>
+      <c r="BW236" t="inlineStr"/>
+      <c r="BX236" t="inlineStr"/>
+      <c r="BY236" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="BZ236" t="n">
+        <v>178</v>
+      </c>
+      <c r="CA236" t="n">
+        <v>65.83333333333333</v>
+      </c>
+      <c r="CB236" t="inlineStr"/>
+      <c r="CC236" t="n">
+        <v>800000</v>
+      </c>
+      <c r="CD236" t="n">
+        <v>70.83333333333333</v>
+      </c>
+      <c r="CE236" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF236" t="n">
+        <v>25.16666666666667</v>
+      </c>
+      <c r="CG236" t="n">
+        <v>180.8333333333333</v>
+      </c>
+      <c r="CH236" t="n">
+        <v>62</v>
+      </c>
+      <c r="CI236" t="inlineStr"/>
+      <c r="CJ236" t="n">
+        <v>562500</v>
+      </c>
+      <c r="CK236" t="n">
+        <v>65.66666666666667</v>
+      </c>
+      <c r="CL236" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM236" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="CN236" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="CO236" t="n">
+        <v>2</v>
+      </c>
+      <c r="CP236" t="n">
+        <v>135</v>
+      </c>
+      <c r="CQ236" t="n">
+        <v>5000</v>
+      </c>
+      <c r="CR236" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="CS236" t="n">
+        <v>135</v>
+      </c>
+      <c r="CT236" t="n">
+        <v>2</v>
+      </c>
+      <c r="CU236" t="inlineStr"/>
+      <c r="CV236" t="inlineStr"/>
+      <c r="CW236" t="inlineStr"/>
+      <c r="CX236" t="inlineStr"/>
+      <c r="CY236" t="inlineStr"/>
+      <c r="CZ236" t="inlineStr"/>
+      <c r="DA236" t="inlineStr"/>
+      <c r="DB236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>dheSbdqf</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="n">
+        <v>45591.375</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petit a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade michel d ornano
+  caen </t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>20300</v>
+      </c>
+      <c r="F237" t="n">
+        <v>15771</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>1</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="n">
+        <v>67</v>
+      </c>
+      <c r="N237" t="n">
+        <v>33</v>
+      </c>
+      <c r="O237" t="n">
+        <v>14</v>
+      </c>
+      <c r="P237" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>4</v>
+      </c>
+      <c r="R237" t="n">
+        <v>5</v>
+      </c>
+      <c r="S237" t="n">
+        <v>4</v>
+      </c>
+      <c r="T237" t="n">
+        <v>3</v>
+      </c>
+      <c r="U237" t="n">
+        <v>6</v>
+      </c>
+      <c r="V237" t="n">
+        <v>2</v>
+      </c>
+      <c r="W237" t="inlineStr"/>
+      <c r="X237" t="inlineStr"/>
+      <c r="Y237" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC237" t="inlineStr"/>
+      <c r="AD237" t="inlineStr"/>
+      <c r="AE237" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF237" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG237" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH237" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK237" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AL237" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="AM237" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN237" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP237" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR237" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS237" t="n">
+        <v>614</v>
+      </c>
+      <c r="AT237" t="n">
+        <v>337</v>
+      </c>
+      <c r="AU237" t="inlineStr"/>
+      <c r="AV237" t="inlineStr"/>
+      <c r="AW237" t="inlineStr"/>
+      <c r="AX237" t="inlineStr"/>
+      <c r="AY237" t="n">
+        <v>518</v>
+      </c>
+      <c r="AZ237" t="n">
+        <v>238</v>
+      </c>
+      <c r="BA237" t="inlineStr"/>
+      <c r="BB237" t="inlineStr"/>
+      <c r="BC237" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD237" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE237" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF237" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG237" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH237" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI237" t="inlineStr"/>
+      <c r="BJ237" t="inlineStr"/>
+      <c r="BK237" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BL237" t="n">
+        <v>182.375</v>
+      </c>
+      <c r="BM237" t="n">
+        <v>66.875</v>
+      </c>
+      <c r="BN237" t="inlineStr"/>
+      <c r="BO237" t="n">
+        <v>1496875</v>
+      </c>
+      <c r="BP237" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="BQ237" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR237" t="n">
+        <v>24.625</v>
+      </c>
+      <c r="BS237" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="BT237" t="n">
+        <v>66.875</v>
+      </c>
+      <c r="BU237" t="inlineStr"/>
+      <c r="BV237" t="n">
+        <v>1306250</v>
+      </c>
+      <c r="BW237" t="n">
+        <v>72.625</v>
+      </c>
+      <c r="BX237" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY237" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BZ237" t="n">
+        <v>183</v>
+      </c>
+      <c r="CA237" t="n">
+        <v>65.77777777777777</v>
+      </c>
+      <c r="CB237" t="inlineStr"/>
+      <c r="CC237" t="n">
+        <v>1205555.555555556</v>
+      </c>
+      <c r="CD237" t="n">
+        <v>71.83333333333333</v>
+      </c>
+      <c r="CE237" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF237" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="CG237" t="n">
+        <v>173.75</v>
+      </c>
+      <c r="CH237" t="n">
+        <v>65.16666666666667</v>
+      </c>
+      <c r="CI237" t="inlineStr"/>
+      <c r="CJ237" t="n">
+        <v>1329166.666666667</v>
+      </c>
+      <c r="CK237" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="CL237" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM237" t="n">
+        <v>20</v>
+      </c>
+      <c r="CN237" t="n">
+        <v>187</v>
+      </c>
+      <c r="CO237" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP237" t="n">
+        <v>60</v>
+      </c>
+      <c r="CQ237" t="inlineStr"/>
+      <c r="CR237" t="n">
+        <v>550000</v>
+      </c>
+      <c r="CS237" t="n">
+        <v>74</v>
+      </c>
+      <c r="CT237" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU237" t="n">
+        <v>28</v>
+      </c>
+      <c r="CV237" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="CW237" t="n">
+        <v>5</v>
+      </c>
+      <c r="CX237" t="n">
+        <v>340</v>
+      </c>
+      <c r="CY237" t="n">
+        <v>19000</v>
+      </c>
+      <c r="CZ237" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="DA237" t="n">
+        <v>356</v>
+      </c>
+      <c r="DB237" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>25dJuiBt</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="n">
+        <v>45591.375</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade charlety
+  paris </t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F238" t="n">
+        <v>15412</v>
+      </c>
+      <c r="G238" t="n">
+        <v>2</v>
+      </c>
+      <c r="H238" t="n">
+        <v>1</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="n">
+        <v>53</v>
+      </c>
+      <c r="N238" t="n">
+        <v>47</v>
+      </c>
+      <c r="O238" t="n">
+        <v>18</v>
+      </c>
+      <c r="P238" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>9</v>
+      </c>
+      <c r="R238" t="n">
+        <v>3</v>
+      </c>
+      <c r="S238" t="n">
+        <v>6</v>
+      </c>
+      <c r="T238" t="n">
+        <v>1</v>
+      </c>
+      <c r="U238" t="n">
+        <v>3</v>
+      </c>
+      <c r="V238" t="n">
+        <v>4</v>
+      </c>
+      <c r="W238" t="inlineStr"/>
+      <c r="X238" t="inlineStr"/>
+      <c r="Y238" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z238" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA238" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC238" t="inlineStr"/>
+      <c r="AD238" t="inlineStr"/>
+      <c r="AE238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF238" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG238" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH238" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ238" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="AL238" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AM238" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN238" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP238" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ238" t="inlineStr"/>
+      <c r="AR238" t="inlineStr"/>
+      <c r="AS238" t="n">
+        <v>569</v>
+      </c>
+      <c r="AT238" t="n">
+        <v>454</v>
+      </c>
+      <c r="AU238" t="inlineStr"/>
+      <c r="AV238" t="inlineStr"/>
+      <c r="AW238" t="inlineStr"/>
+      <c r="AX238" t="inlineStr"/>
+      <c r="AY238" t="n">
+        <v>497</v>
+      </c>
+      <c r="AZ238" t="n">
+        <v>370</v>
+      </c>
+      <c r="BA238" t="inlineStr"/>
+      <c r="BB238" t="inlineStr"/>
+      <c r="BC238" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD238" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE238" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF238" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG238" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH238" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI238" t="inlineStr"/>
+      <c r="BJ238" t="inlineStr"/>
+      <c r="BK238" t="n">
+        <v>24.625</v>
+      </c>
+      <c r="BL238" t="n">
+        <v>179.625</v>
+      </c>
+      <c r="BM238" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="BN238" t="n">
+        <v>3250</v>
+      </c>
+      <c r="BO238" t="n">
+        <v>1771875</v>
+      </c>
+      <c r="BP238" t="n">
+        <v>71.625</v>
+      </c>
+      <c r="BQ238" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="BR238" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="BS238" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="BT238" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="BU238" t="inlineStr"/>
+      <c r="BV238" t="n">
+        <v>1377500</v>
+      </c>
+      <c r="BW238" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BX238" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY238" t="n">
+        <v>26.47058823529412</v>
+      </c>
+      <c r="BZ238" t="n">
+        <v>177</v>
+      </c>
+      <c r="CA238" t="n">
+        <v>66.29411764705883</v>
+      </c>
+      <c r="CB238" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CC238" t="n">
+        <v>1130882.352941176</v>
+      </c>
+      <c r="CD238" t="n">
+        <v>69.47058823529412</v>
+      </c>
+      <c r="CE238" t="n">
+        <v>1.058823529411765</v>
+      </c>
+      <c r="CF238" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="CG238" t="n">
+        <v>176.8666666666667</v>
+      </c>
+      <c r="CH238" t="n">
+        <v>66.73333333333333</v>
+      </c>
+      <c r="CI238" t="n">
+        <v>3600</v>
+      </c>
+      <c r="CJ238" t="n">
+        <v>1766666.666666667</v>
+      </c>
+      <c r="CK238" t="n">
+        <v>73</v>
+      </c>
+      <c r="CL238" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM238" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="CN238" t="n">
+        <v>181</v>
+      </c>
+      <c r="CO238" t="n">
+        <v>5</v>
+      </c>
+      <c r="CP238" t="n">
+        <v>332</v>
+      </c>
+      <c r="CQ238" t="inlineStr"/>
+      <c r="CR238" t="n">
+        <v>6750000</v>
+      </c>
+      <c r="CS238" t="n">
+        <v>357</v>
+      </c>
+      <c r="CT238" t="n">
+        <v>5</v>
+      </c>
+      <c r="CU238" t="n">
+        <v>28</v>
+      </c>
+      <c r="CV238" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="CW238" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX238" t="n">
+        <v>197</v>
+      </c>
+      <c r="CY238" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CZ238" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="DA238" t="n">
+        <v>204</v>
+      </c>
+      <c r="DB238" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>dW3GHvPj</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="n">
+        <v>45590.625</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des sports
+  annecy </t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>15660</v>
+      </c>
+      <c r="F239" t="n">
+        <v>5362</v>
+      </c>
+      <c r="G239" t="n">
+        <v>2</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="n">
+        <v>50</v>
+      </c>
+      <c r="N239" t="n">
+        <v>50</v>
+      </c>
+      <c r="O239" t="n">
+        <v>14</v>
+      </c>
+      <c r="P239" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>4</v>
+      </c>
+      <c r="R239" t="n">
+        <v>2</v>
+      </c>
+      <c r="S239" t="n">
+        <v>5</v>
+      </c>
+      <c r="T239" t="n">
+        <v>8</v>
+      </c>
+      <c r="U239" t="n">
+        <v>5</v>
+      </c>
+      <c r="V239" t="n">
+        <v>3</v>
+      </c>
+      <c r="W239" t="inlineStr"/>
+      <c r="X239" t="inlineStr"/>
+      <c r="Y239" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z239" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB239" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC239" t="inlineStr"/>
+      <c r="AD239" t="inlineStr"/>
+      <c r="AE239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG239" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH239" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI239" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="AL239" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AM239" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN239" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP239" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ239" t="inlineStr"/>
+      <c r="AR239" t="inlineStr"/>
+      <c r="AS239" t="n">
+        <v>394</v>
+      </c>
+      <c r="AT239" t="n">
+        <v>383</v>
+      </c>
+      <c r="AU239" t="inlineStr"/>
+      <c r="AV239" t="inlineStr"/>
+      <c r="AW239" t="inlineStr"/>
+      <c r="AX239" t="inlineStr"/>
+      <c r="AY239" t="n">
+        <v>256</v>
+      </c>
+      <c r="AZ239" t="n">
+        <v>235</v>
+      </c>
+      <c r="BA239" t="inlineStr"/>
+      <c r="BB239" t="inlineStr"/>
+      <c r="BC239" t="n">
+        <v>33</v>
+      </c>
+      <c r="BD239" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE239" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF239" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG239" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH239" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI239" t="inlineStr"/>
+      <c r="BJ239" t="inlineStr"/>
+      <c r="BK239" t="inlineStr"/>
+      <c r="BL239" t="inlineStr"/>
+      <c r="BM239" t="inlineStr"/>
+      <c r="BN239" t="inlineStr"/>
+      <c r="BO239" t="inlineStr"/>
+      <c r="BP239" t="inlineStr"/>
+      <c r="BQ239" t="inlineStr"/>
+      <c r="BR239" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="BS239" t="n">
+        <v>182.875</v>
+      </c>
+      <c r="BT239" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="BU239" t="n">
+        <v>1875</v>
+      </c>
+      <c r="BV239" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="BW239" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="BX239" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY239" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="BZ239" t="n">
+        <v>178.375</v>
+      </c>
+      <c r="CA239" t="n">
+        <v>62.375</v>
+      </c>
+      <c r="CB239" t="inlineStr"/>
+      <c r="CC239" t="n">
+        <v>631250</v>
+      </c>
+      <c r="CD239" t="n">
+        <v>67</v>
+      </c>
+      <c r="CE239" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF239" t="n">
+        <v>26.91666666666667</v>
+      </c>
+      <c r="CG239" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="CH239" t="n">
+        <v>65.66666666666667</v>
+      </c>
+      <c r="CI239" t="n">
+        <v>2666.666666666667</v>
+      </c>
+      <c r="CJ239" t="n">
+        <v>1030416.666666667</v>
+      </c>
+      <c r="CK239" t="n">
+        <v>71</v>
+      </c>
+      <c r="CL239" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM239" t="inlineStr"/>
+      <c r="CN239" t="inlineStr"/>
+      <c r="CO239" t="inlineStr"/>
+      <c r="CP239" t="inlineStr"/>
+      <c r="CQ239" t="inlineStr"/>
+      <c r="CR239" t="inlineStr"/>
+      <c r="CS239" t="inlineStr"/>
+      <c r="CT239" t="inlineStr"/>
+      <c r="CU239" t="n">
+        <v>34</v>
+      </c>
+      <c r="CV239" t="n">
+        <v>183</v>
+      </c>
+      <c r="CW239" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX239" t="n">
+        <v>66</v>
+      </c>
+      <c r="CY239" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CZ239" t="n">
+        <v>400000</v>
+      </c>
+      <c r="DA239" t="n">
+        <v>66</v>
+      </c>
+      <c r="DB239" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>OvR8LmQO</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="n">
+        <v>45590.625</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valnet a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade gabriel montpied
+  clermont ferrand </t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F240" t="n">
+        <v>5004</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>1</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="n">
+        <v>59</v>
+      </c>
+      <c r="N240" t="n">
+        <v>41</v>
+      </c>
+      <c r="O240" t="n">
+        <v>10</v>
+      </c>
+      <c r="P240" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>2</v>
+      </c>
+      <c r="R240" t="n">
+        <v>4</v>
+      </c>
+      <c r="S240" t="n">
+        <v>4</v>
+      </c>
+      <c r="T240" t="n">
+        <v>4</v>
+      </c>
+      <c r="U240" t="n">
+        <v>4</v>
+      </c>
+      <c r="V240" t="n">
+        <v>2</v>
+      </c>
+      <c r="W240" t="inlineStr"/>
+      <c r="X240" t="inlineStr"/>
+      <c r="Y240" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC240" t="inlineStr"/>
+      <c r="AD240" t="inlineStr"/>
+      <c r="AE240" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG240" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH240" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ240" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK240" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="AL240" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AM240" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN240" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP240" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ240" t="inlineStr"/>
+      <c r="AR240" t="inlineStr"/>
+      <c r="AS240" t="n">
+        <v>526</v>
+      </c>
+      <c r="AT240" t="n">
+        <v>396</v>
+      </c>
+      <c r="AU240" t="inlineStr"/>
+      <c r="AV240" t="inlineStr"/>
+      <c r="AW240" t="inlineStr"/>
+      <c r="AX240" t="inlineStr"/>
+      <c r="AY240" t="n">
+        <v>424</v>
+      </c>
+      <c r="AZ240" t="n">
+        <v>293</v>
+      </c>
+      <c r="BA240" t="inlineStr"/>
+      <c r="BB240" t="inlineStr"/>
+      <c r="BC240" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD240" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE240" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF240" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG240" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH240" t="n">
+        <v>17</v>
+      </c>
+      <c r="BI240" t="inlineStr"/>
+      <c r="BJ240" t="inlineStr"/>
+      <c r="BK240" t="inlineStr"/>
+      <c r="BL240" t="inlineStr"/>
+      <c r="BM240" t="inlineStr"/>
+      <c r="BN240" t="inlineStr"/>
+      <c r="BO240" t="inlineStr"/>
+      <c r="BP240" t="inlineStr"/>
+      <c r="BQ240" t="inlineStr"/>
+      <c r="BR240" t="inlineStr"/>
+      <c r="BS240" t="inlineStr"/>
+      <c r="BT240" t="inlineStr"/>
+      <c r="BU240" t="inlineStr"/>
+      <c r="BV240" t="inlineStr"/>
+      <c r="BW240" t="inlineStr"/>
+      <c r="BX240" t="inlineStr"/>
+      <c r="BY240" t="inlineStr"/>
+      <c r="BZ240" t="inlineStr"/>
+      <c r="CA240" t="inlineStr"/>
+      <c r="CB240" t="inlineStr"/>
+      <c r="CC240" t="inlineStr"/>
+      <c r="CD240" t="inlineStr"/>
+      <c r="CE240" t="inlineStr"/>
+      <c r="CF240" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="CG240" t="n">
+        <v>182</v>
+      </c>
+      <c r="CH240" t="n">
+        <v>65</v>
+      </c>
+      <c r="CI240" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CJ240" t="n">
+        <v>825000</v>
+      </c>
+      <c r="CK240" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="CL240" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM240" t="inlineStr"/>
+      <c r="CN240" t="inlineStr"/>
+      <c r="CO240" t="inlineStr"/>
+      <c r="CP240" t="inlineStr"/>
+      <c r="CQ240" t="inlineStr"/>
+      <c r="CR240" t="inlineStr"/>
+      <c r="CS240" t="inlineStr"/>
+      <c r="CT240" t="inlineStr"/>
+      <c r="CU240" t="inlineStr"/>
+      <c r="CV240" t="inlineStr"/>
+      <c r="CW240" t="inlineStr"/>
+      <c r="CX240" t="inlineStr"/>
+      <c r="CY240" t="inlineStr"/>
+      <c r="CZ240" t="inlineStr"/>
+      <c r="DA240" t="inlineStr"/>
+      <c r="DB240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>xrirzmuI</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="n">
+        <v>45590.625</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lesage m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade marcel tribut
+  dunkerque </t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>4933</v>
+      </c>
+      <c r="F241" t="n">
+        <v>4605</v>
+      </c>
+      <c r="G241" t="n">
+        <v>2</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="n">
+        <v>48</v>
+      </c>
+      <c r="N241" t="n">
+        <v>52</v>
+      </c>
+      <c r="O241" t="n">
+        <v>13</v>
+      </c>
+      <c r="P241" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>6</v>
+      </c>
+      <c r="R241" t="n">
+        <v>1</v>
+      </c>
+      <c r="S241" t="n">
+        <v>2</v>
+      </c>
+      <c r="T241" t="n">
+        <v>5</v>
+      </c>
+      <c r="U241" t="n">
+        <v>5</v>
+      </c>
+      <c r="V241" t="n">
+        <v>1</v>
+      </c>
+      <c r="W241" t="inlineStr"/>
+      <c r="X241" t="inlineStr"/>
+      <c r="Y241" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z241" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC241" t="inlineStr"/>
+      <c r="AD241" t="inlineStr"/>
+      <c r="AE241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF241" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG241" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH241" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK241" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AL241" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AM241" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN241" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP241" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ241" t="inlineStr"/>
+      <c r="AR241" t="inlineStr"/>
+      <c r="AS241" t="n">
+        <v>429</v>
+      </c>
+      <c r="AT241" t="n">
+        <v>466</v>
+      </c>
+      <c r="AU241" t="inlineStr"/>
+      <c r="AV241" t="inlineStr"/>
+      <c r="AW241" t="inlineStr"/>
+      <c r="AX241" t="inlineStr"/>
+      <c r="AY241" t="n">
+        <v>352</v>
+      </c>
+      <c r="AZ241" t="n">
+        <v>379</v>
+      </c>
+      <c r="BA241" t="inlineStr"/>
+      <c r="BB241" t="inlineStr"/>
+      <c r="BC241" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD241" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE241" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF241" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG241" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH241" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI241" t="inlineStr"/>
+      <c r="BJ241" t="inlineStr"/>
+      <c r="BK241" t="inlineStr"/>
+      <c r="BL241" t="inlineStr"/>
+      <c r="BM241" t="inlineStr"/>
+      <c r="BN241" t="inlineStr"/>
+      <c r="BO241" t="inlineStr"/>
+      <c r="BP241" t="inlineStr"/>
+      <c r="BQ241" t="inlineStr"/>
+      <c r="BR241" t="inlineStr"/>
+      <c r="BS241" t="inlineStr"/>
+      <c r="BT241" t="inlineStr"/>
+      <c r="BU241" t="inlineStr"/>
+      <c r="BV241" t="inlineStr"/>
+      <c r="BW241" t="inlineStr"/>
+      <c r="BX241" t="inlineStr"/>
+      <c r="BY241" t="n">
+        <v>26</v>
+      </c>
+      <c r="BZ241" t="n">
+        <v>176.4444444444445</v>
+      </c>
+      <c r="CA241" t="n">
+        <v>64.88888888888889</v>
+      </c>
+      <c r="CB241" t="inlineStr"/>
+      <c r="CC241" t="n">
+        <v>775000</v>
+      </c>
+      <c r="CD241" t="n">
+        <v>72</v>
+      </c>
+      <c r="CE241" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF241" t="inlineStr"/>
+      <c r="CG241" t="inlineStr"/>
+      <c r="CH241" t="inlineStr"/>
+      <c r="CI241" t="inlineStr"/>
+      <c r="CJ241" t="inlineStr"/>
+      <c r="CK241" t="inlineStr"/>
+      <c r="CL241" t="inlineStr"/>
+      <c r="CM241" t="inlineStr"/>
+      <c r="CN241" t="inlineStr"/>
+      <c r="CO241" t="inlineStr"/>
+      <c r="CP241" t="inlineStr"/>
+      <c r="CQ241" t="inlineStr"/>
+      <c r="CR241" t="inlineStr"/>
+      <c r="CS241" t="inlineStr"/>
+      <c r="CT241" t="inlineStr"/>
+      <c r="CU241" t="inlineStr"/>
+      <c r="CV241" t="inlineStr"/>
+      <c r="CW241" t="inlineStr"/>
+      <c r="CX241" t="inlineStr"/>
+      <c r="CY241" t="inlineStr"/>
+      <c r="CZ241" t="inlineStr"/>
+      <c r="DA241" t="inlineStr"/>
+      <c r="DB241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>8rypRidm</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="n">
+        <v>45590.625</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taleb a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade saint symphorien
+  metz </t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>28786</v>
+      </c>
+      <c r="F242" t="n">
+        <v>19290</v>
+      </c>
+      <c r="G242" t="n">
+        <v>1</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="n">
+        <v>53</v>
+      </c>
+      <c r="N242" t="n">
+        <v>47</v>
+      </c>
+      <c r="O242" t="n">
+        <v>14</v>
+      </c>
+      <c r="P242" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>7</v>
+      </c>
+      <c r="R242" t="n">
+        <v>3</v>
+      </c>
+      <c r="S242" t="n">
+        <v>4</v>
+      </c>
+      <c r="T242" t="n">
+        <v>4</v>
+      </c>
+      <c r="U242" t="n">
+        <v>3</v>
+      </c>
+      <c r="V242" t="n">
+        <v>3</v>
+      </c>
+      <c r="W242" t="inlineStr"/>
+      <c r="X242" t="inlineStr"/>
+      <c r="Y242" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z242" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC242" t="inlineStr"/>
+      <c r="AD242" t="inlineStr"/>
+      <c r="AE242" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF242" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG242" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH242" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI242" t="inlineStr"/>
+      <c r="AJ242" t="inlineStr"/>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AL242" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="AM242" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN242" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP242" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ242" t="inlineStr"/>
+      <c r="AR242" t="inlineStr"/>
+      <c r="AS242" t="n">
+        <v>546</v>
+      </c>
+      <c r="AT242" t="n">
+        <v>479</v>
+      </c>
+      <c r="AU242" t="inlineStr"/>
+      <c r="AV242" t="inlineStr"/>
+      <c r="AW242" t="inlineStr"/>
+      <c r="AX242" t="inlineStr"/>
+      <c r="AY242" t="n">
+        <v>465</v>
+      </c>
+      <c r="AZ242" t="n">
+        <v>388</v>
+      </c>
+      <c r="BA242" t="inlineStr"/>
+      <c r="BB242" t="inlineStr"/>
+      <c r="BC242" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD242" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE242" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF242" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG242" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH242" t="n">
+        <v>18</v>
+      </c>
+      <c r="BI242" t="inlineStr"/>
+      <c r="BJ242" t="inlineStr"/>
+      <c r="BK242" t="inlineStr"/>
+      <c r="BL242" t="inlineStr"/>
+      <c r="BM242" t="inlineStr"/>
+      <c r="BN242" t="inlineStr"/>
+      <c r="BO242" t="inlineStr"/>
+      <c r="BP242" t="inlineStr"/>
+      <c r="BQ242" t="inlineStr"/>
+      <c r="BR242" t="n">
+        <v>24.88888888888889</v>
+      </c>
+      <c r="BS242" t="n">
+        <v>180.4444444444445</v>
+      </c>
+      <c r="BT242" t="n">
+        <v>65.33333333333333</v>
+      </c>
+      <c r="BU242" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BV242" t="n">
+        <v>983333.3333333334</v>
+      </c>
+      <c r="BW242" t="n">
+        <v>69.44444444444444</v>
+      </c>
+      <c r="BX242" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY242" t="inlineStr"/>
+      <c r="BZ242" t="inlineStr"/>
+      <c r="CA242" t="inlineStr"/>
+      <c r="CB242" t="inlineStr"/>
+      <c r="CC242" t="inlineStr"/>
+      <c r="CD242" t="inlineStr"/>
+      <c r="CE242" t="inlineStr"/>
+      <c r="CF242" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="CG242" t="n">
+        <v>175.1875</v>
+      </c>
+      <c r="CH242" t="n">
+        <v>64.0625</v>
+      </c>
+      <c r="CI242" t="n">
+        <v>1812.5</v>
+      </c>
+      <c r="CJ242" t="n">
+        <v>915625</v>
+      </c>
+      <c r="CK242" t="n">
+        <v>69</v>
+      </c>
+      <c r="CL242" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM242" t="inlineStr"/>
+      <c r="CN242" t="inlineStr"/>
+      <c r="CO242" t="inlineStr"/>
+      <c r="CP242" t="inlineStr"/>
+      <c r="CQ242" t="inlineStr"/>
+      <c r="CR242" t="inlineStr"/>
+      <c r="CS242" t="inlineStr"/>
+      <c r="CT242" t="inlineStr"/>
+      <c r="CU242" t="inlineStr"/>
+      <c r="CV242" t="inlineStr"/>
+      <c r="CW242" t="inlineStr"/>
+      <c r="CX242" t="inlineStr"/>
+      <c r="CY242" t="inlineStr"/>
+      <c r="CZ242" t="inlineStr"/>
+      <c r="DA242" t="inlineStr"/>
+      <c r="DB242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>zJfRwVug</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="n">
+        <v>45590.625</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">benchabane f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nouste camp
+  pau </t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>4031</v>
+      </c>
+      <c r="F243" t="n">
+        <v>3034</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>2</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="n">
+        <v>64</v>
+      </c>
+      <c r="N243" t="n">
+        <v>36</v>
+      </c>
+      <c r="O243" t="n">
+        <v>11</v>
+      </c>
+      <c r="P243" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>3</v>
+      </c>
+      <c r="R243" t="n">
+        <v>4</v>
+      </c>
+      <c r="S243" t="n">
+        <v>5</v>
+      </c>
+      <c r="T243" t="n">
+        <v>4</v>
+      </c>
+      <c r="U243" t="n">
+        <v>3</v>
+      </c>
+      <c r="V243" t="n">
+        <v>2</v>
+      </c>
+      <c r="W243" t="inlineStr"/>
+      <c r="X243" t="inlineStr"/>
+      <c r="Y243" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z243" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB243" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC243" t="inlineStr"/>
+      <c r="AD243" t="inlineStr"/>
+      <c r="AE243" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF243" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG243" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH243" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK243" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AL243" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AM243" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN243" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP243" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ243" t="inlineStr"/>
+      <c r="AR243" t="inlineStr"/>
+      <c r="AS243" t="n">
+        <v>575</v>
+      </c>
+      <c r="AT243" t="n">
+        <v>385</v>
+      </c>
+      <c r="AU243" t="inlineStr"/>
+      <c r="AV243" t="inlineStr"/>
+      <c r="AW243" t="inlineStr"/>
+      <c r="AX243" t="inlineStr"/>
+      <c r="AY243" t="n">
+        <v>486</v>
+      </c>
+      <c r="AZ243" t="n">
+        <v>275</v>
+      </c>
+      <c r="BA243" t="inlineStr"/>
+      <c r="BB243" t="inlineStr"/>
+      <c r="BC243" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD243" t="n">
+        <v>45</v>
+      </c>
+      <c r="BE243" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF243" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG243" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH243" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI243" t="inlineStr"/>
+      <c r="BJ243" t="inlineStr"/>
+      <c r="BK243" t="n">
+        <v>28.44444444444444</v>
+      </c>
+      <c r="BL243" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="BM243" t="n">
+        <v>67</v>
+      </c>
+      <c r="BN243" t="inlineStr"/>
+      <c r="BO243" t="n">
+        <v>930555.5555555555</v>
+      </c>
+      <c r="BP243" t="n">
+        <v>69.22222222222223</v>
+      </c>
+      <c r="BQ243" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR243" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="BS243" t="n">
+        <v>179.2</v>
+      </c>
+      <c r="BT243" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="BU243" t="inlineStr"/>
+      <c r="BV243" t="n">
+        <v>1215000</v>
+      </c>
+      <c r="BW243" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="BX243" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY243" t="n">
+        <v>22.42857142857143</v>
+      </c>
+      <c r="BZ243" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="CA243" t="n">
+        <v>63.35714285714285</v>
+      </c>
+      <c r="CB243" t="inlineStr"/>
+      <c r="CC243" t="n">
+        <v>919642.8571428572</v>
+      </c>
+      <c r="CD243" t="n">
+        <v>72.28571428571429</v>
+      </c>
+      <c r="CE243" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF243" t="n">
+        <v>21.22222222222222</v>
+      </c>
+      <c r="CG243" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="CH243" t="n">
+        <v>62.77777777777778</v>
+      </c>
+      <c r="CI243" t="inlineStr"/>
+      <c r="CJ243" t="n">
+        <v>1031944.444444444</v>
+      </c>
+      <c r="CK243" t="n">
+        <v>73.44444444444444</v>
+      </c>
+      <c r="CL243" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM243" t="n">
+        <v>29</v>
+      </c>
+      <c r="CN243" t="n">
+        <v>170</v>
+      </c>
+      <c r="CO243" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP243" t="n">
+        <v>66</v>
+      </c>
+      <c r="CQ243" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CR243" t="n">
+        <v>750000</v>
+      </c>
+      <c r="CS243" t="n">
+        <v>66</v>
+      </c>
+      <c r="CT243" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU243" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV243" t="n">
+        <v>175</v>
+      </c>
+      <c r="CW243" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX243" t="n">
+        <v>57</v>
+      </c>
+      <c r="CY243" t="inlineStr"/>
+      <c r="CZ243" t="n">
+        <v>425000</v>
+      </c>
+      <c r="DA243" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB243" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>xOS0N9eC</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="n">
+        <v>45590.625</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bouille t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade paul lignon
+  rodez </t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>5955</v>
+      </c>
+      <c r="F244" t="n">
+        <v>4024</v>
+      </c>
+      <c r="G244" t="n">
+        <v>3</v>
+      </c>
+      <c r="H244" t="n">
+        <v>3</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="n">
+        <v>44</v>
+      </c>
+      <c r="N244" t="n">
+        <v>56</v>
+      </c>
+      <c r="O244" t="n">
+        <v>15</v>
+      </c>
+      <c r="P244" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>5</v>
+      </c>
+      <c r="R244" t="n">
+        <v>4</v>
+      </c>
+      <c r="S244" t="n">
+        <v>6</v>
+      </c>
+      <c r="T244" t="n">
+        <v>7</v>
+      </c>
+      <c r="U244" t="n">
+        <v>4</v>
+      </c>
+      <c r="V244" t="n">
+        <v>2</v>
+      </c>
+      <c r="W244" t="inlineStr"/>
+      <c r="X244" t="inlineStr"/>
+      <c r="Y244" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z244" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC244" t="inlineStr"/>
+      <c r="AD244" t="inlineStr"/>
+      <c r="AE244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF244" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG244" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH244" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ244" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AL244" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="AM244" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN244" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP244" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ244" t="inlineStr"/>
+      <c r="AR244" t="inlineStr"/>
+      <c r="AS244" t="n">
+        <v>397</v>
+      </c>
+      <c r="AT244" t="n">
+        <v>530</v>
+      </c>
+      <c r="AU244" t="inlineStr"/>
+      <c r="AV244" t="inlineStr"/>
+      <c r="AW244" t="inlineStr"/>
+      <c r="AX244" t="inlineStr"/>
+      <c r="AY244" t="n">
+        <v>308</v>
+      </c>
+      <c r="AZ244" t="n">
+        <v>435</v>
+      </c>
+      <c r="BA244" t="inlineStr"/>
+      <c r="BB244" t="inlineStr"/>
+      <c r="BC244" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD244" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE244" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF244" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG244" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH244" t="n">
+        <v>13</v>
+      </c>
+      <c r="BI244" t="inlineStr"/>
+      <c r="BJ244" t="inlineStr"/>
+      <c r="BK244" t="inlineStr"/>
+      <c r="BL244" t="inlineStr"/>
+      <c r="BM244" t="inlineStr"/>
+      <c r="BN244" t="inlineStr"/>
+      <c r="BO244" t="inlineStr"/>
+      <c r="BP244" t="inlineStr"/>
+      <c r="BQ244" t="inlineStr"/>
+      <c r="BR244" t="inlineStr"/>
+      <c r="BS244" t="inlineStr"/>
+      <c r="BT244" t="inlineStr"/>
+      <c r="BU244" t="inlineStr"/>
+      <c r="BV244" t="inlineStr"/>
+      <c r="BW244" t="inlineStr"/>
+      <c r="BX244" t="inlineStr"/>
+      <c r="BY244" t="n">
+        <v>20</v>
+      </c>
+      <c r="BZ244" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="CA244" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="CB244" t="inlineStr"/>
+      <c r="CC244" t="n">
+        <v>790000</v>
+      </c>
+      <c r="CD244" t="n">
+        <v>75</v>
+      </c>
+      <c r="CE244" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF244" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="CG244" t="n">
+        <v>181.8571428571429</v>
+      </c>
+      <c r="CH244" t="n">
+        <v>67.14285714285714</v>
+      </c>
+      <c r="CI244" t="n">
+        <v>6428.571428571428</v>
+      </c>
+      <c r="CJ244" t="n">
+        <v>1846428.571428571</v>
+      </c>
+      <c r="CK244" t="n">
+        <v>75.71428571428571</v>
+      </c>
+      <c r="CL244" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM244" t="n">
+        <v>20</v>
+      </c>
+      <c r="CN244" t="n">
+        <v>181</v>
+      </c>
+      <c r="CO244" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP244" t="n">
+        <v>61</v>
+      </c>
+      <c r="CQ244" t="inlineStr"/>
+      <c r="CR244" t="n">
+        <v>675000</v>
+      </c>
+      <c r="CS244" t="n">
+        <v>69</v>
+      </c>
+      <c r="CT244" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU244" t="n">
+        <v>24</v>
+      </c>
+      <c r="CV244" t="n">
+        <v>173</v>
+      </c>
+      <c r="CW244" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX244" t="n">
+        <v>71</v>
+      </c>
+      <c r="CY244" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CZ244" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="DA244" t="n">
+        <v>74</v>
+      </c>
+      <c r="DB244" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="n">
+        <v>45592.69791666666</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F245" t="n">
+        <v>66115</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>3</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="K245" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L245" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="M245" t="n">
+        <v>25</v>
+      </c>
+      <c r="N245" t="n">
+        <v>75</v>
+      </c>
+      <c r="O245" t="n">
+        <v>5</v>
+      </c>
+      <c r="P245" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>1</v>
+      </c>
+      <c r="R245" t="n">
+        <v>8</v>
+      </c>
+      <c r="S245" t="n">
+        <v>2</v>
+      </c>
+      <c r="T245" t="n">
+        <v>9</v>
+      </c>
+      <c r="U245" t="n">
+        <v>2</v>
+      </c>
+      <c r="V245" t="n">
+        <v>2</v>
+      </c>
+      <c r="W245" t="n">
+        <v>7</v>
+      </c>
+      <c r="X245" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB245" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC245" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD245" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG245" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH245" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="AL245" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AM245" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN245" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP245" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS245" t="n">
+        <v>309</v>
+      </c>
+      <c r="AT245" t="n">
+        <v>918</v>
+      </c>
+      <c r="AU245" t="inlineStr"/>
+      <c r="AV245" t="inlineStr"/>
+      <c r="AW245" t="inlineStr"/>
+      <c r="AX245" t="inlineStr"/>
+      <c r="AY245" t="n">
+        <v>241</v>
+      </c>
+      <c r="AZ245" t="n">
+        <v>863</v>
+      </c>
+      <c r="BA245" t="inlineStr"/>
+      <c r="BB245" t="inlineStr"/>
+      <c r="BC245" t="inlineStr"/>
+      <c r="BD245" t="inlineStr"/>
+      <c r="BE245" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF245" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG245" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH245" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI245" t="inlineStr"/>
+      <c r="BJ245" t="inlineStr"/>
+      <c r="BK245" t="inlineStr"/>
+      <c r="BL245" t="inlineStr"/>
+      <c r="BM245" t="inlineStr"/>
+      <c r="BN245" t="inlineStr"/>
+      <c r="BO245" t="inlineStr"/>
+      <c r="BP245" t="inlineStr"/>
+      <c r="BQ245" t="inlineStr"/>
+      <c r="BR245" t="inlineStr"/>
+      <c r="BS245" t="inlineStr"/>
+      <c r="BT245" t="inlineStr"/>
+      <c r="BU245" t="inlineStr"/>
+      <c r="BV245" t="inlineStr"/>
+      <c r="BW245" t="inlineStr"/>
+      <c r="BX245" t="inlineStr"/>
+      <c r="BY245" t="inlineStr"/>
+      <c r="BZ245" t="inlineStr"/>
+      <c r="CA245" t="inlineStr"/>
+      <c r="CB245" t="inlineStr"/>
+      <c r="CC245" t="inlineStr"/>
+      <c r="CD245" t="inlineStr"/>
+      <c r="CE245" t="inlineStr"/>
+      <c r="CF245" t="inlineStr"/>
+      <c r="CG245" t="inlineStr"/>
+      <c r="CH245" t="inlineStr"/>
+      <c r="CI245" t="inlineStr"/>
+      <c r="CJ245" t="inlineStr"/>
+      <c r="CK245" t="inlineStr"/>
+      <c r="CL245" t="inlineStr"/>
+      <c r="CM245" t="inlineStr"/>
+      <c r="CN245" t="inlineStr"/>
+      <c r="CO245" t="inlineStr"/>
+      <c r="CP245" t="inlineStr"/>
+      <c r="CQ245" t="inlineStr"/>
+      <c r="CR245" t="inlineStr"/>
+      <c r="CS245" t="inlineStr"/>
+      <c r="CT245" t="inlineStr"/>
+      <c r="CU245" t="inlineStr"/>
+      <c r="CV245" t="inlineStr"/>
+      <c r="CW245" t="inlineStr"/>
+      <c r="CX245" t="inlineStr"/>
+      <c r="CY245" t="inlineStr"/>
+      <c r="CZ245" t="inlineStr"/>
+      <c r="DA245" t="inlineStr"/>
+      <c r="DB245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F246" t="n">
+        <v>14111</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>3</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="K246" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L246" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M246" t="n">
+        <v>52</v>
+      </c>
+      <c r="N246" t="n">
+        <v>48</v>
+      </c>
+      <c r="O246" t="n">
+        <v>9</v>
+      </c>
+      <c r="P246" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>2</v>
+      </c>
+      <c r="R246" t="n">
+        <v>6</v>
+      </c>
+      <c r="S246" t="n">
+        <v>5</v>
+      </c>
+      <c r="T246" t="n">
+        <v>5</v>
+      </c>
+      <c r="U246" t="n">
+        <v>2</v>
+      </c>
+      <c r="V246" t="n">
+        <v>4</v>
+      </c>
+      <c r="W246" t="n">
+        <v>20</v>
+      </c>
+      <c r="X246" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD246" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG246" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH246" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK246" t="inlineStr">
+        <is>
+          <t>EgvyJSJo</t>
+        </is>
+      </c>
+      <c r="AL246" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AM246" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN246" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP246" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS246" t="n">
+        <v>487</v>
+      </c>
+      <c r="AT246" t="n">
+        <v>465</v>
+      </c>
+      <c r="AU246" t="inlineStr"/>
+      <c r="AV246" t="inlineStr"/>
+      <c r="AW246" t="inlineStr"/>
+      <c r="AX246" t="inlineStr"/>
+      <c r="AY246" t="n">
+        <v>416</v>
+      </c>
+      <c r="AZ246" t="n">
+        <v>403</v>
+      </c>
+      <c r="BA246" t="inlineStr"/>
+      <c r="BB246" t="inlineStr"/>
+      <c r="BC246" t="inlineStr"/>
+      <c r="BD246" t="inlineStr"/>
+      <c r="BE246" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF246" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG246" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH246" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI246" t="inlineStr"/>
+      <c r="BJ246" t="inlineStr"/>
+      <c r="BK246" t="inlineStr"/>
+      <c r="BL246" t="inlineStr"/>
+      <c r="BM246" t="inlineStr"/>
+      <c r="BN246" t="inlineStr"/>
+      <c r="BO246" t="inlineStr"/>
+      <c r="BP246" t="inlineStr"/>
+      <c r="BQ246" t="inlineStr"/>
+      <c r="BR246" t="inlineStr"/>
+      <c r="BS246" t="inlineStr"/>
+      <c r="BT246" t="inlineStr"/>
+      <c r="BU246" t="inlineStr"/>
+      <c r="BV246" t="inlineStr"/>
+      <c r="BW246" t="inlineStr"/>
+      <c r="BX246" t="inlineStr"/>
+      <c r="BY246" t="inlineStr"/>
+      <c r="BZ246" t="inlineStr"/>
+      <c r="CA246" t="inlineStr"/>
+      <c r="CB246" t="inlineStr"/>
+      <c r="CC246" t="inlineStr"/>
+      <c r="CD246" t="inlineStr"/>
+      <c r="CE246" t="inlineStr"/>
+      <c r="CF246" t="inlineStr"/>
+      <c r="CG246" t="inlineStr"/>
+      <c r="CH246" t="inlineStr"/>
+      <c r="CI246" t="inlineStr"/>
+      <c r="CJ246" t="inlineStr"/>
+      <c r="CK246" t="inlineStr"/>
+      <c r="CL246" t="inlineStr"/>
+      <c r="CM246" t="inlineStr"/>
+      <c r="CN246" t="inlineStr"/>
+      <c r="CO246" t="inlineStr"/>
+      <c r="CP246" t="inlineStr"/>
+      <c r="CQ246" t="inlineStr"/>
+      <c r="CR246" t="inlineStr"/>
+      <c r="CS246" t="inlineStr"/>
+      <c r="CT246" t="inlineStr"/>
+      <c r="CU246" t="inlineStr"/>
+      <c r="CV246" t="inlineStr"/>
+      <c r="CW246" t="inlineStr"/>
+      <c r="CX246" t="inlineStr"/>
+      <c r="CY246" t="inlineStr"/>
+      <c r="CZ246" t="inlineStr"/>
+      <c r="DA246" t="inlineStr"/>
+      <c r="DB246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F247" t="n">
+        <v>29795</v>
+      </c>
+      <c r="G247" t="n">
+        <v>2</v>
+      </c>
+      <c r="H247" t="n">
+        <v>1</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="K247" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L247" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M247" t="n">
+        <v>40</v>
+      </c>
+      <c r="N247" t="n">
+        <v>60</v>
+      </c>
+      <c r="O247" t="n">
+        <v>17</v>
+      </c>
+      <c r="P247" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>9</v>
+      </c>
+      <c r="R247" t="n">
+        <v>5</v>
+      </c>
+      <c r="S247" t="n">
+        <v>6</v>
+      </c>
+      <c r="T247" t="n">
+        <v>1</v>
+      </c>
+      <c r="U247" t="n">
+        <v>2</v>
+      </c>
+      <c r="V247" t="n">
+        <v>5</v>
+      </c>
+      <c r="W247" t="n">
+        <v>11</v>
+      </c>
+      <c r="X247" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD247" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF247" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG247" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH247" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI247" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ247" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AL247" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AM247" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN247" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP247" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS247" t="n">
+        <v>313</v>
+      </c>
+      <c r="AT247" t="n">
+        <v>477</v>
+      </c>
+      <c r="AU247" t="inlineStr"/>
+      <c r="AV247" t="inlineStr"/>
+      <c r="AW247" t="inlineStr"/>
+      <c r="AX247" t="inlineStr"/>
+      <c r="AY247" t="n">
+        <v>246</v>
+      </c>
+      <c r="AZ247" t="n">
+        <v>396</v>
+      </c>
+      <c r="BA247" t="inlineStr"/>
+      <c r="BB247" t="inlineStr"/>
+      <c r="BC247" t="inlineStr"/>
+      <c r="BD247" t="inlineStr"/>
+      <c r="BE247" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF247" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG247" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH247" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI247" t="inlineStr"/>
+      <c r="BJ247" t="inlineStr"/>
+      <c r="BK247" t="inlineStr"/>
+      <c r="BL247" t="inlineStr"/>
+      <c r="BM247" t="inlineStr"/>
+      <c r="BN247" t="inlineStr"/>
+      <c r="BO247" t="inlineStr"/>
+      <c r="BP247" t="inlineStr"/>
+      <c r="BQ247" t="inlineStr"/>
+      <c r="BR247" t="inlineStr"/>
+      <c r="BS247" t="inlineStr"/>
+      <c r="BT247" t="inlineStr"/>
+      <c r="BU247" t="inlineStr"/>
+      <c r="BV247" t="inlineStr"/>
+      <c r="BW247" t="inlineStr"/>
+      <c r="BX247" t="inlineStr"/>
+      <c r="BY247" t="inlineStr"/>
+      <c r="BZ247" t="inlineStr"/>
+      <c r="CA247" t="inlineStr"/>
+      <c r="CB247" t="inlineStr"/>
+      <c r="CC247" t="inlineStr"/>
+      <c r="CD247" t="inlineStr"/>
+      <c r="CE247" t="inlineStr"/>
+      <c r="CF247" t="inlineStr"/>
+      <c r="CG247" t="inlineStr"/>
+      <c r="CH247" t="inlineStr"/>
+      <c r="CI247" t="inlineStr"/>
+      <c r="CJ247" t="inlineStr"/>
+      <c r="CK247" t="inlineStr"/>
+      <c r="CL247" t="inlineStr"/>
+      <c r="CM247" t="inlineStr"/>
+      <c r="CN247" t="inlineStr"/>
+      <c r="CO247" t="inlineStr"/>
+      <c r="CP247" t="inlineStr"/>
+      <c r="CQ247" t="inlineStr"/>
+      <c r="CR247" t="inlineStr"/>
+      <c r="CS247" t="inlineStr"/>
+      <c r="CT247" t="inlineStr"/>
+      <c r="CU247" t="inlineStr"/>
+      <c r="CV247" t="inlineStr"/>
+      <c r="CW247" t="inlineStr"/>
+      <c r="CX247" t="inlineStr"/>
+      <c r="CY247" t="inlineStr"/>
+      <c r="CZ247" t="inlineStr"/>
+      <c r="DA247" t="inlineStr"/>
+      <c r="DB247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F248" t="n">
+        <v>19398</v>
+      </c>
+      <c r="G248" t="n">
+        <v>3</v>
+      </c>
+      <c r="H248" t="n">
+        <v>1</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="K248" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L248" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M248" t="n">
+        <v>50</v>
+      </c>
+      <c r="N248" t="n">
+        <v>50</v>
+      </c>
+      <c r="O248" t="n">
+        <v>9</v>
+      </c>
+      <c r="P248" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>5</v>
+      </c>
+      <c r="R248" t="n">
+        <v>6</v>
+      </c>
+      <c r="S248" t="n">
+        <v>1</v>
+      </c>
+      <c r="T248" t="n">
+        <v>1</v>
+      </c>
+      <c r="U248" t="n">
+        <v>3</v>
+      </c>
+      <c r="V248" t="n">
+        <v>1</v>
+      </c>
+      <c r="W248" t="n">
+        <v>17</v>
+      </c>
+      <c r="X248" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD248" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG248" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH248" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ248" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AL248" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AM248" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN248" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP248" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ248" t="inlineStr"/>
+      <c r="AR248" t="inlineStr"/>
+      <c r="AS248" t="n">
+        <v>487</v>
+      </c>
+      <c r="AT248" t="n">
+        <v>479</v>
+      </c>
+      <c r="AU248" t="inlineStr"/>
+      <c r="AV248" t="inlineStr"/>
+      <c r="AW248" t="inlineStr"/>
+      <c r="AX248" t="inlineStr"/>
+      <c r="AY248" t="n">
+        <v>412</v>
+      </c>
+      <c r="AZ248" t="n">
+        <v>401</v>
+      </c>
+      <c r="BA248" t="inlineStr"/>
+      <c r="BB248" t="inlineStr"/>
+      <c r="BC248" t="inlineStr"/>
+      <c r="BD248" t="inlineStr"/>
+      <c r="BE248" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF248" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG248" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH248" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI248" t="inlineStr"/>
+      <c r="BJ248" t="inlineStr"/>
+      <c r="BK248" t="inlineStr"/>
+      <c r="BL248" t="inlineStr"/>
+      <c r="BM248" t="inlineStr"/>
+      <c r="BN248" t="inlineStr"/>
+      <c r="BO248" t="inlineStr"/>
+      <c r="BP248" t="inlineStr"/>
+      <c r="BQ248" t="inlineStr"/>
+      <c r="BR248" t="inlineStr"/>
+      <c r="BS248" t="inlineStr"/>
+      <c r="BT248" t="inlineStr"/>
+      <c r="BU248" t="inlineStr"/>
+      <c r="BV248" t="inlineStr"/>
+      <c r="BW248" t="inlineStr"/>
+      <c r="BX248" t="inlineStr"/>
+      <c r="BY248" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="BZ248" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="CA248" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="CB248" t="n">
+        <v>3600</v>
+      </c>
+      <c r="CC248" t="n">
+        <v>2725000</v>
+      </c>
+      <c r="CD248" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="CE248" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF248" t="inlineStr"/>
+      <c r="CG248" t="inlineStr"/>
+      <c r="CH248" t="inlineStr"/>
+      <c r="CI248" t="inlineStr"/>
+      <c r="CJ248" t="inlineStr"/>
+      <c r="CK248" t="inlineStr"/>
+      <c r="CL248" t="inlineStr"/>
+      <c r="CM248" t="inlineStr"/>
+      <c r="CN248" t="inlineStr"/>
+      <c r="CO248" t="inlineStr"/>
+      <c r="CP248" t="inlineStr"/>
+      <c r="CQ248" t="inlineStr"/>
+      <c r="CR248" t="inlineStr"/>
+      <c r="CS248" t="inlineStr"/>
+      <c r="CT248" t="inlineStr"/>
+      <c r="CU248" t="inlineStr"/>
+      <c r="CV248" t="inlineStr"/>
+      <c r="CW248" t="inlineStr"/>
+      <c r="CX248" t="inlineStr"/>
+      <c r="CY248" t="inlineStr"/>
+      <c r="CZ248" t="inlineStr"/>
+      <c r="DA248" t="inlineStr"/>
+      <c r="DB248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>WdE2Z2y1</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F249" t="n">
+        <v>54868</v>
+      </c>
+      <c r="G249" t="n">
+        <v>2</v>
+      </c>
+      <c r="H249" t="n">
+        <v>2</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="K249" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L249" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M249" t="n">
+        <v>63</v>
+      </c>
+      <c r="N249" t="n">
+        <v>37</v>
+      </c>
+      <c r="O249" t="n">
+        <v>12</v>
+      </c>
+      <c r="P249" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>8</v>
+      </c>
+      <c r="R249" t="n">
+        <v>4</v>
+      </c>
+      <c r="S249" t="n">
+        <v>2</v>
+      </c>
+      <c r="T249" t="n">
+        <v>7</v>
+      </c>
+      <c r="U249" t="n">
+        <v>2</v>
+      </c>
+      <c r="V249" t="n">
+        <v>6</v>
+      </c>
+      <c r="W249" t="n">
+        <v>14</v>
+      </c>
+      <c r="X249" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB249" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD249" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF249" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG249" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH249" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ249" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AL249" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="AM249" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN249" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP249" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ249" t="inlineStr"/>
+      <c r="AR249" t="inlineStr"/>
+      <c r="AS249" t="n">
+        <v>519</v>
+      </c>
+      <c r="AT249" t="n">
+        <v>286</v>
+      </c>
+      <c r="AU249" t="inlineStr"/>
+      <c r="AV249" t="inlineStr"/>
+      <c r="AW249" t="inlineStr"/>
+      <c r="AX249" t="inlineStr"/>
+      <c r="AY249" t="n">
+        <v>442</v>
+      </c>
+      <c r="AZ249" t="n">
+        <v>219</v>
+      </c>
+      <c r="BA249" t="inlineStr"/>
+      <c r="BB249" t="inlineStr"/>
+      <c r="BC249" t="inlineStr"/>
+      <c r="BD249" t="inlineStr"/>
+      <c r="BE249" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF249" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG249" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH249" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI249" t="inlineStr"/>
+      <c r="BJ249" t="inlineStr"/>
+      <c r="BK249" t="inlineStr"/>
+      <c r="BL249" t="inlineStr"/>
+      <c r="BM249" t="inlineStr"/>
+      <c r="BN249" t="inlineStr"/>
+      <c r="BO249" t="inlineStr"/>
+      <c r="BP249" t="inlineStr"/>
+      <c r="BQ249" t="inlineStr"/>
+      <c r="BR249" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="BS249" t="n">
+        <v>182</v>
+      </c>
+      <c r="BT249" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="BU249" t="inlineStr"/>
+      <c r="BV249" t="n">
+        <v>1362500</v>
+      </c>
+      <c r="BW249" t="n">
+        <v>71.125</v>
+      </c>
+      <c r="BX249" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY249" t="inlineStr"/>
+      <c r="BZ249" t="inlineStr"/>
+      <c r="CA249" t="inlineStr"/>
+      <c r="CB249" t="inlineStr"/>
+      <c r="CC249" t="inlineStr"/>
+      <c r="CD249" t="inlineStr"/>
+      <c r="CE249" t="inlineStr"/>
+      <c r="CF249" t="n">
+        <v>24.73684210526316</v>
+      </c>
+      <c r="CG249" t="n">
+        <v>180.7894736842105</v>
+      </c>
+      <c r="CH249" t="n">
+        <v>67.10526315789474</v>
+      </c>
+      <c r="CI249" t="inlineStr"/>
+      <c r="CJ249" t="n">
+        <v>1460526.315789474</v>
+      </c>
+      <c r="CK249" t="n">
+        <v>71.52631578947368</v>
+      </c>
+      <c r="CL249" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM249" t="inlineStr"/>
+      <c r="CN249" t="inlineStr"/>
+      <c r="CO249" t="inlineStr"/>
+      <c r="CP249" t="inlineStr"/>
+      <c r="CQ249" t="inlineStr"/>
+      <c r="CR249" t="inlineStr"/>
+      <c r="CS249" t="inlineStr"/>
+      <c r="CT249" t="inlineStr"/>
+      <c r="CU249" t="n">
+        <v>24</v>
+      </c>
+      <c r="CV249" t="n">
+        <v>186</v>
+      </c>
+      <c r="CW249" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX249" t="n">
+        <v>198</v>
+      </c>
+      <c r="CY249" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CZ249" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="DA249" t="n">
+        <v>219</v>
+      </c>
+      <c r="DB249" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB249"/>
+  <dimension ref="A1:DB258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66707,6 +66707,2400 @@
         <v>3</v>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>K4kBwMoA</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="n">
+        <v>45594.6875</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landry r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>12097</v>
+      </c>
+      <c r="F250" t="n">
+        <v>8171</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="n">
+        <v>31</v>
+      </c>
+      <c r="N250" t="n">
+        <v>69</v>
+      </c>
+      <c r="O250" t="n">
+        <v>15</v>
+      </c>
+      <c r="P250" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>3</v>
+      </c>
+      <c r="R250" t="n">
+        <v>4</v>
+      </c>
+      <c r="S250" t="n">
+        <v>5</v>
+      </c>
+      <c r="T250" t="n">
+        <v>9</v>
+      </c>
+      <c r="U250" t="n">
+        <v>7</v>
+      </c>
+      <c r="V250" t="n">
+        <v>1</v>
+      </c>
+      <c r="W250" t="inlineStr"/>
+      <c r="X250" t="inlineStr"/>
+      <c r="Y250" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB250" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC250" t="inlineStr"/>
+      <c r="AD250" t="inlineStr"/>
+      <c r="AE250" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF250" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG250" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH250" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ250" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AL250" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="AM250" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN250" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP250" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ250" t="inlineStr"/>
+      <c r="AR250" t="inlineStr"/>
+      <c r="AS250" t="n">
+        <v>320</v>
+      </c>
+      <c r="AT250" t="n">
+        <v>686</v>
+      </c>
+      <c r="AU250" t="inlineStr"/>
+      <c r="AV250" t="inlineStr"/>
+      <c r="AW250" t="inlineStr"/>
+      <c r="AX250" t="inlineStr"/>
+      <c r="AY250" t="n">
+        <v>250</v>
+      </c>
+      <c r="AZ250" t="n">
+        <v>643</v>
+      </c>
+      <c r="BA250" t="inlineStr"/>
+      <c r="BB250" t="inlineStr"/>
+      <c r="BC250" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD250" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE250" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF250" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG250" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH250" t="n">
+        <v>11</v>
+      </c>
+      <c r="BI250" t="inlineStr"/>
+      <c r="BJ250" t="inlineStr"/>
+      <c r="BK250" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BL250" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="BM250" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="BN250" t="inlineStr"/>
+      <c r="BO250" t="n">
+        <v>1195000</v>
+      </c>
+      <c r="BP250" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BQ250" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR250" t="n">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="BS250" t="n">
+        <v>177.1111111111111</v>
+      </c>
+      <c r="BT250" t="n">
+        <v>67.55555555555556</v>
+      </c>
+      <c r="BU250" t="n">
+        <v>3333.333333333333</v>
+      </c>
+      <c r="BV250" t="n">
+        <v>1722222.222222222</v>
+      </c>
+      <c r="BW250" t="n">
+        <v>71.88888888888889</v>
+      </c>
+      <c r="BX250" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="BY250" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="BZ250" t="n">
+        <v>182.9333333333333</v>
+      </c>
+      <c r="CA250" t="n">
+        <v>64</v>
+      </c>
+      <c r="CB250" t="inlineStr"/>
+      <c r="CC250" t="n">
+        <v>1036666.666666667</v>
+      </c>
+      <c r="CD250" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="CE250" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF250" t="n">
+        <v>26.53846153846154</v>
+      </c>
+      <c r="CG250" t="n">
+        <v>179.3076923076923</v>
+      </c>
+      <c r="CH250" t="n">
+        <v>67.38461538461539</v>
+      </c>
+      <c r="CI250" t="n">
+        <v>3384.615384615385</v>
+      </c>
+      <c r="CJ250" t="n">
+        <v>1340384.615384615</v>
+      </c>
+      <c r="CK250" t="n">
+        <v>68.92307692307692</v>
+      </c>
+      <c r="CL250" t="n">
+        <v>1.076923076923077</v>
+      </c>
+      <c r="CM250" t="inlineStr"/>
+      <c r="CN250" t="inlineStr"/>
+      <c r="CO250" t="inlineStr"/>
+      <c r="CP250" t="inlineStr"/>
+      <c r="CQ250" t="inlineStr"/>
+      <c r="CR250" t="inlineStr"/>
+      <c r="CS250" t="inlineStr"/>
+      <c r="CT250" t="inlineStr"/>
+      <c r="CU250" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="CV250" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="CW250" t="n">
+        <v>6</v>
+      </c>
+      <c r="CX250" t="n">
+        <v>400</v>
+      </c>
+      <c r="CY250" t="inlineStr"/>
+      <c r="CZ250" t="n">
+        <v>7950000</v>
+      </c>
+      <c r="DA250" t="n">
+        <v>425</v>
+      </c>
+      <c r="DB250" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>hImJy0GM</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="n">
+        <v>45594.6875</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buquet r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade armand cesari
+  bastia </t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>16048</v>
+      </c>
+      <c r="F251" t="n">
+        <v>9809</v>
+      </c>
+      <c r="G251" t="n">
+        <v>2</v>
+      </c>
+      <c r="H251" t="n">
+        <v>2</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="n">
+        <v>62</v>
+      </c>
+      <c r="N251" t="n">
+        <v>38</v>
+      </c>
+      <c r="O251" t="n">
+        <v>17</v>
+      </c>
+      <c r="P251" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>6</v>
+      </c>
+      <c r="R251" t="n">
+        <v>3</v>
+      </c>
+      <c r="S251" t="n">
+        <v>6</v>
+      </c>
+      <c r="T251" t="n">
+        <v>4</v>
+      </c>
+      <c r="U251" t="n">
+        <v>5</v>
+      </c>
+      <c r="V251" t="n">
+        <v>7</v>
+      </c>
+      <c r="W251" t="inlineStr"/>
+      <c r="X251" t="inlineStr"/>
+      <c r="Y251" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC251" t="inlineStr"/>
+      <c r="AD251" t="inlineStr"/>
+      <c r="AE251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF251" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG251" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH251" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AL251" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AM251" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN251" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP251" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ251" t="inlineStr"/>
+      <c r="AR251" t="inlineStr"/>
+      <c r="AS251" t="n">
+        <v>445</v>
+      </c>
+      <c r="AT251" t="n">
+        <v>300</v>
+      </c>
+      <c r="AU251" t="inlineStr"/>
+      <c r="AV251" t="inlineStr"/>
+      <c r="AW251" t="inlineStr"/>
+      <c r="AX251" t="inlineStr"/>
+      <c r="AY251" t="n">
+        <v>356</v>
+      </c>
+      <c r="AZ251" t="n">
+        <v>189</v>
+      </c>
+      <c r="BA251" t="inlineStr"/>
+      <c r="BB251" t="inlineStr"/>
+      <c r="BC251" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD251" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE251" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF251" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG251" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH251" t="n">
+        <v>13</v>
+      </c>
+      <c r="BI251" t="inlineStr"/>
+      <c r="BJ251" t="inlineStr"/>
+      <c r="BK251" t="inlineStr"/>
+      <c r="BL251" t="inlineStr"/>
+      <c r="BM251" t="inlineStr"/>
+      <c r="BN251" t="inlineStr"/>
+      <c r="BO251" t="inlineStr"/>
+      <c r="BP251" t="inlineStr"/>
+      <c r="BQ251" t="inlineStr"/>
+      <c r="BR251" t="inlineStr"/>
+      <c r="BS251" t="inlineStr"/>
+      <c r="BT251" t="inlineStr"/>
+      <c r="BU251" t="inlineStr"/>
+      <c r="BV251" t="inlineStr"/>
+      <c r="BW251" t="inlineStr"/>
+      <c r="BX251" t="inlineStr"/>
+      <c r="BY251" t="n">
+        <v>24.82352941176471</v>
+      </c>
+      <c r="BZ251" t="n">
+        <v>180.0588235294118</v>
+      </c>
+      <c r="CA251" t="n">
+        <v>63.64705882352941</v>
+      </c>
+      <c r="CB251" t="inlineStr"/>
+      <c r="CC251" t="n">
+        <v>794117.6470588235</v>
+      </c>
+      <c r="CD251" t="n">
+        <v>67.35294117647059</v>
+      </c>
+      <c r="CE251" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF251" t="n">
+        <v>19.83333333333333</v>
+      </c>
+      <c r="CG251" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="CH251" t="n">
+        <v>61.66666666666666</v>
+      </c>
+      <c r="CI251" t="inlineStr"/>
+      <c r="CJ251" t="n">
+        <v>775000</v>
+      </c>
+      <c r="CK251" t="n">
+        <v>74.33333333333333</v>
+      </c>
+      <c r="CL251" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM251" t="n">
+        <v>26</v>
+      </c>
+      <c r="CN251" t="n">
+        <v>172</v>
+      </c>
+      <c r="CO251" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP251" t="n">
+        <v>66</v>
+      </c>
+      <c r="CQ251" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CR251" t="n">
+        <v>925000</v>
+      </c>
+      <c r="CS251" t="n">
+        <v>67</v>
+      </c>
+      <c r="CT251" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU251" t="n">
+        <v>24</v>
+      </c>
+      <c r="CV251" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="CW251" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX251" t="n">
+        <v>185</v>
+      </c>
+      <c r="CY251" t="inlineStr"/>
+      <c r="CZ251" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="DA251" t="n">
+        <v>203</v>
+      </c>
+      <c r="DB251" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>UD9kUH8d</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="n">
+        <v>45594.6875</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abed k 
+  fra </t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>20068</v>
+      </c>
+      <c r="F252" t="n">
+        <v>7920</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="n">
+        <v>49</v>
+      </c>
+      <c r="N252" t="n">
+        <v>51</v>
+      </c>
+      <c r="O252" t="n">
+        <v>7</v>
+      </c>
+      <c r="P252" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>2</v>
+      </c>
+      <c r="R252" t="n">
+        <v>6</v>
+      </c>
+      <c r="S252" t="n">
+        <v>1</v>
+      </c>
+      <c r="T252" t="n">
+        <v>6</v>
+      </c>
+      <c r="U252" t="n">
+        <v>4</v>
+      </c>
+      <c r="V252" t="n">
+        <v>4</v>
+      </c>
+      <c r="W252" t="inlineStr"/>
+      <c r="X252" t="inlineStr"/>
+      <c r="Y252" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA252" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC252" t="inlineStr"/>
+      <c r="AD252" t="inlineStr"/>
+      <c r="AE252" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF252" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG252" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH252" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ252" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AL252" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="AM252" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN252" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP252" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ252" t="inlineStr"/>
+      <c r="AR252" t="inlineStr"/>
+      <c r="AS252" t="n">
+        <v>459</v>
+      </c>
+      <c r="AT252" t="n">
+        <v>469</v>
+      </c>
+      <c r="AU252" t="inlineStr"/>
+      <c r="AV252" t="inlineStr"/>
+      <c r="AW252" t="inlineStr"/>
+      <c r="AX252" t="inlineStr"/>
+      <c r="AY252" t="n">
+        <v>312</v>
+      </c>
+      <c r="AZ252" t="n">
+        <v>340</v>
+      </c>
+      <c r="BA252" t="inlineStr"/>
+      <c r="BB252" t="inlineStr"/>
+      <c r="BC252" t="n">
+        <v>41</v>
+      </c>
+      <c r="BD252" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE252" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF252" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG252" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH252" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI252" t="inlineStr"/>
+      <c r="BJ252" t="inlineStr"/>
+      <c r="BK252" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="BL252" t="n">
+        <v>184.2222222222222</v>
+      </c>
+      <c r="BM252" t="n">
+        <v>66.11111111111111</v>
+      </c>
+      <c r="BN252" t="inlineStr"/>
+      <c r="BO252" t="n">
+        <v>1619444.444444444</v>
+      </c>
+      <c r="BP252" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="BQ252" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR252" t="n">
+        <v>26.625</v>
+      </c>
+      <c r="BS252" t="n">
+        <v>182.125</v>
+      </c>
+      <c r="BT252" t="n">
+        <v>63.875</v>
+      </c>
+      <c r="BU252" t="inlineStr"/>
+      <c r="BV252" t="n">
+        <v>615625</v>
+      </c>
+      <c r="BW252" t="n">
+        <v>66.375</v>
+      </c>
+      <c r="BX252" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY252" t="n">
+        <v>26.07142857142857</v>
+      </c>
+      <c r="BZ252" t="n">
+        <v>184.0714285714286</v>
+      </c>
+      <c r="CA252" t="n">
+        <v>65</v>
+      </c>
+      <c r="CB252" t="n">
+        <v>2785.714285714286</v>
+      </c>
+      <c r="CC252" t="n">
+        <v>1083928.571428571</v>
+      </c>
+      <c r="CD252" t="n">
+        <v>68.42857142857143</v>
+      </c>
+      <c r="CE252" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF252" t="n">
+        <v>22</v>
+      </c>
+      <c r="CG252" t="n">
+        <v>177.3333333333333</v>
+      </c>
+      <c r="CH252" t="n">
+        <v>59.66666666666666</v>
+      </c>
+      <c r="CI252" t="inlineStr"/>
+      <c r="CJ252" t="n">
+        <v>470833.3333333333</v>
+      </c>
+      <c r="CK252" t="n">
+        <v>68</v>
+      </c>
+      <c r="CL252" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM252" t="n">
+        <v>34</v>
+      </c>
+      <c r="CN252" t="n">
+        <v>179</v>
+      </c>
+      <c r="CO252" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP252" t="n">
+        <v>68</v>
+      </c>
+      <c r="CQ252" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CR252" t="n">
+        <v>400000</v>
+      </c>
+      <c r="CS252" t="n">
+        <v>68</v>
+      </c>
+      <c r="CT252" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU252" t="inlineStr"/>
+      <c r="CV252" t="inlineStr"/>
+      <c r="CW252" t="inlineStr"/>
+      <c r="CX252" t="inlineStr"/>
+      <c r="CY252" t="inlineStr"/>
+      <c r="CZ252" t="inlineStr"/>
+      <c r="DA252" t="inlineStr"/>
+      <c r="DB252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>Mm6sWwvp</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="n">
+        <v>45594.6875</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valnet a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de roudourou
+  guingamp </t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>19060</v>
+      </c>
+      <c r="F253" t="n">
+        <v>7187</v>
+      </c>
+      <c r="G253" t="n">
+        <v>1</v>
+      </c>
+      <c r="H253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="n">
+        <v>57</v>
+      </c>
+      <c r="N253" t="n">
+        <v>43</v>
+      </c>
+      <c r="O253" t="n">
+        <v>11</v>
+      </c>
+      <c r="P253" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>5</v>
+      </c>
+      <c r="R253" t="n">
+        <v>4</v>
+      </c>
+      <c r="S253" t="n">
+        <v>4</v>
+      </c>
+      <c r="T253" t="n">
+        <v>1</v>
+      </c>
+      <c r="U253" t="n">
+        <v>2</v>
+      </c>
+      <c r="V253" t="n">
+        <v>1</v>
+      </c>
+      <c r="W253" t="inlineStr"/>
+      <c r="X253" t="inlineStr"/>
+      <c r="Y253" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA253" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC253" t="inlineStr"/>
+      <c r="AD253" t="inlineStr"/>
+      <c r="AE253" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF253" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG253" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH253" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="AL253" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AM253" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN253" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP253" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ253" t="inlineStr"/>
+      <c r="AR253" t="inlineStr"/>
+      <c r="AS253" t="n">
+        <v>498</v>
+      </c>
+      <c r="AT253" t="n">
+        <v>418</v>
+      </c>
+      <c r="AU253" t="inlineStr"/>
+      <c r="AV253" t="inlineStr"/>
+      <c r="AW253" t="inlineStr"/>
+      <c r="AX253" t="inlineStr"/>
+      <c r="AY253" t="n">
+        <v>397</v>
+      </c>
+      <c r="AZ253" t="n">
+        <v>326</v>
+      </c>
+      <c r="BA253" t="inlineStr"/>
+      <c r="BB253" t="inlineStr"/>
+      <c r="BC253" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD253" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE253" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF253" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG253" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH253" t="n">
+        <v>24</v>
+      </c>
+      <c r="BI253" t="inlineStr"/>
+      <c r="BJ253" t="inlineStr"/>
+      <c r="BK253" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="BL253" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="BM253" t="n">
+        <v>66.125</v>
+      </c>
+      <c r="BN253" t="n">
+        <v>2250</v>
+      </c>
+      <c r="BO253" t="n">
+        <v>1103125</v>
+      </c>
+      <c r="BP253" t="n">
+        <v>69.875</v>
+      </c>
+      <c r="BQ253" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR253" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="BS253" t="n">
+        <v>180.125</v>
+      </c>
+      <c r="BT253" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="BU253" t="inlineStr"/>
+      <c r="BV253" t="n">
+        <v>937500</v>
+      </c>
+      <c r="BW253" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BX253" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY253" t="n">
+        <v>24.05882352941176</v>
+      </c>
+      <c r="BZ253" t="n">
+        <v>179.2352941176471</v>
+      </c>
+      <c r="CA253" t="n">
+        <v>63.88235294117647</v>
+      </c>
+      <c r="CB253" t="n">
+        <v>1647.058823529412</v>
+      </c>
+      <c r="CC253" t="n">
+        <v>888235.2941176471</v>
+      </c>
+      <c r="CD253" t="n">
+        <v>69.29411764705883</v>
+      </c>
+      <c r="CE253" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF253" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="CG253" t="n">
+        <v>179.5333333333333</v>
+      </c>
+      <c r="CH253" t="n">
+        <v>63.06666666666667</v>
+      </c>
+      <c r="CI253" t="inlineStr"/>
+      <c r="CJ253" t="n">
+        <v>840000</v>
+      </c>
+      <c r="CK253" t="n">
+        <v>69.13333333333334</v>
+      </c>
+      <c r="CL253" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM253" t="inlineStr"/>
+      <c r="CN253" t="inlineStr"/>
+      <c r="CO253" t="inlineStr"/>
+      <c r="CP253" t="inlineStr"/>
+      <c r="CQ253" t="inlineStr"/>
+      <c r="CR253" t="inlineStr"/>
+      <c r="CS253" t="inlineStr"/>
+      <c r="CT253" t="inlineStr"/>
+      <c r="CU253" t="n">
+        <v>36</v>
+      </c>
+      <c r="CV253" t="n">
+        <v>179</v>
+      </c>
+      <c r="CW253" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX253" t="n">
+        <v>67</v>
+      </c>
+      <c r="CY253" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CZ253" t="n">
+        <v>350000</v>
+      </c>
+      <c r="DA253" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB253" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>CYrglw0S</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="n">
+        <v>45594.6875</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kubler g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le basser
+  laval </t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>11017</v>
+      </c>
+      <c r="F254" t="n">
+        <v>6799</v>
+      </c>
+      <c r="G254" t="n">
+        <v>1</v>
+      </c>
+      <c r="H254" t="n">
+        <v>2</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="n">
+        <v>45</v>
+      </c>
+      <c r="N254" t="n">
+        <v>55</v>
+      </c>
+      <c r="O254" t="n">
+        <v>14</v>
+      </c>
+      <c r="P254" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>4</v>
+      </c>
+      <c r="R254" t="n">
+        <v>4</v>
+      </c>
+      <c r="S254" t="n">
+        <v>6</v>
+      </c>
+      <c r="T254" t="n">
+        <v>2</v>
+      </c>
+      <c r="U254" t="n">
+        <v>4</v>
+      </c>
+      <c r="V254" t="n">
+        <v>3</v>
+      </c>
+      <c r="W254" t="inlineStr"/>
+      <c r="X254" t="inlineStr"/>
+      <c r="Y254" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC254" t="inlineStr"/>
+      <c r="AD254" t="inlineStr"/>
+      <c r="AE254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF254" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG254" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH254" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AL254" t="inlineStr">
+        <is>
+          <t>E3v5aJXp</t>
+        </is>
+      </c>
+      <c r="AM254" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN254" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP254" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ254" t="inlineStr"/>
+      <c r="AR254" t="inlineStr"/>
+      <c r="AS254" t="n">
+        <v>449</v>
+      </c>
+      <c r="AT254" t="n">
+        <v>547</v>
+      </c>
+      <c r="AU254" t="inlineStr"/>
+      <c r="AV254" t="inlineStr"/>
+      <c r="AW254" t="inlineStr"/>
+      <c r="AX254" t="inlineStr"/>
+      <c r="AY254" t="n">
+        <v>360</v>
+      </c>
+      <c r="AZ254" t="n">
+        <v>471</v>
+      </c>
+      <c r="BA254" t="inlineStr"/>
+      <c r="BB254" t="inlineStr"/>
+      <c r="BC254" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD254" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE254" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF254" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG254" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH254" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI254" t="inlineStr"/>
+      <c r="BJ254" t="inlineStr"/>
+      <c r="BK254" t="inlineStr"/>
+      <c r="BL254" t="inlineStr"/>
+      <c r="BM254" t="inlineStr"/>
+      <c r="BN254" t="inlineStr"/>
+      <c r="BO254" t="inlineStr"/>
+      <c r="BP254" t="inlineStr"/>
+      <c r="BQ254" t="inlineStr"/>
+      <c r="BR254" t="inlineStr"/>
+      <c r="BS254" t="inlineStr"/>
+      <c r="BT254" t="inlineStr"/>
+      <c r="BU254" t="inlineStr"/>
+      <c r="BV254" t="inlineStr"/>
+      <c r="BW254" t="inlineStr"/>
+      <c r="BX254" t="inlineStr"/>
+      <c r="BY254" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="BZ254" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="CA254" t="n">
+        <v>63.93333333333333</v>
+      </c>
+      <c r="CB254" t="inlineStr"/>
+      <c r="CC254" t="n">
+        <v>1027666.666666667</v>
+      </c>
+      <c r="CD254" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="CE254" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF254" t="n">
+        <v>24.71428571428572</v>
+      </c>
+      <c r="CG254" t="n">
+        <v>177.5714285714286</v>
+      </c>
+      <c r="CH254" t="n">
+        <v>63.42857142857143</v>
+      </c>
+      <c r="CI254" t="n">
+        <v>2285.714285714286</v>
+      </c>
+      <c r="CJ254" t="n">
+        <v>939285.7142857143</v>
+      </c>
+      <c r="CK254" t="n">
+        <v>68.14285714285714</v>
+      </c>
+      <c r="CL254" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM254" t="n">
+        <v>30</v>
+      </c>
+      <c r="CN254" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="CO254" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP254" t="n">
+        <v>197</v>
+      </c>
+      <c r="CQ254" t="n">
+        <v>6000</v>
+      </c>
+      <c r="CR254" t="n">
+        <v>2025000</v>
+      </c>
+      <c r="CS254" t="n">
+        <v>202</v>
+      </c>
+      <c r="CT254" t="n">
+        <v>3</v>
+      </c>
+      <c r="CU254" t="inlineStr"/>
+      <c r="CV254" t="inlineStr"/>
+      <c r="CW254" t="inlineStr"/>
+      <c r="CX254" t="inlineStr"/>
+      <c r="CY254" t="inlineStr"/>
+      <c r="CZ254" t="inlineStr"/>
+      <c r="DA254" t="inlineStr"/>
+      <c r="DB254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>A9nxhL03</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="n">
+        <v>45594.6875</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gaillouste p 
+  fra </t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade du moustoir
+  lorient </t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>16787</v>
+      </c>
+      <c r="F255" t="n">
+        <v>12036</v>
+      </c>
+      <c r="G255" t="n">
+        <v>4</v>
+      </c>
+      <c r="H255" t="n">
+        <v>2</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="n">
+        <v>47</v>
+      </c>
+      <c r="N255" t="n">
+        <v>53</v>
+      </c>
+      <c r="O255" t="n">
+        <v>11</v>
+      </c>
+      <c r="P255" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>5</v>
+      </c>
+      <c r="R255" t="n">
+        <v>4</v>
+      </c>
+      <c r="S255" t="n">
+        <v>1</v>
+      </c>
+      <c r="T255" t="n">
+        <v>2</v>
+      </c>
+      <c r="U255" t="n">
+        <v>5</v>
+      </c>
+      <c r="V255" t="n">
+        <v>3</v>
+      </c>
+      <c r="W255" t="inlineStr"/>
+      <c r="X255" t="inlineStr"/>
+      <c r="Y255" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA255" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC255" t="inlineStr"/>
+      <c r="AD255" t="inlineStr"/>
+      <c r="AE255" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG255" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH255" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ255" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="AL255" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AM255" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN255" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP255" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS255" t="n">
+        <v>396</v>
+      </c>
+      <c r="AT255" t="n">
+        <v>473</v>
+      </c>
+      <c r="AU255" t="inlineStr"/>
+      <c r="AV255" t="inlineStr"/>
+      <c r="AW255" t="inlineStr"/>
+      <c r="AX255" t="inlineStr"/>
+      <c r="AY255" t="n">
+        <v>308</v>
+      </c>
+      <c r="AZ255" t="n">
+        <v>378</v>
+      </c>
+      <c r="BA255" t="inlineStr"/>
+      <c r="BB255" t="inlineStr"/>
+      <c r="BC255" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD255" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE255" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF255" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG255" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH255" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI255" t="inlineStr"/>
+      <c r="BJ255" t="inlineStr"/>
+      <c r="BK255" t="inlineStr"/>
+      <c r="BL255" t="inlineStr"/>
+      <c r="BM255" t="inlineStr"/>
+      <c r="BN255" t="inlineStr"/>
+      <c r="BO255" t="inlineStr"/>
+      <c r="BP255" t="inlineStr"/>
+      <c r="BQ255" t="inlineStr"/>
+      <c r="BR255" t="inlineStr"/>
+      <c r="BS255" t="inlineStr"/>
+      <c r="BT255" t="inlineStr"/>
+      <c r="BU255" t="inlineStr"/>
+      <c r="BV255" t="inlineStr"/>
+      <c r="BW255" t="inlineStr"/>
+      <c r="BX255" t="inlineStr"/>
+      <c r="BY255" t="inlineStr"/>
+      <c r="BZ255" t="inlineStr"/>
+      <c r="CA255" t="inlineStr"/>
+      <c r="CB255" t="inlineStr"/>
+      <c r="CC255" t="inlineStr"/>
+      <c r="CD255" t="inlineStr"/>
+      <c r="CE255" t="inlineStr"/>
+      <c r="CF255" t="n">
+        <v>25.91666666666667</v>
+      </c>
+      <c r="CG255" t="n">
+        <v>177.4166666666667</v>
+      </c>
+      <c r="CH255" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="CI255" t="inlineStr"/>
+      <c r="CJ255" t="n">
+        <v>741666.6666666666</v>
+      </c>
+      <c r="CK255" t="n">
+        <v>70.58333333333333</v>
+      </c>
+      <c r="CL255" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM255" t="n">
+        <v>24</v>
+      </c>
+      <c r="CN255" t="n">
+        <v>173</v>
+      </c>
+      <c r="CO255" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP255" t="n">
+        <v>71</v>
+      </c>
+      <c r="CQ255" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CR255" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="CS255" t="n">
+        <v>74</v>
+      </c>
+      <c r="CT255" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU255" t="inlineStr"/>
+      <c r="CV255" t="inlineStr"/>
+      <c r="CW255" t="inlineStr"/>
+      <c r="CX255" t="inlineStr"/>
+      <c r="CY255" t="inlineStr"/>
+      <c r="CZ255" t="inlineStr"/>
+      <c r="DA255" t="inlineStr"/>
+      <c r="DB255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>Oxd2urHc</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="n">
+        <v>45594.6875</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rosier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis turcan
+  martigues </t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>11500</v>
+      </c>
+      <c r="F256" t="n">
+        <v>580</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" t="n">
+        <v>3</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="n">
+        <v>42</v>
+      </c>
+      <c r="N256" t="n">
+        <v>58</v>
+      </c>
+      <c r="O256" t="n">
+        <v>10</v>
+      </c>
+      <c r="P256" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>1</v>
+      </c>
+      <c r="R256" t="n">
+        <v>7</v>
+      </c>
+      <c r="S256" t="n">
+        <v>4</v>
+      </c>
+      <c r="T256" t="n">
+        <v>6</v>
+      </c>
+      <c r="U256" t="n">
+        <v>5</v>
+      </c>
+      <c r="V256" t="n">
+        <v>2</v>
+      </c>
+      <c r="W256" t="inlineStr"/>
+      <c r="X256" t="inlineStr"/>
+      <c r="Y256" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA256" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC256" t="inlineStr"/>
+      <c r="AD256" t="inlineStr"/>
+      <c r="AE256" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG256" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH256" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI256" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ256" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK256" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AL256" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AM256" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN256" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP256" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS256" t="n">
+        <v>359</v>
+      </c>
+      <c r="AT256" t="n">
+        <v>479</v>
+      </c>
+      <c r="AU256" t="inlineStr"/>
+      <c r="AV256" t="inlineStr"/>
+      <c r="AW256" t="inlineStr"/>
+      <c r="AX256" t="inlineStr"/>
+      <c r="AY256" t="n">
+        <v>270</v>
+      </c>
+      <c r="AZ256" t="n">
+        <v>393</v>
+      </c>
+      <c r="BA256" t="inlineStr"/>
+      <c r="BB256" t="inlineStr"/>
+      <c r="BC256" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD256" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE256" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF256" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG256" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH256" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI256" t="inlineStr"/>
+      <c r="BJ256" t="inlineStr"/>
+      <c r="BK256" t="inlineStr"/>
+      <c r="BL256" t="inlineStr"/>
+      <c r="BM256" t="inlineStr"/>
+      <c r="BN256" t="inlineStr"/>
+      <c r="BO256" t="inlineStr"/>
+      <c r="BP256" t="inlineStr"/>
+      <c r="BQ256" t="inlineStr"/>
+      <c r="BR256" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BS256" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="BT256" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="BU256" t="inlineStr"/>
+      <c r="BV256" t="n">
+        <v>1543750</v>
+      </c>
+      <c r="BW256" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="BX256" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY256" t="n">
+        <v>26.42857142857143</v>
+      </c>
+      <c r="BZ256" t="n">
+        <v>183.2857142857143</v>
+      </c>
+      <c r="CA256" t="n">
+        <v>65.14285714285714</v>
+      </c>
+      <c r="CB256" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CC256" t="n">
+        <v>850000</v>
+      </c>
+      <c r="CD256" t="n">
+        <v>66.85714285714286</v>
+      </c>
+      <c r="CE256" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF256" t="n">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="CG256" t="n">
+        <v>186</v>
+      </c>
+      <c r="CH256" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="CI256" t="inlineStr"/>
+      <c r="CJ256" t="n">
+        <v>1115909.090909091</v>
+      </c>
+      <c r="CK256" t="n">
+        <v>70.81818181818181</v>
+      </c>
+      <c r="CL256" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM256" t="inlineStr"/>
+      <c r="CN256" t="inlineStr"/>
+      <c r="CO256" t="inlineStr"/>
+      <c r="CP256" t="inlineStr"/>
+      <c r="CQ256" t="inlineStr"/>
+      <c r="CR256" t="inlineStr"/>
+      <c r="CS256" t="inlineStr"/>
+      <c r="CT256" t="inlineStr"/>
+      <c r="CU256" t="inlineStr"/>
+      <c r="CV256" t="inlineStr"/>
+      <c r="CW256" t="inlineStr"/>
+      <c r="CX256" t="inlineStr"/>
+      <c r="CY256" t="inlineStr"/>
+      <c r="CZ256" t="inlineStr"/>
+      <c r="DA256" t="inlineStr"/>
+      <c r="DB256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>IZkpjaVF</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="n">
+        <v>45594.6875</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapapria r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bauer
+  paris   saint ouen </t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F257" t="n">
+        <v>4643</v>
+      </c>
+      <c r="G257" t="n">
+        <v>1</v>
+      </c>
+      <c r="H257" t="n">
+        <v>0</v>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="n">
+        <v>36</v>
+      </c>
+      <c r="N257" t="n">
+        <v>64</v>
+      </c>
+      <c r="O257" t="n">
+        <v>6</v>
+      </c>
+      <c r="P257" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>2</v>
+      </c>
+      <c r="R257" t="n">
+        <v>1</v>
+      </c>
+      <c r="S257" t="n">
+        <v>2</v>
+      </c>
+      <c r="T257" t="n">
+        <v>9</v>
+      </c>
+      <c r="U257" t="n">
+        <v>2</v>
+      </c>
+      <c r="V257" t="n">
+        <v>6</v>
+      </c>
+      <c r="W257" t="inlineStr"/>
+      <c r="X257" t="inlineStr"/>
+      <c r="Y257" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB257" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC257" t="inlineStr"/>
+      <c r="AD257" t="inlineStr"/>
+      <c r="AE257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG257" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH257" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI257" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AL257" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AM257" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN257" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP257" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ257" t="inlineStr"/>
+      <c r="AR257" t="inlineStr"/>
+      <c r="AS257" t="n">
+        <v>373</v>
+      </c>
+      <c r="AT257" t="n">
+        <v>642</v>
+      </c>
+      <c r="AU257" t="inlineStr"/>
+      <c r="AV257" t="inlineStr"/>
+      <c r="AW257" t="inlineStr"/>
+      <c r="AX257" t="inlineStr"/>
+      <c r="AY257" t="n">
+        <v>301</v>
+      </c>
+      <c r="AZ257" t="n">
+        <v>579</v>
+      </c>
+      <c r="BA257" t="inlineStr"/>
+      <c r="BB257" t="inlineStr"/>
+      <c r="BC257" t="n">
+        <v>43</v>
+      </c>
+      <c r="BD257" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE257" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF257" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG257" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH257" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI257" t="inlineStr"/>
+      <c r="BJ257" t="inlineStr"/>
+      <c r="BK257" t="inlineStr"/>
+      <c r="BL257" t="inlineStr"/>
+      <c r="BM257" t="inlineStr"/>
+      <c r="BN257" t="inlineStr"/>
+      <c r="BO257" t="inlineStr"/>
+      <c r="BP257" t="inlineStr"/>
+      <c r="BQ257" t="inlineStr"/>
+      <c r="BR257" t="inlineStr"/>
+      <c r="BS257" t="inlineStr"/>
+      <c r="BT257" t="inlineStr"/>
+      <c r="BU257" t="inlineStr"/>
+      <c r="BV257" t="inlineStr"/>
+      <c r="BW257" t="inlineStr"/>
+      <c r="BX257" t="inlineStr"/>
+      <c r="BY257" t="inlineStr"/>
+      <c r="BZ257" t="inlineStr"/>
+      <c r="CA257" t="inlineStr"/>
+      <c r="CB257" t="inlineStr"/>
+      <c r="CC257" t="inlineStr"/>
+      <c r="CD257" t="inlineStr"/>
+      <c r="CE257" t="inlineStr"/>
+      <c r="CF257" t="inlineStr"/>
+      <c r="CG257" t="inlineStr"/>
+      <c r="CH257" t="inlineStr"/>
+      <c r="CI257" t="inlineStr"/>
+      <c r="CJ257" t="inlineStr"/>
+      <c r="CK257" t="inlineStr"/>
+      <c r="CL257" t="inlineStr"/>
+      <c r="CM257" t="inlineStr"/>
+      <c r="CN257" t="inlineStr"/>
+      <c r="CO257" t="inlineStr"/>
+      <c r="CP257" t="inlineStr"/>
+      <c r="CQ257" t="inlineStr"/>
+      <c r="CR257" t="inlineStr"/>
+      <c r="CS257" t="inlineStr"/>
+      <c r="CT257" t="inlineStr"/>
+      <c r="CU257" t="inlineStr"/>
+      <c r="CV257" t="inlineStr"/>
+      <c r="CW257" t="inlineStr"/>
+      <c r="CX257" t="inlineStr"/>
+      <c r="CY257" t="inlineStr"/>
+      <c r="CZ257" t="inlineStr"/>
+      <c r="DA257" t="inlineStr"/>
+      <c r="DB257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>U5gzczE6</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="n">
+        <v>45594.6875</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bouille t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l aube
+  troyes </t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>20420</v>
+      </c>
+      <c r="F258" t="n">
+        <v>4810</v>
+      </c>
+      <c r="G258" t="n">
+        <v>3</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0</v>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="n">
+        <v>38</v>
+      </c>
+      <c r="N258" t="n">
+        <v>62</v>
+      </c>
+      <c r="O258" t="n">
+        <v>18</v>
+      </c>
+      <c r="P258" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>10</v>
+      </c>
+      <c r="R258" t="n">
+        <v>2</v>
+      </c>
+      <c r="S258" t="n">
+        <v>7</v>
+      </c>
+      <c r="T258" t="n">
+        <v>4</v>
+      </c>
+      <c r="U258" t="n">
+        <v>1</v>
+      </c>
+      <c r="V258" t="n">
+        <v>3</v>
+      </c>
+      <c r="W258" t="inlineStr"/>
+      <c r="X258" t="inlineStr"/>
+      <c r="Y258" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC258" t="inlineStr"/>
+      <c r="AD258" t="inlineStr"/>
+      <c r="AE258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF258" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG258" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH258" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI258" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ258" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="AL258" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AM258" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN258" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP258" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ258" t="inlineStr"/>
+      <c r="AR258" t="inlineStr"/>
+      <c r="AS258" t="n">
+        <v>409</v>
+      </c>
+      <c r="AT258" t="n">
+        <v>673</v>
+      </c>
+      <c r="AU258" t="inlineStr"/>
+      <c r="AV258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr"/>
+      <c r="AX258" t="inlineStr"/>
+      <c r="AY258" t="n">
+        <v>337</v>
+      </c>
+      <c r="AZ258" t="n">
+        <v>585</v>
+      </c>
+      <c r="BA258" t="inlineStr"/>
+      <c r="BB258" t="inlineStr"/>
+      <c r="BC258" t="n">
+        <v>33</v>
+      </c>
+      <c r="BD258" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE258" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF258" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG258" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH258" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI258" t="inlineStr"/>
+      <c r="BJ258" t="inlineStr"/>
+      <c r="BK258" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="BL258" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="BM258" t="n">
+        <v>66</v>
+      </c>
+      <c r="BN258" t="inlineStr"/>
+      <c r="BO258" t="n">
+        <v>1206250</v>
+      </c>
+      <c r="BP258" t="n">
+        <v>71.625</v>
+      </c>
+      <c r="BQ258" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR258" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="BS258" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="BT258" t="n">
+        <v>64.88888888888889</v>
+      </c>
+      <c r="BU258" t="inlineStr"/>
+      <c r="BV258" t="n">
+        <v>1069444.444444444</v>
+      </c>
+      <c r="BW258" t="n">
+        <v>71.44444444444444</v>
+      </c>
+      <c r="BX258" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY258" t="n">
+        <v>24.06666666666667</v>
+      </c>
+      <c r="BZ258" t="n">
+        <v>174.9333333333333</v>
+      </c>
+      <c r="CA258" t="n">
+        <v>64.86666666666666</v>
+      </c>
+      <c r="CB258" t="inlineStr"/>
+      <c r="CC258" t="n">
+        <v>1116666.666666667</v>
+      </c>
+      <c r="CD258" t="n">
+        <v>70.73333333333333</v>
+      </c>
+      <c r="CE258" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF258" t="n">
+        <v>29.06666666666667</v>
+      </c>
+      <c r="CG258" t="n">
+        <v>180.0666666666667</v>
+      </c>
+      <c r="CH258" t="n">
+        <v>66.53333333333333</v>
+      </c>
+      <c r="CI258" t="inlineStr"/>
+      <c r="CJ258" t="n">
+        <v>796666.6666666666</v>
+      </c>
+      <c r="CK258" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="CL258" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM258" t="n">
+        <v>28</v>
+      </c>
+      <c r="CN258" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="CO258" t="n">
+        <v>5</v>
+      </c>
+      <c r="CP258" t="n">
+        <v>340</v>
+      </c>
+      <c r="CQ258" t="n">
+        <v>19000</v>
+      </c>
+      <c r="CR258" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="CS258" t="n">
+        <v>356</v>
+      </c>
+      <c r="CT258" t="n">
+        <v>6</v>
+      </c>
+      <c r="CU258" t="n">
+        <v>29</v>
+      </c>
+      <c r="CV258" t="n">
+        <v>170</v>
+      </c>
+      <c r="CW258" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX258" t="n">
+        <v>66</v>
+      </c>
+      <c r="CY258" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CZ258" t="n">
+        <v>750000</v>
+      </c>
+      <c r="DA258" t="n">
+        <v>66</v>
+      </c>
+      <c r="DB258" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB258"/>
+  <dimension ref="A1:DB276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69101,6 +69101,4480 @@
         <v>1</v>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>UTsToXQN</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="n">
+        <v>45599.69791666666</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dechepy b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="n">
+        <v>1</v>
+      </c>
+      <c r="H259" t="n">
+        <v>2</v>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="K259" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L259" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M259" t="n">
+        <v>26</v>
+      </c>
+      <c r="N259" t="n">
+        <v>74</v>
+      </c>
+      <c r="O259" t="n">
+        <v>7</v>
+      </c>
+      <c r="P259" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>3</v>
+      </c>
+      <c r="R259" t="n">
+        <v>4</v>
+      </c>
+      <c r="S259" t="n">
+        <v>3</v>
+      </c>
+      <c r="T259" t="n">
+        <v>3</v>
+      </c>
+      <c r="U259" t="n">
+        <v>1</v>
+      </c>
+      <c r="V259" t="n">
+        <v>2</v>
+      </c>
+      <c r="W259" t="n">
+        <v>6</v>
+      </c>
+      <c r="X259" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA259" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC259" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD259" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE259" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF259" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG259" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH259" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK259" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AL259" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="AM259" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN259" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP259" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ259" t="inlineStr"/>
+      <c r="AR259" t="inlineStr"/>
+      <c r="AS259" t="n">
+        <v>269</v>
+      </c>
+      <c r="AT259" t="n">
+        <v>777</v>
+      </c>
+      <c r="AU259" t="inlineStr"/>
+      <c r="AV259" t="inlineStr"/>
+      <c r="AW259" t="inlineStr"/>
+      <c r="AX259" t="inlineStr"/>
+      <c r="AY259" t="n">
+        <v>203</v>
+      </c>
+      <c r="AZ259" t="n">
+        <v>722</v>
+      </c>
+      <c r="BA259" t="inlineStr"/>
+      <c r="BB259" t="inlineStr"/>
+      <c r="BC259" t="inlineStr"/>
+      <c r="BD259" t="inlineStr"/>
+      <c r="BE259" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF259" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG259" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH259" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI259" t="inlineStr"/>
+      <c r="BJ259" t="inlineStr"/>
+      <c r="BK259" t="inlineStr"/>
+      <c r="BL259" t="inlineStr"/>
+      <c r="BM259" t="inlineStr"/>
+      <c r="BN259" t="inlineStr"/>
+      <c r="BO259" t="inlineStr"/>
+      <c r="BP259" t="inlineStr"/>
+      <c r="BQ259" t="inlineStr"/>
+      <c r="BR259" t="inlineStr"/>
+      <c r="BS259" t="inlineStr"/>
+      <c r="BT259" t="inlineStr"/>
+      <c r="BU259" t="inlineStr"/>
+      <c r="BV259" t="inlineStr"/>
+      <c r="BW259" t="inlineStr"/>
+      <c r="BX259" t="inlineStr"/>
+      <c r="BY259" t="inlineStr"/>
+      <c r="BZ259" t="inlineStr"/>
+      <c r="CA259" t="inlineStr"/>
+      <c r="CB259" t="inlineStr"/>
+      <c r="CC259" t="inlineStr"/>
+      <c r="CD259" t="inlineStr"/>
+      <c r="CE259" t="inlineStr"/>
+      <c r="CF259" t="inlineStr"/>
+      <c r="CG259" t="inlineStr"/>
+      <c r="CH259" t="inlineStr"/>
+      <c r="CI259" t="inlineStr"/>
+      <c r="CJ259" t="inlineStr"/>
+      <c r="CK259" t="inlineStr"/>
+      <c r="CL259" t="inlineStr"/>
+      <c r="CM259" t="inlineStr"/>
+      <c r="CN259" t="inlineStr"/>
+      <c r="CO259" t="inlineStr"/>
+      <c r="CP259" t="inlineStr"/>
+      <c r="CQ259" t="inlineStr"/>
+      <c r="CR259" t="inlineStr"/>
+      <c r="CS259" t="inlineStr"/>
+      <c r="CT259" t="inlineStr"/>
+      <c r="CU259" t="inlineStr"/>
+      <c r="CV259" t="inlineStr"/>
+      <c r="CW259" t="inlineStr"/>
+      <c r="CX259" t="inlineStr"/>
+      <c r="CY259" t="inlineStr"/>
+      <c r="CZ259" t="inlineStr"/>
+      <c r="DA259" t="inlineStr"/>
+      <c r="DB259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>EuWhpKkJ</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="n">
+        <v>45599.54166666666</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angoula g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F260" t="n">
+        <v>16366</v>
+      </c>
+      <c r="G260" t="n">
+        <v>4</v>
+      </c>
+      <c r="H260" t="n">
+        <v>0</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="K260" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="L260" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M260" t="n">
+        <v>39</v>
+      </c>
+      <c r="N260" t="n">
+        <v>61</v>
+      </c>
+      <c r="O260" t="n">
+        <v>16</v>
+      </c>
+      <c r="P260" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>8</v>
+      </c>
+      <c r="R260" t="n">
+        <v>4</v>
+      </c>
+      <c r="S260" t="n">
+        <v>7</v>
+      </c>
+      <c r="T260" t="n">
+        <v>1</v>
+      </c>
+      <c r="U260" t="n">
+        <v>1</v>
+      </c>
+      <c r="V260" t="n">
+        <v>2</v>
+      </c>
+      <c r="W260" t="n">
+        <v>15</v>
+      </c>
+      <c r="X260" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD260" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE260" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF260" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG260" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH260" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK260" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="AL260" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AM260" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN260" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP260" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ260" t="inlineStr"/>
+      <c r="AR260" t="inlineStr"/>
+      <c r="AS260" t="n">
+        <v>326</v>
+      </c>
+      <c r="AT260" t="n">
+        <v>510</v>
+      </c>
+      <c r="AU260" t="inlineStr"/>
+      <c r="AV260" t="inlineStr"/>
+      <c r="AW260" t="inlineStr"/>
+      <c r="AX260" t="inlineStr"/>
+      <c r="AY260" t="n">
+        <v>258</v>
+      </c>
+      <c r="AZ260" t="n">
+        <v>440</v>
+      </c>
+      <c r="BA260" t="inlineStr"/>
+      <c r="BB260" t="inlineStr"/>
+      <c r="BC260" t="inlineStr"/>
+      <c r="BD260" t="inlineStr"/>
+      <c r="BE260" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF260" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG260" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH260" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI260" t="inlineStr"/>
+      <c r="BJ260" t="inlineStr"/>
+      <c r="BK260" t="inlineStr"/>
+      <c r="BL260" t="inlineStr"/>
+      <c r="BM260" t="inlineStr"/>
+      <c r="BN260" t="inlineStr"/>
+      <c r="BO260" t="inlineStr"/>
+      <c r="BP260" t="inlineStr"/>
+      <c r="BQ260" t="inlineStr"/>
+      <c r="BR260" t="inlineStr"/>
+      <c r="BS260" t="inlineStr"/>
+      <c r="BT260" t="inlineStr"/>
+      <c r="BU260" t="inlineStr"/>
+      <c r="BV260" t="inlineStr"/>
+      <c r="BW260" t="inlineStr"/>
+      <c r="BX260" t="inlineStr"/>
+      <c r="BY260" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="BZ260" t="n">
+        <v>180.8</v>
+      </c>
+      <c r="CA260" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="CB260" t="inlineStr"/>
+      <c r="CC260" t="n">
+        <v>1503750</v>
+      </c>
+      <c r="CD260" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="CE260" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF260" t="inlineStr"/>
+      <c r="CG260" t="inlineStr"/>
+      <c r="CH260" t="inlineStr"/>
+      <c r="CI260" t="inlineStr"/>
+      <c r="CJ260" t="inlineStr"/>
+      <c r="CK260" t="inlineStr"/>
+      <c r="CL260" t="inlineStr"/>
+      <c r="CM260" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="CN260" t="n">
+        <v>184.75</v>
+      </c>
+      <c r="CO260" t="n">
+        <v>4</v>
+      </c>
+      <c r="CP260" t="n">
+        <v>258</v>
+      </c>
+      <c r="CQ260" t="inlineStr"/>
+      <c r="CR260" t="n">
+        <v>5850000</v>
+      </c>
+      <c r="CS260" t="n">
+        <v>294</v>
+      </c>
+      <c r="CT260" t="n">
+        <v>4</v>
+      </c>
+      <c r="CU260" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV260" t="n">
+        <v>189</v>
+      </c>
+      <c r="CW260" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX260" t="n">
+        <v>72</v>
+      </c>
+      <c r="CY260" t="n">
+        <v>14000</v>
+      </c>
+      <c r="CZ260" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="DA260" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB260" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>Y1lKmgdB</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="n">
+        <v>45599.54166666666</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="n">
+        <v>1</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="K261" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="L261" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="M261" t="n">
+        <v>48</v>
+      </c>
+      <c r="N261" t="n">
+        <v>52</v>
+      </c>
+      <c r="O261" t="n">
+        <v>12</v>
+      </c>
+      <c r="P261" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>4</v>
+      </c>
+      <c r="R261" t="n">
+        <v>1</v>
+      </c>
+      <c r="S261" t="n">
+        <v>4</v>
+      </c>
+      <c r="T261" t="n">
+        <v>7</v>
+      </c>
+      <c r="U261" t="n">
+        <v>4</v>
+      </c>
+      <c r="V261" t="n">
+        <v>7</v>
+      </c>
+      <c r="W261" t="n">
+        <v>13</v>
+      </c>
+      <c r="X261" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD261" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF261" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG261" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH261" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ261" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK261" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="AL261" t="inlineStr">
+        <is>
+          <t>EgvyJSJo</t>
+        </is>
+      </c>
+      <c r="AM261" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN261" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP261" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ261" t="inlineStr"/>
+      <c r="AR261" t="inlineStr"/>
+      <c r="AS261" t="n">
+        <v>433</v>
+      </c>
+      <c r="AT261" t="n">
+        <v>462</v>
+      </c>
+      <c r="AU261" t="inlineStr"/>
+      <c r="AV261" t="inlineStr"/>
+      <c r="AW261" t="inlineStr"/>
+      <c r="AX261" t="inlineStr"/>
+      <c r="AY261" t="n">
+        <v>358</v>
+      </c>
+      <c r="AZ261" t="n">
+        <v>383</v>
+      </c>
+      <c r="BA261" t="inlineStr"/>
+      <c r="BB261" t="inlineStr"/>
+      <c r="BC261" t="inlineStr"/>
+      <c r="BD261" t="inlineStr"/>
+      <c r="BE261" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF261" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG261" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH261" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI261" t="inlineStr"/>
+      <c r="BJ261" t="inlineStr"/>
+      <c r="BK261" t="inlineStr"/>
+      <c r="BL261" t="inlineStr"/>
+      <c r="BM261" t="inlineStr"/>
+      <c r="BN261" t="inlineStr"/>
+      <c r="BO261" t="inlineStr"/>
+      <c r="BP261" t="inlineStr"/>
+      <c r="BQ261" t="inlineStr"/>
+      <c r="BR261" t="inlineStr"/>
+      <c r="BS261" t="inlineStr"/>
+      <c r="BT261" t="inlineStr"/>
+      <c r="BU261" t="inlineStr"/>
+      <c r="BV261" t="inlineStr"/>
+      <c r="BW261" t="inlineStr"/>
+      <c r="BX261" t="inlineStr"/>
+      <c r="BY261" t="inlineStr"/>
+      <c r="BZ261" t="inlineStr"/>
+      <c r="CA261" t="inlineStr"/>
+      <c r="CB261" t="inlineStr"/>
+      <c r="CC261" t="inlineStr"/>
+      <c r="CD261" t="inlineStr"/>
+      <c r="CE261" t="inlineStr"/>
+      <c r="CF261" t="inlineStr"/>
+      <c r="CG261" t="inlineStr"/>
+      <c r="CH261" t="inlineStr"/>
+      <c r="CI261" t="inlineStr"/>
+      <c r="CJ261" t="inlineStr"/>
+      <c r="CK261" t="inlineStr"/>
+      <c r="CL261" t="inlineStr"/>
+      <c r="CM261" t="inlineStr"/>
+      <c r="CN261" t="inlineStr"/>
+      <c r="CO261" t="inlineStr"/>
+      <c r="CP261" t="inlineStr"/>
+      <c r="CQ261" t="inlineStr"/>
+      <c r="CR261" t="inlineStr"/>
+      <c r="CS261" t="inlineStr"/>
+      <c r="CT261" t="inlineStr"/>
+      <c r="CU261" t="inlineStr"/>
+      <c r="CV261" t="inlineStr"/>
+      <c r="CW261" t="inlineStr"/>
+      <c r="CX261" t="inlineStr"/>
+      <c r="CY261" t="inlineStr"/>
+      <c r="CZ261" t="inlineStr"/>
+      <c r="DA261" t="inlineStr"/>
+      <c r="DB261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>4Md3iycn</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="n">
+        <v>45599.45833333334</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F262" t="n">
+        <v>23752</v>
+      </c>
+      <c r="G262" t="n">
+        <v>1</v>
+      </c>
+      <c r="H262" t="n">
+        <v>0</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="K262" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L262" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M262" t="n">
+        <v>50</v>
+      </c>
+      <c r="N262" t="n">
+        <v>50</v>
+      </c>
+      <c r="O262" t="n">
+        <v>13</v>
+      </c>
+      <c r="P262" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>6</v>
+      </c>
+      <c r="R262" t="n">
+        <v>2</v>
+      </c>
+      <c r="S262" t="n">
+        <v>5</v>
+      </c>
+      <c r="T262" t="n">
+        <v>4</v>
+      </c>
+      <c r="U262" t="n">
+        <v>2</v>
+      </c>
+      <c r="V262" t="n">
+        <v>7</v>
+      </c>
+      <c r="W262" t="n">
+        <v>15</v>
+      </c>
+      <c r="X262" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB262" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD262" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF262" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG262" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH262" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ262" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK262" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AL262" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AM262" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN262" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP262" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ262" t="inlineStr"/>
+      <c r="AR262" t="inlineStr"/>
+      <c r="AS262" t="n">
+        <v>377</v>
+      </c>
+      <c r="AT262" t="n">
+        <v>377</v>
+      </c>
+      <c r="AU262" t="inlineStr"/>
+      <c r="AV262" t="inlineStr"/>
+      <c r="AW262" t="inlineStr"/>
+      <c r="AX262" t="inlineStr"/>
+      <c r="AY262" t="n">
+        <v>291</v>
+      </c>
+      <c r="AZ262" t="n">
+        <v>297</v>
+      </c>
+      <c r="BA262" t="inlineStr"/>
+      <c r="BB262" t="inlineStr"/>
+      <c r="BC262" t="inlineStr"/>
+      <c r="BD262" t="inlineStr"/>
+      <c r="BE262" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF262" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG262" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH262" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI262" t="inlineStr"/>
+      <c r="BJ262" t="inlineStr"/>
+      <c r="BK262" t="inlineStr"/>
+      <c r="BL262" t="inlineStr"/>
+      <c r="BM262" t="inlineStr"/>
+      <c r="BN262" t="inlineStr"/>
+      <c r="BO262" t="inlineStr"/>
+      <c r="BP262" t="inlineStr"/>
+      <c r="BQ262" t="inlineStr"/>
+      <c r="BR262" t="inlineStr"/>
+      <c r="BS262" t="inlineStr"/>
+      <c r="BT262" t="inlineStr"/>
+      <c r="BU262" t="inlineStr"/>
+      <c r="BV262" t="inlineStr"/>
+      <c r="BW262" t="inlineStr"/>
+      <c r="BX262" t="inlineStr"/>
+      <c r="BY262" t="inlineStr"/>
+      <c r="BZ262" t="inlineStr"/>
+      <c r="CA262" t="inlineStr"/>
+      <c r="CB262" t="inlineStr"/>
+      <c r="CC262" t="inlineStr"/>
+      <c r="CD262" t="inlineStr"/>
+      <c r="CE262" t="inlineStr"/>
+      <c r="CF262" t="inlineStr"/>
+      <c r="CG262" t="inlineStr"/>
+      <c r="CH262" t="inlineStr"/>
+      <c r="CI262" t="inlineStr"/>
+      <c r="CJ262" t="inlineStr"/>
+      <c r="CK262" t="inlineStr"/>
+      <c r="CL262" t="inlineStr"/>
+      <c r="CM262" t="inlineStr"/>
+      <c r="CN262" t="inlineStr"/>
+      <c r="CO262" t="inlineStr"/>
+      <c r="CP262" t="inlineStr"/>
+      <c r="CQ262" t="inlineStr"/>
+      <c r="CR262" t="inlineStr"/>
+      <c r="CS262" t="inlineStr"/>
+      <c r="CT262" t="inlineStr"/>
+      <c r="CU262" t="inlineStr"/>
+      <c r="CV262" t="inlineStr"/>
+      <c r="CW262" t="inlineStr"/>
+      <c r="CX262" t="inlineStr"/>
+      <c r="CY262" t="inlineStr"/>
+      <c r="CZ262" t="inlineStr"/>
+      <c r="DA262" t="inlineStr"/>
+      <c r="DB262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>vuBo4Eth</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="n">
+        <v>45598.70833333334</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F263" t="n">
+        <v>33043</v>
+      </c>
+      <c r="G263" t="n">
+        <v>2</v>
+      </c>
+      <c r="H263" t="n">
+        <v>0</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="K263" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L263" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M263" t="n">
+        <v>35</v>
+      </c>
+      <c r="N263" t="n">
+        <v>65</v>
+      </c>
+      <c r="O263" t="n">
+        <v>13</v>
+      </c>
+      <c r="P263" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>3</v>
+      </c>
+      <c r="R263" t="n">
+        <v>3</v>
+      </c>
+      <c r="S263" t="n">
+        <v>8</v>
+      </c>
+      <c r="T263" t="n">
+        <v>4</v>
+      </c>
+      <c r="U263" t="n">
+        <v>2</v>
+      </c>
+      <c r="V263" t="n">
+        <v>2</v>
+      </c>
+      <c r="W263" t="n">
+        <v>4</v>
+      </c>
+      <c r="X263" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG263" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH263" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK263" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AL263" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AM263" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN263" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP263" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ263" t="inlineStr"/>
+      <c r="AR263" t="inlineStr"/>
+      <c r="AS263" t="n">
+        <v>388</v>
+      </c>
+      <c r="AT263" t="n">
+        <v>729</v>
+      </c>
+      <c r="AU263" t="inlineStr"/>
+      <c r="AV263" t="inlineStr"/>
+      <c r="AW263" t="inlineStr"/>
+      <c r="AX263" t="inlineStr"/>
+      <c r="AY263" t="n">
+        <v>322</v>
+      </c>
+      <c r="AZ263" t="n">
+        <v>670</v>
+      </c>
+      <c r="BA263" t="inlineStr"/>
+      <c r="BB263" t="inlineStr"/>
+      <c r="BC263" t="inlineStr"/>
+      <c r="BD263" t="inlineStr"/>
+      <c r="BE263" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF263" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG263" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH263" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI263" t="inlineStr"/>
+      <c r="BJ263" t="inlineStr"/>
+      <c r="BK263" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="BL263" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="BM263" t="n">
+        <v>68.875</v>
+      </c>
+      <c r="BN263" t="n">
+        <v>4250</v>
+      </c>
+      <c r="BO263" t="n">
+        <v>2175000</v>
+      </c>
+      <c r="BP263" t="n">
+        <v>74.625</v>
+      </c>
+      <c r="BQ263" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR263" t="inlineStr"/>
+      <c r="BS263" t="inlineStr"/>
+      <c r="BT263" t="inlineStr"/>
+      <c r="BU263" t="inlineStr"/>
+      <c r="BV263" t="inlineStr"/>
+      <c r="BW263" t="inlineStr"/>
+      <c r="BX263" t="inlineStr"/>
+      <c r="BY263" t="n">
+        <v>26.3125</v>
+      </c>
+      <c r="BZ263" t="n">
+        <v>182.5625</v>
+      </c>
+      <c r="CA263" t="n">
+        <v>70.3125</v>
+      </c>
+      <c r="CB263" t="n">
+        <v>5750</v>
+      </c>
+      <c r="CC263" t="n">
+        <v>2182812.5</v>
+      </c>
+      <c r="CD263" t="n">
+        <v>73</v>
+      </c>
+      <c r="CE263" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF263" t="inlineStr"/>
+      <c r="CG263" t="inlineStr"/>
+      <c r="CH263" t="inlineStr"/>
+      <c r="CI263" t="inlineStr"/>
+      <c r="CJ263" t="inlineStr"/>
+      <c r="CK263" t="inlineStr"/>
+      <c r="CL263" t="inlineStr"/>
+      <c r="CM263" t="n">
+        <v>29.33333333333333</v>
+      </c>
+      <c r="CN263" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="CO263" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP263" t="n">
+        <v>209</v>
+      </c>
+      <c r="CQ263" t="n">
+        <v>16000</v>
+      </c>
+      <c r="CR263" t="n">
+        <v>4275000</v>
+      </c>
+      <c r="CS263" t="n">
+        <v>210</v>
+      </c>
+      <c r="CT263" t="n">
+        <v>3</v>
+      </c>
+      <c r="CU263" t="inlineStr"/>
+      <c r="CV263" t="inlineStr"/>
+      <c r="CW263" t="inlineStr"/>
+      <c r="CX263" t="inlineStr"/>
+      <c r="CY263" t="inlineStr"/>
+      <c r="CZ263" t="inlineStr"/>
+      <c r="DA263" t="inlineStr"/>
+      <c r="DB263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="n">
+        <v>45598.625</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F264" t="n">
+        <v>14534</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" t="n">
+        <v>1</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="K264" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L264" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M264" t="n">
+        <v>63</v>
+      </c>
+      <c r="N264" t="n">
+        <v>37</v>
+      </c>
+      <c r="O264" t="n">
+        <v>16</v>
+      </c>
+      <c r="P264" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>6</v>
+      </c>
+      <c r="R264" t="n">
+        <v>3</v>
+      </c>
+      <c r="S264" t="n">
+        <v>9</v>
+      </c>
+      <c r="T264" t="n">
+        <v>8</v>
+      </c>
+      <c r="U264" t="n">
+        <v>1</v>
+      </c>
+      <c r="V264" t="n">
+        <v>1</v>
+      </c>
+      <c r="W264" t="n">
+        <v>4</v>
+      </c>
+      <c r="X264" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB264" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD264" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF264" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG264" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH264" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK264" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AL264" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AM264" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN264" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP264" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ264" t="inlineStr"/>
+      <c r="AR264" t="inlineStr"/>
+      <c r="AS264" t="n">
+        <v>593</v>
+      </c>
+      <c r="AT264" t="n">
+        <v>345</v>
+      </c>
+      <c r="AU264" t="inlineStr"/>
+      <c r="AV264" t="inlineStr"/>
+      <c r="AW264" t="inlineStr"/>
+      <c r="AX264" t="inlineStr"/>
+      <c r="AY264" t="n">
+        <v>506</v>
+      </c>
+      <c r="AZ264" t="n">
+        <v>269</v>
+      </c>
+      <c r="BA264" t="inlineStr"/>
+      <c r="BB264" t="inlineStr"/>
+      <c r="BC264" t="inlineStr"/>
+      <c r="BD264" t="inlineStr"/>
+      <c r="BE264" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF264" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG264" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH264" t="n">
+        <v>11</v>
+      </c>
+      <c r="BI264" t="inlineStr"/>
+      <c r="BJ264" t="inlineStr"/>
+      <c r="BK264" t="inlineStr"/>
+      <c r="BL264" t="inlineStr"/>
+      <c r="BM264" t="inlineStr"/>
+      <c r="BN264" t="inlineStr"/>
+      <c r="BO264" t="inlineStr"/>
+      <c r="BP264" t="inlineStr"/>
+      <c r="BQ264" t="inlineStr"/>
+      <c r="BR264" t="inlineStr"/>
+      <c r="BS264" t="inlineStr"/>
+      <c r="BT264" t="inlineStr"/>
+      <c r="BU264" t="inlineStr"/>
+      <c r="BV264" t="inlineStr"/>
+      <c r="BW264" t="inlineStr"/>
+      <c r="BX264" t="inlineStr"/>
+      <c r="BY264" t="inlineStr"/>
+      <c r="BZ264" t="inlineStr"/>
+      <c r="CA264" t="inlineStr"/>
+      <c r="CB264" t="inlineStr"/>
+      <c r="CC264" t="inlineStr"/>
+      <c r="CD264" t="inlineStr"/>
+      <c r="CE264" t="inlineStr"/>
+      <c r="CF264" t="inlineStr"/>
+      <c r="CG264" t="inlineStr"/>
+      <c r="CH264" t="inlineStr"/>
+      <c r="CI264" t="inlineStr"/>
+      <c r="CJ264" t="inlineStr"/>
+      <c r="CK264" t="inlineStr"/>
+      <c r="CL264" t="inlineStr"/>
+      <c r="CM264" t="inlineStr"/>
+      <c r="CN264" t="inlineStr"/>
+      <c r="CO264" t="inlineStr"/>
+      <c r="CP264" t="inlineStr"/>
+      <c r="CQ264" t="inlineStr"/>
+      <c r="CR264" t="inlineStr"/>
+      <c r="CS264" t="inlineStr"/>
+      <c r="CT264" t="inlineStr"/>
+      <c r="CU264" t="inlineStr"/>
+      <c r="CV264" t="inlineStr"/>
+      <c r="CW264" t="inlineStr"/>
+      <c r="CX264" t="inlineStr"/>
+      <c r="CY264" t="inlineStr"/>
+      <c r="CZ264" t="inlineStr"/>
+      <c r="DA264" t="inlineStr"/>
+      <c r="DB264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="n">
+        <v>45598.54166666666</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F265" t="n">
+        <v>47926</v>
+      </c>
+      <c r="G265" t="n">
+        <v>1</v>
+      </c>
+      <c r="H265" t="n">
+        <v>0</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="K265" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L265" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M265" t="n">
+        <v>68</v>
+      </c>
+      <c r="N265" t="n">
+        <v>32</v>
+      </c>
+      <c r="O265" t="n">
+        <v>18</v>
+      </c>
+      <c r="P265" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>8</v>
+      </c>
+      <c r="R265" t="n">
+        <v>2</v>
+      </c>
+      <c r="S265" t="n">
+        <v>5</v>
+      </c>
+      <c r="T265" t="n">
+        <v>6</v>
+      </c>
+      <c r="U265" t="n">
+        <v>5</v>
+      </c>
+      <c r="V265" t="n">
+        <v>5</v>
+      </c>
+      <c r="W265" t="n">
+        <v>20</v>
+      </c>
+      <c r="X265" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF265" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH265" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK265" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AL265" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AM265" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN265" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP265" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS265" t="n">
+        <v>707</v>
+      </c>
+      <c r="AT265" t="n">
+        <v>321</v>
+      </c>
+      <c r="AU265" t="inlineStr"/>
+      <c r="AV265" t="inlineStr"/>
+      <c r="AW265" t="inlineStr"/>
+      <c r="AX265" t="inlineStr"/>
+      <c r="AY265" t="n">
+        <v>627</v>
+      </c>
+      <c r="AZ265" t="n">
+        <v>252</v>
+      </c>
+      <c r="BA265" t="inlineStr"/>
+      <c r="BB265" t="inlineStr"/>
+      <c r="BC265" t="inlineStr"/>
+      <c r="BD265" t="inlineStr"/>
+      <c r="BE265" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF265" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG265" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH265" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI265" t="inlineStr"/>
+      <c r="BJ265" t="inlineStr"/>
+      <c r="BK265" t="inlineStr"/>
+      <c r="BL265" t="inlineStr"/>
+      <c r="BM265" t="inlineStr"/>
+      <c r="BN265" t="inlineStr"/>
+      <c r="BO265" t="inlineStr"/>
+      <c r="BP265" t="inlineStr"/>
+      <c r="BQ265" t="inlineStr"/>
+      <c r="BR265" t="inlineStr"/>
+      <c r="BS265" t="inlineStr"/>
+      <c r="BT265" t="inlineStr"/>
+      <c r="BU265" t="inlineStr"/>
+      <c r="BV265" t="inlineStr"/>
+      <c r="BW265" t="inlineStr"/>
+      <c r="BX265" t="inlineStr"/>
+      <c r="BY265" t="inlineStr"/>
+      <c r="BZ265" t="inlineStr"/>
+      <c r="CA265" t="inlineStr"/>
+      <c r="CB265" t="inlineStr"/>
+      <c r="CC265" t="inlineStr"/>
+      <c r="CD265" t="inlineStr"/>
+      <c r="CE265" t="inlineStr"/>
+      <c r="CF265" t="inlineStr"/>
+      <c r="CG265" t="inlineStr"/>
+      <c r="CH265" t="inlineStr"/>
+      <c r="CI265" t="inlineStr"/>
+      <c r="CJ265" t="inlineStr"/>
+      <c r="CK265" t="inlineStr"/>
+      <c r="CL265" t="inlineStr"/>
+      <c r="CM265" t="inlineStr"/>
+      <c r="CN265" t="inlineStr"/>
+      <c r="CO265" t="inlineStr"/>
+      <c r="CP265" t="inlineStr"/>
+      <c r="CQ265" t="inlineStr"/>
+      <c r="CR265" t="inlineStr"/>
+      <c r="CS265" t="inlineStr"/>
+      <c r="CT265" t="inlineStr"/>
+      <c r="CU265" t="inlineStr"/>
+      <c r="CV265" t="inlineStr"/>
+      <c r="CW265" t="inlineStr"/>
+      <c r="CX265" t="inlineStr"/>
+      <c r="CY265" t="inlineStr"/>
+      <c r="CZ265" t="inlineStr"/>
+      <c r="DA265" t="inlineStr"/>
+      <c r="DB265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="n">
+        <v>45597.70833333334</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F266" t="n">
+        <v>45084</v>
+      </c>
+      <c r="G266" t="n">
+        <v>1</v>
+      </c>
+      <c r="H266" t="n">
+        <v>1</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="K266" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L266" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M266" t="n">
+        <v>47</v>
+      </c>
+      <c r="N266" t="n">
+        <v>53</v>
+      </c>
+      <c r="O266" t="n">
+        <v>14</v>
+      </c>
+      <c r="P266" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>2</v>
+      </c>
+      <c r="R266" t="n">
+        <v>3</v>
+      </c>
+      <c r="S266" t="n">
+        <v>8</v>
+      </c>
+      <c r="T266" t="n">
+        <v>6</v>
+      </c>
+      <c r="U266" t="n">
+        <v>4</v>
+      </c>
+      <c r="V266" t="n">
+        <v>5</v>
+      </c>
+      <c r="W266" t="n">
+        <v>10</v>
+      </c>
+      <c r="X266" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK266" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AL266" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AM266" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN266" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP266" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ266" t="inlineStr"/>
+      <c r="AR266" t="inlineStr"/>
+      <c r="AS266" t="n">
+        <v>400</v>
+      </c>
+      <c r="AT266" t="n">
+        <v>445</v>
+      </c>
+      <c r="AU266" t="inlineStr"/>
+      <c r="AV266" t="inlineStr"/>
+      <c r="AW266" t="inlineStr"/>
+      <c r="AX266" t="inlineStr"/>
+      <c r="AY266" t="n">
+        <v>333</v>
+      </c>
+      <c r="AZ266" t="n">
+        <v>354</v>
+      </c>
+      <c r="BA266" t="inlineStr"/>
+      <c r="BB266" t="inlineStr"/>
+      <c r="BC266" t="inlineStr"/>
+      <c r="BD266" t="inlineStr"/>
+      <c r="BE266" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF266" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG266" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH266" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI266" t="inlineStr"/>
+      <c r="BJ266" t="inlineStr"/>
+      <c r="BK266" t="inlineStr"/>
+      <c r="BL266" t="inlineStr"/>
+      <c r="BM266" t="inlineStr"/>
+      <c r="BN266" t="inlineStr"/>
+      <c r="BO266" t="inlineStr"/>
+      <c r="BP266" t="inlineStr"/>
+      <c r="BQ266" t="inlineStr"/>
+      <c r="BR266" t="inlineStr"/>
+      <c r="BS266" t="inlineStr"/>
+      <c r="BT266" t="inlineStr"/>
+      <c r="BU266" t="inlineStr"/>
+      <c r="BV266" t="inlineStr"/>
+      <c r="BW266" t="inlineStr"/>
+      <c r="BX266" t="inlineStr"/>
+      <c r="BY266" t="inlineStr"/>
+      <c r="BZ266" t="inlineStr"/>
+      <c r="CA266" t="inlineStr"/>
+      <c r="CB266" t="inlineStr"/>
+      <c r="CC266" t="inlineStr"/>
+      <c r="CD266" t="inlineStr"/>
+      <c r="CE266" t="inlineStr"/>
+      <c r="CF266" t="inlineStr"/>
+      <c r="CG266" t="inlineStr"/>
+      <c r="CH266" t="inlineStr"/>
+      <c r="CI266" t="inlineStr"/>
+      <c r="CJ266" t="inlineStr"/>
+      <c r="CK266" t="inlineStr"/>
+      <c r="CL266" t="inlineStr"/>
+      <c r="CM266" t="n">
+        <v>28</v>
+      </c>
+      <c r="CN266" t="n">
+        <v>187</v>
+      </c>
+      <c r="CO266" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP266" t="n">
+        <v>75</v>
+      </c>
+      <c r="CQ266" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CR266" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="CS266" t="n">
+        <v>76</v>
+      </c>
+      <c r="CT266" t="n">
+        <v>2</v>
+      </c>
+      <c r="CU266" t="inlineStr"/>
+      <c r="CV266" t="inlineStr"/>
+      <c r="CW266" t="inlineStr"/>
+      <c r="CX266" t="inlineStr"/>
+      <c r="CY266" t="inlineStr"/>
+      <c r="CZ266" t="inlineStr"/>
+      <c r="DA266" t="inlineStr"/>
+      <c r="DB266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="n">
+        <v>45597.625</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F267" t="n">
+        <v>10540</v>
+      </c>
+      <c r="G267" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" t="n">
+        <v>1</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="K267" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L267" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M267" t="n">
+        <v>64</v>
+      </c>
+      <c r="N267" t="n">
+        <v>36</v>
+      </c>
+      <c r="O267" t="n">
+        <v>11</v>
+      </c>
+      <c r="P267" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>3</v>
+      </c>
+      <c r="R267" t="n">
+        <v>3</v>
+      </c>
+      <c r="S267" t="n">
+        <v>4</v>
+      </c>
+      <c r="T267" t="n">
+        <v>3</v>
+      </c>
+      <c r="U267" t="n">
+        <v>4</v>
+      </c>
+      <c r="V267" t="n">
+        <v>4</v>
+      </c>
+      <c r="W267" t="n">
+        <v>12</v>
+      </c>
+      <c r="X267" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH267" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK267" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AL267" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AM267" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN267" t="n">
+        <v>551</v>
+      </c>
+      <c r="AO267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP267" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ267" t="inlineStr"/>
+      <c r="AR267" t="inlineStr"/>
+      <c r="AS267" t="n">
+        <v>563</v>
+      </c>
+      <c r="AT267" t="n">
+        <v>309</v>
+      </c>
+      <c r="AU267" t="inlineStr"/>
+      <c r="AV267" t="inlineStr"/>
+      <c r="AW267" t="inlineStr"/>
+      <c r="AX267" t="inlineStr"/>
+      <c r="AY267" t="n">
+        <v>474</v>
+      </c>
+      <c r="AZ267" t="n">
+        <v>236</v>
+      </c>
+      <c r="BA267" t="inlineStr"/>
+      <c r="BB267" t="inlineStr"/>
+      <c r="BC267" t="inlineStr"/>
+      <c r="BD267" t="inlineStr"/>
+      <c r="BE267" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF267" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG267" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH267" t="n">
+        <v>17</v>
+      </c>
+      <c r="BI267" t="inlineStr"/>
+      <c r="BJ267" t="inlineStr"/>
+      <c r="BK267" t="inlineStr"/>
+      <c r="BL267" t="inlineStr"/>
+      <c r="BM267" t="inlineStr"/>
+      <c r="BN267" t="inlineStr"/>
+      <c r="BO267" t="inlineStr"/>
+      <c r="BP267" t="inlineStr"/>
+      <c r="BQ267" t="inlineStr"/>
+      <c r="BR267" t="inlineStr"/>
+      <c r="BS267" t="inlineStr"/>
+      <c r="BT267" t="inlineStr"/>
+      <c r="BU267" t="inlineStr"/>
+      <c r="BV267" t="inlineStr"/>
+      <c r="BW267" t="inlineStr"/>
+      <c r="BX267" t="inlineStr"/>
+      <c r="BY267" t="inlineStr"/>
+      <c r="BZ267" t="inlineStr"/>
+      <c r="CA267" t="inlineStr"/>
+      <c r="CB267" t="inlineStr"/>
+      <c r="CC267" t="inlineStr"/>
+      <c r="CD267" t="inlineStr"/>
+      <c r="CE267" t="inlineStr"/>
+      <c r="CF267" t="n">
+        <v>25.26666666666667</v>
+      </c>
+      <c r="CG267" t="n">
+        <v>178.9333333333333</v>
+      </c>
+      <c r="CH267" t="n">
+        <v>64.86666666666666</v>
+      </c>
+      <c r="CI267" t="inlineStr"/>
+      <c r="CJ267" t="n">
+        <v>895000</v>
+      </c>
+      <c r="CK267" t="n">
+        <v>71.13333333333334</v>
+      </c>
+      <c r="CL267" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM267" t="inlineStr"/>
+      <c r="CN267" t="inlineStr"/>
+      <c r="CO267" t="inlineStr"/>
+      <c r="CP267" t="inlineStr"/>
+      <c r="CQ267" t="inlineStr"/>
+      <c r="CR267" t="inlineStr"/>
+      <c r="CS267" t="inlineStr"/>
+      <c r="CT267" t="inlineStr"/>
+      <c r="CU267" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="CV267" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="CW267" t="n">
+        <v>5</v>
+      </c>
+      <c r="CX267" t="n">
+        <v>330</v>
+      </c>
+      <c r="CY267" t="inlineStr"/>
+      <c r="CZ267" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="DA267" t="n">
+        <v>359</v>
+      </c>
+      <c r="DB267" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>W6sFgYy8</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="n">
+        <v>45598.66666666666</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kubler g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de roudourou
+  guingamp </t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>19060</v>
+      </c>
+      <c r="F268" t="n">
+        <v>6733</v>
+      </c>
+      <c r="G268" t="n">
+        <v>3</v>
+      </c>
+      <c r="H268" t="n">
+        <v>0</v>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="n">
+        <v>49</v>
+      </c>
+      <c r="N268" t="n">
+        <v>51</v>
+      </c>
+      <c r="O268" t="n">
+        <v>18</v>
+      </c>
+      <c r="P268" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>8</v>
+      </c>
+      <c r="R268" t="n">
+        <v>5</v>
+      </c>
+      <c r="S268" t="n">
+        <v>6</v>
+      </c>
+      <c r="T268" t="n">
+        <v>8</v>
+      </c>
+      <c r="U268" t="n">
+        <v>4</v>
+      </c>
+      <c r="V268" t="n">
+        <v>3</v>
+      </c>
+      <c r="W268" t="inlineStr"/>
+      <c r="X268" t="inlineStr"/>
+      <c r="Y268" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC268" t="inlineStr"/>
+      <c r="AD268" t="inlineStr"/>
+      <c r="AE268" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF268" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG268" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH268" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI268" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK268" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="AL268" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AM268" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN268" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP268" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ268" t="inlineStr"/>
+      <c r="AR268" t="inlineStr"/>
+      <c r="AS268" t="n">
+        <v>477</v>
+      </c>
+      <c r="AT268" t="n">
+        <v>485</v>
+      </c>
+      <c r="AU268" t="inlineStr"/>
+      <c r="AV268" t="inlineStr"/>
+      <c r="AW268" t="inlineStr"/>
+      <c r="AX268" t="inlineStr"/>
+      <c r="AY268" t="n">
+        <v>399</v>
+      </c>
+      <c r="AZ268" t="n">
+        <v>415</v>
+      </c>
+      <c r="BA268" t="inlineStr"/>
+      <c r="BB268" t="inlineStr"/>
+      <c r="BC268" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD268" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE268" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF268" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG268" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH268" t="n">
+        <v>13</v>
+      </c>
+      <c r="BI268" t="inlineStr"/>
+      <c r="BJ268" t="inlineStr"/>
+      <c r="BK268" t="n">
+        <v>25</v>
+      </c>
+      <c r="BL268" t="n">
+        <v>180</v>
+      </c>
+      <c r="BM268" t="n">
+        <v>65.77777777777777</v>
+      </c>
+      <c r="BN268" t="n">
+        <v>2111.111111111111</v>
+      </c>
+      <c r="BO268" t="n">
+        <v>1058333.333333333</v>
+      </c>
+      <c r="BP268" t="n">
+        <v>69.77777777777777</v>
+      </c>
+      <c r="BQ268" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR268" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BS268" t="n">
+        <v>184.75</v>
+      </c>
+      <c r="BT268" t="n">
+        <v>66.125</v>
+      </c>
+      <c r="BU268" t="inlineStr"/>
+      <c r="BV268" t="n">
+        <v>1296875</v>
+      </c>
+      <c r="BW268" t="n">
+        <v>69.375</v>
+      </c>
+      <c r="BX268" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY268" t="n">
+        <v>24.23076923076923</v>
+      </c>
+      <c r="BZ268" t="n">
+        <v>179.5384615384615</v>
+      </c>
+      <c r="CA268" t="n">
+        <v>63.53846153846154</v>
+      </c>
+      <c r="CB268" t="n">
+        <v>1538.461538461539</v>
+      </c>
+      <c r="CC268" t="n">
+        <v>815384.6153846154</v>
+      </c>
+      <c r="CD268" t="n">
+        <v>68.76923076923077</v>
+      </c>
+      <c r="CE268" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF268" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="CG268" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="CH268" t="n">
+        <v>64.72222222222223</v>
+      </c>
+      <c r="CI268" t="inlineStr"/>
+      <c r="CJ268" t="n">
+        <v>1481944.444444444</v>
+      </c>
+      <c r="CK268" t="n">
+        <v>71.88888888888889</v>
+      </c>
+      <c r="CL268" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM268" t="n">
+        <v>26</v>
+      </c>
+      <c r="CN268" t="n">
+        <v>186.6666666666667</v>
+      </c>
+      <c r="CO268" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP268" t="n">
+        <v>189</v>
+      </c>
+      <c r="CQ268" t="inlineStr"/>
+      <c r="CR268" t="n">
+        <v>2075000</v>
+      </c>
+      <c r="CS268" t="n">
+        <v>204</v>
+      </c>
+      <c r="CT268" t="n">
+        <v>3</v>
+      </c>
+      <c r="CU268" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="CV268" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="CW268" t="n">
+        <v>2</v>
+      </c>
+      <c r="CX268" t="n">
+        <v>139</v>
+      </c>
+      <c r="CY268" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CZ268" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="DA268" t="n">
+        <v>139</v>
+      </c>
+      <c r="DB268" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>2RkbcGxq</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="n">
+        <v>45598.41666666666</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taleb a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade michel d ornano
+  caen </t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>20300</v>
+      </c>
+      <c r="F269" t="n">
+        <v>15441</v>
+      </c>
+      <c r="G269" t="n">
+        <v>2</v>
+      </c>
+      <c r="H269" t="n">
+        <v>0</v>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="n">
+        <v>44</v>
+      </c>
+      <c r="N269" t="n">
+        <v>56</v>
+      </c>
+      <c r="O269" t="n">
+        <v>3</v>
+      </c>
+      <c r="P269" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>2</v>
+      </c>
+      <c r="R269" t="n">
+        <v>1</v>
+      </c>
+      <c r="S269" t="n">
+        <v>0</v>
+      </c>
+      <c r="T269" t="n">
+        <v>9</v>
+      </c>
+      <c r="U269" t="n">
+        <v>1</v>
+      </c>
+      <c r="V269" t="n">
+        <v>7</v>
+      </c>
+      <c r="W269" t="inlineStr"/>
+      <c r="X269" t="inlineStr"/>
+      <c r="Y269" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC269" t="inlineStr"/>
+      <c r="AD269" t="inlineStr"/>
+      <c r="AE269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH269" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK269" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AL269" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AM269" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN269" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP269" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ269" t="inlineStr"/>
+      <c r="AR269" t="inlineStr"/>
+      <c r="AS269" t="n">
+        <v>430</v>
+      </c>
+      <c r="AT269" t="n">
+        <v>500</v>
+      </c>
+      <c r="AU269" t="inlineStr"/>
+      <c r="AV269" t="inlineStr"/>
+      <c r="AW269" t="inlineStr"/>
+      <c r="AX269" t="inlineStr"/>
+      <c r="AY269" t="n">
+        <v>330</v>
+      </c>
+      <c r="AZ269" t="n">
+        <v>397</v>
+      </c>
+      <c r="BA269" t="inlineStr"/>
+      <c r="BB269" t="inlineStr"/>
+      <c r="BC269" t="n">
+        <v>54</v>
+      </c>
+      <c r="BD269" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE269" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF269" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG269" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH269" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI269" t="inlineStr"/>
+      <c r="BJ269" t="inlineStr"/>
+      <c r="BK269" t="inlineStr"/>
+      <c r="BL269" t="inlineStr"/>
+      <c r="BM269" t="inlineStr"/>
+      <c r="BN269" t="inlineStr"/>
+      <c r="BO269" t="inlineStr"/>
+      <c r="BP269" t="inlineStr"/>
+      <c r="BQ269" t="inlineStr"/>
+      <c r="BR269" t="inlineStr"/>
+      <c r="BS269" t="inlineStr"/>
+      <c r="BT269" t="inlineStr"/>
+      <c r="BU269" t="inlineStr"/>
+      <c r="BV269" t="inlineStr"/>
+      <c r="BW269" t="inlineStr"/>
+      <c r="BX269" t="inlineStr"/>
+      <c r="BY269" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BZ269" t="n">
+        <v>180.9</v>
+      </c>
+      <c r="CA269" t="n">
+        <v>66.15000000000001</v>
+      </c>
+      <c r="CB269" t="inlineStr"/>
+      <c r="CC269" t="n">
+        <v>1376250</v>
+      </c>
+      <c r="CD269" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="CE269" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF269" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="CG269" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="CH269" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="CI269" t="inlineStr"/>
+      <c r="CJ269" t="n">
+        <v>823333.3333333334</v>
+      </c>
+      <c r="CK269" t="n">
+        <v>67.26666666666667</v>
+      </c>
+      <c r="CL269" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM269" t="inlineStr"/>
+      <c r="CN269" t="inlineStr"/>
+      <c r="CO269" t="inlineStr"/>
+      <c r="CP269" t="inlineStr"/>
+      <c r="CQ269" t="inlineStr"/>
+      <c r="CR269" t="inlineStr"/>
+      <c r="CS269" t="inlineStr"/>
+      <c r="CT269" t="inlineStr"/>
+      <c r="CU269" t="inlineStr"/>
+      <c r="CV269" t="inlineStr"/>
+      <c r="CW269" t="inlineStr"/>
+      <c r="CX269" t="inlineStr"/>
+      <c r="CY269" t="inlineStr"/>
+      <c r="CZ269" t="inlineStr"/>
+      <c r="DA269" t="inlineStr"/>
+      <c r="DB269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>lrCa1peE</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="n">
+        <v>45597.66666666666</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des sports
+  annecy </t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>15660</v>
+      </c>
+      <c r="F270" t="n">
+        <v>5333</v>
+      </c>
+      <c r="G270" t="n">
+        <v>2</v>
+      </c>
+      <c r="H270" t="n">
+        <v>0</v>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="n">
+        <v>33</v>
+      </c>
+      <c r="N270" t="n">
+        <v>67</v>
+      </c>
+      <c r="O270" t="n">
+        <v>8</v>
+      </c>
+      <c r="P270" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>5</v>
+      </c>
+      <c r="R270" t="n">
+        <v>2</v>
+      </c>
+      <c r="S270" t="n">
+        <v>0</v>
+      </c>
+      <c r="T270" t="n">
+        <v>5</v>
+      </c>
+      <c r="U270" t="n">
+        <v>3</v>
+      </c>
+      <c r="V270" t="n">
+        <v>2</v>
+      </c>
+      <c r="W270" t="inlineStr"/>
+      <c r="X270" t="inlineStr"/>
+      <c r="Y270" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB270" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC270" t="inlineStr"/>
+      <c r="AD270" t="inlineStr"/>
+      <c r="AE270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF270" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG270" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH270" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI270" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ270" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK270" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="AL270" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AM270" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN270" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP270" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS270" t="n">
+        <v>228</v>
+      </c>
+      <c r="AT270" t="n">
+        <v>457</v>
+      </c>
+      <c r="AU270" t="inlineStr"/>
+      <c r="AV270" t="inlineStr"/>
+      <c r="AW270" t="inlineStr"/>
+      <c r="AX270" t="inlineStr"/>
+      <c r="AY270" t="n">
+        <v>127</v>
+      </c>
+      <c r="AZ270" t="n">
+        <v>336</v>
+      </c>
+      <c r="BA270" t="inlineStr"/>
+      <c r="BB270" t="inlineStr"/>
+      <c r="BC270" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD270" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE270" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF270" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG270" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH270" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI270" t="inlineStr"/>
+      <c r="BJ270" t="inlineStr"/>
+      <c r="BK270" t="inlineStr"/>
+      <c r="BL270" t="inlineStr"/>
+      <c r="BM270" t="inlineStr"/>
+      <c r="BN270" t="inlineStr"/>
+      <c r="BO270" t="inlineStr"/>
+      <c r="BP270" t="inlineStr"/>
+      <c r="BQ270" t="inlineStr"/>
+      <c r="BR270" t="n">
+        <v>26.11111111111111</v>
+      </c>
+      <c r="BS270" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="BT270" t="n">
+        <v>66</v>
+      </c>
+      <c r="BU270" t="inlineStr"/>
+      <c r="BV270" t="n">
+        <v>1011111.111111111</v>
+      </c>
+      <c r="BW270" t="n">
+        <v>69.88888888888889</v>
+      </c>
+      <c r="BX270" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY270" t="n">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="BZ270" t="n">
+        <v>180</v>
+      </c>
+      <c r="CA270" t="n">
+        <v>61.30769230769231</v>
+      </c>
+      <c r="CB270" t="inlineStr"/>
+      <c r="CC270" t="n">
+        <v>555769.2307692308</v>
+      </c>
+      <c r="CD270" t="n">
+        <v>67.23076923076923</v>
+      </c>
+      <c r="CE270" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF270" t="n">
+        <v>23.91666666666667</v>
+      </c>
+      <c r="CG270" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="CH270" t="n">
+        <v>64.58333333333333</v>
+      </c>
+      <c r="CI270" t="inlineStr"/>
+      <c r="CJ270" t="n">
+        <v>958333.3333333334</v>
+      </c>
+      <c r="CK270" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="CL270" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM270" t="inlineStr"/>
+      <c r="CN270" t="inlineStr"/>
+      <c r="CO270" t="inlineStr"/>
+      <c r="CP270" t="inlineStr"/>
+      <c r="CQ270" t="inlineStr"/>
+      <c r="CR270" t="inlineStr"/>
+      <c r="CS270" t="inlineStr"/>
+      <c r="CT270" t="inlineStr"/>
+      <c r="CU270" t="n">
+        <v>29</v>
+      </c>
+      <c r="CV270" t="n">
+        <v>170</v>
+      </c>
+      <c r="CW270" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX270" t="n">
+        <v>66</v>
+      </c>
+      <c r="CY270" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CZ270" t="n">
+        <v>750000</v>
+      </c>
+      <c r="DA270" t="n">
+        <v>66</v>
+      </c>
+      <c r="DB270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>hh4S2xFL</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="n">
+        <v>45597.66666666666</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lesage m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade gabriel montpied
+  clermont ferrand </t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F271" t="n">
+        <v>5423</v>
+      </c>
+      <c r="G271" t="n">
+        <v>2</v>
+      </c>
+      <c r="H271" t="n">
+        <v>1</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="n">
+        <v>44</v>
+      </c>
+      <c r="N271" t="n">
+        <v>56</v>
+      </c>
+      <c r="O271" t="n">
+        <v>12</v>
+      </c>
+      <c r="P271" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>4</v>
+      </c>
+      <c r="R271" t="n">
+        <v>2</v>
+      </c>
+      <c r="S271" t="n">
+        <v>4</v>
+      </c>
+      <c r="T271" t="n">
+        <v>4</v>
+      </c>
+      <c r="U271" t="n">
+        <v>4</v>
+      </c>
+      <c r="V271" t="n">
+        <v>3</v>
+      </c>
+      <c r="W271" t="inlineStr"/>
+      <c r="X271" t="inlineStr"/>
+      <c r="Y271" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC271" t="inlineStr"/>
+      <c r="AD271" t="inlineStr"/>
+      <c r="AE271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF271" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG271" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH271" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK271" t="inlineStr">
+        <is>
+          <t>YLrocixH</t>
+        </is>
+      </c>
+      <c r="AL271" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="AM271" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN271" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP271" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ271" t="inlineStr"/>
+      <c r="AR271" t="inlineStr"/>
+      <c r="AS271" t="n">
+        <v>453</v>
+      </c>
+      <c r="AT271" t="n">
+        <v>569</v>
+      </c>
+      <c r="AU271" t="inlineStr"/>
+      <c r="AV271" t="inlineStr"/>
+      <c r="AW271" t="inlineStr"/>
+      <c r="AX271" t="inlineStr"/>
+      <c r="AY271" t="n">
+        <v>361</v>
+      </c>
+      <c r="AZ271" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA271" t="inlineStr"/>
+      <c r="BB271" t="inlineStr"/>
+      <c r="BC271" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD271" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE271" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF271" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG271" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH271" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI271" t="inlineStr"/>
+      <c r="BJ271" t="inlineStr"/>
+      <c r="BK271" t="inlineStr"/>
+      <c r="BL271" t="inlineStr"/>
+      <c r="BM271" t="inlineStr"/>
+      <c r="BN271" t="inlineStr"/>
+      <c r="BO271" t="inlineStr"/>
+      <c r="BP271" t="inlineStr"/>
+      <c r="BQ271" t="inlineStr"/>
+      <c r="BR271" t="inlineStr"/>
+      <c r="BS271" t="inlineStr"/>
+      <c r="BT271" t="inlineStr"/>
+      <c r="BU271" t="inlineStr"/>
+      <c r="BV271" t="inlineStr"/>
+      <c r="BW271" t="inlineStr"/>
+      <c r="BX271" t="inlineStr"/>
+      <c r="BY271" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="BZ271" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="CA271" t="n">
+        <v>62</v>
+      </c>
+      <c r="CB271" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CC271" t="n">
+        <v>755000</v>
+      </c>
+      <c r="CD271" t="n">
+        <v>67</v>
+      </c>
+      <c r="CE271" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF271" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="CG271" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="CH271" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="CI271" t="n">
+        <v>5400</v>
+      </c>
+      <c r="CJ271" t="n">
+        <v>1585000</v>
+      </c>
+      <c r="CK271" t="n">
+        <v>76</v>
+      </c>
+      <c r="CL271" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM271" t="inlineStr"/>
+      <c r="CN271" t="inlineStr"/>
+      <c r="CO271" t="inlineStr"/>
+      <c r="CP271" t="inlineStr"/>
+      <c r="CQ271" t="inlineStr"/>
+      <c r="CR271" t="inlineStr"/>
+      <c r="CS271" t="inlineStr"/>
+      <c r="CT271" t="inlineStr"/>
+      <c r="CU271" t="n">
+        <v>24</v>
+      </c>
+      <c r="CV271" t="n">
+        <v>173</v>
+      </c>
+      <c r="CW271" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX271" t="n">
+        <v>71</v>
+      </c>
+      <c r="CY271" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CZ271" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="DA271" t="n">
+        <v>74</v>
+      </c>
+      <c r="DB271" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>tjU6aOPQ</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="n">
+        <v>45597.66666666666</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thual o 
+  fra </t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade marcel tribut
+  dunkerque </t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>4933</v>
+      </c>
+      <c r="F272" t="n">
+        <v>4933</v>
+      </c>
+      <c r="G272" t="n">
+        <v>3</v>
+      </c>
+      <c r="H272" t="n">
+        <v>1</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>52</v>
+      </c>
+      <c r="N272" t="n">
+        <v>48</v>
+      </c>
+      <c r="O272" t="n">
+        <v>15</v>
+      </c>
+      <c r="P272" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>8</v>
+      </c>
+      <c r="R272" t="n">
+        <v>6</v>
+      </c>
+      <c r="S272" t="n">
+        <v>1</v>
+      </c>
+      <c r="T272" t="n">
+        <v>4</v>
+      </c>
+      <c r="U272" t="n">
+        <v>6</v>
+      </c>
+      <c r="V272" t="n">
+        <v>2</v>
+      </c>
+      <c r="W272" t="inlineStr"/>
+      <c r="X272" t="inlineStr"/>
+      <c r="Y272" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC272" t="inlineStr"/>
+      <c r="AD272" t="inlineStr"/>
+      <c r="AE272" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF272" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG272" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH272" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI272" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK272" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AL272" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AM272" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN272" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP272" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ272" t="inlineStr"/>
+      <c r="AR272" t="inlineStr"/>
+      <c r="AS272" t="n">
+        <v>475</v>
+      </c>
+      <c r="AT272" t="n">
+        <v>458</v>
+      </c>
+      <c r="AU272" t="inlineStr"/>
+      <c r="AV272" t="inlineStr"/>
+      <c r="AW272" t="inlineStr"/>
+      <c r="AX272" t="inlineStr"/>
+      <c r="AY272" t="n">
+        <v>394</v>
+      </c>
+      <c r="AZ272" t="n">
+        <v>381</v>
+      </c>
+      <c r="BA272" t="inlineStr"/>
+      <c r="BB272" t="inlineStr"/>
+      <c r="BC272" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD272" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE272" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF272" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG272" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH272" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI272" t="inlineStr"/>
+      <c r="BJ272" t="inlineStr"/>
+      <c r="BK272" t="inlineStr"/>
+      <c r="BL272" t="inlineStr"/>
+      <c r="BM272" t="inlineStr"/>
+      <c r="BN272" t="inlineStr"/>
+      <c r="BO272" t="inlineStr"/>
+      <c r="BP272" t="inlineStr"/>
+      <c r="BQ272" t="inlineStr"/>
+      <c r="BR272" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="BS272" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="BT272" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="BU272" t="n">
+        <v>3300</v>
+      </c>
+      <c r="BV272" t="n">
+        <v>1295000</v>
+      </c>
+      <c r="BW272" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="BX272" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY272" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BZ272" t="n">
+        <v>176.9</v>
+      </c>
+      <c r="CA272" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="CB272" t="inlineStr"/>
+      <c r="CC272" t="n">
+        <v>847500</v>
+      </c>
+      <c r="CD272" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="CE272" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF272" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="CG272" t="n">
+        <v>176.9166666666667</v>
+      </c>
+      <c r="CH272" t="n">
+        <v>61.83333333333334</v>
+      </c>
+      <c r="CI272" t="inlineStr"/>
+      <c r="CJ272" t="n">
+        <v>795833.3333333334</v>
+      </c>
+      <c r="CK272" t="n">
+        <v>70.91666666666667</v>
+      </c>
+      <c r="CL272" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM272" t="inlineStr"/>
+      <c r="CN272" t="inlineStr"/>
+      <c r="CO272" t="inlineStr"/>
+      <c r="CP272" t="inlineStr"/>
+      <c r="CQ272" t="inlineStr"/>
+      <c r="CR272" t="inlineStr"/>
+      <c r="CS272" t="inlineStr"/>
+      <c r="CT272" t="inlineStr"/>
+      <c r="CU272" t="inlineStr"/>
+      <c r="CV272" t="inlineStr"/>
+      <c r="CW272" t="inlineStr"/>
+      <c r="CX272" t="inlineStr"/>
+      <c r="CY272" t="inlineStr"/>
+      <c r="CZ272" t="inlineStr"/>
+      <c r="DA272" t="inlineStr"/>
+      <c r="DB272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>QN5wf2ml</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="n">
+        <v>45597.66666666666</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petit a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis turcan
+  martigues </t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>11500</v>
+      </c>
+      <c r="F273" t="n">
+        <v>532</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" t="n">
+        <v>1</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>32</v>
+      </c>
+      <c r="N273" t="n">
+        <v>68</v>
+      </c>
+      <c r="O273" t="n">
+        <v>7</v>
+      </c>
+      <c r="P273" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>0</v>
+      </c>
+      <c r="R273" t="n">
+        <v>6</v>
+      </c>
+      <c r="S273" t="n">
+        <v>4</v>
+      </c>
+      <c r="T273" t="n">
+        <v>10</v>
+      </c>
+      <c r="U273" t="n">
+        <v>3</v>
+      </c>
+      <c r="V273" t="n">
+        <v>2</v>
+      </c>
+      <c r="W273" t="inlineStr"/>
+      <c r="X273" t="inlineStr"/>
+      <c r="Y273" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC273" t="inlineStr"/>
+      <c r="AD273" t="inlineStr"/>
+      <c r="AE273" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG273" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH273" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI273" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AL273" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AM273" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN273" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP273" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS273" t="n">
+        <v>305</v>
+      </c>
+      <c r="AT273" t="n">
+        <v>600</v>
+      </c>
+      <c r="AU273" t="inlineStr"/>
+      <c r="AV273" t="inlineStr"/>
+      <c r="AW273" t="inlineStr"/>
+      <c r="AX273" t="inlineStr"/>
+      <c r="AY273" t="n">
+        <v>220</v>
+      </c>
+      <c r="AZ273" t="n">
+        <v>524</v>
+      </c>
+      <c r="BA273" t="inlineStr"/>
+      <c r="BB273" t="inlineStr"/>
+      <c r="BC273" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD273" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE273" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF273" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG273" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH273" t="n">
+        <v>17</v>
+      </c>
+      <c r="BI273" t="inlineStr"/>
+      <c r="BJ273" t="inlineStr"/>
+      <c r="BK273" t="inlineStr"/>
+      <c r="BL273" t="inlineStr"/>
+      <c r="BM273" t="inlineStr"/>
+      <c r="BN273" t="inlineStr"/>
+      <c r="BO273" t="inlineStr"/>
+      <c r="BP273" t="inlineStr"/>
+      <c r="BQ273" t="inlineStr"/>
+      <c r="BR273" t="inlineStr"/>
+      <c r="BS273" t="inlineStr"/>
+      <c r="BT273" t="inlineStr"/>
+      <c r="BU273" t="inlineStr"/>
+      <c r="BV273" t="inlineStr"/>
+      <c r="BW273" t="inlineStr"/>
+      <c r="BX273" t="inlineStr"/>
+      <c r="BY273" t="inlineStr"/>
+      <c r="BZ273" t="inlineStr"/>
+      <c r="CA273" t="inlineStr"/>
+      <c r="CB273" t="inlineStr"/>
+      <c r="CC273" t="inlineStr"/>
+      <c r="CD273" t="inlineStr"/>
+      <c r="CE273" t="inlineStr"/>
+      <c r="CF273" t="inlineStr"/>
+      <c r="CG273" t="inlineStr"/>
+      <c r="CH273" t="inlineStr"/>
+      <c r="CI273" t="inlineStr"/>
+      <c r="CJ273" t="inlineStr"/>
+      <c r="CK273" t="inlineStr"/>
+      <c r="CL273" t="inlineStr"/>
+      <c r="CM273" t="inlineStr"/>
+      <c r="CN273" t="inlineStr"/>
+      <c r="CO273" t="inlineStr"/>
+      <c r="CP273" t="inlineStr"/>
+      <c r="CQ273" t="inlineStr"/>
+      <c r="CR273" t="inlineStr"/>
+      <c r="CS273" t="inlineStr"/>
+      <c r="CT273" t="inlineStr"/>
+      <c r="CU273" t="inlineStr"/>
+      <c r="CV273" t="inlineStr"/>
+      <c r="CW273" t="inlineStr"/>
+      <c r="CX273" t="inlineStr"/>
+      <c r="CY273" t="inlineStr"/>
+      <c r="CZ273" t="inlineStr"/>
+      <c r="DA273" t="inlineStr"/>
+      <c r="DB273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>bgq7ef7e</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="n">
+        <v>45597.66666666666</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">benchabane f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade charlety
+  paris </t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F274" t="n">
+        <v>12377</v>
+      </c>
+      <c r="G274" t="n">
+        <v>3</v>
+      </c>
+      <c r="H274" t="n">
+        <v>3</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>76</v>
+      </c>
+      <c r="N274" t="n">
+        <v>24</v>
+      </c>
+      <c r="O274" t="n">
+        <v>13</v>
+      </c>
+      <c r="P274" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>7</v>
+      </c>
+      <c r="R274" t="n">
+        <v>6</v>
+      </c>
+      <c r="S274" t="n">
+        <v>4</v>
+      </c>
+      <c r="T274" t="n">
+        <v>4</v>
+      </c>
+      <c r="U274" t="n">
+        <v>2</v>
+      </c>
+      <c r="V274" t="n">
+        <v>2</v>
+      </c>
+      <c r="W274" t="inlineStr"/>
+      <c r="X274" t="inlineStr"/>
+      <c r="Y274" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC274" t="inlineStr"/>
+      <c r="AD274" t="inlineStr"/>
+      <c r="AE274" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF274" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG274" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH274" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ274" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK274" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="AL274" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AM274" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN274" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP274" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ274" t="inlineStr"/>
+      <c r="AR274" t="inlineStr"/>
+      <c r="AS274" t="n">
+        <v>790</v>
+      </c>
+      <c r="AT274" t="n">
+        <v>257</v>
+      </c>
+      <c r="AU274" t="inlineStr"/>
+      <c r="AV274" t="inlineStr"/>
+      <c r="AW274" t="inlineStr"/>
+      <c r="AX274" t="inlineStr"/>
+      <c r="AY274" t="n">
+        <v>682</v>
+      </c>
+      <c r="AZ274" t="n">
+        <v>181</v>
+      </c>
+      <c r="BA274" t="inlineStr"/>
+      <c r="BB274" t="inlineStr"/>
+      <c r="BC274" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD274" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE274" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF274" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG274" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH274" t="n">
+        <v>13</v>
+      </c>
+      <c r="BI274" t="inlineStr"/>
+      <c r="BJ274" t="inlineStr"/>
+      <c r="BK274" t="inlineStr"/>
+      <c r="BL274" t="inlineStr"/>
+      <c r="BM274" t="inlineStr"/>
+      <c r="BN274" t="inlineStr"/>
+      <c r="BO274" t="inlineStr"/>
+      <c r="BP274" t="inlineStr"/>
+      <c r="BQ274" t="inlineStr"/>
+      <c r="BR274" t="inlineStr"/>
+      <c r="BS274" t="inlineStr"/>
+      <c r="BT274" t="inlineStr"/>
+      <c r="BU274" t="inlineStr"/>
+      <c r="BV274" t="inlineStr"/>
+      <c r="BW274" t="inlineStr"/>
+      <c r="BX274" t="inlineStr"/>
+      <c r="BY274" t="n">
+        <v>27.27777777777778</v>
+      </c>
+      <c r="BZ274" t="n">
+        <v>177.5555555555555</v>
+      </c>
+      <c r="CA274" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="CB274" t="n">
+        <v>3055.555555555556</v>
+      </c>
+      <c r="CC274" t="n">
+        <v>1131944.444444444</v>
+      </c>
+      <c r="CD274" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="CE274" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="CF274" t="n">
+        <v>21.71428571428572</v>
+      </c>
+      <c r="CG274" t="n">
+        <v>179.4285714285714</v>
+      </c>
+      <c r="CH274" t="n">
+        <v>62.85714285714285</v>
+      </c>
+      <c r="CI274" t="inlineStr"/>
+      <c r="CJ274" t="n">
+        <v>878571.4285714285</v>
+      </c>
+      <c r="CK274" t="n">
+        <v>73.28571428571429</v>
+      </c>
+      <c r="CL274" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM274" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="CN274" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="CO274" t="n">
+        <v>6</v>
+      </c>
+      <c r="CP274" t="n">
+        <v>400</v>
+      </c>
+      <c r="CQ274" t="inlineStr"/>
+      <c r="CR274" t="n">
+        <v>7950000</v>
+      </c>
+      <c r="CS274" t="n">
+        <v>425</v>
+      </c>
+      <c r="CT274" t="n">
+        <v>6</v>
+      </c>
+      <c r="CU274" t="n">
+        <v>20.66666666666667</v>
+      </c>
+      <c r="CV274" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="CW274" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX274" t="n">
+        <v>183</v>
+      </c>
+      <c r="CY274" t="inlineStr"/>
+      <c r="CZ274" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="DA274" t="n">
+        <v>206</v>
+      </c>
+      <c r="DB274" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>QXnqeErJ</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="n">
+        <v>45597.66666666666</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leleu m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l aube
+  troyes </t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>20420</v>
+      </c>
+      <c r="F275" t="n">
+        <v>5365</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" t="n">
+        <v>0</v>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>59</v>
+      </c>
+      <c r="N275" t="n">
+        <v>41</v>
+      </c>
+      <c r="O275" t="n">
+        <v>9</v>
+      </c>
+      <c r="P275" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>5</v>
+      </c>
+      <c r="R275" t="n">
+        <v>1</v>
+      </c>
+      <c r="S275" t="n">
+        <v>3</v>
+      </c>
+      <c r="T275" t="n">
+        <v>2</v>
+      </c>
+      <c r="U275" t="n">
+        <v>1</v>
+      </c>
+      <c r="V275" t="n">
+        <v>6</v>
+      </c>
+      <c r="W275" t="inlineStr"/>
+      <c r="X275" t="inlineStr"/>
+      <c r="Y275" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC275" t="inlineStr"/>
+      <c r="AD275" t="inlineStr"/>
+      <c r="AE275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF275" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG275" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH275" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI275" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK275" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="AL275" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AM275" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN275" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP275" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ275" t="inlineStr"/>
+      <c r="AR275" t="inlineStr"/>
+      <c r="AS275" t="n">
+        <v>590</v>
+      </c>
+      <c r="AT275" t="n">
+        <v>396</v>
+      </c>
+      <c r="AU275" t="inlineStr"/>
+      <c r="AV275" t="inlineStr"/>
+      <c r="AW275" t="inlineStr"/>
+      <c r="AX275" t="inlineStr"/>
+      <c r="AY275" t="n">
+        <v>502</v>
+      </c>
+      <c r="AZ275" t="n">
+        <v>315</v>
+      </c>
+      <c r="BA275" t="inlineStr"/>
+      <c r="BB275" t="inlineStr"/>
+      <c r="BC275" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD275" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE275" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF275" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG275" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH275" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI275" t="inlineStr"/>
+      <c r="BJ275" t="inlineStr"/>
+      <c r="BK275" t="inlineStr"/>
+      <c r="BL275" t="inlineStr"/>
+      <c r="BM275" t="inlineStr"/>
+      <c r="BN275" t="inlineStr"/>
+      <c r="BO275" t="inlineStr"/>
+      <c r="BP275" t="inlineStr"/>
+      <c r="BQ275" t="inlineStr"/>
+      <c r="BR275" t="inlineStr"/>
+      <c r="BS275" t="inlineStr"/>
+      <c r="BT275" t="inlineStr"/>
+      <c r="BU275" t="inlineStr"/>
+      <c r="BV275" t="inlineStr"/>
+      <c r="BW275" t="inlineStr"/>
+      <c r="BX275" t="inlineStr"/>
+      <c r="BY275" t="n">
+        <v>23.88235294117647</v>
+      </c>
+      <c r="BZ275" t="n">
+        <v>176.7647058823529</v>
+      </c>
+      <c r="CA275" t="n">
+        <v>65.47058823529412</v>
+      </c>
+      <c r="CB275" t="inlineStr"/>
+      <c r="CC275" t="n">
+        <v>1291176.470588235</v>
+      </c>
+      <c r="CD275" t="n">
+        <v>71.58823529411765</v>
+      </c>
+      <c r="CE275" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF275" t="n">
+        <v>25.78571428571428</v>
+      </c>
+      <c r="CG275" t="n">
+        <v>181.0714285714286</v>
+      </c>
+      <c r="CH275" t="n">
+        <v>64.71428571428571</v>
+      </c>
+      <c r="CI275" t="inlineStr"/>
+      <c r="CJ275" t="n">
+        <v>949285.7142857143</v>
+      </c>
+      <c r="CK275" t="n">
+        <v>71.28571428571429</v>
+      </c>
+      <c r="CL275" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM275" t="n">
+        <v>28</v>
+      </c>
+      <c r="CN275" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="CO275" t="n">
+        <v>5</v>
+      </c>
+      <c r="CP275" t="n">
+        <v>340</v>
+      </c>
+      <c r="CQ275" t="n">
+        <v>19000</v>
+      </c>
+      <c r="CR275" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="CS275" t="n">
+        <v>356</v>
+      </c>
+      <c r="CT275" t="n">
+        <v>6</v>
+      </c>
+      <c r="CU275" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="CV275" t="n">
+        <v>184</v>
+      </c>
+      <c r="CW275" t="n">
+        <v>2</v>
+      </c>
+      <c r="CX275" t="n">
+        <v>132</v>
+      </c>
+      <c r="CY275" t="n">
+        <v>4000</v>
+      </c>
+      <c r="CZ275" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="DA275" t="n">
+        <v>137</v>
+      </c>
+      <c r="DB275" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>4WNXteh2</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="n">
+        <v>45600.69791666666</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buquet r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michel moretti stadium
+  ajaccio </t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>8470</v>
+      </c>
+      <c r="F276" t="n">
+        <v>2757</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" t="n">
+        <v>1</v>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>61</v>
+      </c>
+      <c r="N276" t="n">
+        <v>39</v>
+      </c>
+      <c r="O276" t="n">
+        <v>16</v>
+      </c>
+      <c r="P276" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>4</v>
+      </c>
+      <c r="R276" t="n">
+        <v>6</v>
+      </c>
+      <c r="S276" t="n">
+        <v>4</v>
+      </c>
+      <c r="T276" t="n">
+        <v>3</v>
+      </c>
+      <c r="U276" t="n">
+        <v>8</v>
+      </c>
+      <c r="V276" t="n">
+        <v>1</v>
+      </c>
+      <c r="W276" t="inlineStr"/>
+      <c r="X276" t="inlineStr"/>
+      <c r="Y276" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA276" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB276" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC276" t="inlineStr"/>
+      <c r="AD276" t="inlineStr"/>
+      <c r="AE276" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF276" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG276" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH276" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK276" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AL276" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AM276" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN276" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP276" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AQ276" t="inlineStr"/>
+      <c r="AR276" t="inlineStr"/>
+      <c r="AS276" t="n">
+        <v>509</v>
+      </c>
+      <c r="AT276" t="n">
+        <v>293</v>
+      </c>
+      <c r="AU276" t="inlineStr"/>
+      <c r="AV276" t="inlineStr"/>
+      <c r="AW276" t="inlineStr"/>
+      <c r="AX276" t="inlineStr"/>
+      <c r="AY276" t="n">
+        <v>379</v>
+      </c>
+      <c r="AZ276" t="n">
+        <v>173</v>
+      </c>
+      <c r="BA276" t="inlineStr"/>
+      <c r="BB276" t="inlineStr"/>
+      <c r="BC276" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD276" t="n">
+        <v>35</v>
+      </c>
+      <c r="BE276" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF276" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG276" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH276" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI276" t="inlineStr"/>
+      <c r="BJ276" t="inlineStr"/>
+      <c r="BK276" t="inlineStr"/>
+      <c r="BL276" t="inlineStr"/>
+      <c r="BM276" t="inlineStr"/>
+      <c r="BN276" t="inlineStr"/>
+      <c r="BO276" t="inlineStr"/>
+      <c r="BP276" t="inlineStr"/>
+      <c r="BQ276" t="inlineStr"/>
+      <c r="BR276" t="inlineStr"/>
+      <c r="BS276" t="inlineStr"/>
+      <c r="BT276" t="inlineStr"/>
+      <c r="BU276" t="inlineStr"/>
+      <c r="BV276" t="inlineStr"/>
+      <c r="BW276" t="inlineStr"/>
+      <c r="BX276" t="inlineStr"/>
+      <c r="BY276" t="n">
+        <v>24.71428571428572</v>
+      </c>
+      <c r="BZ276" t="n">
+        <v>180.9047619047619</v>
+      </c>
+      <c r="CA276" t="n">
+        <v>64.04761904761905</v>
+      </c>
+      <c r="CB276" t="inlineStr"/>
+      <c r="CC276" t="n">
+        <v>798809.5238095238</v>
+      </c>
+      <c r="CD276" t="n">
+        <v>70.04761904761905</v>
+      </c>
+      <c r="CE276" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF276" t="inlineStr"/>
+      <c r="CG276" t="inlineStr"/>
+      <c r="CH276" t="inlineStr"/>
+      <c r="CI276" t="inlineStr"/>
+      <c r="CJ276" t="inlineStr"/>
+      <c r="CK276" t="inlineStr"/>
+      <c r="CL276" t="inlineStr"/>
+      <c r="CM276" t="n">
+        <v>36</v>
+      </c>
+      <c r="CN276" t="n">
+        <v>179</v>
+      </c>
+      <c r="CO276" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP276" t="n">
+        <v>67</v>
+      </c>
+      <c r="CQ276" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CR276" t="n">
+        <v>350000</v>
+      </c>
+      <c r="CS276" t="n">
+        <v>67</v>
+      </c>
+      <c r="CT276" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU276" t="inlineStr"/>
+      <c r="CV276" t="inlineStr"/>
+      <c r="CW276" t="inlineStr"/>
+      <c r="CX276" t="inlineStr"/>
+      <c r="CY276" t="inlineStr"/>
+      <c r="CZ276" t="inlineStr"/>
+      <c r="DA276" t="inlineStr"/>
+      <c r="DB276" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
